--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51FDC033-B0FC-4F59-9377-7088DF886B9E}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{314FF19D-E644-4827-A62E-DD14149C9AEB}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" firstSheet="4" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -1385,16 +1385,17 @@
     <t>On Flight</t>
   </si>
   <si>
-    <t>Depart HAN on flight VJ 932 to NRT from HAN</t>
+    <t>Depart HAN on flight VJ 932 to NRT</t>
   </si>
   <si>
     <t>08:00 - 11:00</t>
   </si>
   <si>
-    <t>Arrival &amp; Immigration</t>
-  </si>
-  <si>
-    <t>Complete immigration and Send Luggage at Narita Airport.</t>
+    <t>Send Luggage</t>
+  </si>
+  <si>
+    <t>Send Luggage at Yamato Transport
+(Terminal 2, 3rd Floor)</t>
   </si>
   <si>
     <t>11:00 - 12:00</t>
@@ -1403,7 +1404,8 @@
     <t>Airport Transfer</t>
   </si>
   <si>
-    <t>Transfer from Narita Airport to Tokyo (Ota-ku / Heiwajima) via Keisei Skyliner / Train.</t>
+    <t>Transfer from Narita Airport to Tokyo (Ota-ku / Heiwajima) via Keisei Skyliner / Train
+(Airbnb address: https://maps.app.goo.gl/DBmdvffro3LetJej6)</t>
   </si>
   <si>
     <t>12:00 - 13:00</t>
@@ -1744,7 +1746,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1958,51 +1960,32 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF123056"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF333333"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF222222"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
-      <scheme val="major"/>
+      <color rgb="FF123056"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2057,8 +2040,14 @@
         <bgColor rgb="FFF9FBFD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2164,13 +2153,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D7DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D7DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7DE"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D7DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="263">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2812,30 +2829,51 @@
     <xf numFmtId="0" fontId="29" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="32" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="31" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -2860,8 +2898,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -5937,7 +5976,7 @@
     <row r="137" spans="1:8" ht="15" customHeight="1">
       <c r="A137" s="37"/>
       <c r="B137" s="38"/>
-      <c r="C137" s="245" t="s">
+      <c r="C137" s="252" t="s">
         <v>179</v>
       </c>
       <c r="D137" s="38"/>
@@ -5952,7 +5991,7 @@
     <row r="138" spans="1:8" ht="15" customHeight="1">
       <c r="A138" s="37"/>
       <c r="B138" s="38"/>
-      <c r="C138" s="245"/>
+      <c r="C138" s="252"/>
       <c r="D138" s="38"/>
       <c r="E138" s="39"/>
       <c r="F138" s="38"/>
@@ -6678,8 +6717,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="246" customFormat="1">
-      <c r="A2" s="246" t="s">
+    <row r="2" spans="1:10" s="253" customFormat="1">
+      <c r="A2" s="253" t="s">
         <v>226</v>
       </c>
     </row>
@@ -6786,10 +6825,10 @@
     <row r="8" spans="1:10">
       <c r="A8" s="84"/>
       <c r="B8" s="85"/>
-      <c r="C8" s="247" t="s">
+      <c r="C8" s="254" t="s">
         <v>230</v>
       </c>
-      <c r="D8" s="247"/>
+      <c r="D8" s="254"/>
       <c r="E8" s="96">
         <v>1500</v>
       </c>
@@ -6832,10 +6871,10 @@
       <c r="J10" s="85"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="247" t="s">
+      <c r="A11" s="254" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="247"/>
+      <c r="B11" s="254"/>
       <c r="C11" s="99">
         <v>27</v>
       </c>
@@ -9169,8 +9208,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="246" customFormat="1">
-      <c r="A2" s="246" t="s">
+    <row r="2" spans="1:12" s="253" customFormat="1">
+      <c r="A2" s="253" t="s">
         <v>226</v>
       </c>
     </row>
@@ -9331,10 +9370,10 @@
     <row r="10" spans="1:12">
       <c r="A10" s="84"/>
       <c r="B10" s="85"/>
-      <c r="C10" s="247" t="s">
+      <c r="C10" s="254" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="247"/>
+      <c r="D10" s="254"/>
       <c r="E10" s="96">
         <v>3000</v>
       </c>
@@ -9377,10 +9416,10 @@
       <c r="J12" s="85"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="247" t="s">
+      <c r="A13" s="254" t="s">
         <v>233</v>
       </c>
-      <c r="B13" s="247"/>
+      <c r="B13" s="254"/>
       <c r="C13" s="99">
         <v>13</v>
       </c>
@@ -9804,10 +9843,10 @@
     <row r="34" spans="1:12">
       <c r="A34" s="114"/>
       <c r="B34" s="127"/>
-      <c r="C34" s="249" t="s">
+      <c r="C34" s="256" t="s">
         <v>338</v>
       </c>
-      <c r="D34" s="249"/>
+      <c r="D34" s="256"/>
       <c r="E34" s="128"/>
       <c r="F34" s="129"/>
       <c r="G34" s="127"/>
@@ -9820,10 +9859,10 @@
     <row r="35" spans="1:12">
       <c r="A35" s="114"/>
       <c r="B35" s="127"/>
-      <c r="C35" s="250" t="s">
+      <c r="C35" s="257" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="250"/>
+      <c r="D35" s="257"/>
       <c r="E35" s="128"/>
       <c r="F35" s="129"/>
       <c r="G35" s="127"/>
@@ -9840,10 +9879,10 @@
       <c r="B36" s="101">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C36" s="252" t="s">
+      <c r="C36" s="259" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="252"/>
+      <c r="D36" s="259"/>
       <c r="E36" s="132"/>
       <c r="F36" s="133"/>
       <c r="G36" s="134"/>
@@ -10090,10 +10129,10 @@
     <row r="48" spans="1:12">
       <c r="A48" s="114"/>
       <c r="B48" s="109"/>
-      <c r="C48" s="251" t="s">
+      <c r="C48" s="258" t="s">
         <v>352</v>
       </c>
-      <c r="D48" s="251"/>
+      <c r="D48" s="258"/>
       <c r="E48" s="96">
         <f>370+220</f>
         <v>590</v>
@@ -10896,7 +10935,7 @@
     <row r="83" spans="1:10">
       <c r="A83" s="114"/>
       <c r="B83" s="109"/>
-      <c r="C83" s="248" t="s">
+      <c r="C83" s="255" t="s">
         <v>377</v>
       </c>
       <c r="D83" s="148" t="s">
@@ -10922,7 +10961,7 @@
     <row r="84" spans="1:10">
       <c r="A84" s="114"/>
       <c r="B84" s="109"/>
-      <c r="C84" s="248"/>
+      <c r="C84" s="255"/>
       <c r="D84" s="148" t="s">
         <v>379</v>
       </c>
@@ -12707,16 +12746,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18" style="10" customWidth="1"/>
-    <col min="2" max="2" width="28" style="10" customWidth="1"/>
-    <col min="3" max="3" width="81" style="10" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="10"/>
+    <col min="1" max="1" width="18" style="216" customWidth="1"/>
+    <col min="2" max="2" width="28" style="216" customWidth="1"/>
+    <col min="3" max="3" width="81" style="216" customWidth="1"/>
+    <col min="4" max="16384" width="8.85546875" style="216"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:3">
       <c r="A1" s="236" t="s">
         <v>432</v>
       </c>
@@ -12726,16 +12765,15 @@
       <c r="C1" s="236" t="s">
         <v>434</v>
       </c>
-      <c r="D1" s="253"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="244" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="250" t="s">
         <v>435</v>
       </c>
-      <c r="B2" s="254"/>
-      <c r="C2" s="254"/>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="B2" s="260"/>
+      <c r="C2" s="260"/>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="237" t="s">
         <v>436</v>
       </c>
@@ -12746,7 +12784,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:3" ht="29.25">
       <c r="A4" s="240" t="s">
         <v>439</v>
       </c>
@@ -12757,7 +12795,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:3" ht="29.25">
       <c r="A5" s="237" t="s">
         <v>442</v>
       </c>
@@ -12768,7 +12806,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:3">
       <c r="A6" s="240" t="s">
         <v>445</v>
       </c>
@@ -12779,7 +12817,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:3">
       <c r="A7" s="237" t="s">
         <v>448</v>
       </c>
@@ -12790,7 +12828,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:3">
       <c r="A8" s="240" t="s">
         <v>451</v>
       </c>
@@ -12801,7 +12839,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:3">
       <c r="A9" s="237" t="s">
         <v>454</v>
       </c>
@@ -12812,7 +12850,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:3">
       <c r="A10" s="240" t="s">
         <v>457</v>
       </c>
@@ -12823,25 +12861,25 @@
         <v>459</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A11" s="237" t="s">
+    <row r="11" spans="1:3">
+      <c r="A11" s="243" t="s">
         <v>460</v>
       </c>
-      <c r="B11" s="238" t="s">
+      <c r="B11" s="244" t="s">
         <v>461</v>
       </c>
-      <c r="C11" s="239" t="s">
+      <c r="C11" s="245" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="244" t="s">
+    <row r="12" spans="1:3">
+      <c r="A12" s="251" t="s">
         <v>463</v>
       </c>
-      <c r="B12" s="254"/>
-      <c r="C12" s="254"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="B12" s="261"/>
+      <c r="C12" s="261"/>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" s="237" t="s">
         <v>464</v>
       </c>
@@ -12852,7 +12890,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="24">
+    <row r="14" spans="1:3" ht="29.25">
       <c r="A14" s="240" t="s">
         <v>467</v>
       </c>
@@ -12863,7 +12901,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:3">
       <c r="A15" s="237" t="s">
         <v>470</v>
       </c>
@@ -12874,23 +12912,23 @@
         <v>471</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A16" s="243">
+    <row r="16" spans="1:3">
+      <c r="A16" s="246">
         <v>0.875</v>
       </c>
-      <c r="B16" s="241" t="s">
+      <c r="B16" s="247" t="s">
         <v>472</v>
       </c>
-      <c r="C16" s="242" t="s">
+      <c r="C16" s="248" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="244" t="s">
+      <c r="A17" s="251" t="s">
         <v>474</v>
       </c>
-      <c r="B17" s="254"/>
-      <c r="C17" s="254"/>
+      <c r="B17" s="261"/>
+      <c r="C17" s="261"/>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="237" t="s">
@@ -12903,7 +12941,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" ht="29.25">
       <c r="A19" s="240" t="s">
         <v>478</v>
       </c>
@@ -12947,7 +12985,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.75" thickBot="1">
+    <row r="23" spans="1:3">
       <c r="A23" s="240" t="s">
         <v>457</v>
       </c>
@@ -12959,11 +12997,11 @@
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="244" t="s">
+      <c r="A24" s="249" t="s">
         <v>490</v>
       </c>
-      <c r="B24" s="254"/>
-      <c r="C24" s="254"/>
+      <c r="B24" s="262"/>
+      <c r="C24" s="262"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="237" t="s">
@@ -13009,7 +13047,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.75" thickBot="1">
+    <row r="29" spans="1:3">
       <c r="A29" s="237" t="s">
         <v>500</v>
       </c>
@@ -13021,13 +13059,13 @@
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="244" t="s">
+      <c r="A30" s="249" t="s">
         <v>503</v>
       </c>
-      <c r="B30" s="254"/>
-      <c r="C30" s="254"/>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="B30" s="262"/>
+      <c r="C30" s="262"/>
+    </row>
+    <row r="31" spans="1:3" ht="29.25">
       <c r="A31" s="237" t="s">
         <v>504</v>
       </c>
@@ -13038,7 +13076,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" ht="29.25">
       <c r="A32" s="240" t="s">
         <v>507</v>
       </c>
@@ -13060,7 +13098,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.75" thickBot="1">
+    <row r="34" spans="1:3">
       <c r="A34" s="240" t="s">
         <v>500</v>
       </c>
@@ -13072,11 +13110,11 @@
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="244" t="s">
+      <c r="A35" s="249" t="s">
         <v>514</v>
       </c>
-      <c r="B35" s="254"/>
-      <c r="C35" s="254"/>
+      <c r="B35" s="262"/>
+      <c r="C35" s="262"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="237" t="s">
@@ -13122,7 +13160,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.75" thickBot="1">
+    <row r="40" spans="1:3">
       <c r="A40" s="237" t="s">
         <v>523</v>
       </c>
@@ -13134,13 +13172,13 @@
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="244" t="s">
+      <c r="A41" s="249" t="s">
         <v>525</v>
       </c>
-      <c r="B41" s="254"/>
-      <c r="C41" s="254"/>
-    </row>
-    <row r="42" spans="1:3">
+      <c r="B41" s="262"/>
+      <c r="C41" s="262"/>
+    </row>
+    <row r="42" spans="1:3" ht="29.25">
       <c r="A42" s="237" t="s">
         <v>478</v>
       </c>
@@ -13173,7 +13211,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" thickBot="1">
+    <row r="45" spans="1:3" ht="15.75">
       <c r="A45" s="240" t="s">
         <v>531</v>
       </c>
@@ -13185,13 +13223,13 @@
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="244" t="s">
+      <c r="A46" s="249" t="s">
         <v>534</v>
       </c>
-      <c r="B46" s="254"/>
-      <c r="C46" s="254"/>
-    </row>
-    <row r="47" spans="1:3">
+      <c r="B46" s="262"/>
+      <c r="C46" s="262"/>
+    </row>
+    <row r="47" spans="1:3" ht="29.25">
       <c r="A47" s="237" t="s">
         <v>515</v>
       </c>
@@ -13224,7 +13262,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.75" thickBot="1">
+    <row r="50" spans="1:3">
       <c r="A50" s="240" t="s">
         <v>500</v>
       </c>
@@ -13236,11 +13274,11 @@
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="244" t="s">
+      <c r="A51" s="249" t="s">
         <v>543</v>
       </c>
-      <c r="B51" s="254"/>
-      <c r="C51" s="254"/>
+      <c r="B51" s="262"/>
+      <c r="C51" s="262"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="237" t="s">
@@ -13304,23 +13342,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005A4695005C4BEE4A8751FEE2C473E10D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df7fcaa21f93254d26451ff7a6d04ad2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xmlns:ns4="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fefbcb393e90fe08e3723c038b505a33" ns3:_="" ns4:_="">
     <xsd:import namespace="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
@@ -13559,14 +13580,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6EF48D-28DC-4A85-AE0A-77598A9ABE97}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}"/>
 </file>
--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{314FF19D-E644-4827-A62E-DD14149C9AEB}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E389A87-3248-4459-8203-BC4A9AB53504}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" firstSheet="4" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="558">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1376,6 +1376,12 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>Link</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Day 1: Hanoi • Tokyo • Odaiba Sunset</t>
   </si>
   <si>
@@ -1394,8 +1400,7 @@
     <t>Send Luggage</t>
   </si>
   <si>
-    <t>Send Luggage at Yamato Transport
-(Terminal 2, 3rd Floor)</t>
+    <t>Send Luggage at Yamato Transport - Terminal 2, 3rd Floor</t>
   </si>
   <si>
     <t>11:00 - 12:00</t>
@@ -1405,7 +1410,10 @@
   </si>
   <si>
     <t>Transfer from Narita Airport to Tokyo (Ota-ku / Heiwajima) via Keisei Skyliner / Train
-(Airbnb address: https://maps.app.goo.gl/DBmdvffro3LetJej6)</t>
+Airbnb: 6-chōme-12-1 Ōmorikita エルメゾン大森203, Thành phố Ota, Tỉnh Tokyo 143-0016, Nhật Bản</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/DBmdvffro3LetJej6</t>
   </si>
   <si>
     <t>12:00 - 13:00</t>
@@ -1746,7 +1754,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1984,8 +1992,20 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2043,6 +2063,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2187,7 +2213,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="263">
+  <cellXfs count="270">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2898,6 +2924,19 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -12746,16 +12785,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" style="216" customWidth="1"/>
     <col min="2" max="2" width="28" style="216" customWidth="1"/>
     <col min="3" max="3" width="81" style="216" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="216"/>
+    <col min="4" max="4" width="11.28515625" style="216" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="216"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="236" t="s">
         <v>432</v>
       </c>
@@ -12765,564 +12805,627 @@
       <c r="C1" s="236" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="262" t="s">
+        <v>435</v>
+      </c>
+      <c r="E1" s="260" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="250" t="s">
-        <v>435</v>
-      </c>
-      <c r="B2" s="260"/>
-      <c r="C2" s="260"/>
-    </row>
-    <row r="3" spans="1:3">
+        <v>437</v>
+      </c>
+      <c r="B2" s="267"/>
+      <c r="C2" s="267"/>
+      <c r="D2" s="263"/>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="237" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B3" s="238" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C3" s="239" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="29.25">
+        <v>440</v>
+      </c>
+      <c r="D3" s="264"/>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="240" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B4" s="241" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C4" s="242" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="29.25">
+        <v>443</v>
+      </c>
+      <c r="D4" s="265"/>
+    </row>
+    <row r="5" spans="1:5" ht="45">
       <c r="A5" s="237" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B5" s="238" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C5" s="239" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>446</v>
+      </c>
+      <c r="D5" s="264"/>
+      <c r="E5" s="261" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="240" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B6" s="241" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C6" s="242" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>450</v>
+      </c>
+      <c r="D6" s="265"/>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="237" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B7" s="241" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C7" s="242" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>453</v>
+      </c>
+      <c r="D7" s="265"/>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="240" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B8" s="241" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C8" s="242" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>456</v>
+      </c>
+      <c r="D8" s="265"/>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="237" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B9" s="238" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C9" s="239" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>459</v>
+      </c>
+      <c r="D9" s="264"/>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="240" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B10" s="241" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C10" s="242" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>462</v>
+      </c>
+      <c r="D10" s="265"/>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="243" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B11" s="244" t="s">
+        <v>464</v>
+      </c>
+      <c r="C11" s="245" t="s">
+        <v>465</v>
+      </c>
+      <c r="D11" s="264"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="251" t="s">
+        <v>466</v>
+      </c>
+      <c r="B12" s="268"/>
+      <c r="C12" s="268"/>
+      <c r="D12" s="266"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="237" t="s">
+        <v>467</v>
+      </c>
+      <c r="B13" s="238" t="s">
+        <v>468</v>
+      </c>
+      <c r="C13" s="239" t="s">
+        <v>469</v>
+      </c>
+      <c r="D13" s="264"/>
+    </row>
+    <row r="14" spans="1:5" ht="29.25">
+      <c r="A14" s="240" t="s">
+        <v>470</v>
+      </c>
+      <c r="B14" s="241" t="s">
+        <v>471</v>
+      </c>
+      <c r="C14" s="242" t="s">
+        <v>472</v>
+      </c>
+      <c r="D14" s="265"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="237" t="s">
+        <v>473</v>
+      </c>
+      <c r="B15" s="238" t="s">
         <v>461</v>
       </c>
-      <c r="C11" s="245" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="251" t="s">
-        <v>463</v>
-      </c>
-      <c r="B12" s="261"/>
-      <c r="C12" s="261"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="237" t="s">
-        <v>464</v>
-      </c>
-      <c r="B13" s="238" t="s">
-        <v>465</v>
-      </c>
-      <c r="C13" s="239" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="29.25">
-      <c r="A14" s="240" t="s">
-        <v>467</v>
-      </c>
-      <c r="B14" s="241" t="s">
-        <v>468</v>
-      </c>
-      <c r="C14" s="242" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="237" t="s">
-        <v>470</v>
-      </c>
-      <c r="B15" s="238" t="s">
-        <v>458</v>
-      </c>
       <c r="C15" s="239" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>474</v>
+      </c>
+      <c r="D15" s="264"/>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="246">
         <v>0.875</v>
       </c>
       <c r="B16" s="247" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C16" s="248" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>476</v>
+      </c>
+      <c r="D16" s="265"/>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="251" t="s">
-        <v>474</v>
-      </c>
-      <c r="B17" s="261"/>
-      <c r="C17" s="261"/>
-    </row>
-    <row r="18" spans="1:3">
+        <v>477</v>
+      </c>
+      <c r="B17" s="268"/>
+      <c r="C17" s="268"/>
+      <c r="D17" s="266"/>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="237" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B18" s="238" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C18" s="239" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="29.25">
+        <v>480</v>
+      </c>
+      <c r="D18" s="264"/>
+    </row>
+    <row r="19" spans="1:4" ht="29.25">
       <c r="A19" s="240" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B19" s="241" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C19" s="242" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>483</v>
+      </c>
+      <c r="D19" s="265"/>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="237" t="s">
+        <v>484</v>
+      </c>
+      <c r="B20" s="238" t="s">
+        <v>449</v>
+      </c>
+      <c r="C20" s="239" t="s">
+        <v>485</v>
+      </c>
+      <c r="D20" s="264"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="240" t="s">
+        <v>486</v>
+      </c>
+      <c r="B21" s="241" t="s">
+        <v>487</v>
+      </c>
+      <c r="C21" s="242" t="s">
+        <v>488</v>
+      </c>
+      <c r="D21" s="265"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="237" t="s">
+        <v>489</v>
+      </c>
+      <c r="B22" s="238" t="s">
+        <v>490</v>
+      </c>
+      <c r="C22" s="239" t="s">
+        <v>491</v>
+      </c>
+      <c r="D22" s="264"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="240" t="s">
+        <v>460</v>
+      </c>
+      <c r="B23" s="241" t="s">
+        <v>461</v>
+      </c>
+      <c r="C23" s="242" t="s">
+        <v>492</v>
+      </c>
+      <c r="D23" s="265"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="249" t="s">
+        <v>493</v>
+      </c>
+      <c r="B24" s="269"/>
+      <c r="C24" s="269"/>
+      <c r="D24" s="266"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="237" t="s">
+        <v>494</v>
+      </c>
+      <c r="B25" s="238" t="s">
+        <v>495</v>
+      </c>
+      <c r="C25" s="239" t="s">
+        <v>496</v>
+      </c>
+      <c r="D25" s="264"/>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="240" t="s">
+        <v>497</v>
+      </c>
+      <c r="B26" s="241" t="s">
+        <v>449</v>
+      </c>
+      <c r="C26" s="242" t="s">
+        <v>498</v>
+      </c>
+      <c r="D26" s="265"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="237" t="s">
+        <v>499</v>
+      </c>
+      <c r="B27" s="238" t="s">
+        <v>500</v>
+      </c>
+      <c r="C27" s="239" t="s">
+        <v>501</v>
+      </c>
+      <c r="D27" s="264"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="240" t="s">
+        <v>489</v>
+      </c>
+      <c r="B28" s="241" t="s">
+        <v>490</v>
+      </c>
+      <c r="C28" s="242" t="s">
+        <v>502</v>
+      </c>
+      <c r="D28" s="265"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="237" t="s">
+        <v>503</v>
+      </c>
+      <c r="B29" s="238" t="s">
+        <v>504</v>
+      </c>
+      <c r="C29" s="239" t="s">
+        <v>505</v>
+      </c>
+      <c r="D29" s="264"/>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="249" t="s">
+        <v>506</v>
+      </c>
+      <c r="B30" s="269"/>
+      <c r="C30" s="269"/>
+      <c r="D30" s="266"/>
+    </row>
+    <row r="31" spans="1:4" ht="29.25">
+      <c r="A31" s="237" t="s">
+        <v>507</v>
+      </c>
+      <c r="B31" s="238" t="s">
+        <v>508</v>
+      </c>
+      <c r="C31" s="239" t="s">
+        <v>509</v>
+      </c>
+      <c r="D31" s="264"/>
+    </row>
+    <row r="32" spans="1:4" ht="29.25">
+      <c r="A32" s="240" t="s">
+        <v>510</v>
+      </c>
+      <c r="B32" s="241" t="s">
+        <v>511</v>
+      </c>
+      <c r="C32" s="242" t="s">
+        <v>512</v>
+      </c>
+      <c r="D32" s="265"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="237" t="s">
+        <v>513</v>
+      </c>
+      <c r="B33" s="238" t="s">
+        <v>514</v>
+      </c>
+      <c r="C33" s="239" t="s">
+        <v>515</v>
+      </c>
+      <c r="D33" s="264"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="240" t="s">
+        <v>503</v>
+      </c>
+      <c r="B34" s="241" t="s">
+        <v>461</v>
+      </c>
+      <c r="C34" s="242" t="s">
+        <v>516</v>
+      </c>
+      <c r="D34" s="265"/>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="249" t="s">
+        <v>517</v>
+      </c>
+      <c r="B35" s="269"/>
+      <c r="C35" s="269"/>
+      <c r="D35" s="266"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="237" t="s">
+        <v>518</v>
+      </c>
+      <c r="B36" s="238" t="s">
+        <v>519</v>
+      </c>
+      <c r="C36" s="239" t="s">
+        <v>520</v>
+      </c>
+      <c r="D36" s="264"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="240" t="s">
+        <v>497</v>
+      </c>
+      <c r="B37" s="241" t="s">
+        <v>449</v>
+      </c>
+      <c r="C37" s="242" t="s">
+        <v>521</v>
+      </c>
+      <c r="D37" s="265"/>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="237" t="s">
+        <v>499</v>
+      </c>
+      <c r="B38" s="238" t="s">
+        <v>522</v>
+      </c>
+      <c r="C38" s="239" t="s">
+        <v>523</v>
+      </c>
+      <c r="D38" s="264"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="240" t="s">
+        <v>524</v>
+      </c>
+      <c r="B39" s="241" t="s">
+        <v>490</v>
+      </c>
+      <c r="C39" s="242" t="s">
+        <v>525</v>
+      </c>
+      <c r="D39" s="265"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="237" t="s">
+        <v>526</v>
+      </c>
+      <c r="B40" s="238" t="s">
+        <v>461</v>
+      </c>
+      <c r="C40" s="239" t="s">
+        <v>527</v>
+      </c>
+      <c r="D40" s="264"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="249" t="s">
+        <v>528</v>
+      </c>
+      <c r="B41" s="269"/>
+      <c r="C41" s="269"/>
+      <c r="D41" s="266"/>
+    </row>
+    <row r="42" spans="1:4" ht="29.25">
+      <c r="A42" s="237" t="s">
         <v>481</v>
       </c>
-      <c r="B20" s="238" t="s">
-        <v>446</v>
-      </c>
-      <c r="C20" s="239" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="240" t="s">
-        <v>483</v>
-      </c>
-      <c r="B21" s="241" t="s">
+      <c r="B42" s="238" t="s">
+        <v>529</v>
+      </c>
+      <c r="C42" s="239" t="s">
+        <v>530</v>
+      </c>
+      <c r="D42" s="264"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="240" t="s">
         <v>484</v>
       </c>
-      <c r="C21" s="242" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="237" t="s">
-        <v>486</v>
-      </c>
-      <c r="B22" s="238" t="s">
-        <v>487</v>
-      </c>
-      <c r="C22" s="239" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="240" t="s">
-        <v>457</v>
-      </c>
-      <c r="B23" s="241" t="s">
-        <v>458</v>
-      </c>
-      <c r="C23" s="242" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="249" t="s">
-        <v>490</v>
-      </c>
-      <c r="B24" s="262"/>
-      <c r="C24" s="262"/>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="237" t="s">
-        <v>491</v>
-      </c>
-      <c r="B25" s="238" t="s">
-        <v>492</v>
-      </c>
-      <c r="C25" s="239" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="240" t="s">
-        <v>494</v>
-      </c>
-      <c r="B26" s="241" t="s">
-        <v>446</v>
-      </c>
-      <c r="C26" s="242" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="237" t="s">
-        <v>496</v>
-      </c>
-      <c r="B27" s="238" t="s">
+      <c r="B43" s="241" t="s">
+        <v>449</v>
+      </c>
+      <c r="C43" s="242" t="s">
+        <v>531</v>
+      </c>
+      <c r="D43" s="265"/>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="237" t="s">
+        <v>499</v>
+      </c>
+      <c r="B44" s="238" t="s">
+        <v>532</v>
+      </c>
+      <c r="C44" s="239" t="s">
+        <v>533</v>
+      </c>
+      <c r="D44" s="264"/>
+    </row>
+    <row r="45" spans="1:4" ht="15.75">
+      <c r="A45" s="240" t="s">
+        <v>534</v>
+      </c>
+      <c r="B45" s="241" t="s">
+        <v>535</v>
+      </c>
+      <c r="C45" s="242" t="s">
+        <v>536</v>
+      </c>
+      <c r="D45" s="265"/>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="249" t="s">
+        <v>537</v>
+      </c>
+      <c r="B46" s="269"/>
+      <c r="C46" s="269"/>
+      <c r="D46" s="266"/>
+    </row>
+    <row r="47" spans="1:4" ht="29.25">
+      <c r="A47" s="237" t="s">
+        <v>518</v>
+      </c>
+      <c r="B47" s="238" t="s">
+        <v>538</v>
+      </c>
+      <c r="C47" s="239" t="s">
+        <v>539</v>
+      </c>
+      <c r="D47" s="264"/>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="240" t="s">
         <v>497</v>
       </c>
-      <c r="C27" s="239" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="240" t="s">
-        <v>486</v>
-      </c>
-      <c r="B28" s="241" t="s">
-        <v>487</v>
-      </c>
-      <c r="C28" s="242" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="237" t="s">
-        <v>500</v>
-      </c>
-      <c r="B29" s="238" t="s">
-        <v>501</v>
-      </c>
-      <c r="C29" s="239" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="249" t="s">
+      <c r="B48" s="241" t="s">
+        <v>449</v>
+      </c>
+      <c r="C48" s="242" t="s">
+        <v>540</v>
+      </c>
+      <c r="D48" s="265"/>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="237" t="s">
+        <v>541</v>
+      </c>
+      <c r="B49" s="238" t="s">
+        <v>542</v>
+      </c>
+      <c r="C49" s="239" t="s">
+        <v>543</v>
+      </c>
+      <c r="D49" s="264"/>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="240" t="s">
         <v>503</v>
       </c>
-      <c r="B30" s="262"/>
-      <c r="C30" s="262"/>
-    </row>
-    <row r="31" spans="1:3" ht="29.25">
-      <c r="A31" s="237" t="s">
-        <v>504</v>
-      </c>
-      <c r="B31" s="238" t="s">
-        <v>505</v>
-      </c>
-      <c r="C31" s="239" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="29.25">
-      <c r="A32" s="240" t="s">
-        <v>507</v>
-      </c>
-      <c r="B32" s="241" t="s">
-        <v>508</v>
-      </c>
-      <c r="C32" s="242" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="237" t="s">
-        <v>510</v>
-      </c>
-      <c r="B33" s="238" t="s">
-        <v>511</v>
-      </c>
-      <c r="C33" s="239" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="240" t="s">
-        <v>500</v>
-      </c>
-      <c r="B34" s="241" t="s">
-        <v>458</v>
-      </c>
-      <c r="C34" s="242" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="249" t="s">
-        <v>514</v>
-      </c>
-      <c r="B35" s="262"/>
-      <c r="C35" s="262"/>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="237" t="s">
-        <v>515</v>
-      </c>
-      <c r="B36" s="238" t="s">
-        <v>516</v>
-      </c>
-      <c r="C36" s="239" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="240" t="s">
-        <v>494</v>
-      </c>
-      <c r="B37" s="241" t="s">
-        <v>446</v>
-      </c>
-      <c r="C37" s="242" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="237" t="s">
-        <v>496</v>
-      </c>
-      <c r="B38" s="238" t="s">
-        <v>519</v>
-      </c>
-      <c r="C38" s="239" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="240" t="s">
-        <v>521</v>
-      </c>
-      <c r="B39" s="241" t="s">
-        <v>487</v>
-      </c>
-      <c r="C39" s="242" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="237" t="s">
-        <v>523</v>
-      </c>
-      <c r="B40" s="238" t="s">
-        <v>458</v>
-      </c>
-      <c r="C40" s="239" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="249" t="s">
-        <v>525</v>
-      </c>
-      <c r="B41" s="262"/>
-      <c r="C41" s="262"/>
-    </row>
-    <row r="42" spans="1:3" ht="29.25">
-      <c r="A42" s="237" t="s">
-        <v>478</v>
-      </c>
-      <c r="B42" s="238" t="s">
-        <v>526</v>
-      </c>
-      <c r="C42" s="239" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="240" t="s">
-        <v>481</v>
-      </c>
-      <c r="B43" s="241" t="s">
-        <v>446</v>
-      </c>
-      <c r="C43" s="242" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="237" t="s">
-        <v>496</v>
-      </c>
-      <c r="B44" s="238" t="s">
-        <v>529</v>
-      </c>
-      <c r="C44" s="239" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.75">
-      <c r="A45" s="240" t="s">
-        <v>531</v>
-      </c>
-      <c r="B45" s="241" t="s">
-        <v>532</v>
-      </c>
-      <c r="C45" s="242" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="249" t="s">
-        <v>534</v>
-      </c>
-      <c r="B46" s="262"/>
-      <c r="C46" s="262"/>
-    </row>
-    <row r="47" spans="1:3" ht="29.25">
-      <c r="A47" s="237" t="s">
-        <v>515</v>
-      </c>
-      <c r="B47" s="238" t="s">
-        <v>535</v>
-      </c>
-      <c r="C47" s="239" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="240" t="s">
-        <v>494</v>
-      </c>
-      <c r="B48" s="241" t="s">
-        <v>446</v>
-      </c>
-      <c r="C48" s="242" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="237" t="s">
-        <v>538</v>
-      </c>
-      <c r="B49" s="238" t="s">
-        <v>539</v>
-      </c>
-      <c r="C49" s="239" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="240" t="s">
-        <v>500</v>
-      </c>
       <c r="B50" s="241" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C50" s="242" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>545</v>
+      </c>
+      <c r="D50" s="265"/>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" s="249" t="s">
-        <v>543</v>
-      </c>
-      <c r="B51" s="262"/>
-      <c r="C51" s="262"/>
-    </row>
-    <row r="52" spans="1:3">
+        <v>546</v>
+      </c>
+      <c r="B51" s="269"/>
+      <c r="C51" s="269"/>
+      <c r="D51" s="266"/>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="237" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="B52" s="238" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C52" s="239" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>549</v>
+      </c>
+      <c r="D52" s="264"/>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" s="240" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B53" s="241" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C53" s="242" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>551</v>
+      </c>
+      <c r="D53" s="265"/>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" s="237" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="B54" s="238" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C54" s="239" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>554</v>
+      </c>
+      <c r="D54" s="264"/>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" s="240" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B55" s="241" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C55" s="242" t="s">
-        <v>554</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="D55" s="265"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E389A87-3248-4459-8203-BC4A9AB53504}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54F1CD7F-463B-4D32-9D5A-3DEEAD61640C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" firstSheet="4" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="560">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1376,6 +1376,9 @@
     <t>Description</t>
   </si>
   <si>
+    <t>Note</t>
+  </si>
+  <si>
     <t>Image</t>
   </si>
   <si>
@@ -1409,8 +1412,10 @@
     <t>Airport Transfer</t>
   </si>
   <si>
-    <t>Transfer from Narita Airport to Tokyo (Ota-ku / Heiwajima) via Keisei Skyliner / Train
-Airbnb: 6-chōme-12-1 Ōmorikita エルメゾン大森203, Thành phố Ota, Tỉnh Tokyo 143-0016, Nhật Bản</t>
+    <t>Transfer from Narita Airport to Tokyo via Keisei Skyliner / Train</t>
+  </si>
+  <si>
+    <t>Airbnb: 6-chōme-12-1 Ōmorikita エルメゾン大森203, Thành phố Ota, Tỉnh Tokyo 143-0016, Nhật Bản</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/DBmdvffro3LetJej6</t>
@@ -2213,7 +2218,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="270">
+  <cellXfs count="274">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2891,6 +2896,18 @@
     <xf numFmtId="0" fontId="32" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2924,8 +2941,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6015,7 +6030,7 @@
     <row r="137" spans="1:8" ht="15" customHeight="1">
       <c r="A137" s="37"/>
       <c r="B137" s="38"/>
-      <c r="C137" s="252" t="s">
+      <c r="C137" s="258" t="s">
         <v>179</v>
       </c>
       <c r="D137" s="38"/>
@@ -6030,7 +6045,7 @@
     <row r="138" spans="1:8" ht="15" customHeight="1">
       <c r="A138" s="37"/>
       <c r="B138" s="38"/>
-      <c r="C138" s="252"/>
+      <c r="C138" s="258"/>
       <c r="D138" s="38"/>
       <c r="E138" s="39"/>
       <c r="F138" s="38"/>
@@ -6756,8 +6771,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="253" customFormat="1">
-      <c r="A2" s="253" t="s">
+    <row r="2" spans="1:10" s="259" customFormat="1">
+      <c r="A2" s="259" t="s">
         <v>226</v>
       </c>
     </row>
@@ -6864,10 +6879,10 @@
     <row r="8" spans="1:10">
       <c r="A8" s="84"/>
       <c r="B8" s="85"/>
-      <c r="C8" s="254" t="s">
+      <c r="C8" s="260" t="s">
         <v>230</v>
       </c>
-      <c r="D8" s="254"/>
+      <c r="D8" s="260"/>
       <c r="E8" s="96">
         <v>1500</v>
       </c>
@@ -6910,10 +6925,10 @@
       <c r="J10" s="85"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="254" t="s">
+      <c r="A11" s="260" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="254"/>
+      <c r="B11" s="260"/>
       <c r="C11" s="99">
         <v>27</v>
       </c>
@@ -9247,8 +9262,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="253" customFormat="1">
-      <c r="A2" s="253" t="s">
+    <row r="2" spans="1:12" s="259" customFormat="1">
+      <c r="A2" s="259" t="s">
         <v>226</v>
       </c>
     </row>
@@ -9409,10 +9424,10 @@
     <row r="10" spans="1:12">
       <c r="A10" s="84"/>
       <c r="B10" s="85"/>
-      <c r="C10" s="254" t="s">
+      <c r="C10" s="260" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="254"/>
+      <c r="D10" s="260"/>
       <c r="E10" s="96">
         <v>3000</v>
       </c>
@@ -9455,10 +9470,10 @@
       <c r="J12" s="85"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="254" t="s">
+      <c r="A13" s="260" t="s">
         <v>233</v>
       </c>
-      <c r="B13" s="254"/>
+      <c r="B13" s="260"/>
       <c r="C13" s="99">
         <v>13</v>
       </c>
@@ -9882,10 +9897,10 @@
     <row r="34" spans="1:12">
       <c r="A34" s="114"/>
       <c r="B34" s="127"/>
-      <c r="C34" s="256" t="s">
+      <c r="C34" s="262" t="s">
         <v>338</v>
       </c>
-      <c r="D34" s="256"/>
+      <c r="D34" s="262"/>
       <c r="E34" s="128"/>
       <c r="F34" s="129"/>
       <c r="G34" s="127"/>
@@ -9898,10 +9913,10 @@
     <row r="35" spans="1:12">
       <c r="A35" s="114"/>
       <c r="B35" s="127"/>
-      <c r="C35" s="257" t="s">
+      <c r="C35" s="263" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="257"/>
+      <c r="D35" s="263"/>
       <c r="E35" s="128"/>
       <c r="F35" s="129"/>
       <c r="G35" s="127"/>
@@ -9918,10 +9933,10 @@
       <c r="B36" s="101">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C36" s="259" t="s">
+      <c r="C36" s="265" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="259"/>
+      <c r="D36" s="265"/>
       <c r="E36" s="132"/>
       <c r="F36" s="133"/>
       <c r="G36" s="134"/>
@@ -10168,10 +10183,10 @@
     <row r="48" spans="1:12">
       <c r="A48" s="114"/>
       <c r="B48" s="109"/>
-      <c r="C48" s="258" t="s">
+      <c r="C48" s="264" t="s">
         <v>352</v>
       </c>
-      <c r="D48" s="258"/>
+      <c r="D48" s="264"/>
       <c r="E48" s="96">
         <f>370+220</f>
         <v>590</v>
@@ -10974,7 +10989,7 @@
     <row r="83" spans="1:10">
       <c r="A83" s="114"/>
       <c r="B83" s="109"/>
-      <c r="C83" s="255" t="s">
+      <c r="C83" s="261" t="s">
         <v>377</v>
       </c>
       <c r="D83" s="148" t="s">
@@ -11000,7 +11015,7 @@
     <row r="84" spans="1:10">
       <c r="A84" s="114"/>
       <c r="B84" s="109"/>
-      <c r="C84" s="255"/>
+      <c r="C84" s="261"/>
       <c r="D84" s="148" t="s">
         <v>379</v>
       </c>
@@ -12785,17 +12800,18 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" style="216" customWidth="1"/>
     <col min="2" max="2" width="28" style="216" customWidth="1"/>
     <col min="3" max="3" width="81" style="216" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" style="216" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="216"/>
+    <col min="4" max="4" width="41.42578125" style="216" customWidth="1"/>
+    <col min="5" max="5" width="6.5703125" style="216" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="216"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="236" t="s">
         <v>432</v>
       </c>
@@ -12805,627 +12821,678 @@
       <c r="C1" s="236" t="s">
         <v>434</v>
       </c>
-      <c r="D1" s="262" t="s">
+      <c r="D1" s="266" t="s">
         <v>435</v>
       </c>
-      <c r="E1" s="260" t="s">
+      <c r="E1" s="251" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="250" t="s">
+      <c r="F1" s="249" t="s">
         <v>437</v>
       </c>
-      <c r="B2" s="267"/>
-      <c r="C2" s="267"/>
-      <c r="D2" s="263"/>
-    </row>
-    <row r="3" spans="1:5">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="256" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="271"/>
+      <c r="C2" s="271"/>
+      <c r="D2" s="267"/>
+      <c r="E2" s="252"/>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="237" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B3" s="238" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C3" s="239" t="s">
-        <v>440</v>
-      </c>
-      <c r="D3" s="264"/>
-    </row>
-    <row r="4" spans="1:5">
+        <v>441</v>
+      </c>
+      <c r="D3" s="268"/>
+      <c r="E3" s="253"/>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="240" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B4" s="241" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C4" s="242" t="s">
-        <v>443</v>
-      </c>
-      <c r="D4" s="265"/>
-    </row>
-    <row r="5" spans="1:5" ht="45">
+        <v>444</v>
+      </c>
+      <c r="D4" s="269"/>
+      <c r="E4" s="254"/>
+    </row>
+    <row r="5" spans="1:6" ht="45">
       <c r="A5" s="237" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B5" s="238" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C5" s="239" t="s">
-        <v>446</v>
-      </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="261" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="D5" s="268" t="s">
+        <v>448</v>
+      </c>
+      <c r="E5" s="253"/>
+      <c r="F5" s="250" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="240" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B6" s="241" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C6" s="242" t="s">
-        <v>450</v>
-      </c>
-      <c r="D6" s="265"/>
-    </row>
-    <row r="7" spans="1:5">
+        <v>452</v>
+      </c>
+      <c r="D6" s="269"/>
+      <c r="E6" s="254"/>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="237" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B7" s="241" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C7" s="242" t="s">
-        <v>453</v>
-      </c>
-      <c r="D7" s="265"/>
-    </row>
-    <row r="8" spans="1:5">
+        <v>455</v>
+      </c>
+      <c r="D7" s="269"/>
+      <c r="E7" s="254"/>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="240" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B8" s="241" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C8" s="242" t="s">
-        <v>456</v>
-      </c>
-      <c r="D8" s="265"/>
-    </row>
-    <row r="9" spans="1:5">
+        <v>458</v>
+      </c>
+      <c r="D8" s="269"/>
+      <c r="E8" s="254"/>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="237" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B9" s="238" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C9" s="239" t="s">
-        <v>459</v>
-      </c>
-      <c r="D9" s="264"/>
-    </row>
-    <row r="10" spans="1:5">
+        <v>461</v>
+      </c>
+      <c r="D9" s="268"/>
+      <c r="E9" s="253"/>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="240" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B10" s="241" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C10" s="242" t="s">
-        <v>462</v>
-      </c>
-      <c r="D10" s="265"/>
-    </row>
-    <row r="11" spans="1:5">
+        <v>464</v>
+      </c>
+      <c r="D10" s="269"/>
+      <c r="E10" s="254"/>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="243" t="s">
+        <v>465</v>
+      </c>
+      <c r="B11" s="244" t="s">
+        <v>466</v>
+      </c>
+      <c r="C11" s="245" t="s">
+        <v>467</v>
+      </c>
+      <c r="D11" s="268"/>
+      <c r="E11" s="253"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="257" t="s">
+        <v>468</v>
+      </c>
+      <c r="B12" s="272"/>
+      <c r="C12" s="272"/>
+      <c r="D12" s="270"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="237" t="s">
+        <v>469</v>
+      </c>
+      <c r="B13" s="238" t="s">
+        <v>470</v>
+      </c>
+      <c r="C13" s="239" t="s">
+        <v>471</v>
+      </c>
+      <c r="D13" s="268"/>
+      <c r="E13" s="253"/>
+    </row>
+    <row r="14" spans="1:6" ht="29.25">
+      <c r="A14" s="240" t="s">
+        <v>472</v>
+      </c>
+      <c r="B14" s="241" t="s">
+        <v>473</v>
+      </c>
+      <c r="C14" s="242" t="s">
+        <v>474</v>
+      </c>
+      <c r="D14" s="269"/>
+      <c r="E14" s="254"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="237" t="s">
+        <v>475</v>
+      </c>
+      <c r="B15" s="238" t="s">
         <v>463</v>
       </c>
-      <c r="B11" s="244" t="s">
-        <v>464</v>
-      </c>
-      <c r="C11" s="245" t="s">
-        <v>465</v>
-      </c>
-      <c r="D11" s="264"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="251" t="s">
-        <v>466</v>
-      </c>
-      <c r="B12" s="268"/>
-      <c r="C12" s="268"/>
-      <c r="D12" s="266"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="237" t="s">
-        <v>467</v>
-      </c>
-      <c r="B13" s="238" t="s">
-        <v>468</v>
-      </c>
-      <c r="C13" s="239" t="s">
-        <v>469</v>
-      </c>
-      <c r="D13" s="264"/>
-    </row>
-    <row r="14" spans="1:5" ht="29.25">
-      <c r="A14" s="240" t="s">
-        <v>470</v>
-      </c>
-      <c r="B14" s="241" t="s">
-        <v>471</v>
-      </c>
-      <c r="C14" s="242" t="s">
-        <v>472</v>
-      </c>
-      <c r="D14" s="265"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="237" t="s">
-        <v>473</v>
-      </c>
-      <c r="B15" s="238" t="s">
-        <v>461</v>
-      </c>
       <c r="C15" s="239" t="s">
-        <v>474</v>
-      </c>
-      <c r="D15" s="264"/>
-    </row>
-    <row r="16" spans="1:5">
+        <v>476</v>
+      </c>
+      <c r="D15" s="268"/>
+      <c r="E15" s="253"/>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="246">
         <v>0.875</v>
       </c>
       <c r="B16" s="247" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C16" s="248" t="s">
-        <v>476</v>
-      </c>
-      <c r="D16" s="265"/>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="251" t="s">
-        <v>477</v>
-      </c>
-      <c r="B17" s="268"/>
-      <c r="C17" s="268"/>
-      <c r="D17" s="266"/>
-    </row>
-    <row r="18" spans="1:4">
+        <v>478</v>
+      </c>
+      <c r="D16" s="269"/>
+      <c r="E16" s="254"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="257" t="s">
+        <v>479</v>
+      </c>
+      <c r="B17" s="272"/>
+      <c r="C17" s="272"/>
+      <c r="D17" s="270"/>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="237" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B18" s="238" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C18" s="239" t="s">
-        <v>480</v>
-      </c>
-      <c r="D18" s="264"/>
-    </row>
-    <row r="19" spans="1:4" ht="29.25">
+        <v>482</v>
+      </c>
+      <c r="D18" s="268"/>
+      <c r="E18" s="253"/>
+    </row>
+    <row r="19" spans="1:5" ht="29.25">
       <c r="A19" s="240" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B19" s="241" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C19" s="242" t="s">
+        <v>485</v>
+      </c>
+      <c r="D19" s="269"/>
+      <c r="E19" s="254"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="237" t="s">
+        <v>486</v>
+      </c>
+      <c r="B20" s="238" t="s">
+        <v>451</v>
+      </c>
+      <c r="C20" s="239" t="s">
+        <v>487</v>
+      </c>
+      <c r="D20" s="268"/>
+      <c r="E20" s="253"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="240" t="s">
+        <v>488</v>
+      </c>
+      <c r="B21" s="241" t="s">
+        <v>489</v>
+      </c>
+      <c r="C21" s="242" t="s">
+        <v>490</v>
+      </c>
+      <c r="D21" s="269"/>
+      <c r="E21" s="254"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="237" t="s">
+        <v>491</v>
+      </c>
+      <c r="B22" s="238" t="s">
+        <v>492</v>
+      </c>
+      <c r="C22" s="239" t="s">
+        <v>493</v>
+      </c>
+      <c r="D22" s="268"/>
+      <c r="E22" s="253"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="240" t="s">
+        <v>462</v>
+      </c>
+      <c r="B23" s="241" t="s">
+        <v>463</v>
+      </c>
+      <c r="C23" s="242" t="s">
+        <v>494</v>
+      </c>
+      <c r="D23" s="269"/>
+      <c r="E23" s="254"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="255" t="s">
+        <v>495</v>
+      </c>
+      <c r="B24" s="273"/>
+      <c r="C24" s="273"/>
+      <c r="D24" s="270"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="237" t="s">
+        <v>496</v>
+      </c>
+      <c r="B25" s="238" t="s">
+        <v>497</v>
+      </c>
+      <c r="C25" s="239" t="s">
+        <v>498</v>
+      </c>
+      <c r="D25" s="268"/>
+      <c r="E25" s="253"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="240" t="s">
+        <v>499</v>
+      </c>
+      <c r="B26" s="241" t="s">
+        <v>451</v>
+      </c>
+      <c r="C26" s="242" t="s">
+        <v>500</v>
+      </c>
+      <c r="D26" s="269"/>
+      <c r="E26" s="254"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="237" t="s">
+        <v>501</v>
+      </c>
+      <c r="B27" s="238" t="s">
+        <v>502</v>
+      </c>
+      <c r="C27" s="239" t="s">
+        <v>503</v>
+      </c>
+      <c r="D27" s="268"/>
+      <c r="E27" s="253"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="240" t="s">
+        <v>491</v>
+      </c>
+      <c r="B28" s="241" t="s">
+        <v>492</v>
+      </c>
+      <c r="C28" s="242" t="s">
+        <v>504</v>
+      </c>
+      <c r="D28" s="269"/>
+      <c r="E28" s="254"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="237" t="s">
+        <v>505</v>
+      </c>
+      <c r="B29" s="238" t="s">
+        <v>506</v>
+      </c>
+      <c r="C29" s="239" t="s">
+        <v>507</v>
+      </c>
+      <c r="D29" s="268"/>
+      <c r="E29" s="253"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="255" t="s">
+        <v>508</v>
+      </c>
+      <c r="B30" s="273"/>
+      <c r="C30" s="273"/>
+      <c r="D30" s="270"/>
+    </row>
+    <row r="31" spans="1:5" ht="29.25">
+      <c r="A31" s="237" t="s">
+        <v>509</v>
+      </c>
+      <c r="B31" s="238" t="s">
+        <v>510</v>
+      </c>
+      <c r="C31" s="239" t="s">
+        <v>511</v>
+      </c>
+      <c r="D31" s="268"/>
+      <c r="E31" s="253"/>
+    </row>
+    <row r="32" spans="1:5" ht="29.25">
+      <c r="A32" s="240" t="s">
+        <v>512</v>
+      </c>
+      <c r="B32" s="241" t="s">
+        <v>513</v>
+      </c>
+      <c r="C32" s="242" t="s">
+        <v>514</v>
+      </c>
+      <c r="D32" s="269"/>
+      <c r="E32" s="254"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="237" t="s">
+        <v>515</v>
+      </c>
+      <c r="B33" s="238" t="s">
+        <v>516</v>
+      </c>
+      <c r="C33" s="239" t="s">
+        <v>517</v>
+      </c>
+      <c r="D33" s="268"/>
+      <c r="E33" s="253"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="240" t="s">
+        <v>505</v>
+      </c>
+      <c r="B34" s="241" t="s">
+        <v>463</v>
+      </c>
+      <c r="C34" s="242" t="s">
+        <v>518</v>
+      </c>
+      <c r="D34" s="269"/>
+      <c r="E34" s="254"/>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="255" t="s">
+        <v>519</v>
+      </c>
+      <c r="B35" s="273"/>
+      <c r="C35" s="273"/>
+      <c r="D35" s="270"/>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="237" t="s">
+        <v>520</v>
+      </c>
+      <c r="B36" s="238" t="s">
+        <v>521</v>
+      </c>
+      <c r="C36" s="239" t="s">
+        <v>522</v>
+      </c>
+      <c r="D36" s="268"/>
+      <c r="E36" s="253"/>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="240" t="s">
+        <v>499</v>
+      </c>
+      <c r="B37" s="241" t="s">
+        <v>451</v>
+      </c>
+      <c r="C37" s="242" t="s">
+        <v>523</v>
+      </c>
+      <c r="D37" s="269"/>
+      <c r="E37" s="254"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="237" t="s">
+        <v>501</v>
+      </c>
+      <c r="B38" s="238" t="s">
+        <v>524</v>
+      </c>
+      <c r="C38" s="239" t="s">
+        <v>525</v>
+      </c>
+      <c r="D38" s="268"/>
+      <c r="E38" s="253"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="240" t="s">
+        <v>526</v>
+      </c>
+      <c r="B39" s="241" t="s">
+        <v>492</v>
+      </c>
+      <c r="C39" s="242" t="s">
+        <v>527</v>
+      </c>
+      <c r="D39" s="269"/>
+      <c r="E39" s="254"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="237" t="s">
+        <v>528</v>
+      </c>
+      <c r="B40" s="238" t="s">
+        <v>463</v>
+      </c>
+      <c r="C40" s="239" t="s">
+        <v>529</v>
+      </c>
+      <c r="D40" s="268"/>
+      <c r="E40" s="253"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="255" t="s">
+        <v>530</v>
+      </c>
+      <c r="B41" s="273"/>
+      <c r="C41" s="273"/>
+      <c r="D41" s="270"/>
+    </row>
+    <row r="42" spans="1:5" ht="29.25">
+      <c r="A42" s="237" t="s">
         <v>483</v>
       </c>
-      <c r="D19" s="265"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="237" t="s">
-        <v>484</v>
-      </c>
-      <c r="B20" s="238" t="s">
-        <v>449</v>
-      </c>
-      <c r="C20" s="239" t="s">
-        <v>485</v>
-      </c>
-      <c r="D20" s="264"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="240" t="s">
+      <c r="B42" s="238" t="s">
+        <v>531</v>
+      </c>
+      <c r="C42" s="239" t="s">
+        <v>532</v>
+      </c>
+      <c r="D42" s="268"/>
+      <c r="E42" s="253"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="240" t="s">
         <v>486</v>
       </c>
-      <c r="B21" s="241" t="s">
-        <v>487</v>
-      </c>
-      <c r="C21" s="242" t="s">
-        <v>488</v>
-      </c>
-      <c r="D21" s="265"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="237" t="s">
-        <v>489</v>
-      </c>
-      <c r="B22" s="238" t="s">
-        <v>490</v>
-      </c>
-      <c r="C22" s="239" t="s">
-        <v>491</v>
-      </c>
-      <c r="D22" s="264"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="240" t="s">
-        <v>460</v>
-      </c>
-      <c r="B23" s="241" t="s">
-        <v>461</v>
-      </c>
-      <c r="C23" s="242" t="s">
-        <v>492</v>
-      </c>
-      <c r="D23" s="265"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="249" t="s">
-        <v>493</v>
-      </c>
-      <c r="B24" s="269"/>
-      <c r="C24" s="269"/>
-      <c r="D24" s="266"/>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="237" t="s">
-        <v>494</v>
-      </c>
-      <c r="B25" s="238" t="s">
-        <v>495</v>
-      </c>
-      <c r="C25" s="239" t="s">
-        <v>496</v>
-      </c>
-      <c r="D25" s="264"/>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="240" t="s">
-        <v>497</v>
-      </c>
-      <c r="B26" s="241" t="s">
-        <v>449</v>
-      </c>
-      <c r="C26" s="242" t="s">
-        <v>498</v>
-      </c>
-      <c r="D26" s="265"/>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" s="237" t="s">
+      <c r="B43" s="241" t="s">
+        <v>451</v>
+      </c>
+      <c r="C43" s="242" t="s">
+        <v>533</v>
+      </c>
+      <c r="D43" s="269"/>
+      <c r="E43" s="254"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="237" t="s">
+        <v>501</v>
+      </c>
+      <c r="B44" s="238" t="s">
+        <v>534</v>
+      </c>
+      <c r="C44" s="239" t="s">
+        <v>535</v>
+      </c>
+      <c r="D44" s="268"/>
+      <c r="E44" s="253"/>
+    </row>
+    <row r="45" spans="1:5" ht="15.75">
+      <c r="A45" s="240" t="s">
+        <v>536</v>
+      </c>
+      <c r="B45" s="241" t="s">
+        <v>537</v>
+      </c>
+      <c r="C45" s="242" t="s">
+        <v>538</v>
+      </c>
+      <c r="D45" s="269"/>
+      <c r="E45" s="254"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="255" t="s">
+        <v>539</v>
+      </c>
+      <c r="B46" s="273"/>
+      <c r="C46" s="273"/>
+      <c r="D46" s="270"/>
+    </row>
+    <row r="47" spans="1:5" ht="29.25">
+      <c r="A47" s="237" t="s">
+        <v>520</v>
+      </c>
+      <c r="B47" s="238" t="s">
+        <v>540</v>
+      </c>
+      <c r="C47" s="239" t="s">
+        <v>541</v>
+      </c>
+      <c r="D47" s="268"/>
+      <c r="E47" s="253"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="240" t="s">
         <v>499</v>
       </c>
-      <c r="B27" s="238" t="s">
-        <v>500</v>
-      </c>
-      <c r="C27" s="239" t="s">
-        <v>501</v>
-      </c>
-      <c r="D27" s="264"/>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="240" t="s">
-        <v>489</v>
-      </c>
-      <c r="B28" s="241" t="s">
-        <v>490</v>
-      </c>
-      <c r="C28" s="242" t="s">
-        <v>502</v>
-      </c>
-      <c r="D28" s="265"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="237" t="s">
-        <v>503</v>
-      </c>
-      <c r="B29" s="238" t="s">
-        <v>504</v>
-      </c>
-      <c r="C29" s="239" t="s">
+      <c r="B48" s="241" t="s">
+        <v>451</v>
+      </c>
+      <c r="C48" s="242" t="s">
+        <v>542</v>
+      </c>
+      <c r="D48" s="269"/>
+      <c r="E48" s="254"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="237" t="s">
+        <v>543</v>
+      </c>
+      <c r="B49" s="238" t="s">
+        <v>544</v>
+      </c>
+      <c r="C49" s="239" t="s">
+        <v>545</v>
+      </c>
+      <c r="D49" s="268"/>
+      <c r="E49" s="253"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="240" t="s">
         <v>505</v>
       </c>
-      <c r="D29" s="264"/>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="249" t="s">
-        <v>506</v>
-      </c>
-      <c r="B30" s="269"/>
-      <c r="C30" s="269"/>
-      <c r="D30" s="266"/>
-    </row>
-    <row r="31" spans="1:4" ht="29.25">
-      <c r="A31" s="237" t="s">
-        <v>507</v>
-      </c>
-      <c r="B31" s="238" t="s">
-        <v>508</v>
-      </c>
-      <c r="C31" s="239" t="s">
-        <v>509</v>
-      </c>
-      <c r="D31" s="264"/>
-    </row>
-    <row r="32" spans="1:4" ht="29.25">
-      <c r="A32" s="240" t="s">
-        <v>510</v>
-      </c>
-      <c r="B32" s="241" t="s">
-        <v>511</v>
-      </c>
-      <c r="C32" s="242" t="s">
-        <v>512</v>
-      </c>
-      <c r="D32" s="265"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="237" t="s">
-        <v>513</v>
-      </c>
-      <c r="B33" s="238" t="s">
-        <v>514</v>
-      </c>
-      <c r="C33" s="239" t="s">
-        <v>515</v>
-      </c>
-      <c r="D33" s="264"/>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="240" t="s">
-        <v>503</v>
-      </c>
-      <c r="B34" s="241" t="s">
-        <v>461</v>
-      </c>
-      <c r="C34" s="242" t="s">
-        <v>516</v>
-      </c>
-      <c r="D34" s="265"/>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="249" t="s">
-        <v>517</v>
-      </c>
-      <c r="B35" s="269"/>
-      <c r="C35" s="269"/>
-      <c r="D35" s="266"/>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" s="237" t="s">
-        <v>518</v>
-      </c>
-      <c r="B36" s="238" t="s">
-        <v>519</v>
-      </c>
-      <c r="C36" s="239" t="s">
-        <v>520</v>
-      </c>
-      <c r="D36" s="264"/>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" s="240" t="s">
-        <v>497</v>
-      </c>
-      <c r="B37" s="241" t="s">
-        <v>449</v>
-      </c>
-      <c r="C37" s="242" t="s">
-        <v>521</v>
-      </c>
-      <c r="D37" s="265"/>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="237" t="s">
-        <v>499</v>
-      </c>
-      <c r="B38" s="238" t="s">
-        <v>522</v>
-      </c>
-      <c r="C38" s="239" t="s">
-        <v>523</v>
-      </c>
-      <c r="D38" s="264"/>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="240" t="s">
-        <v>524</v>
-      </c>
-      <c r="B39" s="241" t="s">
-        <v>490</v>
-      </c>
-      <c r="C39" s="242" t="s">
-        <v>525</v>
-      </c>
-      <c r="D39" s="265"/>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" s="237" t="s">
-        <v>526</v>
-      </c>
-      <c r="B40" s="238" t="s">
-        <v>461</v>
-      </c>
-      <c r="C40" s="239" t="s">
-        <v>527</v>
-      </c>
-      <c r="D40" s="264"/>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" s="249" t="s">
-        <v>528</v>
-      </c>
-      <c r="B41" s="269"/>
-      <c r="C41" s="269"/>
-      <c r="D41" s="266"/>
-    </row>
-    <row r="42" spans="1:4" ht="29.25">
-      <c r="A42" s="237" t="s">
-        <v>481</v>
-      </c>
-      <c r="B42" s="238" t="s">
-        <v>529</v>
-      </c>
-      <c r="C42" s="239" t="s">
-        <v>530</v>
-      </c>
-      <c r="D42" s="264"/>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="240" t="s">
-        <v>484</v>
-      </c>
-      <c r="B43" s="241" t="s">
-        <v>449</v>
-      </c>
-      <c r="C43" s="242" t="s">
-        <v>531</v>
-      </c>
-      <c r="D43" s="265"/>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="237" t="s">
-        <v>499</v>
-      </c>
-      <c r="B44" s="238" t="s">
-        <v>532</v>
-      </c>
-      <c r="C44" s="239" t="s">
-        <v>533</v>
-      </c>
-      <c r="D44" s="264"/>
-    </row>
-    <row r="45" spans="1:4" ht="15.75">
-      <c r="A45" s="240" t="s">
-        <v>534</v>
-      </c>
-      <c r="B45" s="241" t="s">
-        <v>535</v>
-      </c>
-      <c r="C45" s="242" t="s">
-        <v>536</v>
-      </c>
-      <c r="D45" s="265"/>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" s="249" t="s">
-        <v>537</v>
-      </c>
-      <c r="B46" s="269"/>
-      <c r="C46" s="269"/>
-      <c r="D46" s="266"/>
-    </row>
-    <row r="47" spans="1:4" ht="29.25">
-      <c r="A47" s="237" t="s">
-        <v>518</v>
-      </c>
-      <c r="B47" s="238" t="s">
-        <v>538</v>
-      </c>
-      <c r="C47" s="239" t="s">
-        <v>539</v>
-      </c>
-      <c r="D47" s="264"/>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="240" t="s">
-        <v>497</v>
-      </c>
-      <c r="B48" s="241" t="s">
-        <v>449</v>
-      </c>
-      <c r="C48" s="242" t="s">
-        <v>540</v>
-      </c>
-      <c r="D48" s="265"/>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" s="237" t="s">
-        <v>541</v>
-      </c>
-      <c r="B49" s="238" t="s">
-        <v>542</v>
-      </c>
-      <c r="C49" s="239" t="s">
-        <v>543</v>
-      </c>
-      <c r="D49" s="264"/>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="240" t="s">
-        <v>503</v>
-      </c>
       <c r="B50" s="241" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C50" s="242" t="s">
-        <v>545</v>
-      </c>
-      <c r="D50" s="265"/>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" s="249" t="s">
-        <v>546</v>
-      </c>
-      <c r="B51" s="269"/>
-      <c r="C51" s="269"/>
-      <c r="D51" s="266"/>
-    </row>
-    <row r="52" spans="1:4">
+        <v>547</v>
+      </c>
+      <c r="D50" s="269"/>
+      <c r="E50" s="254"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="255" t="s">
+        <v>548</v>
+      </c>
+      <c r="B51" s="273"/>
+      <c r="C51" s="273"/>
+      <c r="D51" s="270"/>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" s="237" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B52" s="238" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C52" s="239" t="s">
-        <v>549</v>
-      </c>
-      <c r="D52" s="264"/>
-    </row>
-    <row r="53" spans="1:4">
+        <v>551</v>
+      </c>
+      <c r="D52" s="268"/>
+      <c r="E52" s="253"/>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" s="240" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B53" s="241" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C53" s="242" t="s">
-        <v>551</v>
-      </c>
-      <c r="D53" s="265"/>
-    </row>
-    <row r="54" spans="1:4">
+        <v>553</v>
+      </c>
+      <c r="D53" s="269"/>
+      <c r="E53" s="254"/>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" s="237" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B54" s="238" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C54" s="239" t="s">
-        <v>554</v>
-      </c>
-      <c r="D54" s="264"/>
-    </row>
-    <row r="55" spans="1:4">
+        <v>556</v>
+      </c>
+      <c r="D54" s="268"/>
+      <c r="E54" s="253"/>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" s="240" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B55" s="241" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C55" s="242" t="s">
-        <v>557</v>
-      </c>
-      <c r="D55" s="265"/>
+        <v>559</v>
+      </c>
+      <c r="D55" s="269"/>
+      <c r="E55" s="254"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -13445,6 +13512,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005A4695005C4BEE4A8751FEE2C473E10D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df7fcaa21f93254d26451ff7a6d04ad2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xmlns:ns4="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fefbcb393e90fe08e3723c038b505a33" ns3:_="" ns4:_="">
     <xsd:import namespace="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
@@ -13683,15 +13759,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -13701,11 +13768,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54F1CD7F-463B-4D32-9D5A-3DEEAD61640C}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B59818CB-455F-4711-86E1-8C5361AD4E42}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" firstSheet="4" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="562">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1403,7 +1403,13 @@
     <t>Send Luggage</t>
   </si>
   <si>
-    <t>Send Luggage at Yamato Transport - Terminal 2, 3rd Floor</t>
+    <t>Send Luggage at Yamato Transport</t>
+  </si>
+  <si>
+    <t>Yamato: Terminal 2, 3rd Floor</t>
+  </si>
+  <si>
+    <t>https://www.kuronekoyamato.co.jp/ytc/en/send/services/airport/narita2_send.html</t>
   </si>
   <si>
     <t>11:00 - 12:00</t>
@@ -1415,7 +1421,7 @@
     <t>Transfer from Narita Airport to Tokyo via Keisei Skyliner / Train</t>
   </si>
   <si>
-    <t>Airbnb: 6-chōme-12-1 Ōmorikita エルメゾン大森203, Thành phố Ota, Tỉnh Tokyo 143-0016, Nhật Bản</t>
+    <t>Airbnb: 6-chōme-12-1 Ōmorikita エルメゾン大森203, Ota City, Tokyo</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/DBmdvffro3LetJej6</t>
@@ -12863,108 +12869,113 @@
       <c r="C4" s="242" t="s">
         <v>444</v>
       </c>
-      <c r="D4" s="269"/>
+      <c r="D4" s="269" t="s">
+        <v>445</v>
+      </c>
       <c r="E4" s="254"/>
-    </row>
-    <row r="5" spans="1:6" ht="45">
+      <c r="F4" s="8" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30.75">
       <c r="A5" s="237" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B5" s="238" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C5" s="239" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D5" s="268" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E5" s="253"/>
       <c r="F5" s="250" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="240" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B6" s="241" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C6" s="242" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D6" s="269"/>
       <c r="E6" s="254"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="237" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B7" s="241" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C7" s="242" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="D7" s="269"/>
       <c r="E7" s="254"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="240" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B8" s="241" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C8" s="242" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D8" s="269"/>
       <c r="E8" s="254"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="237" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B9" s="238" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C9" s="239" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D9" s="268"/>
       <c r="E9" s="253"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="240" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B10" s="241" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C10" s="242" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D10" s="269"/>
       <c r="E10" s="254"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="243" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B11" s="244" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C11" s="245" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D11" s="268"/>
       <c r="E11" s="253"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="257" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B12" s="272"/>
       <c r="C12" s="272"/>
@@ -12972,39 +12983,39 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="237" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B13" s="238" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C13" s="239" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D13" s="268"/>
       <c r="E13" s="253"/>
     </row>
     <row r="14" spans="1:6" ht="29.25">
       <c r="A14" s="240" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B14" s="241" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C14" s="242" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D14" s="269"/>
       <c r="E14" s="254"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="237" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B15" s="238" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C15" s="239" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D15" s="268"/>
       <c r="E15" s="253"/>
@@ -13014,17 +13025,17 @@
         <v>0.875</v>
       </c>
       <c r="B16" s="247" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C16" s="248" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D16" s="269"/>
       <c r="E16" s="254"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="257" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B17" s="272"/>
       <c r="C17" s="272"/>
@@ -13032,85 +13043,85 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="237" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B18" s="238" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C18" s="239" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D18" s="268"/>
       <c r="E18" s="253"/>
     </row>
     <row r="19" spans="1:5" ht="29.25">
       <c r="A19" s="240" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B19" s="241" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C19" s="242" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D19" s="269"/>
       <c r="E19" s="254"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="237" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B20" s="238" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C20" s="239" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D20" s="268"/>
       <c r="E20" s="253"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="240" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B21" s="241" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C21" s="242" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D21" s="269"/>
       <c r="E21" s="254"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="237" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B22" s="238" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C22" s="239" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D22" s="268"/>
       <c r="E22" s="253"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="240" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B23" s="241" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C23" s="242" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D23" s="269"/>
       <c r="E23" s="254"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="255" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B24" s="273"/>
       <c r="C24" s="273"/>
@@ -13118,72 +13129,72 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="237" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B25" s="238" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C25" s="239" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D25" s="268"/>
       <c r="E25" s="253"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="240" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B26" s="241" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C26" s="242" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D26" s="269"/>
       <c r="E26" s="254"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="237" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B27" s="238" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C27" s="239" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D27" s="268"/>
       <c r="E27" s="253"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="240" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B28" s="241" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C28" s="242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D28" s="269"/>
       <c r="E28" s="254"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="237" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B29" s="238" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C29" s="239" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D29" s="268"/>
       <c r="E29" s="253"/>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="255" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B30" s="273"/>
       <c r="C30" s="273"/>
@@ -13191,59 +13202,59 @@
     </row>
     <row r="31" spans="1:5" ht="29.25">
       <c r="A31" s="237" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B31" s="238" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C31" s="239" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D31" s="268"/>
       <c r="E31" s="253"/>
     </row>
     <row r="32" spans="1:5" ht="29.25">
       <c r="A32" s="240" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B32" s="241" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C32" s="242" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D32" s="269"/>
       <c r="E32" s="254"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="237" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B33" s="238" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C33" s="239" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D33" s="268"/>
       <c r="E33" s="253"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="240" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B34" s="241" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C34" s="242" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D34" s="269"/>
       <c r="E34" s="254"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="255" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B35" s="273"/>
       <c r="C35" s="273"/>
@@ -13251,72 +13262,72 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="237" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B36" s="238" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C36" s="239" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D36" s="268"/>
       <c r="E36" s="253"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="240" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B37" s="241" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C37" s="242" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D37" s="269"/>
       <c r="E37" s="254"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="237" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B38" s="238" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C38" s="239" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D38" s="268"/>
       <c r="E38" s="253"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="240" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B39" s="241" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C39" s="242" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D39" s="269"/>
       <c r="E39" s="254"/>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="237" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B40" s="238" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C40" s="239" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D40" s="268"/>
       <c r="E40" s="253"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="255" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B41" s="273"/>
       <c r="C41" s="273"/>
@@ -13324,59 +13335,59 @@
     </row>
     <row r="42" spans="1:5" ht="29.25">
       <c r="A42" s="237" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B42" s="238" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C42" s="239" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D42" s="268"/>
       <c r="E42" s="253"/>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="240" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B43" s="241" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C43" s="242" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D43" s="269"/>
       <c r="E43" s="254"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="237" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B44" s="238" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C44" s="239" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D44" s="268"/>
       <c r="E44" s="253"/>
     </row>
     <row r="45" spans="1:5" ht="15.75">
       <c r="A45" s="240" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B45" s="241" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C45" s="242" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D45" s="269"/>
       <c r="E45" s="254"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="255" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B46" s="273"/>
       <c r="C46" s="273"/>
@@ -13384,59 +13395,59 @@
     </row>
     <row r="47" spans="1:5" ht="29.25">
       <c r="A47" s="237" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B47" s="238" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C47" s="239" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D47" s="268"/>
       <c r="E47" s="253"/>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="240" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B48" s="241" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C48" s="242" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D48" s="269"/>
       <c r="E48" s="254"/>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="237" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B49" s="238" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C49" s="239" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D49" s="268"/>
       <c r="E49" s="253"/>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="240" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B50" s="241" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C50" s="242" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D50" s="269"/>
       <c r="E50" s="254"/>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="255" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B51" s="273"/>
       <c r="C51" s="273"/>
@@ -13444,52 +13455,52 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="237" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B52" s="238" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C52" s="239" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D52" s="268"/>
       <c r="E52" s="253"/>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="240" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B53" s="241" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C53" s="242" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D53" s="269"/>
       <c r="E53" s="254"/>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="237" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B54" s="238" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C54" s="239" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D54" s="268"/>
       <c r="E54" s="253"/>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="240" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B55" s="241" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C55" s="242" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D55" s="269"/>
       <c r="E55" s="254"/>
@@ -13506,8 +13517,11 @@
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A35:C35"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{6D84B550-56D9-418A-9D1C-EC3261D9DE2C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B59818CB-455F-4711-86E1-8C5361AD4E42}"/>
+  <xr:revisionPtr revIDLastSave="165" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2B685CF-E5ED-4784-BE59-CD773F258209}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" firstSheet="4" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="571">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1403,10 +1403,7 @@
     <t>Send Luggage</t>
   </si>
   <si>
-    <t>Send Luggage at Yamato Transport</t>
-  </si>
-  <si>
-    <t>Yamato: Terminal 2, 3rd Floor</t>
+    <t>Yamato Transport on Terminal 2, 3rd Floor</t>
   </si>
   <si>
     <t>https://www.kuronekoyamato.co.jp/ytc/en/send/services/airport/narita2_send.html</t>
@@ -1418,10 +1415,10 @@
     <t>Airport Transfer</t>
   </si>
   <si>
-    <t>Transfer from Narita Airport to Tokyo via Keisei Skyliner / Train</t>
-  </si>
-  <si>
-    <t>Airbnb: 6-chōme-12-1 Ōmorikita エルメゾン大森203, Ota City, Tokyo</t>
+    <t>Transfer from Narita to Tokyo via Keisei Skyliner / Train</t>
+  </si>
+  <si>
+    <t>Airbnb</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/DBmdvffro3LetJej6</t>
@@ -1433,16 +1430,19 @@
     <t>Lunch</t>
   </si>
   <si>
-    <t>Enjoy authentic Japanese curry at CoCo Ichibanya.</t>
+    <t xml:space="preserve">Enjoy Japanese curry </t>
+  </si>
+  <si>
+    <t>CoCo Ichibanya</t>
   </si>
   <si>
     <t>13:00 - 14:00</t>
   </si>
   <si>
-    <t>Check-in &amp; Refresh</t>
-  </si>
-  <si>
-    <t>Airbnb Check in</t>
+    <t>Check-in</t>
+  </si>
+  <si>
+    <t>Airbnb Check in at 6-chōme-12-1 Ōmorikita エルメゾン大森203, Ota City, Tokyo</t>
   </si>
   <si>
     <t>14:00 - 16:30</t>
@@ -1451,7 +1451,13 @@
     <t>Miraikan Museum</t>
   </si>
   <si>
-    <t>Visit Miraikan (National Museum of Emerging Science and Innovation)</t>
+    <t>Visit National Museum of Emerging Science and Innovation</t>
+  </si>
+  <si>
+    <t>Miraikan</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/BmYZxEzfSyLjgQyp9</t>
   </si>
   <si>
     <t>16:30 - 17:30</t>
@@ -1460,7 +1466,13 @@
     <t>Odaiba Sunset</t>
   </si>
   <si>
-    <t>Sunset stroll at Odaiba Seaside Park; admire Rainbow Bridge and Tokyo Bay skyline.</t>
+    <t>Sunset stroll at Odaiba Seaside Park; Admire Rainbow Bridge and Tokyo Bay skyline.</t>
+  </si>
+  <si>
+    <t>Sunset point</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/t1SnqWYUNsLD9mvk7</t>
   </si>
   <si>
     <t>18:00 - 20:00</t>
@@ -1469,16 +1481,13 @@
     <t>Dinner</t>
   </si>
   <si>
-    <t>Traditional Tokyo Monjayaki specialty dinner</t>
-  </si>
-  <si>
-    <t>20:00 - 21:00</t>
-  </si>
-  <si>
-    <t>Evening Leisure</t>
-  </si>
-  <si>
-    <t>Night at Tokyo Tower and return hotel to rest</t>
+    <t>Traditional Tokyo Monjayaki dinner</t>
+  </si>
+  <si>
+    <t>Evening</t>
+  </si>
+  <si>
+    <t>Night at Tokyo and Return hotel to rest</t>
   </si>
   <si>
     <t xml:space="preserve">  Day 2: Tokyo DisneySea</t>
@@ -1490,28 +1499,31 @@
     <t>Transfer to Disney</t>
   </si>
   <si>
-    <t>Transfer from hotel to Tokyo DisneySea (Maihama, Chiba).</t>
+    <t>Transfer from hotel to Tokyo DisneySea</t>
+  </si>
+  <si>
+    <t>Tokyo DisneySea</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mFXM4V9B9K4DBWVz8</t>
   </si>
   <si>
     <t>09:00 - 16:00</t>
   </si>
   <si>
-    <t>Tokyo DisneySea</t>
-  </si>
-  <si>
     <t>Full day exploring themed ports: Mediterranean Harbor, Mysterious Island, Arabian Coast &amp; thrilling attractions. Lunch inside park.</t>
   </si>
   <si>
     <t>17:00 - 21:00</t>
   </si>
   <si>
-    <t>Fresh kaiten-sushi dinner at Sushiro (Omorikita branch).</t>
-  </si>
-  <si>
-    <t>Return to Hotel</t>
-  </si>
-  <si>
-    <t>Evening leisure &amp; rest at hotel.</t>
+    <t>Fresh sushi dinner at Sushiro</t>
+  </si>
+  <si>
+    <t>Omorikita branch</t>
+  </si>
+  <si>
+    <t>https://share.google/glhiHLvLUNFKbIXOL</t>
   </si>
   <si>
     <t xml:space="preserve">  Day 3: Mount Fuji • Oshino Hakkai • Lake Kawaguchiko</t>
@@ -1523,7 +1535,7 @@
     <t>Depart for Mt. Fuji</t>
   </si>
   <si>
-    <t>Check out hotel; transfer from Tokyo toward Fuji Five Lakes region.</t>
+    <t>Check out hotel; Transfer from Tokyo toward Fuji Mount</t>
   </si>
   <si>
     <t>08:00 - 12:00</t>
@@ -1538,7 +1550,13 @@
     <t>12:00 - 13:30</t>
   </si>
   <si>
-    <t>Authentic Koshu Hoto Kosaku noodles (pumpkin miso noodle stew).</t>
+    <t>Authentic Koshu Hoto Kosaku noodles (Pumpkin miso noodle stew).</t>
+  </si>
+  <si>
+    <t>Huto Noodle</t>
+  </si>
+  <si>
+    <t>https://share.google/07foiHP82iKKrDXLN</t>
   </si>
   <si>
     <t>13:30 - 16:00</t>
@@ -1559,7 +1577,16 @@
     <t>Check in Fuji Kawaguchiko Resort Hotel; relax with Mount Fuji view.</t>
   </si>
   <si>
+    <t xml:space="preserve"> Fuji Kawaguchiko Resort Hotel</t>
+  </si>
+  <si>
+    <t>https://share.google/HkyzWgzwgKD1EYvWY</t>
+  </si>
+  <si>
     <t>Charcoal-grilled BBQ/ Yakitori dinner at Sanrokuen.</t>
+  </si>
+  <si>
+    <t>tiktok.com/@wethecurioustravelers/video/7350291288496901394?is_from_webapp=1&amp;sender_device=pc&amp;web_id=7410061434220971537</t>
   </si>
   <si>
     <t xml:space="preserve">  Day 4: Kawaguchiko • Matsumoto City</t>
@@ -2084,7 +2111,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -2147,74 +2174,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD0D7DE"/>
+        <color theme="2"/>
       </left>
       <right style="thin">
-        <color rgb="FFD0D7DE"/>
+        <color theme="2"/>
       </right>
-      <top style="medium">
-        <color rgb="FF123056"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF123056"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD0D7DE"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D7DE"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF123056"/>
+      <top style="thin">
+        <color theme="2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFD0D7DE"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD0D7DE"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D7DE"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D7DE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD0D7DE"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD0D7DE"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D7DE"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD0D7DE"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD0D7DE"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD0D7DE"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD0D7DE"/>
+        <color theme="2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2224,7 +2193,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="274">
+  <cellXfs count="261">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2863,104 +2832,67 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="31" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="31" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -6036,7 +5968,7 @@
     <row r="137" spans="1:8" ht="15" customHeight="1">
       <c r="A137" s="37"/>
       <c r="B137" s="38"/>
-      <c r="C137" s="258" t="s">
+      <c r="C137" s="236" t="s">
         <v>179</v>
       </c>
       <c r="D137" s="38"/>
@@ -6051,7 +5983,7 @@
     <row r="138" spans="1:8" ht="15" customHeight="1">
       <c r="A138" s="37"/>
       <c r="B138" s="38"/>
-      <c r="C138" s="258"/>
+      <c r="C138" s="236"/>
       <c r="D138" s="38"/>
       <c r="E138" s="39"/>
       <c r="F138" s="38"/>
@@ -6777,8 +6709,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="259" customFormat="1">
-      <c r="A2" s="259" t="s">
+    <row r="2" spans="1:10" s="237" customFormat="1">
+      <c r="A2" s="237" t="s">
         <v>226</v>
       </c>
     </row>
@@ -6885,10 +6817,10 @@
     <row r="8" spans="1:10">
       <c r="A8" s="84"/>
       <c r="B8" s="85"/>
-      <c r="C8" s="260" t="s">
+      <c r="C8" s="238" t="s">
         <v>230</v>
       </c>
-      <c r="D8" s="260"/>
+      <c r="D8" s="238"/>
       <c r="E8" s="96">
         <v>1500</v>
       </c>
@@ -6931,10 +6863,10 @@
       <c r="J10" s="85"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="260" t="s">
+      <c r="A11" s="238" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="260"/>
+      <c r="B11" s="238"/>
       <c r="C11" s="99">
         <v>27</v>
       </c>
@@ -9268,8 +9200,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="259" customFormat="1">
-      <c r="A2" s="259" t="s">
+    <row r="2" spans="1:12" s="237" customFormat="1">
+      <c r="A2" s="237" t="s">
         <v>226</v>
       </c>
     </row>
@@ -9430,10 +9362,10 @@
     <row r="10" spans="1:12">
       <c r="A10" s="84"/>
       <c r="B10" s="85"/>
-      <c r="C10" s="260" t="s">
+      <c r="C10" s="238" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="260"/>
+      <c r="D10" s="238"/>
       <c r="E10" s="96">
         <v>3000</v>
       </c>
@@ -9476,10 +9408,10 @@
       <c r="J12" s="85"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="260" t="s">
+      <c r="A13" s="238" t="s">
         <v>233</v>
       </c>
-      <c r="B13" s="260"/>
+      <c r="B13" s="238"/>
       <c r="C13" s="99">
         <v>13</v>
       </c>
@@ -9903,10 +9835,10 @@
     <row r="34" spans="1:12">
       <c r="A34" s="114"/>
       <c r="B34" s="127"/>
-      <c r="C34" s="262" t="s">
+      <c r="C34" s="240" t="s">
         <v>338</v>
       </c>
-      <c r="D34" s="262"/>
+      <c r="D34" s="240"/>
       <c r="E34" s="128"/>
       <c r="F34" s="129"/>
       <c r="G34" s="127"/>
@@ -9919,10 +9851,10 @@
     <row r="35" spans="1:12">
       <c r="A35" s="114"/>
       <c r="B35" s="127"/>
-      <c r="C35" s="263" t="s">
+      <c r="C35" s="241" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="263"/>
+      <c r="D35" s="241"/>
       <c r="E35" s="128"/>
       <c r="F35" s="129"/>
       <c r="G35" s="127"/>
@@ -9939,10 +9871,10 @@
       <c r="B36" s="101">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C36" s="265" t="s">
+      <c r="C36" s="243" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="265"/>
+      <c r="D36" s="243"/>
       <c r="E36" s="132"/>
       <c r="F36" s="133"/>
       <c r="G36" s="134"/>
@@ -10189,10 +10121,10 @@
     <row r="48" spans="1:12">
       <c r="A48" s="114"/>
       <c r="B48" s="109"/>
-      <c r="C48" s="264" t="s">
+      <c r="C48" s="242" t="s">
         <v>352</v>
       </c>
-      <c r="D48" s="264"/>
+      <c r="D48" s="242"/>
       <c r="E48" s="96">
         <f>370+220</f>
         <v>590</v>
@@ -10995,7 +10927,7 @@
     <row r="83" spans="1:10">
       <c r="A83" s="114"/>
       <c r="B83" s="109"/>
-      <c r="C83" s="261" t="s">
+      <c r="C83" s="239" t="s">
         <v>377</v>
       </c>
       <c r="D83" s="148" t="s">
@@ -11021,7 +10953,7 @@
     <row r="84" spans="1:10">
       <c r="A84" s="114"/>
       <c r="B84" s="109"/>
-      <c r="C84" s="261"/>
+      <c r="C84" s="239"/>
       <c r="D84" s="148" t="s">
         <v>379</v>
       </c>
@@ -12812,698 +12744,788 @@
     <col min="1" max="1" width="18" style="216" customWidth="1"/>
     <col min="2" max="2" width="28" style="216" customWidth="1"/>
     <col min="3" max="3" width="81" style="216" customWidth="1"/>
-    <col min="4" max="4" width="41.42578125" style="216" customWidth="1"/>
+    <col min="4" max="4" width="38" style="216" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5703125" style="216" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.85546875" style="216"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="236" t="s">
+      <c r="A1" s="244" t="s">
         <v>432</v>
       </c>
-      <c r="B1" s="236" t="s">
+      <c r="B1" s="244" t="s">
         <v>433</v>
       </c>
-      <c r="C1" s="236" t="s">
+      <c r="C1" s="244" t="s">
         <v>434</v>
       </c>
-      <c r="D1" s="266" t="s">
+      <c r="D1" s="244" t="s">
         <v>435</v>
       </c>
-      <c r="E1" s="251" t="s">
+      <c r="E1" s="244" t="s">
         <v>436</v>
       </c>
-      <c r="F1" s="249" t="s">
+      <c r="F1" s="245" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="256" t="s">
+      <c r="A2" s="246" t="s">
         <v>438</v>
       </c>
-      <c r="B2" s="271"/>
-      <c r="C2" s="271"/>
-      <c r="D2" s="267"/>
-      <c r="E2" s="252"/>
+      <c r="B2" s="259"/>
+      <c r="C2" s="259"/>
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="248"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="237" t="s">
+      <c r="A3" s="249" t="s">
         <v>439</v>
       </c>
-      <c r="B3" s="238" t="s">
+      <c r="B3" s="250" t="s">
         <v>440</v>
       </c>
-      <c r="C3" s="239" t="s">
+      <c r="C3" s="251" t="s">
         <v>441</v>
       </c>
-      <c r="D3" s="268"/>
-      <c r="E3" s="253"/>
+      <c r="D3" s="251"/>
+      <c r="E3" s="251"/>
+      <c r="F3" s="248"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="240" t="s">
+      <c r="A4" s="252" t="s">
         <v>442</v>
       </c>
-      <c r="B4" s="241" t="s">
+      <c r="B4" s="253" t="s">
         <v>443</v>
       </c>
-      <c r="C4" s="242" t="s">
+      <c r="C4" s="254" t="s">
+        <v>443</v>
+      </c>
+      <c r="D4" s="254" t="s">
         <v>444</v>
       </c>
-      <c r="D4" s="269" t="s">
+      <c r="E4" s="254"/>
+      <c r="F4" s="255" t="s">
         <v>445</v>
       </c>
-      <c r="E4" s="254"/>
-      <c r="F4" s="8" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="249" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="30.75">
-      <c r="A5" s="237" t="s">
+      <c r="B5" s="250" t="s">
         <v>447</v>
       </c>
-      <c r="B5" s="238" t="s">
+      <c r="C5" s="251" t="s">
         <v>448</v>
       </c>
-      <c r="C5" s="239" t="s">
+      <c r="D5" s="251" t="s">
         <v>449</v>
       </c>
-      <c r="D5" s="268" t="s">
+      <c r="E5" s="251"/>
+      <c r="F5" s="256" t="s">
         <v>450</v>
       </c>
-      <c r="E5" s="253"/>
-      <c r="F5" s="250" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="252" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="240" t="s">
+      <c r="B6" s="253" t="s">
         <v>452</v>
       </c>
-      <c r="B6" s="241" t="s">
+      <c r="C6" s="254" t="s">
         <v>453</v>
       </c>
-      <c r="C6" s="242" t="s">
+      <c r="D6" s="254" t="s">
         <v>454</v>
       </c>
-      <c r="D6" s="269"/>
       <c r="E6" s="254"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="237" t="s">
+      <c r="F6" s="256" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75">
+      <c r="A7" s="249" t="s">
         <v>455</v>
       </c>
-      <c r="B7" s="241" t="s">
+      <c r="B7" s="253" t="s">
         <v>456</v>
       </c>
-      <c r="C7" s="242" t="s">
+      <c r="C7" s="254" t="s">
         <v>457</v>
       </c>
-      <c r="D7" s="269"/>
+      <c r="D7" s="254"/>
       <c r="E7" s="254"/>
+      <c r="F7" s="248"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="240" t="s">
+      <c r="A8" s="252" t="s">
         <v>458</v>
       </c>
-      <c r="B8" s="241" t="s">
+      <c r="B8" s="253" t="s">
         <v>459</v>
       </c>
-      <c r="C8" s="242" t="s">
+      <c r="C8" s="254" t="s">
         <v>460</v>
       </c>
-      <c r="D8" s="269"/>
+      <c r="D8" s="254" t="s">
+        <v>461</v>
+      </c>
       <c r="E8" s="254"/>
+      <c r="F8" s="255" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="237" t="s">
-        <v>461</v>
-      </c>
-      <c r="B9" s="238" t="s">
-        <v>462</v>
-      </c>
-      <c r="C9" s="239" t="s">
+      <c r="A9" s="249" t="s">
         <v>463</v>
       </c>
-      <c r="D9" s="268"/>
-      <c r="E9" s="253"/>
+      <c r="B9" s="250" t="s">
+        <v>464</v>
+      </c>
+      <c r="C9" s="251" t="s">
+        <v>465</v>
+      </c>
+      <c r="D9" s="251" t="s">
+        <v>466</v>
+      </c>
+      <c r="E9" s="251"/>
+      <c r="F9" s="255" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="240" t="s">
-        <v>464</v>
-      </c>
-      <c r="B10" s="241" t="s">
-        <v>465</v>
-      </c>
-      <c r="C10" s="242" t="s">
-        <v>466</v>
-      </c>
-      <c r="D10" s="269"/>
+      <c r="A10" s="252" t="s">
+        <v>468</v>
+      </c>
+      <c r="B10" s="253" t="s">
+        <v>469</v>
+      </c>
+      <c r="C10" s="254" t="s">
+        <v>470</v>
+      </c>
+      <c r="D10" s="254"/>
       <c r="E10" s="254"/>
+      <c r="F10" s="248"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="243" t="s">
-        <v>467</v>
-      </c>
-      <c r="B11" s="244" t="s">
-        <v>468</v>
-      </c>
-      <c r="C11" s="245" t="s">
-        <v>469</v>
-      </c>
-      <c r="D11" s="268"/>
-      <c r="E11" s="253"/>
+      <c r="A11" s="258">
+        <v>0.875</v>
+      </c>
+      <c r="B11" s="250" t="s">
+        <v>471</v>
+      </c>
+      <c r="C11" s="251" t="s">
+        <v>472</v>
+      </c>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="248"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="257" t="s">
-        <v>470</v>
-      </c>
-      <c r="B12" s="272"/>
-      <c r="C12" s="272"/>
-      <c r="D12" s="270"/>
+        <v>473</v>
+      </c>
+      <c r="B12" s="260"/>
+      <c r="C12" s="260"/>
+      <c r="D12" s="248"/>
+      <c r="E12" s="248"/>
+      <c r="F12" s="248"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="237" t="s">
+      <c r="A13" s="249" t="s">
+        <v>474</v>
+      </c>
+      <c r="B13" s="250" t="s">
+        <v>475</v>
+      </c>
+      <c r="C13" s="251" t="s">
+        <v>476</v>
+      </c>
+      <c r="D13" s="251" t="s">
+        <v>477</v>
+      </c>
+      <c r="E13" s="251"/>
+      <c r="F13" s="255" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="29.25">
+      <c r="A14" s="252" t="s">
+        <v>479</v>
+      </c>
+      <c r="B14" s="253" t="s">
+        <v>477</v>
+      </c>
+      <c r="C14" s="254" t="s">
+        <v>480</v>
+      </c>
+      <c r="D14" s="254"/>
+      <c r="E14" s="254"/>
+      <c r="F14" s="248"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="249" t="s">
+        <v>481</v>
+      </c>
+      <c r="B15" s="250" t="s">
+        <v>469</v>
+      </c>
+      <c r="C15" s="251" t="s">
+        <v>482</v>
+      </c>
+      <c r="D15" s="251" t="s">
+        <v>483</v>
+      </c>
+      <c r="E15" s="251"/>
+      <c r="F15" s="255" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="258">
+        <v>0.875</v>
+      </c>
+      <c r="B16" s="250" t="s">
         <v>471</v>
       </c>
-      <c r="B13" s="238" t="s">
+      <c r="C16" s="251" t="s">
         <v>472</v>
       </c>
-      <c r="C13" s="239" t="s">
-        <v>473</v>
-      </c>
-      <c r="D13" s="268"/>
-      <c r="E13" s="253"/>
-    </row>
-    <row r="14" spans="1:6" ht="29.25">
-      <c r="A14" s="240" t="s">
-        <v>474</v>
-      </c>
-      <c r="B14" s="241" t="s">
-        <v>475</v>
-      </c>
-      <c r="C14" s="242" t="s">
-        <v>476</v>
-      </c>
-      <c r="D14" s="269"/>
-      <c r="E14" s="254"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="237" t="s">
-        <v>477</v>
-      </c>
-      <c r="B15" s="238" t="s">
-        <v>465</v>
-      </c>
-      <c r="C15" s="239" t="s">
-        <v>478</v>
-      </c>
-      <c r="D15" s="268"/>
-      <c r="E15" s="253"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="246">
-        <v>0.875</v>
-      </c>
-      <c r="B16" s="247" t="s">
-        <v>479</v>
-      </c>
-      <c r="C16" s="248" t="s">
-        <v>480</v>
-      </c>
-      <c r="D16" s="269"/>
+      <c r="D16" s="254"/>
       <c r="E16" s="254"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="248"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="257" t="s">
-        <v>481</v>
-      </c>
-      <c r="B17" s="272"/>
-      <c r="C17" s="272"/>
-      <c r="D17" s="270"/>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="237" t="s">
-        <v>482</v>
-      </c>
-      <c r="B18" s="238" t="s">
-        <v>483</v>
-      </c>
-      <c r="C18" s="239" t="s">
-        <v>484</v>
-      </c>
-      <c r="D18" s="268"/>
-      <c r="E18" s="253"/>
-    </row>
-    <row r="19" spans="1:5" ht="29.25">
-      <c r="A19" s="240" t="s">
         <v>485</v>
       </c>
-      <c r="B19" s="241" t="s">
+      <c r="B17" s="260"/>
+      <c r="C17" s="260"/>
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="248"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="249" t="s">
         <v>486</v>
       </c>
-      <c r="C19" s="242" t="s">
+      <c r="B18" s="250" t="s">
         <v>487</v>
       </c>
-      <c r="D19" s="269"/>
+      <c r="C18" s="251" t="s">
+        <v>488</v>
+      </c>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="248"/>
+    </row>
+    <row r="19" spans="1:6" ht="29.25">
+      <c r="A19" s="252" t="s">
+        <v>489</v>
+      </c>
+      <c r="B19" s="253" t="s">
+        <v>490</v>
+      </c>
+      <c r="C19" s="254" t="s">
+        <v>491</v>
+      </c>
+      <c r="D19" s="254"/>
       <c r="E19" s="254"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="237" t="s">
-        <v>488</v>
-      </c>
-      <c r="B20" s="238" t="s">
-        <v>453</v>
-      </c>
-      <c r="C20" s="239" t="s">
+      <c r="F19" s="248"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="249" t="s">
+        <v>492</v>
+      </c>
+      <c r="B20" s="250" t="s">
+        <v>452</v>
+      </c>
+      <c r="C20" s="251" t="s">
+        <v>493</v>
+      </c>
+      <c r="D20" s="251" t="s">
+        <v>494</v>
+      </c>
+      <c r="E20" s="251"/>
+      <c r="F20" s="255" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="252" t="s">
+        <v>496</v>
+      </c>
+      <c r="B21" s="253" t="s">
+        <v>497</v>
+      </c>
+      <c r="C21" s="254" t="s">
+        <v>498</v>
+      </c>
+      <c r="D21" s="254"/>
+      <c r="E21" s="254"/>
+      <c r="F21" s="248"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="249" t="s">
+        <v>499</v>
+      </c>
+      <c r="B22" s="250" t="s">
+        <v>500</v>
+      </c>
+      <c r="C22" s="251" t="s">
+        <v>501</v>
+      </c>
+      <c r="D22" s="251" t="s">
+        <v>502</v>
+      </c>
+      <c r="E22" s="251"/>
+      <c r="F22" s="255" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="252" t="s">
+        <v>468</v>
+      </c>
+      <c r="B23" s="253" t="s">
+        <v>469</v>
+      </c>
+      <c r="C23" s="254" t="s">
+        <v>504</v>
+      </c>
+      <c r="D23" s="254"/>
+      <c r="E23" s="254"/>
+      <c r="F23" s="8" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="257" t="s">
+        <v>506</v>
+      </c>
+      <c r="B24" s="260"/>
+      <c r="C24" s="260"/>
+      <c r="D24" s="248"/>
+      <c r="E24" s="248"/>
+      <c r="F24" s="248"/>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" s="249" t="s">
+        <v>507</v>
+      </c>
+      <c r="B25" s="250" t="s">
+        <v>508</v>
+      </c>
+      <c r="C25" s="251" t="s">
+        <v>509</v>
+      </c>
+      <c r="D25" s="251"/>
+      <c r="E25" s="251"/>
+      <c r="F25" s="248"/>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" s="252" t="s">
+        <v>510</v>
+      </c>
+      <c r="B26" s="253" t="s">
+        <v>452</v>
+      </c>
+      <c r="C26" s="254" t="s">
+        <v>511</v>
+      </c>
+      <c r="D26" s="254"/>
+      <c r="E26" s="254"/>
+      <c r="F26" s="248"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="249" t="s">
+        <v>512</v>
+      </c>
+      <c r="B27" s="250" t="s">
+        <v>513</v>
+      </c>
+      <c r="C27" s="251" t="s">
+        <v>514</v>
+      </c>
+      <c r="D27" s="251"/>
+      <c r="E27" s="251"/>
+      <c r="F27" s="248"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="252" t="s">
+        <v>499</v>
+      </c>
+      <c r="B28" s="253" t="s">
+        <v>500</v>
+      </c>
+      <c r="C28" s="254" t="s">
+        <v>515</v>
+      </c>
+      <c r="D28" s="254"/>
+      <c r="E28" s="254"/>
+      <c r="F28" s="248"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="249" t="s">
+        <v>516</v>
+      </c>
+      <c r="B29" s="250" t="s">
+        <v>517</v>
+      </c>
+      <c r="C29" s="251" t="s">
+        <v>518</v>
+      </c>
+      <c r="D29" s="251"/>
+      <c r="E29" s="251"/>
+      <c r="F29" s="248"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="257" t="s">
+        <v>519</v>
+      </c>
+      <c r="B30" s="260"/>
+      <c r="C30" s="260"/>
+      <c r="D30" s="248"/>
+      <c r="E30" s="248"/>
+      <c r="F30" s="248"/>
+    </row>
+    <row r="31" spans="1:6" ht="29.25">
+      <c r="A31" s="249" t="s">
+        <v>520</v>
+      </c>
+      <c r="B31" s="250" t="s">
+        <v>521</v>
+      </c>
+      <c r="C31" s="251" t="s">
+        <v>522</v>
+      </c>
+      <c r="D31" s="251"/>
+      <c r="E31" s="251"/>
+      <c r="F31" s="248"/>
+    </row>
+    <row r="32" spans="1:6" ht="29.25">
+      <c r="A32" s="252" t="s">
+        <v>523</v>
+      </c>
+      <c r="B32" s="253" t="s">
+        <v>524</v>
+      </c>
+      <c r="C32" s="254" t="s">
+        <v>525</v>
+      </c>
+      <c r="D32" s="254"/>
+      <c r="E32" s="254"/>
+      <c r="F32" s="248"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="249" t="s">
+        <v>526</v>
+      </c>
+      <c r="B33" s="250" t="s">
+        <v>527</v>
+      </c>
+      <c r="C33" s="251" t="s">
+        <v>528</v>
+      </c>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="248"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="252" t="s">
+        <v>516</v>
+      </c>
+      <c r="B34" s="253" t="s">
+        <v>469</v>
+      </c>
+      <c r="C34" s="254" t="s">
+        <v>529</v>
+      </c>
+      <c r="D34" s="254"/>
+      <c r="E34" s="254"/>
+      <c r="F34" s="248"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="257" t="s">
+        <v>530</v>
+      </c>
+      <c r="B35" s="260"/>
+      <c r="C35" s="260"/>
+      <c r="D35" s="248"/>
+      <c r="E35" s="248"/>
+      <c r="F35" s="248"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="249" t="s">
+        <v>531</v>
+      </c>
+      <c r="B36" s="250" t="s">
+        <v>532</v>
+      </c>
+      <c r="C36" s="251" t="s">
+        <v>533</v>
+      </c>
+      <c r="D36" s="251"/>
+      <c r="E36" s="251"/>
+      <c r="F36" s="248"/>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="252" t="s">
+        <v>510</v>
+      </c>
+      <c r="B37" s="253" t="s">
+        <v>452</v>
+      </c>
+      <c r="C37" s="254" t="s">
+        <v>534</v>
+      </c>
+      <c r="D37" s="254"/>
+      <c r="E37" s="254"/>
+      <c r="F37" s="248"/>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="249" t="s">
+        <v>512</v>
+      </c>
+      <c r="B38" s="250" t="s">
+        <v>535</v>
+      </c>
+      <c r="C38" s="251" t="s">
+        <v>536</v>
+      </c>
+      <c r="D38" s="251"/>
+      <c r="E38" s="251"/>
+      <c r="F38" s="248"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="252" t="s">
+        <v>537</v>
+      </c>
+      <c r="B39" s="253" t="s">
+        <v>500</v>
+      </c>
+      <c r="C39" s="254" t="s">
+        <v>538</v>
+      </c>
+      <c r="D39" s="254"/>
+      <c r="E39" s="254"/>
+      <c r="F39" s="248"/>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="249" t="s">
+        <v>539</v>
+      </c>
+      <c r="B40" s="250" t="s">
+        <v>469</v>
+      </c>
+      <c r="C40" s="251" t="s">
+        <v>540</v>
+      </c>
+      <c r="D40" s="251"/>
+      <c r="E40" s="251"/>
+      <c r="F40" s="248"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="257" t="s">
+        <v>541</v>
+      </c>
+      <c r="B41" s="260"/>
+      <c r="C41" s="260"/>
+      <c r="D41" s="248"/>
+      <c r="E41" s="248"/>
+      <c r="F41" s="248"/>
+    </row>
+    <row r="42" spans="1:6" ht="29.25">
+      <c r="A42" s="249" t="s">
         <v>489</v>
       </c>
-      <c r="D20" s="268"/>
-      <c r="E20" s="253"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="240" t="s">
-        <v>490</v>
-      </c>
-      <c r="B21" s="241" t="s">
-        <v>491</v>
-      </c>
-      <c r="C21" s="242" t="s">
+      <c r="B42" s="250" t="s">
+        <v>542</v>
+      </c>
+      <c r="C42" s="251" t="s">
+        <v>543</v>
+      </c>
+      <c r="D42" s="251"/>
+      <c r="E42" s="251"/>
+      <c r="F42" s="248"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" s="252" t="s">
         <v>492</v>
       </c>
-      <c r="D21" s="269"/>
-      <c r="E21" s="254"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="237" t="s">
-        <v>493</v>
-      </c>
-      <c r="B22" s="238" t="s">
-        <v>494</v>
-      </c>
-      <c r="C22" s="239" t="s">
-        <v>495</v>
-      </c>
-      <c r="D22" s="268"/>
-      <c r="E22" s="253"/>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="240" t="s">
-        <v>464</v>
-      </c>
-      <c r="B23" s="241" t="s">
-        <v>465</v>
-      </c>
-      <c r="C23" s="242" t="s">
-        <v>496</v>
-      </c>
-      <c r="D23" s="269"/>
-      <c r="E23" s="254"/>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="255" t="s">
-        <v>497</v>
-      </c>
-      <c r="B24" s="273"/>
-      <c r="C24" s="273"/>
-      <c r="D24" s="270"/>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="237" t="s">
-        <v>498</v>
-      </c>
-      <c r="B25" s="238" t="s">
-        <v>499</v>
-      </c>
-      <c r="C25" s="239" t="s">
-        <v>500</v>
-      </c>
-      <c r="D25" s="268"/>
-      <c r="E25" s="253"/>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="240" t="s">
-        <v>501</v>
-      </c>
-      <c r="B26" s="241" t="s">
-        <v>453</v>
-      </c>
-      <c r="C26" s="242" t="s">
-        <v>502</v>
-      </c>
-      <c r="D26" s="269"/>
-      <c r="E26" s="254"/>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="237" t="s">
-        <v>503</v>
-      </c>
-      <c r="B27" s="238" t="s">
-        <v>504</v>
-      </c>
-      <c r="C27" s="239" t="s">
-        <v>505</v>
-      </c>
-      <c r="D27" s="268"/>
-      <c r="E27" s="253"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="240" t="s">
-        <v>493</v>
-      </c>
-      <c r="B28" s="241" t="s">
-        <v>494</v>
-      </c>
-      <c r="C28" s="242" t="s">
-        <v>506</v>
-      </c>
-      <c r="D28" s="269"/>
-      <c r="E28" s="254"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="237" t="s">
-        <v>507</v>
-      </c>
-      <c r="B29" s="238" t="s">
-        <v>508</v>
-      </c>
-      <c r="C29" s="239" t="s">
-        <v>509</v>
-      </c>
-      <c r="D29" s="268"/>
-      <c r="E29" s="253"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="255" t="s">
+      <c r="B43" s="253" t="s">
+        <v>452</v>
+      </c>
+      <c r="C43" s="254" t="s">
+        <v>544</v>
+      </c>
+      <c r="D43" s="254"/>
+      <c r="E43" s="254"/>
+      <c r="F43" s="248"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" s="249" t="s">
+        <v>512</v>
+      </c>
+      <c r="B44" s="250" t="s">
+        <v>545</v>
+      </c>
+      <c r="C44" s="251" t="s">
+        <v>546</v>
+      </c>
+      <c r="D44" s="251"/>
+      <c r="E44" s="251"/>
+      <c r="F44" s="248"/>
+    </row>
+    <row r="45" spans="1:6" ht="15.75">
+      <c r="A45" s="252" t="s">
+        <v>547</v>
+      </c>
+      <c r="B45" s="253" t="s">
+        <v>548</v>
+      </c>
+      <c r="C45" s="254" t="s">
+        <v>549</v>
+      </c>
+      <c r="D45" s="254"/>
+      <c r="E45" s="254"/>
+      <c r="F45" s="248"/>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="257" t="s">
+        <v>550</v>
+      </c>
+      <c r="B46" s="260"/>
+      <c r="C46" s="260"/>
+      <c r="D46" s="248"/>
+      <c r="E46" s="248"/>
+      <c r="F46" s="248"/>
+    </row>
+    <row r="47" spans="1:6" ht="29.25">
+      <c r="A47" s="249" t="s">
+        <v>531</v>
+      </c>
+      <c r="B47" s="250" t="s">
+        <v>551</v>
+      </c>
+      <c r="C47" s="251" t="s">
+        <v>552</v>
+      </c>
+      <c r="D47" s="251"/>
+      <c r="E47" s="251"/>
+      <c r="F47" s="248"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="252" t="s">
         <v>510</v>
       </c>
-      <c r="B30" s="273"/>
-      <c r="C30" s="273"/>
-      <c r="D30" s="270"/>
-    </row>
-    <row r="31" spans="1:5" ht="29.25">
-      <c r="A31" s="237" t="s">
-        <v>511</v>
-      </c>
-      <c r="B31" s="238" t="s">
-        <v>512</v>
-      </c>
-      <c r="C31" s="239" t="s">
-        <v>513</v>
-      </c>
-      <c r="D31" s="268"/>
-      <c r="E31" s="253"/>
-    </row>
-    <row r="32" spans="1:5" ht="29.25">
-      <c r="A32" s="240" t="s">
-        <v>514</v>
-      </c>
-      <c r="B32" s="241" t="s">
-        <v>515</v>
-      </c>
-      <c r="C32" s="242" t="s">
+      <c r="B48" s="253" t="s">
+        <v>452</v>
+      </c>
+      <c r="C48" s="254" t="s">
+        <v>553</v>
+      </c>
+      <c r="D48" s="254"/>
+      <c r="E48" s="254"/>
+      <c r="F48" s="248"/>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="249" t="s">
+        <v>554</v>
+      </c>
+      <c r="B49" s="250" t="s">
+        <v>555</v>
+      </c>
+      <c r="C49" s="251" t="s">
+        <v>556</v>
+      </c>
+      <c r="D49" s="251"/>
+      <c r="E49" s="251"/>
+      <c r="F49" s="248"/>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="252" t="s">
         <v>516</v>
       </c>
-      <c r="D32" s="269"/>
-      <c r="E32" s="254"/>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="237" t="s">
-        <v>517</v>
-      </c>
-      <c r="B33" s="238" t="s">
-        <v>518</v>
-      </c>
-      <c r="C33" s="239" t="s">
-        <v>519</v>
-      </c>
-      <c r="D33" s="268"/>
-      <c r="E33" s="253"/>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="240" t="s">
-        <v>507</v>
-      </c>
-      <c r="B34" s="241" t="s">
-        <v>465</v>
-      </c>
-      <c r="C34" s="242" t="s">
-        <v>520</v>
-      </c>
-      <c r="D34" s="269"/>
-      <c r="E34" s="254"/>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="255" t="s">
-        <v>521</v>
-      </c>
-      <c r="B35" s="273"/>
-      <c r="C35" s="273"/>
-      <c r="D35" s="270"/>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="237" t="s">
-        <v>522</v>
-      </c>
-      <c r="B36" s="238" t="s">
-        <v>523</v>
-      </c>
-      <c r="C36" s="239" t="s">
-        <v>524</v>
-      </c>
-      <c r="D36" s="268"/>
-      <c r="E36" s="253"/>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="240" t="s">
-        <v>501</v>
-      </c>
-      <c r="B37" s="241" t="s">
-        <v>453</v>
-      </c>
-      <c r="C37" s="242" t="s">
-        <v>525</v>
-      </c>
-      <c r="D37" s="269"/>
-      <c r="E37" s="254"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="237" t="s">
-        <v>503</v>
-      </c>
-      <c r="B38" s="238" t="s">
-        <v>526</v>
-      </c>
-      <c r="C38" s="239" t="s">
-        <v>527</v>
-      </c>
-      <c r="D38" s="268"/>
-      <c r="E38" s="253"/>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="240" t="s">
-        <v>528</v>
-      </c>
-      <c r="B39" s="241" t="s">
-        <v>494</v>
-      </c>
-      <c r="C39" s="242" t="s">
-        <v>529</v>
-      </c>
-      <c r="D39" s="269"/>
-      <c r="E39" s="254"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="237" t="s">
-        <v>530</v>
-      </c>
-      <c r="B40" s="238" t="s">
-        <v>465</v>
-      </c>
-      <c r="C40" s="239" t="s">
-        <v>531</v>
-      </c>
-      <c r="D40" s="268"/>
-      <c r="E40" s="253"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="255" t="s">
-        <v>532</v>
-      </c>
-      <c r="B41" s="273"/>
-      <c r="C41" s="273"/>
-      <c r="D41" s="270"/>
-    </row>
-    <row r="42" spans="1:5" ht="29.25">
-      <c r="A42" s="237" t="s">
-        <v>485</v>
-      </c>
-      <c r="B42" s="238" t="s">
-        <v>533</v>
-      </c>
-      <c r="C42" s="239" t="s">
-        <v>534</v>
-      </c>
-      <c r="D42" s="268"/>
-      <c r="E42" s="253"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="240" t="s">
-        <v>488</v>
-      </c>
-      <c r="B43" s="241" t="s">
-        <v>453</v>
-      </c>
-      <c r="C43" s="242" t="s">
-        <v>535</v>
-      </c>
-      <c r="D43" s="269"/>
-      <c r="E43" s="254"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="237" t="s">
-        <v>503</v>
-      </c>
-      <c r="B44" s="238" t="s">
-        <v>536</v>
-      </c>
-      <c r="C44" s="239" t="s">
-        <v>537</v>
-      </c>
-      <c r="D44" s="268"/>
-      <c r="E44" s="253"/>
-    </row>
-    <row r="45" spans="1:5" ht="15.75">
-      <c r="A45" s="240" t="s">
-        <v>538</v>
-      </c>
-      <c r="B45" s="241" t="s">
-        <v>539</v>
-      </c>
-      <c r="C45" s="242" t="s">
-        <v>540</v>
-      </c>
-      <c r="D45" s="269"/>
-      <c r="E45" s="254"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="255" t="s">
-        <v>541</v>
-      </c>
-      <c r="B46" s="273"/>
-      <c r="C46" s="273"/>
-      <c r="D46" s="270"/>
-    </row>
-    <row r="47" spans="1:5" ht="29.25">
-      <c r="A47" s="237" t="s">
-        <v>522</v>
-      </c>
-      <c r="B47" s="238" t="s">
-        <v>542</v>
-      </c>
-      <c r="C47" s="239" t="s">
-        <v>543</v>
-      </c>
-      <c r="D47" s="268"/>
-      <c r="E47" s="253"/>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="240" t="s">
-        <v>501</v>
-      </c>
-      <c r="B48" s="241" t="s">
-        <v>453</v>
-      </c>
-      <c r="C48" s="242" t="s">
-        <v>544</v>
-      </c>
-      <c r="D48" s="269"/>
-      <c r="E48" s="254"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="237" t="s">
-        <v>545</v>
-      </c>
-      <c r="B49" s="238" t="s">
-        <v>546</v>
-      </c>
-      <c r="C49" s="239" t="s">
-        <v>547</v>
-      </c>
-      <c r="D49" s="268"/>
-      <c r="E49" s="253"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="240" t="s">
-        <v>507</v>
-      </c>
-      <c r="B50" s="241" t="s">
-        <v>548</v>
-      </c>
-      <c r="C50" s="242" t="s">
-        <v>549</v>
-      </c>
-      <c r="D50" s="269"/>
+      <c r="B50" s="253" t="s">
+        <v>557</v>
+      </c>
+      <c r="C50" s="254" t="s">
+        <v>558</v>
+      </c>
+      <c r="D50" s="254"/>
       <c r="E50" s="254"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="255" t="s">
-        <v>550</v>
-      </c>
-      <c r="B51" s="273"/>
-      <c r="C51" s="273"/>
-      <c r="D51" s="270"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="237" t="s">
-        <v>551</v>
-      </c>
-      <c r="B52" s="238" t="s">
-        <v>552</v>
-      </c>
-      <c r="C52" s="239" t="s">
-        <v>553</v>
-      </c>
-      <c r="D52" s="268"/>
-      <c r="E52" s="253"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="240" t="s">
-        <v>554</v>
-      </c>
-      <c r="B53" s="241" t="s">
-        <v>453</v>
-      </c>
-      <c r="C53" s="242" t="s">
-        <v>555</v>
-      </c>
-      <c r="D53" s="269"/>
+      <c r="F50" s="248"/>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="257" t="s">
+        <v>559</v>
+      </c>
+      <c r="B51" s="260"/>
+      <c r="C51" s="260"/>
+      <c r="D51" s="248"/>
+      <c r="E51" s="248"/>
+      <c r="F51" s="248"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="249" t="s">
+        <v>560</v>
+      </c>
+      <c r="B52" s="250" t="s">
+        <v>561</v>
+      </c>
+      <c r="C52" s="251" t="s">
+        <v>562</v>
+      </c>
+      <c r="D52" s="251"/>
+      <c r="E52" s="251"/>
+      <c r="F52" s="248"/>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" s="252" t="s">
+        <v>563</v>
+      </c>
+      <c r="B53" s="253" t="s">
+        <v>452</v>
+      </c>
+      <c r="C53" s="254" t="s">
+        <v>564</v>
+      </c>
+      <c r="D53" s="254"/>
       <c r="E53" s="254"/>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="237" t="s">
-        <v>556</v>
-      </c>
-      <c r="B54" s="238" t="s">
-        <v>557</v>
-      </c>
-      <c r="C54" s="239" t="s">
-        <v>558</v>
-      </c>
-      <c r="D54" s="268"/>
-      <c r="E54" s="253"/>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="240" t="s">
-        <v>559</v>
-      </c>
-      <c r="B55" s="241" t="s">
-        <v>560</v>
-      </c>
-      <c r="C55" s="242" t="s">
-        <v>561</v>
-      </c>
-      <c r="D55" s="269"/>
+      <c r="F53" s="248"/>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" s="249" t="s">
+        <v>565</v>
+      </c>
+      <c r="B54" s="250" t="s">
+        <v>566</v>
+      </c>
+      <c r="C54" s="251" t="s">
+        <v>567</v>
+      </c>
+      <c r="D54" s="251"/>
+      <c r="E54" s="251"/>
+      <c r="F54" s="248"/>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" s="252" t="s">
+        <v>568</v>
+      </c>
+      <c r="B55" s="253" t="s">
+        <v>569</v>
+      </c>
+      <c r="C55" s="254" t="s">
+        <v>570</v>
+      </c>
+      <c r="D55" s="254"/>
       <c r="E55" s="254"/>
+      <c r="F55" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -13519,9 +13541,16 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F4" r:id="rId1" xr:uid="{6D84B550-56D9-418A-9D1C-EC3261D9DE2C}"/>
+    <hyperlink ref="F8" r:id="rId2" xr:uid="{362D1549-C6B0-4DBA-AF53-F162C8958291}"/>
+    <hyperlink ref="F9" r:id="rId3" xr:uid="{ABA130E2-28CF-48C2-9144-36C703EF636A}"/>
+    <hyperlink ref="F13" r:id="rId4" xr:uid="{E5CCB325-1CF9-4D32-BBF7-BAFC64ADBA13}"/>
+    <hyperlink ref="F15" r:id="rId5" xr:uid="{E2214F55-DBDD-417E-89D1-CBE8A004BF1C}"/>
+    <hyperlink ref="F20" r:id="rId6" xr:uid="{83714BB7-E198-4AF2-9E3F-F0EB6C640209}"/>
+    <hyperlink ref="F22" r:id="rId7" xr:uid="{3D986609-D1AD-40CD-9D91-B61C2D40A5ED}"/>
+    <hyperlink ref="F23" r:id="rId8" xr:uid="{9191FE3F-DA50-42C9-A969-CB2607764014}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId2"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId9"/>
 </worksheet>
 </file>
 

--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="165" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2B685CF-E5ED-4784-BE59-CD773F258209}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD04243F-370A-43DE-9081-B5FB59FFBFE7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" firstSheet="4" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="573">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1434,6 +1434,12 @@
   </si>
   <si>
     <t>CoCo Ichibanya</t>
+  </si>
+  <si>
+    <t>1_day1_curryhouse.png</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/QUZeFor2cqwbRkzj7</t>
   </si>
   <si>
     <t>13:00 - 14:00</t>
@@ -2832,37 +2838,10 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2885,11 +2864,38 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="31" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="31" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
@@ -5968,7 +5974,7 @@
     <row r="137" spans="1:8" ht="15" customHeight="1">
       <c r="A137" s="37"/>
       <c r="B137" s="38"/>
-      <c r="C137" s="236" t="s">
+      <c r="C137" s="251" t="s">
         <v>179</v>
       </c>
       <c r="D137" s="38"/>
@@ -5983,7 +5989,7 @@
     <row r="138" spans="1:8" ht="15" customHeight="1">
       <c r="A138" s="37"/>
       <c r="B138" s="38"/>
-      <c r="C138" s="236"/>
+      <c r="C138" s="251"/>
       <c r="D138" s="38"/>
       <c r="E138" s="39"/>
       <c r="F138" s="38"/>
@@ -6709,8 +6715,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="237" customFormat="1">
-      <c r="A2" s="237" t="s">
+    <row r="2" spans="1:10" s="252" customFormat="1">
+      <c r="A2" s="252" t="s">
         <v>226</v>
       </c>
     </row>
@@ -6817,10 +6823,10 @@
     <row r="8" spans="1:10">
       <c r="A8" s="84"/>
       <c r="B8" s="85"/>
-      <c r="C8" s="238" t="s">
+      <c r="C8" s="253" t="s">
         <v>230</v>
       </c>
-      <c r="D8" s="238"/>
+      <c r="D8" s="253"/>
       <c r="E8" s="96">
         <v>1500</v>
       </c>
@@ -6863,10 +6869,10 @@
       <c r="J10" s="85"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="238" t="s">
+      <c r="A11" s="253" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="238"/>
+      <c r="B11" s="253"/>
       <c r="C11" s="99">
         <v>27</v>
       </c>
@@ -9200,8 +9206,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="237" customFormat="1">
-      <c r="A2" s="237" t="s">
+    <row r="2" spans="1:12" s="252" customFormat="1">
+      <c r="A2" s="252" t="s">
         <v>226</v>
       </c>
     </row>
@@ -9362,10 +9368,10 @@
     <row r="10" spans="1:12">
       <c r="A10" s="84"/>
       <c r="B10" s="85"/>
-      <c r="C10" s="238" t="s">
+      <c r="C10" s="253" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="238"/>
+      <c r="D10" s="253"/>
       <c r="E10" s="96">
         <v>3000</v>
       </c>
@@ -9408,10 +9414,10 @@
       <c r="J12" s="85"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="238" t="s">
+      <c r="A13" s="253" t="s">
         <v>233</v>
       </c>
-      <c r="B13" s="238"/>
+      <c r="B13" s="253"/>
       <c r="C13" s="99">
         <v>13</v>
       </c>
@@ -9835,10 +9841,10 @@
     <row r="34" spans="1:12">
       <c r="A34" s="114"/>
       <c r="B34" s="127"/>
-      <c r="C34" s="240" t="s">
+      <c r="C34" s="255" t="s">
         <v>338</v>
       </c>
-      <c r="D34" s="240"/>
+      <c r="D34" s="255"/>
       <c r="E34" s="128"/>
       <c r="F34" s="129"/>
       <c r="G34" s="127"/>
@@ -9851,10 +9857,10 @@
     <row r="35" spans="1:12">
       <c r="A35" s="114"/>
       <c r="B35" s="127"/>
-      <c r="C35" s="241" t="s">
+      <c r="C35" s="256" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="241"/>
+      <c r="D35" s="256"/>
       <c r="E35" s="128"/>
       <c r="F35" s="129"/>
       <c r="G35" s="127"/>
@@ -9871,10 +9877,10 @@
       <c r="B36" s="101">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C36" s="243" t="s">
+      <c r="C36" s="258" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="243"/>
+      <c r="D36" s="258"/>
       <c r="E36" s="132"/>
       <c r="F36" s="133"/>
       <c r="G36" s="134"/>
@@ -10121,10 +10127,10 @@
     <row r="48" spans="1:12">
       <c r="A48" s="114"/>
       <c r="B48" s="109"/>
-      <c r="C48" s="242" t="s">
+      <c r="C48" s="257" t="s">
         <v>352</v>
       </c>
-      <c r="D48" s="242"/>
+      <c r="D48" s="257"/>
       <c r="E48" s="96">
         <f>370+220</f>
         <v>590</v>
@@ -10927,7 +10933,7 @@
     <row r="83" spans="1:10">
       <c r="A83" s="114"/>
       <c r="B83" s="109"/>
-      <c r="C83" s="239" t="s">
+      <c r="C83" s="254" t="s">
         <v>377</v>
       </c>
       <c r="D83" s="148" t="s">
@@ -10953,7 +10959,7 @@
     <row r="84" spans="1:10">
       <c r="A84" s="114"/>
       <c r="B84" s="109"/>
-      <c r="C84" s="239"/>
+      <c r="C84" s="254"/>
       <c r="D84" s="148" t="s">
         <v>379</v>
       </c>
@@ -12750,782 +12756,784 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="244" t="s">
+      <c r="A1" s="236" t="s">
         <v>432</v>
       </c>
-      <c r="B1" s="244" t="s">
+      <c r="B1" s="236" t="s">
         <v>433</v>
       </c>
-      <c r="C1" s="244" t="s">
+      <c r="C1" s="236" t="s">
         <v>434</v>
       </c>
-      <c r="D1" s="244" t="s">
+      <c r="D1" s="236" t="s">
         <v>435</v>
       </c>
-      <c r="E1" s="244" t="s">
+      <c r="E1" s="236" t="s">
         <v>436</v>
       </c>
-      <c r="F1" s="245" t="s">
+      <c r="F1" s="237" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="246" t="s">
+      <c r="A2" s="250" t="s">
         <v>438</v>
       </c>
       <c r="B2" s="259"/>
       <c r="C2" s="259"/>
-      <c r="D2" s="247"/>
-      <c r="E2" s="247"/>
-      <c r="F2" s="248"/>
+      <c r="D2" s="238"/>
+      <c r="E2" s="238"/>
+      <c r="F2" s="239"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="249" t="s">
+      <c r="A3" s="240" t="s">
         <v>439</v>
       </c>
-      <c r="B3" s="250" t="s">
+      <c r="B3" s="241" t="s">
         <v>440</v>
       </c>
-      <c r="C3" s="251" t="s">
+      <c r="C3" s="242" t="s">
         <v>441</v>
       </c>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="248"/>
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="239"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="252" t="s">
+      <c r="A4" s="243" t="s">
         <v>442</v>
       </c>
-      <c r="B4" s="253" t="s">
+      <c r="B4" s="244" t="s">
         <v>443</v>
       </c>
-      <c r="C4" s="254" t="s">
+      <c r="C4" s="245" t="s">
         <v>443</v>
       </c>
-      <c r="D4" s="254" t="s">
+      <c r="D4" s="245" t="s">
         <v>444</v>
       </c>
-      <c r="E4" s="254"/>
-      <c r="F4" s="255" t="s">
+      <c r="E4" s="245"/>
+      <c r="F4" s="246" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="249" t="s">
+      <c r="A5" s="240" t="s">
         <v>446</v>
       </c>
-      <c r="B5" s="250" t="s">
+      <c r="B5" s="241" t="s">
         <v>447</v>
       </c>
-      <c r="C5" s="251" t="s">
+      <c r="C5" s="242" t="s">
         <v>448</v>
       </c>
-      <c r="D5" s="251" t="s">
+      <c r="D5" s="242" t="s">
         <v>449</v>
       </c>
-      <c r="E5" s="251"/>
-      <c r="F5" s="256" t="s">
+      <c r="E5" s="242"/>
+      <c r="F5" s="247" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="252" t="s">
+      <c r="A6" s="243" t="s">
         <v>451</v>
       </c>
-      <c r="B6" s="253" t="s">
+      <c r="B6" s="244" t="s">
         <v>452</v>
       </c>
-      <c r="C6" s="254" t="s">
+      <c r="C6" s="245" t="s">
         <v>453</v>
       </c>
-      <c r="D6" s="254" t="s">
+      <c r="D6" s="245" t="s">
         <v>454</v>
       </c>
-      <c r="E6" s="254"/>
-      <c r="F6" s="256" t="s">
-        <v>450</v>
+      <c r="E6" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="F6" s="246" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75">
-      <c r="A7" s="249" t="s">
-        <v>455</v>
-      </c>
-      <c r="B7" s="253" t="s">
-        <v>456</v>
-      </c>
-      <c r="C7" s="254" t="s">
+      <c r="A7" s="240" t="s">
         <v>457</v>
       </c>
-      <c r="D7" s="254"/>
-      <c r="E7" s="254"/>
-      <c r="F7" s="248"/>
+      <c r="B7" s="244" t="s">
+        <v>458</v>
+      </c>
+      <c r="C7" s="245" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7" s="245"/>
+      <c r="E7" s="245"/>
+      <c r="F7" s="239"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="252" t="s">
-        <v>458</v>
-      </c>
-      <c r="B8" s="253" t="s">
-        <v>459</v>
-      </c>
-      <c r="C8" s="254" t="s">
+      <c r="A8" s="243" t="s">
         <v>460</v>
       </c>
-      <c r="D8" s="254" t="s">
+      <c r="B8" s="244" t="s">
         <v>461</v>
       </c>
-      <c r="E8" s="254"/>
-      <c r="F8" s="255" t="s">
+      <c r="C8" s="245" t="s">
         <v>462</v>
       </c>
+      <c r="D8" s="245" t="s">
+        <v>463</v>
+      </c>
+      <c r="E8" s="245"/>
+      <c r="F8" s="246" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="249" t="s">
-        <v>463</v>
-      </c>
-      <c r="B9" s="250" t="s">
-        <v>464</v>
-      </c>
-      <c r="C9" s="251" t="s">
+      <c r="A9" s="240" t="s">
         <v>465</v>
       </c>
-      <c r="D9" s="251" t="s">
+      <c r="B9" s="241" t="s">
         <v>466</v>
       </c>
-      <c r="E9" s="251"/>
-      <c r="F9" s="255" t="s">
+      <c r="C9" s="242" t="s">
         <v>467</v>
       </c>
+      <c r="D9" s="242" t="s">
+        <v>468</v>
+      </c>
+      <c r="E9" s="242"/>
+      <c r="F9" s="246" t="s">
+        <v>469</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="252" t="s">
-        <v>468</v>
-      </c>
-      <c r="B10" s="253" t="s">
-        <v>469</v>
-      </c>
-      <c r="C10" s="254" t="s">
+      <c r="A10" s="243" t="s">
         <v>470</v>
       </c>
-      <c r="D10" s="254"/>
-      <c r="E10" s="254"/>
-      <c r="F10" s="248"/>
+      <c r="B10" s="244" t="s">
+        <v>471</v>
+      </c>
+      <c r="C10" s="245" t="s">
+        <v>472</v>
+      </c>
+      <c r="D10" s="245"/>
+      <c r="E10" s="245"/>
+      <c r="F10" s="239"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="258">
+      <c r="A11" s="248">
         <v>0.875</v>
       </c>
-      <c r="B11" s="250" t="s">
-        <v>471</v>
-      </c>
-      <c r="C11" s="251" t="s">
-        <v>472</v>
-      </c>
-      <c r="D11" s="251"/>
-      <c r="E11" s="251"/>
-      <c r="F11" s="248"/>
+      <c r="B11" s="241" t="s">
+        <v>473</v>
+      </c>
+      <c r="C11" s="242" t="s">
+        <v>474</v>
+      </c>
+      <c r="D11" s="242"/>
+      <c r="E11" s="242"/>
+      <c r="F11" s="239"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="257" t="s">
-        <v>473</v>
+      <c r="A12" s="249" t="s">
+        <v>475</v>
       </c>
       <c r="B12" s="260"/>
       <c r="C12" s="260"/>
-      <c r="D12" s="248"/>
-      <c r="E12" s="248"/>
-      <c r="F12" s="248"/>
+      <c r="D12" s="239"/>
+      <c r="E12" s="239"/>
+      <c r="F12" s="239"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="249" t="s">
+      <c r="A13" s="240" t="s">
+        <v>476</v>
+      </c>
+      <c r="B13" s="241" t="s">
+        <v>477</v>
+      </c>
+      <c r="C13" s="242" t="s">
+        <v>478</v>
+      </c>
+      <c r="D13" s="242" t="s">
+        <v>479</v>
+      </c>
+      <c r="E13" s="242"/>
+      <c r="F13" s="246" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="29.25">
+      <c r="A14" s="243" t="s">
+        <v>481</v>
+      </c>
+      <c r="B14" s="244" t="s">
+        <v>479</v>
+      </c>
+      <c r="C14" s="245" t="s">
+        <v>482</v>
+      </c>
+      <c r="D14" s="245"/>
+      <c r="E14" s="245"/>
+      <c r="F14" s="239"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="240" t="s">
+        <v>483</v>
+      </c>
+      <c r="B15" s="241" t="s">
+        <v>471</v>
+      </c>
+      <c r="C15" s="242" t="s">
+        <v>484</v>
+      </c>
+      <c r="D15" s="242" t="s">
+        <v>485</v>
+      </c>
+      <c r="E15" s="242"/>
+      <c r="F15" s="246" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="248">
+        <v>0.875</v>
+      </c>
+      <c r="B16" s="241" t="s">
+        <v>473</v>
+      </c>
+      <c r="C16" s="242" t="s">
         <v>474</v>
       </c>
-      <c r="B13" s="250" t="s">
-        <v>475</v>
-      </c>
-      <c r="C13" s="251" t="s">
-        <v>476</v>
-      </c>
-      <c r="D13" s="251" t="s">
-        <v>477</v>
-      </c>
-      <c r="E13" s="251"/>
-      <c r="F13" s="255" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="29.25">
-      <c r="A14" s="252" t="s">
-        <v>479</v>
-      </c>
-      <c r="B14" s="253" t="s">
-        <v>477</v>
-      </c>
-      <c r="C14" s="254" t="s">
-        <v>480</v>
-      </c>
-      <c r="D14" s="254"/>
-      <c r="E14" s="254"/>
-      <c r="F14" s="248"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="249" t="s">
-        <v>481</v>
-      </c>
-      <c r="B15" s="250" t="s">
-        <v>469</v>
-      </c>
-      <c r="C15" s="251" t="s">
-        <v>482</v>
-      </c>
-      <c r="D15" s="251" t="s">
-        <v>483</v>
-      </c>
-      <c r="E15" s="251"/>
-      <c r="F15" s="255" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="258">
-        <v>0.875</v>
-      </c>
-      <c r="B16" s="250" t="s">
-        <v>471</v>
-      </c>
-      <c r="C16" s="251" t="s">
-        <v>472</v>
-      </c>
-      <c r="D16" s="254"/>
-      <c r="E16" s="254"/>
-      <c r="F16" s="248"/>
+      <c r="D16" s="245"/>
+      <c r="E16" s="245"/>
+      <c r="F16" s="239"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="257" t="s">
-        <v>485</v>
+      <c r="A17" s="249" t="s">
+        <v>487</v>
       </c>
       <c r="B17" s="260"/>
       <c r="C17" s="260"/>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
+      <c r="D17" s="239"/>
+      <c r="E17" s="239"/>
+      <c r="F17" s="239"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="249" t="s">
-        <v>486</v>
-      </c>
-      <c r="B18" s="250" t="s">
-        <v>487</v>
-      </c>
-      <c r="C18" s="251" t="s">
+      <c r="A18" s="240" t="s">
         <v>488</v>
       </c>
-      <c r="D18" s="251"/>
-      <c r="E18" s="251"/>
-      <c r="F18" s="248"/>
+      <c r="B18" s="241" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="242" t="s">
+        <v>490</v>
+      </c>
+      <c r="D18" s="242"/>
+      <c r="E18" s="242"/>
+      <c r="F18" s="239"/>
     </row>
     <row r="19" spans="1:6" ht="29.25">
-      <c r="A19" s="252" t="s">
-        <v>489</v>
-      </c>
-      <c r="B19" s="253" t="s">
-        <v>490</v>
-      </c>
-      <c r="C19" s="254" t="s">
+      <c r="A19" s="243" t="s">
         <v>491</v>
       </c>
-      <c r="D19" s="254"/>
-      <c r="E19" s="254"/>
-      <c r="F19" s="248"/>
+      <c r="B19" s="244" t="s">
+        <v>492</v>
+      </c>
+      <c r="C19" s="245" t="s">
+        <v>493</v>
+      </c>
+      <c r="D19" s="245"/>
+      <c r="E19" s="245"/>
+      <c r="F19" s="239"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="249" t="s">
-        <v>492</v>
-      </c>
-      <c r="B20" s="250" t="s">
+      <c r="A20" s="240" t="s">
+        <v>494</v>
+      </c>
+      <c r="B20" s="241" t="s">
         <v>452</v>
       </c>
-      <c r="C20" s="251" t="s">
-        <v>493</v>
-      </c>
-      <c r="D20" s="251" t="s">
-        <v>494</v>
-      </c>
-      <c r="E20" s="251"/>
-      <c r="F20" s="255" t="s">
+      <c r="C20" s="242" t="s">
         <v>495</v>
       </c>
+      <c r="D20" s="242" t="s">
+        <v>496</v>
+      </c>
+      <c r="E20" s="242"/>
+      <c r="F20" s="246" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="252" t="s">
-        <v>496</v>
-      </c>
-      <c r="B21" s="253" t="s">
-        <v>497</v>
-      </c>
-      <c r="C21" s="254" t="s">
+      <c r="A21" s="243" t="s">
         <v>498</v>
       </c>
-      <c r="D21" s="254"/>
-      <c r="E21" s="254"/>
-      <c r="F21" s="248"/>
+      <c r="B21" s="244" t="s">
+        <v>499</v>
+      </c>
+      <c r="C21" s="245" t="s">
+        <v>500</v>
+      </c>
+      <c r="D21" s="245"/>
+      <c r="E21" s="245"/>
+      <c r="F21" s="239"/>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="249" t="s">
-        <v>499</v>
-      </c>
-      <c r="B22" s="250" t="s">
-        <v>500</v>
-      </c>
-      <c r="C22" s="251" t="s">
+      <c r="A22" s="240" t="s">
         <v>501</v>
       </c>
-      <c r="D22" s="251" t="s">
+      <c r="B22" s="241" t="s">
         <v>502</v>
       </c>
-      <c r="E22" s="251"/>
-      <c r="F22" s="255" t="s">
+      <c r="C22" s="242" t="s">
         <v>503</v>
       </c>
+      <c r="D22" s="242" t="s">
+        <v>504</v>
+      </c>
+      <c r="E22" s="242"/>
+      <c r="F22" s="246" t="s">
+        <v>505</v>
+      </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="252" t="s">
-        <v>468</v>
-      </c>
-      <c r="B23" s="253" t="s">
-        <v>469</v>
-      </c>
-      <c r="C23" s="254" t="s">
-        <v>504</v>
-      </c>
-      <c r="D23" s="254"/>
-      <c r="E23" s="254"/>
+      <c r="A23" s="243" t="s">
+        <v>470</v>
+      </c>
+      <c r="B23" s="244" t="s">
+        <v>471</v>
+      </c>
+      <c r="C23" s="245" t="s">
+        <v>506</v>
+      </c>
+      <c r="D23" s="245"/>
+      <c r="E23" s="245"/>
       <c r="F23" s="8" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="257" t="s">
-        <v>506</v>
+      <c r="A24" s="249" t="s">
+        <v>508</v>
       </c>
       <c r="B24" s="260"/>
       <c r="C24" s="260"/>
-      <c r="D24" s="248"/>
-      <c r="E24" s="248"/>
-      <c r="F24" s="248"/>
+      <c r="D24" s="239"/>
+      <c r="E24" s="239"/>
+      <c r="F24" s="239"/>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="249" t="s">
-        <v>507</v>
-      </c>
-      <c r="B25" s="250" t="s">
-        <v>508</v>
-      </c>
-      <c r="C25" s="251" t="s">
+      <c r="A25" s="240" t="s">
         <v>509</v>
       </c>
-      <c r="D25" s="251"/>
-      <c r="E25" s="251"/>
-      <c r="F25" s="248"/>
+      <c r="B25" s="241" t="s">
+        <v>510</v>
+      </c>
+      <c r="C25" s="242" t="s">
+        <v>511</v>
+      </c>
+      <c r="D25" s="242"/>
+      <c r="E25" s="242"/>
+      <c r="F25" s="239"/>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="252" t="s">
-        <v>510</v>
-      </c>
-      <c r="B26" s="253" t="s">
+      <c r="A26" s="243" t="s">
+        <v>512</v>
+      </c>
+      <c r="B26" s="244" t="s">
         <v>452</v>
       </c>
-      <c r="C26" s="254" t="s">
-        <v>511</v>
-      </c>
-      <c r="D26" s="254"/>
-      <c r="E26" s="254"/>
-      <c r="F26" s="248"/>
+      <c r="C26" s="245" t="s">
+        <v>513</v>
+      </c>
+      <c r="D26" s="245"/>
+      <c r="E26" s="245"/>
+      <c r="F26" s="239"/>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="249" t="s">
-        <v>512</v>
-      </c>
-      <c r="B27" s="250" t="s">
-        <v>513</v>
-      </c>
-      <c r="C27" s="251" t="s">
+      <c r="A27" s="240" t="s">
         <v>514</v>
       </c>
-      <c r="D27" s="251"/>
-      <c r="E27" s="251"/>
-      <c r="F27" s="248"/>
+      <c r="B27" s="241" t="s">
+        <v>515</v>
+      </c>
+      <c r="C27" s="242" t="s">
+        <v>516</v>
+      </c>
+      <c r="D27" s="242"/>
+      <c r="E27" s="242"/>
+      <c r="F27" s="239"/>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="252" t="s">
-        <v>499</v>
-      </c>
-      <c r="B28" s="253" t="s">
-        <v>500</v>
-      </c>
-      <c r="C28" s="254" t="s">
-        <v>515</v>
-      </c>
-      <c r="D28" s="254"/>
-      <c r="E28" s="254"/>
-      <c r="F28" s="248"/>
+      <c r="A28" s="243" t="s">
+        <v>501</v>
+      </c>
+      <c r="B28" s="244" t="s">
+        <v>502</v>
+      </c>
+      <c r="C28" s="245" t="s">
+        <v>517</v>
+      </c>
+      <c r="D28" s="245"/>
+      <c r="E28" s="245"/>
+      <c r="F28" s="239"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="249" t="s">
-        <v>516</v>
-      </c>
-      <c r="B29" s="250" t="s">
-        <v>517</v>
-      </c>
-      <c r="C29" s="251" t="s">
+      <c r="A29" s="240" t="s">
         <v>518</v>
       </c>
-      <c r="D29" s="251"/>
-      <c r="E29" s="251"/>
-      <c r="F29" s="248"/>
+      <c r="B29" s="241" t="s">
+        <v>519</v>
+      </c>
+      <c r="C29" s="242" t="s">
+        <v>520</v>
+      </c>
+      <c r="D29" s="242"/>
+      <c r="E29" s="242"/>
+      <c r="F29" s="239"/>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="257" t="s">
-        <v>519</v>
+      <c r="A30" s="249" t="s">
+        <v>521</v>
       </c>
       <c r="B30" s="260"/>
       <c r="C30" s="260"/>
-      <c r="D30" s="248"/>
-      <c r="E30" s="248"/>
-      <c r="F30" s="248"/>
+      <c r="D30" s="239"/>
+      <c r="E30" s="239"/>
+      <c r="F30" s="239"/>
     </row>
     <row r="31" spans="1:6" ht="29.25">
-      <c r="A31" s="249" t="s">
-        <v>520</v>
-      </c>
-      <c r="B31" s="250" t="s">
-        <v>521</v>
-      </c>
-      <c r="C31" s="251" t="s">
+      <c r="A31" s="240" t="s">
         <v>522</v>
       </c>
-      <c r="D31" s="251"/>
-      <c r="E31" s="251"/>
-      <c r="F31" s="248"/>
+      <c r="B31" s="241" t="s">
+        <v>523</v>
+      </c>
+      <c r="C31" s="242" t="s">
+        <v>524</v>
+      </c>
+      <c r="D31" s="242"/>
+      <c r="E31" s="242"/>
+      <c r="F31" s="239"/>
     </row>
     <row r="32" spans="1:6" ht="29.25">
-      <c r="A32" s="252" t="s">
-        <v>523</v>
-      </c>
-      <c r="B32" s="253" t="s">
-        <v>524</v>
-      </c>
-      <c r="C32" s="254" t="s">
+      <c r="A32" s="243" t="s">
         <v>525</v>
       </c>
-      <c r="D32" s="254"/>
-      <c r="E32" s="254"/>
-      <c r="F32" s="248"/>
+      <c r="B32" s="244" t="s">
+        <v>526</v>
+      </c>
+      <c r="C32" s="245" t="s">
+        <v>527</v>
+      </c>
+      <c r="D32" s="245"/>
+      <c r="E32" s="245"/>
+      <c r="F32" s="239"/>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="249" t="s">
-        <v>526</v>
-      </c>
-      <c r="B33" s="250" t="s">
-        <v>527</v>
-      </c>
-      <c r="C33" s="251" t="s">
+      <c r="A33" s="240" t="s">
         <v>528</v>
       </c>
-      <c r="D33" s="251"/>
-      <c r="E33" s="251"/>
-      <c r="F33" s="248"/>
+      <c r="B33" s="241" t="s">
+        <v>529</v>
+      </c>
+      <c r="C33" s="242" t="s">
+        <v>530</v>
+      </c>
+      <c r="D33" s="242"/>
+      <c r="E33" s="242"/>
+      <c r="F33" s="239"/>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="252" t="s">
-        <v>516</v>
-      </c>
-      <c r="B34" s="253" t="s">
-        <v>469</v>
-      </c>
-      <c r="C34" s="254" t="s">
-        <v>529</v>
-      </c>
-      <c r="D34" s="254"/>
-      <c r="E34" s="254"/>
-      <c r="F34" s="248"/>
+      <c r="A34" s="243" t="s">
+        <v>518</v>
+      </c>
+      <c r="B34" s="244" t="s">
+        <v>471</v>
+      </c>
+      <c r="C34" s="245" t="s">
+        <v>531</v>
+      </c>
+      <c r="D34" s="245"/>
+      <c r="E34" s="245"/>
+      <c r="F34" s="239"/>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="257" t="s">
-        <v>530</v>
+      <c r="A35" s="249" t="s">
+        <v>532</v>
       </c>
       <c r="B35" s="260"/>
       <c r="C35" s="260"/>
-      <c r="D35" s="248"/>
-      <c r="E35" s="248"/>
-      <c r="F35" s="248"/>
+      <c r="D35" s="239"/>
+      <c r="E35" s="239"/>
+      <c r="F35" s="239"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="249" t="s">
-        <v>531</v>
-      </c>
-      <c r="B36" s="250" t="s">
-        <v>532</v>
-      </c>
-      <c r="C36" s="251" t="s">
+      <c r="A36" s="240" t="s">
         <v>533</v>
       </c>
-      <c r="D36" s="251"/>
-      <c r="E36" s="251"/>
-      <c r="F36" s="248"/>
+      <c r="B36" s="241" t="s">
+        <v>534</v>
+      </c>
+      <c r="C36" s="242" t="s">
+        <v>535</v>
+      </c>
+      <c r="D36" s="242"/>
+      <c r="E36" s="242"/>
+      <c r="F36" s="239"/>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="252" t="s">
-        <v>510</v>
-      </c>
-      <c r="B37" s="253" t="s">
+      <c r="A37" s="243" t="s">
+        <v>512</v>
+      </c>
+      <c r="B37" s="244" t="s">
         <v>452</v>
       </c>
-      <c r="C37" s="254" t="s">
-        <v>534</v>
-      </c>
-      <c r="D37" s="254"/>
-      <c r="E37" s="254"/>
-      <c r="F37" s="248"/>
+      <c r="C37" s="245" t="s">
+        <v>536</v>
+      </c>
+      <c r="D37" s="245"/>
+      <c r="E37" s="245"/>
+      <c r="F37" s="239"/>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="249" t="s">
-        <v>512</v>
-      </c>
-      <c r="B38" s="250" t="s">
-        <v>535</v>
-      </c>
-      <c r="C38" s="251" t="s">
-        <v>536</v>
-      </c>
-      <c r="D38" s="251"/>
-      <c r="E38" s="251"/>
-      <c r="F38" s="248"/>
+      <c r="A38" s="240" t="s">
+        <v>514</v>
+      </c>
+      <c r="B38" s="241" t="s">
+        <v>537</v>
+      </c>
+      <c r="C38" s="242" t="s">
+        <v>538</v>
+      </c>
+      <c r="D38" s="242"/>
+      <c r="E38" s="242"/>
+      <c r="F38" s="239"/>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="252" t="s">
-        <v>537</v>
-      </c>
-      <c r="B39" s="253" t="s">
-        <v>500</v>
-      </c>
-      <c r="C39" s="254" t="s">
-        <v>538</v>
-      </c>
-      <c r="D39" s="254"/>
-      <c r="E39" s="254"/>
-      <c r="F39" s="248"/>
+      <c r="A39" s="243" t="s">
+        <v>539</v>
+      </c>
+      <c r="B39" s="244" t="s">
+        <v>502</v>
+      </c>
+      <c r="C39" s="245" t="s">
+        <v>540</v>
+      </c>
+      <c r="D39" s="245"/>
+      <c r="E39" s="245"/>
+      <c r="F39" s="239"/>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="249" t="s">
-        <v>539</v>
-      </c>
-      <c r="B40" s="250" t="s">
-        <v>469</v>
-      </c>
-      <c r="C40" s="251" t="s">
-        <v>540</v>
-      </c>
-      <c r="D40" s="251"/>
-      <c r="E40" s="251"/>
-      <c r="F40" s="248"/>
+      <c r="A40" s="240" t="s">
+        <v>541</v>
+      </c>
+      <c r="B40" s="241" t="s">
+        <v>471</v>
+      </c>
+      <c r="C40" s="242" t="s">
+        <v>542</v>
+      </c>
+      <c r="D40" s="242"/>
+      <c r="E40" s="242"/>
+      <c r="F40" s="239"/>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="257" t="s">
-        <v>541</v>
+      <c r="A41" s="249" t="s">
+        <v>543</v>
       </c>
       <c r="B41" s="260"/>
       <c r="C41" s="260"/>
-      <c r="D41" s="248"/>
-      <c r="E41" s="248"/>
-      <c r="F41" s="248"/>
+      <c r="D41" s="239"/>
+      <c r="E41" s="239"/>
+      <c r="F41" s="239"/>
     </row>
     <row r="42" spans="1:6" ht="29.25">
-      <c r="A42" s="249" t="s">
-        <v>489</v>
-      </c>
-      <c r="B42" s="250" t="s">
-        <v>542</v>
-      </c>
-      <c r="C42" s="251" t="s">
-        <v>543</v>
-      </c>
-      <c r="D42" s="251"/>
-      <c r="E42" s="251"/>
-      <c r="F42" s="248"/>
+      <c r="A42" s="240" t="s">
+        <v>491</v>
+      </c>
+      <c r="B42" s="241" t="s">
+        <v>544</v>
+      </c>
+      <c r="C42" s="242" t="s">
+        <v>545</v>
+      </c>
+      <c r="D42" s="242"/>
+      <c r="E42" s="242"/>
+      <c r="F42" s="239"/>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="252" t="s">
-        <v>492</v>
-      </c>
-      <c r="B43" s="253" t="s">
+      <c r="A43" s="243" t="s">
+        <v>494</v>
+      </c>
+      <c r="B43" s="244" t="s">
         <v>452</v>
       </c>
-      <c r="C43" s="254" t="s">
-        <v>544</v>
-      </c>
-      <c r="D43" s="254"/>
-      <c r="E43" s="254"/>
-      <c r="F43" s="248"/>
+      <c r="C43" s="245" t="s">
+        <v>546</v>
+      </c>
+      <c r="D43" s="245"/>
+      <c r="E43" s="245"/>
+      <c r="F43" s="239"/>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="249" t="s">
-        <v>512</v>
-      </c>
-      <c r="B44" s="250" t="s">
-        <v>545</v>
-      </c>
-      <c r="C44" s="251" t="s">
-        <v>546</v>
-      </c>
-      <c r="D44" s="251"/>
-      <c r="E44" s="251"/>
-      <c r="F44" s="248"/>
+      <c r="A44" s="240" t="s">
+        <v>514</v>
+      </c>
+      <c r="B44" s="241" t="s">
+        <v>547</v>
+      </c>
+      <c r="C44" s="242" t="s">
+        <v>548</v>
+      </c>
+      <c r="D44" s="242"/>
+      <c r="E44" s="242"/>
+      <c r="F44" s="239"/>
     </row>
     <row r="45" spans="1:6" ht="15.75">
-      <c r="A45" s="252" t="s">
-        <v>547</v>
-      </c>
-      <c r="B45" s="253" t="s">
-        <v>548</v>
-      </c>
-      <c r="C45" s="254" t="s">
+      <c r="A45" s="243" t="s">
         <v>549</v>
       </c>
-      <c r="D45" s="254"/>
-      <c r="E45" s="254"/>
-      <c r="F45" s="248"/>
+      <c r="B45" s="244" t="s">
+        <v>550</v>
+      </c>
+      <c r="C45" s="245" t="s">
+        <v>551</v>
+      </c>
+      <c r="D45" s="245"/>
+      <c r="E45" s="245"/>
+      <c r="F45" s="239"/>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="257" t="s">
-        <v>550</v>
+      <c r="A46" s="249" t="s">
+        <v>552</v>
       </c>
       <c r="B46" s="260"/>
       <c r="C46" s="260"/>
-      <c r="D46" s="248"/>
-      <c r="E46" s="248"/>
-      <c r="F46" s="248"/>
+      <c r="D46" s="239"/>
+      <c r="E46" s="239"/>
+      <c r="F46" s="239"/>
     </row>
     <row r="47" spans="1:6" ht="29.25">
-      <c r="A47" s="249" t="s">
-        <v>531</v>
-      </c>
-      <c r="B47" s="250" t="s">
-        <v>551</v>
-      </c>
-      <c r="C47" s="251" t="s">
-        <v>552</v>
-      </c>
-      <c r="D47" s="251"/>
-      <c r="E47" s="251"/>
-      <c r="F47" s="248"/>
+      <c r="A47" s="240" t="s">
+        <v>533</v>
+      </c>
+      <c r="B47" s="241" t="s">
+        <v>553</v>
+      </c>
+      <c r="C47" s="242" t="s">
+        <v>554</v>
+      </c>
+      <c r="D47" s="242"/>
+      <c r="E47" s="242"/>
+      <c r="F47" s="239"/>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="252" t="s">
-        <v>510</v>
-      </c>
-      <c r="B48" s="253" t="s">
+      <c r="A48" s="243" t="s">
+        <v>512</v>
+      </c>
+      <c r="B48" s="244" t="s">
         <v>452</v>
       </c>
-      <c r="C48" s="254" t="s">
-        <v>553</v>
-      </c>
-      <c r="D48" s="254"/>
-      <c r="E48" s="254"/>
-      <c r="F48" s="248"/>
+      <c r="C48" s="245" t="s">
+        <v>555</v>
+      </c>
+      <c r="D48" s="245"/>
+      <c r="E48" s="245"/>
+      <c r="F48" s="239"/>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="249" t="s">
-        <v>554</v>
-      </c>
-      <c r="B49" s="250" t="s">
-        <v>555</v>
-      </c>
-      <c r="C49" s="251" t="s">
+      <c r="A49" s="240" t="s">
         <v>556</v>
       </c>
-      <c r="D49" s="251"/>
-      <c r="E49" s="251"/>
-      <c r="F49" s="248"/>
+      <c r="B49" s="241" t="s">
+        <v>557</v>
+      </c>
+      <c r="C49" s="242" t="s">
+        <v>558</v>
+      </c>
+      <c r="D49" s="242"/>
+      <c r="E49" s="242"/>
+      <c r="F49" s="239"/>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="252" t="s">
-        <v>516</v>
-      </c>
-      <c r="B50" s="253" t="s">
-        <v>557</v>
-      </c>
-      <c r="C50" s="254" t="s">
-        <v>558</v>
-      </c>
-      <c r="D50" s="254"/>
-      <c r="E50" s="254"/>
-      <c r="F50" s="248"/>
+      <c r="A50" s="243" t="s">
+        <v>518</v>
+      </c>
+      <c r="B50" s="244" t="s">
+        <v>559</v>
+      </c>
+      <c r="C50" s="245" t="s">
+        <v>560</v>
+      </c>
+      <c r="D50" s="245"/>
+      <c r="E50" s="245"/>
+      <c r="F50" s="239"/>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="257" t="s">
-        <v>559</v>
+      <c r="A51" s="249" t="s">
+        <v>561</v>
       </c>
       <c r="B51" s="260"/>
       <c r="C51" s="260"/>
-      <c r="D51" s="248"/>
-      <c r="E51" s="248"/>
-      <c r="F51" s="248"/>
+      <c r="D51" s="239"/>
+      <c r="E51" s="239"/>
+      <c r="F51" s="239"/>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="249" t="s">
-        <v>560</v>
-      </c>
-      <c r="B52" s="250" t="s">
-        <v>561</v>
-      </c>
-      <c r="C52" s="251" t="s">
+      <c r="A52" s="240" t="s">
         <v>562</v>
       </c>
-      <c r="D52" s="251"/>
-      <c r="E52" s="251"/>
-      <c r="F52" s="248"/>
+      <c r="B52" s="241" t="s">
+        <v>563</v>
+      </c>
+      <c r="C52" s="242" t="s">
+        <v>564</v>
+      </c>
+      <c r="D52" s="242"/>
+      <c r="E52" s="242"/>
+      <c r="F52" s="239"/>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="252" t="s">
-        <v>563</v>
-      </c>
-      <c r="B53" s="253" t="s">
+      <c r="A53" s="243" t="s">
+        <v>565</v>
+      </c>
+      <c r="B53" s="244" t="s">
         <v>452</v>
       </c>
-      <c r="C53" s="254" t="s">
-        <v>564</v>
-      </c>
-      <c r="D53" s="254"/>
-      <c r="E53" s="254"/>
-      <c r="F53" s="248"/>
+      <c r="C53" s="245" t="s">
+        <v>566</v>
+      </c>
+      <c r="D53" s="245"/>
+      <c r="E53" s="245"/>
+      <c r="F53" s="239"/>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="249" t="s">
-        <v>565</v>
-      </c>
-      <c r="B54" s="250" t="s">
-        <v>566</v>
-      </c>
-      <c r="C54" s="251" t="s">
+      <c r="A54" s="240" t="s">
         <v>567</v>
       </c>
-      <c r="D54" s="251"/>
-      <c r="E54" s="251"/>
-      <c r="F54" s="248"/>
+      <c r="B54" s="241" t="s">
+        <v>568</v>
+      </c>
+      <c r="C54" s="242" t="s">
+        <v>569</v>
+      </c>
+      <c r="D54" s="242"/>
+      <c r="E54" s="242"/>
+      <c r="F54" s="239"/>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="252" t="s">
-        <v>568</v>
-      </c>
-      <c r="B55" s="253" t="s">
-        <v>569</v>
-      </c>
-      <c r="C55" s="254" t="s">
+      <c r="A55" s="243" t="s">
         <v>570</v>
       </c>
-      <c r="D55" s="254"/>
-      <c r="E55" s="254"/>
-      <c r="F55" s="248"/>
+      <c r="B55" s="244" t="s">
+        <v>571</v>
+      </c>
+      <c r="C55" s="245" t="s">
+        <v>572</v>
+      </c>
+      <c r="D55" s="245"/>
+      <c r="E55" s="245"/>
+      <c r="F55" s="239"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -13548,19 +13556,20 @@
     <hyperlink ref="F20" r:id="rId6" xr:uid="{83714BB7-E198-4AF2-9E3F-F0EB6C640209}"/>
     <hyperlink ref="F22" r:id="rId7" xr:uid="{3D986609-D1AD-40CD-9D91-B61C2D40A5ED}"/>
     <hyperlink ref="F23" r:id="rId8" xr:uid="{9191FE3F-DA50-42C9-A969-CB2607764014}"/>
+    <hyperlink ref="F6" r:id="rId9" xr:uid="{1A57CA13-D567-426E-8F5E-D61428112166}"/>
+    <hyperlink ref="E6" r:id="rId10" xr:uid="{AD9D2A23-197E-48AD-BEB3-D183F57E51A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId9"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId11"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13803,15 +13812,16 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6EF48D-28DC-4A85-AE0A-77598A9ABE97}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -13819,5 +13829,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6EF48D-28DC-4A85-AE0A-77598A9ABE97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}"/>
 </file>
--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD04243F-370A-43DE-9081-B5FB59FFBFE7}"/>
+  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB8D47EC-124B-4100-A040-E46359791ED3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" firstSheet="4" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="575">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1421,6 +1421,9 @@
     <t>Airbnb</t>
   </si>
   <si>
+    <t>1_day1_airbnb.png</t>
+  </si>
+  <si>
     <t>https://maps.app.goo.gl/DBmdvffro3LetJej6</t>
   </si>
   <si>
@@ -1461,6 +1464,9 @@
   </si>
   <si>
     <t>Miraikan</t>
+  </si>
+  <si>
+    <t>1_day1_miraikan.png</t>
   </si>
   <si>
     <t>https://maps.app.goo.gl/BmYZxEzfSyLjgQyp9</t>
@@ -12830,40 +12836,42 @@
       <c r="D5" s="242" t="s">
         <v>449</v>
       </c>
-      <c r="E5" s="242"/>
+      <c r="E5" s="8" t="s">
+        <v>450</v>
+      </c>
       <c r="F5" s="247" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="243" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B6" s="244" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C6" s="245" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D6" s="245" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F6" s="246" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75">
       <c r="A7" s="240" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B7" s="244" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C7" s="245" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D7" s="245"/>
       <c r="E7" s="245"/>
@@ -12871,49 +12879,51 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="243" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B8" s="244" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C8" s="245" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D8" s="245" t="s">
-        <v>463</v>
-      </c>
-      <c r="E8" s="245"/>
+        <v>464</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>465</v>
+      </c>
       <c r="F8" s="246" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="240" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B9" s="241" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C9" s="242" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D9" s="242" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E9" s="242"/>
       <c r="F9" s="246" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="243" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B10" s="244" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C10" s="245" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D10" s="245"/>
       <c r="E10" s="245"/>
@@ -12924,10 +12934,10 @@
         <v>0.875</v>
       </c>
       <c r="B11" s="241" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C11" s="242" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D11" s="242"/>
       <c r="E11" s="242"/>
@@ -12935,7 +12945,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="249" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B12" s="260"/>
       <c r="C12" s="260"/>
@@ -12945,31 +12955,31 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="240" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B13" s="241" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C13" s="242" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D13" s="242" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E13" s="242"/>
       <c r="F13" s="246" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="29.25">
       <c r="A14" s="243" t="s">
+        <v>483</v>
+      </c>
+      <c r="B14" s="244" t="s">
         <v>481</v>
       </c>
-      <c r="B14" s="244" t="s">
-        <v>479</v>
-      </c>
       <c r="C14" s="245" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D14" s="245"/>
       <c r="E14" s="245"/>
@@ -12977,20 +12987,20 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="240" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B15" s="241" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C15" s="242" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D15" s="242" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E15" s="242"/>
       <c r="F15" s="246" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -12998,10 +13008,10 @@
         <v>0.875</v>
       </c>
       <c r="B16" s="241" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C16" s="242" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
@@ -13009,7 +13019,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="249" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B17" s="260"/>
       <c r="C17" s="260"/>
@@ -13019,13 +13029,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="240" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B18" s="241" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C18" s="242" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D18" s="242"/>
       <c r="E18" s="242"/>
@@ -13033,13 +13043,13 @@
     </row>
     <row r="19" spans="1:6" ht="29.25">
       <c r="A19" s="243" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B19" s="244" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C19" s="245" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D19" s="245"/>
       <c r="E19" s="245"/>
@@ -13047,31 +13057,31 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="240" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B20" s="241" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C20" s="242" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D20" s="242" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E20" s="242"/>
       <c r="F20" s="246" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="243" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B21" s="244" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C21" s="245" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
@@ -13079,41 +13089,41 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="240" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B22" s="241" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C22" s="242" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D22" s="242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E22" s="242"/>
       <c r="F22" s="246" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="243" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B23" s="244" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C23" s="245" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D23" s="245"/>
       <c r="E23" s="245"/>
       <c r="F23" s="8" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="249" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B24" s="260"/>
       <c r="C24" s="260"/>
@@ -13123,13 +13133,13 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="240" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B25" s="241" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C25" s="242" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D25" s="242"/>
       <c r="E25" s="242"/>
@@ -13137,13 +13147,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="243" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B26" s="244" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C26" s="245" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D26" s="245"/>
       <c r="E26" s="245"/>
@@ -13151,13 +13161,13 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="240" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B27" s="241" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C27" s="242" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D27" s="242"/>
       <c r="E27" s="242"/>
@@ -13165,13 +13175,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="243" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B28" s="244" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C28" s="245" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
@@ -13179,13 +13189,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="240" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B29" s="241" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C29" s="242" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D29" s="242"/>
       <c r="E29" s="242"/>
@@ -13193,7 +13203,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="249" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B30" s="260"/>
       <c r="C30" s="260"/>
@@ -13203,13 +13213,13 @@
     </row>
     <row r="31" spans="1:6" ht="29.25">
       <c r="A31" s="240" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B31" s="241" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C31" s="242" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D31" s="242"/>
       <c r="E31" s="242"/>
@@ -13217,13 +13227,13 @@
     </row>
     <row r="32" spans="1:6" ht="29.25">
       <c r="A32" s="243" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B32" s="244" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C32" s="245" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="D32" s="245"/>
       <c r="E32" s="245"/>
@@ -13231,13 +13241,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="240" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B33" s="241" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C33" s="242" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D33" s="242"/>
       <c r="E33" s="242"/>
@@ -13245,13 +13255,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="243" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B34" s="244" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C34" s="245" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D34" s="245"/>
       <c r="E34" s="245"/>
@@ -13259,7 +13269,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="249" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B35" s="260"/>
       <c r="C35" s="260"/>
@@ -13269,13 +13279,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="240" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B36" s="241" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C36" s="242" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D36" s="242"/>
       <c r="E36" s="242"/>
@@ -13283,13 +13293,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="243" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B37" s="244" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C37" s="245" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D37" s="245"/>
       <c r="E37" s="245"/>
@@ -13297,13 +13307,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="240" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B38" s="241" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C38" s="242" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D38" s="242"/>
       <c r="E38" s="242"/>
@@ -13311,13 +13321,13 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="243" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B39" s="244" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C39" s="245" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D39" s="245"/>
       <c r="E39" s="245"/>
@@ -13325,13 +13335,13 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="240" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B40" s="241" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C40" s="242" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D40" s="242"/>
       <c r="E40" s="242"/>
@@ -13339,7 +13349,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="249" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B41" s="260"/>
       <c r="C41" s="260"/>
@@ -13349,13 +13359,13 @@
     </row>
     <row r="42" spans="1:6" ht="29.25">
       <c r="A42" s="240" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B42" s="241" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C42" s="242" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D42" s="242"/>
       <c r="E42" s="242"/>
@@ -13363,13 +13373,13 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="243" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B43" s="244" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C43" s="245" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D43" s="245"/>
       <c r="E43" s="245"/>
@@ -13377,13 +13387,13 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="240" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B44" s="241" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C44" s="242" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D44" s="242"/>
       <c r="E44" s="242"/>
@@ -13391,13 +13401,13 @@
     </row>
     <row r="45" spans="1:6" ht="15.75">
       <c r="A45" s="243" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B45" s="244" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C45" s="245" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D45" s="245"/>
       <c r="E45" s="245"/>
@@ -13405,7 +13415,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="249" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B46" s="260"/>
       <c r="C46" s="260"/>
@@ -13415,13 +13425,13 @@
     </row>
     <row r="47" spans="1:6" ht="29.25">
       <c r="A47" s="240" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B47" s="241" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C47" s="242" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D47" s="242"/>
       <c r="E47" s="242"/>
@@ -13429,13 +13439,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="243" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B48" s="244" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C48" s="245" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D48" s="245"/>
       <c r="E48" s="245"/>
@@ -13443,13 +13453,13 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="240" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B49" s="241" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C49" s="242" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D49" s="242"/>
       <c r="E49" s="242"/>
@@ -13457,13 +13467,13 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="243" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B50" s="244" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C50" s="245" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D50" s="245"/>
       <c r="E50" s="245"/>
@@ -13471,7 +13481,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="249" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B51" s="260"/>
       <c r="C51" s="260"/>
@@ -13481,13 +13491,13 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="240" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B52" s="241" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C52" s="242" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D52" s="242"/>
       <c r="E52" s="242"/>
@@ -13495,13 +13505,13 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="243" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B53" s="244" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C53" s="245" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D53" s="245"/>
       <c r="E53" s="245"/>
@@ -13509,13 +13519,13 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="240" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B54" s="241" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C54" s="242" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D54" s="242"/>
       <c r="E54" s="242"/>
@@ -13523,13 +13533,13 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="243" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B55" s="244" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C55" s="245" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D55" s="245"/>
       <c r="E55" s="245"/>
@@ -13558,9 +13568,11 @@
     <hyperlink ref="F23" r:id="rId8" xr:uid="{9191FE3F-DA50-42C9-A969-CB2607764014}"/>
     <hyperlink ref="F6" r:id="rId9" xr:uid="{1A57CA13-D567-426E-8F5E-D61428112166}"/>
     <hyperlink ref="E6" r:id="rId10" xr:uid="{AD9D2A23-197E-48AD-BEB3-D183F57E51A7}"/>
+    <hyperlink ref="E8" r:id="rId11" xr:uid="{C57DE3BC-5611-4857-AF68-85AE0077E820}"/>
+    <hyperlink ref="E5" r:id="rId12" xr:uid="{51324F1C-9EC8-4171-933D-4D6E14F3B038}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId11"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId13"/>
 </worksheet>
 </file>
 

--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB8D47EC-124B-4100-A040-E46359791ED3}"/>
+  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D2EFD55-84C5-468B-A470-9CE46B604166}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" firstSheet="4" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="577">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1484,6 +1484,9 @@
     <t>Sunset point</t>
   </si>
   <si>
+    <t>1_day1_odaibapark.png</t>
+  </si>
+  <si>
     <t>https://maps.app.goo.gl/t1SnqWYUNsLD9mvk7</t>
   </si>
   <si>
@@ -1494,6 +1497,9 @@
   </si>
   <si>
     <t>Traditional Tokyo Monjayaki dinner</t>
+  </si>
+  <si>
+    <t>https://bscvn-my.sharepoint.com/:i:/g/personal/minhpq_bsc_com_vn/IQBRUb7lv3OXQKmQhgxjWPieAVVa-oUibISNnQYhKMhKaM4?e=u00oyY</t>
   </si>
   <si>
     <t>Evening</t>
@@ -12910,23 +12916,27 @@
       <c r="D9" s="242" t="s">
         <v>470</v>
       </c>
-      <c r="E9" s="242"/>
+      <c r="E9" s="8" t="s">
+        <v>471</v>
+      </c>
       <c r="F9" s="246" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="243" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B10" s="244" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C10" s="245" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D10" s="245"/>
-      <c r="E10" s="245"/>
+      <c r="E10" s="8" t="s">
+        <v>476</v>
+      </c>
       <c r="F10" s="239"/>
     </row>
     <row r="11" spans="1:6">
@@ -12934,10 +12944,10 @@
         <v>0.875</v>
       </c>
       <c r="B11" s="241" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C11" s="242" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D11" s="242"/>
       <c r="E11" s="242"/>
@@ -12945,7 +12955,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="249" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B12" s="260"/>
       <c r="C12" s="260"/>
@@ -12955,31 +12965,31 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="240" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B13" s="241" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C13" s="242" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D13" s="242" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E13" s="242"/>
       <c r="F13" s="246" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="29.25">
       <c r="A14" s="243" t="s">
+        <v>485</v>
+      </c>
+      <c r="B14" s="244" t="s">
         <v>483</v>
       </c>
-      <c r="B14" s="244" t="s">
-        <v>481</v>
-      </c>
       <c r="C14" s="245" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D14" s="245"/>
       <c r="E14" s="245"/>
@@ -12987,20 +12997,20 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="240" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B15" s="241" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C15" s="242" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D15" s="242" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E15" s="242"/>
       <c r="F15" s="246" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -13008,10 +13018,10 @@
         <v>0.875</v>
       </c>
       <c r="B16" s="241" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C16" s="242" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
@@ -13019,7 +13029,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="249" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B17" s="260"/>
       <c r="C17" s="260"/>
@@ -13029,13 +13039,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="240" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B18" s="241" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C18" s="242" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D18" s="242"/>
       <c r="E18" s="242"/>
@@ -13043,13 +13053,13 @@
     </row>
     <row r="19" spans="1:6" ht="29.25">
       <c r="A19" s="243" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B19" s="244" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C19" s="245" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D19" s="245"/>
       <c r="E19" s="245"/>
@@ -13057,31 +13067,31 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="240" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B20" s="241" t="s">
         <v>453</v>
       </c>
       <c r="C20" s="242" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D20" s="242" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E20" s="242"/>
       <c r="F20" s="246" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="243" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B21" s="244" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C21" s="245" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
@@ -13089,41 +13099,41 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B22" s="241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C22" s="242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D22" s="242" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E22" s="242"/>
       <c r="F22" s="246" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="243" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B23" s="244" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C23" s="245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D23" s="245"/>
       <c r="E23" s="245"/>
       <c r="F23" s="8" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="249" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B24" s="260"/>
       <c r="C24" s="260"/>
@@ -13133,13 +13143,13 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="240" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B25" s="241" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C25" s="242" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D25" s="242"/>
       <c r="E25" s="242"/>
@@ -13147,13 +13157,13 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="243" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B26" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C26" s="245" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D26" s="245"/>
       <c r="E26" s="245"/>
@@ -13161,13 +13171,13 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="240" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B27" s="241" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C27" s="242" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D27" s="242"/>
       <c r="E27" s="242"/>
@@ -13175,13 +13185,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="243" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B28" s="244" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C28" s="245" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
@@ -13189,13 +13199,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="240" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B29" s="241" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C29" s="242" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D29" s="242"/>
       <c r="E29" s="242"/>
@@ -13203,7 +13213,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="249" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B30" s="260"/>
       <c r="C30" s="260"/>
@@ -13213,13 +13223,13 @@
     </row>
     <row r="31" spans="1:6" ht="29.25">
       <c r="A31" s="240" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B31" s="241" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C31" s="242" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D31" s="242"/>
       <c r="E31" s="242"/>
@@ -13227,13 +13237,13 @@
     </row>
     <row r="32" spans="1:6" ht="29.25">
       <c r="A32" s="243" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B32" s="244" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C32" s="245" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D32" s="245"/>
       <c r="E32" s="245"/>
@@ -13241,13 +13251,13 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="240" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B33" s="241" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C33" s="242" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D33" s="242"/>
       <c r="E33" s="242"/>
@@ -13255,13 +13265,13 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="243" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B34" s="244" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C34" s="245" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D34" s="245"/>
       <c r="E34" s="245"/>
@@ -13269,7 +13279,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="249" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B35" s="260"/>
       <c r="C35" s="260"/>
@@ -13279,13 +13289,13 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="240" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B36" s="241" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C36" s="242" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D36" s="242"/>
       <c r="E36" s="242"/>
@@ -13293,13 +13303,13 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="243" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B37" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C37" s="245" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D37" s="245"/>
       <c r="E37" s="245"/>
@@ -13307,13 +13317,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="240" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B38" s="241" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C38" s="242" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D38" s="242"/>
       <c r="E38" s="242"/>
@@ -13321,13 +13331,13 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="243" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B39" s="244" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C39" s="245" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D39" s="245"/>
       <c r="E39" s="245"/>
@@ -13335,13 +13345,13 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="240" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B40" s="241" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C40" s="242" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D40" s="242"/>
       <c r="E40" s="242"/>
@@ -13349,7 +13359,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="249" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B41" s="260"/>
       <c r="C41" s="260"/>
@@ -13359,13 +13369,13 @@
     </row>
     <row r="42" spans="1:6" ht="29.25">
       <c r="A42" s="240" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B42" s="241" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C42" s="242" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D42" s="242"/>
       <c r="E42" s="242"/>
@@ -13373,13 +13383,13 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="243" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B43" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C43" s="245" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D43" s="245"/>
       <c r="E43" s="245"/>
@@ -13387,13 +13397,13 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="240" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B44" s="241" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C44" s="242" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D44" s="242"/>
       <c r="E44" s="242"/>
@@ -13401,13 +13411,13 @@
     </row>
     <row r="45" spans="1:6" ht="15.75">
       <c r="A45" s="243" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B45" s="244" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C45" s="245" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D45" s="245"/>
       <c r="E45" s="245"/>
@@ -13415,7 +13425,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="249" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B46" s="260"/>
       <c r="C46" s="260"/>
@@ -13425,13 +13435,13 @@
     </row>
     <row r="47" spans="1:6" ht="29.25">
       <c r="A47" s="240" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B47" s="241" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C47" s="242" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D47" s="242"/>
       <c r="E47" s="242"/>
@@ -13439,13 +13449,13 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="243" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B48" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C48" s="245" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D48" s="245"/>
       <c r="E48" s="245"/>
@@ -13453,13 +13463,13 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="240" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B49" s="241" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C49" s="242" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D49" s="242"/>
       <c r="E49" s="242"/>
@@ -13467,13 +13477,13 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="243" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B50" s="244" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C50" s="245" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D50" s="245"/>
       <c r="E50" s="245"/>
@@ -13481,7 +13491,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="249" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B51" s="260"/>
       <c r="C51" s="260"/>
@@ -13491,13 +13501,13 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="240" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B52" s="241" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C52" s="242" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D52" s="242"/>
       <c r="E52" s="242"/>
@@ -13505,13 +13515,13 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" s="243" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B53" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C53" s="245" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D53" s="245"/>
       <c r="E53" s="245"/>
@@ -13519,13 +13529,13 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" s="240" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B54" s="241" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C54" s="242" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D54" s="242"/>
       <c r="E54" s="242"/>
@@ -13533,13 +13543,13 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="243" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B55" s="244" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C55" s="245" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D55" s="245"/>
       <c r="E55" s="245"/>
@@ -13570,21 +13580,15 @@
     <hyperlink ref="E6" r:id="rId10" xr:uid="{AD9D2A23-197E-48AD-BEB3-D183F57E51A7}"/>
     <hyperlink ref="E8" r:id="rId11" xr:uid="{C57DE3BC-5611-4857-AF68-85AE0077E820}"/>
     <hyperlink ref="E5" r:id="rId12" xr:uid="{51324F1C-9EC8-4171-933D-4D6E14F3B038}"/>
+    <hyperlink ref="E9" r:id="rId13" xr:uid="{2B5871D6-0326-4F93-B09F-9BD757F4381C}"/>
+    <hyperlink ref="E10" r:id="rId14" xr:uid="{A32D7BDB-2BBC-4255-9428-0E5F6DEE5AE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId13"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId15"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005A4695005C4BEE4A8751FEE2C473E10D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df7fcaa21f93254d26451ff7a6d04ad2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xmlns:ns4="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fefbcb393e90fe08e3723c038b505a33" ns3:_="" ns4:_="">
     <xsd:import namespace="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
@@ -13823,6 +13827,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -13833,11 +13845,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6EF48D-28DC-4A85-AE0A-77598A9ABE97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6EF48D-28DC-4A85-AE0A-77598A9ABE97}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D2EFD55-84C5-468B-A470-9CE46B604166}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2628DAD-FC95-4949-A4FD-DFB277BCC235}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" firstSheet="4" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
+    <workbookView xWindow="1120" yWindow="500" windowWidth="27680" windowHeight="17500" tabRatio="458" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
   <sheets>
     <sheet name="CHI PHÍ" sheetId="5" state="hidden" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="598">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1499,7 +1499,7 @@
     <t>Traditional Tokyo Monjayaki dinner</t>
   </si>
   <si>
-    <t>https://bscvn-my.sharepoint.com/:i:/g/personal/minhpq_bsc_com_vn/IQBRUb7lv3OXQKmQhgxjWPieAVVa-oUibISNnQYhKMhKaM4?e=u00oyY</t>
+    <t>1_day1_monja.png</t>
   </si>
   <si>
     <t>Evening</t>
@@ -1517,9 +1517,6 @@
     <t>Transfer to Disney</t>
   </si>
   <si>
-    <t>Transfer from hotel to Tokyo DisneySea</t>
-  </si>
-  <si>
     <t>Tokyo DisneySea</t>
   </si>
   <si>
@@ -1571,9 +1568,6 @@
     <t>Authentic Koshu Hoto Kosaku noodles (Pumpkin miso noodle stew).</t>
   </si>
   <si>
-    <t>Huto Noodle</t>
-  </si>
-  <si>
     <t>https://share.google/07foiHP82iKKrDXLN</t>
   </si>
   <si>
@@ -1616,15 +1610,9 @@
     <t>Lakeside Cycling</t>
   </si>
   <si>
-    <t>Morning bike tour around Lake Kawaguchiko; lakeside coffee break (The Park Cafe / Lake Bake).</t>
-  </si>
-  <si>
     <t>11:30 - 13:00</t>
   </si>
   <si>
-    <t>Crispy Tonkatsu / Tempura at Fuji Tempura Idaten (or Koushuya).</t>
-  </si>
-  <si>
     <t>13:30 - 16:30</t>
   </si>
   <si>
@@ -1634,9 +1622,6 @@
     <t>Scenic transfer by express bus / JR train from Kawaguchiko Station to Matsumoto (Nagano).</t>
   </si>
   <si>
-    <t>Check in Toyoko Inn Matsumoto Station Ekimae.</t>
-  </si>
-  <si>
     <t>18:00 - 20:30</t>
   </si>
   <si>
@@ -1655,9 +1640,6 @@
     <t>Bus to Kamikochi</t>
   </si>
   <si>
-    <t>Depart Matsumoto Bus Terminal via scenic alpine bus to Kamikochi (Chubu Sangaku National Park).</t>
-  </si>
-  <si>
     <t>09:00 - 14:00</t>
   </si>
   <si>
@@ -1800,6 +1782,87 @@
   </si>
   <si>
     <t>Duty-free shopping, flight check-in and board flight returning to Hanoi.</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/WVra6VVmUsb8rW6e6</t>
+  </si>
+  <si>
+    <t>https://share.google/xqkzBGgDAv8kRgixy</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/NUq4LMixjLGYXGEt7</t>
+  </si>
+  <si>
+    <t>Route</t>
+  </si>
+  <si>
+    <t>Koushuya</t>
+  </si>
+  <si>
+    <t>Transfer from Airbnb to Tokyo DisneySea</t>
+  </si>
+  <si>
+    <t>Huto Noodle Restaurant</t>
+  </si>
+  <si>
+    <t>Yakitori Sanrokuen</t>
+  </si>
+  <si>
+    <t>Café</t>
+  </si>
+  <si>
+    <t>Hotel</t>
+  </si>
+  <si>
+    <t>Hamburger Steak</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/KDWpc4to69uYDtj87</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/rQZP4NnC7MZ1EG6X8</t>
+  </si>
+  <si>
+    <t>Morning bike tour around Lake Kawaguchiko; Lakeside coffee break (Choose: The Park Cafe / Lake Bake).</t>
+  </si>
+  <si>
+    <t>Choose: Crispy Tonkatsu / Tempura at Fuji Tempura Idaten (or Beef at Koushuya).</t>
+  </si>
+  <si>
+    <t>Check in Toyoko Inn Matsumoto Station Higashiguchi.</t>
+  </si>
+  <si>
+    <t>Depart Matsumoto Bus Terminal via scenic alpine bus to Kamikochi (Nakanoyu Shop)</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Shs2CW2xCxpwiqqY6</t>
+  </si>
+  <si>
+    <t>Horumon Ya Kaishu</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/mHyBFMSJhLKhSmuSA</t>
+  </si>
+  <si>
+    <t>Kobayashi soba</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/N67EMhP435f74TKF6</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/nesRwvcHFTVAvsaB7</t>
+  </si>
+  <si>
+    <t>Kiori Exec Gojo Kyoto</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>https://bscvn-my.sharepoint.com/:i:/g/personal/minhpq_bsc_com_vn/IQC7CiWwxjiVRIplj078Znx4Acaavv8CDm1gdMSwltIEihE?e=c4WJI5</t>
+  </si>
+  <si>
+    <t>2_day2_disney</t>
   </si>
 </sst>
 </file>
@@ -1810,7 +1873,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2058,7 +2121,6 @@
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Aptos Narrow"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="12">
@@ -2211,7 +2273,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="266">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2879,43 +2941,56 @@
     <xf numFmtId="20" fontId="31" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
-    <cellStyle name="Dấu phẩy" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2928,6 +3003,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3248,19 +3327,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{875223EB-0A06-774B-8ABB-FD2B6BEACF61}">
   <dimension ref="B1:J14"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="2"/>
-    <col min="2" max="2" width="31.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.42578125" style="2"/>
-    <col min="6" max="6" width="19.7109375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="2"/>
-    <col min="8" max="8" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="11.42578125" style="2"/>
+    <col min="1" max="1" width="11.5" style="2"/>
+    <col min="2" max="2" width="31.83203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.5" style="2"/>
+    <col min="6" max="6" width="19.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="2"/>
+    <col min="8" max="8" width="12.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -3278,7 +3357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
@@ -3297,7 +3376,7 @@
         <v>6500000</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3316,13 +3395,13 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="H4" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
@@ -3344,7 +3423,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
@@ -3366,7 +3445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:10">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
@@ -3385,7 +3464,7 @@
         <v>1666666.6666666667</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -3407,7 +3486,7 @@
         <v>2374900</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
@@ -3422,7 +3501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:10">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
@@ -3444,7 +3523,7 @@
         <v>8500000</v>
       </c>
     </row>
-    <row r="12" spans="2:10">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
@@ -3466,12 +3545,12 @@
         <v>2040000</v>
       </c>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="2:10" s="1" customFormat="1">
+    <row r="14" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
@@ -3492,19 +3571,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0814982B-01D3-4F78-9AD3-6ACFB0D4A3C4}">
   <dimension ref="A1:J172"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" style="18" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="65.42578125" style="66" customWidth="1"/>
-    <col min="4" max="4" width="50.42578125" style="67" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.140625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="10" customWidth="1"/>
+    <col min="1" max="1" width="24.5" style="18" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.5" style="66" customWidth="1"/>
+    <col min="4" max="4" width="50.5" style="67" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.1640625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="15.6640625" style="10" customWidth="1"/>
     <col min="9" max="16384" width="0" style="10" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" customHeight="1">
+    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23"/>
       <c r="B1" s="24"/>
       <c r="C1" s="25" t="s">
@@ -3522,7 +3601,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1">
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="28" t="s">
         <v>19</v>
       </c>
@@ -3534,7 +3613,7 @@
       <c r="G2" s="24"/>
       <c r="H2" s="24"/>
     </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1">
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="23"/>
       <c r="B3" s="24"/>
       <c r="C3" s="23" t="s">
@@ -3560,7 +3639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1">
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="23" t="s">
@@ -3581,7 +3660,7 @@
         <v>3900000</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1">
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="24"/>
       <c r="C5" s="23" t="s">
@@ -3603,7 +3682,7 @@
         <v>525000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1">
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
         <v>24</v>
       </c>
@@ -3615,7 +3694,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="30"/>
     </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1">
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="23"/>
       <c r="B7" s="24"/>
       <c r="C7" s="23" t="s">
@@ -3629,7 +3708,7 @@
       <c r="G7" s="24"/>
       <c r="H7" s="30"/>
     </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1">
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="23"/>
       <c r="B8" s="24"/>
       <c r="C8" s="23" t="s">
@@ -3643,7 +3722,7 @@
       <c r="G8" s="24"/>
       <c r="H8" s="24"/>
     </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1">
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="23"/>
       <c r="B9" s="24"/>
       <c r="C9" s="23" t="s">
@@ -3657,7 +3736,7 @@
       <c r="G9" s="24"/>
       <c r="H9" s="24"/>
     </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1">
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="23"/>
       <c r="B10" s="24"/>
       <c r="C10" s="23"/>
@@ -3667,7 +3746,7 @@
       <c r="G10" s="24"/>
       <c r="H10" s="24"/>
     </row>
-    <row r="11" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1">
+    <row r="11" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
         <v>28</v>
       </c>
@@ -3679,7 +3758,7 @@
       <c r="G11" s="32"/>
       <c r="H11" s="32"/>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1">
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="35">
         <v>0.20833333333333334</v>
       </c>
@@ -3695,7 +3774,7 @@
       <c r="G12" s="38"/>
       <c r="H12" s="38"/>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1">
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="37"/>
       <c r="B13" s="38"/>
       <c r="C13" s="40" t="s">
@@ -3716,7 +3795,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1">
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="37"/>
       <c r="B14" s="38"/>
       <c r="C14" s="40" t="s">
@@ -3737,7 +3816,7 @@
         <v>9300000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="37"/>
       <c r="B15" s="38"/>
       <c r="C15" s="40" t="s">
@@ -3749,7 +3828,7 @@
       <c r="G15" s="38"/>
       <c r="H15" s="38"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="37"/>
       <c r="B16" s="36">
         <v>0.64583333333333337</v>
@@ -3763,7 +3842,7 @@
       <c r="G16" s="38"/>
       <c r="H16" s="38"/>
     </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1">
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="35">
         <v>0.66666666666666663</v>
       </c>
@@ -3790,7 +3869,7 @@
         <v>6400000</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1">
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="37"/>
       <c r="B18" s="38"/>
       <c r="C18" s="40" t="s">
@@ -3802,7 +3881,7 @@
       <c r="G18" s="38"/>
       <c r="H18" s="38"/>
     </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1">
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="37"/>
       <c r="B19" s="38"/>
       <c r="C19" s="37" t="s">
@@ -3814,7 +3893,7 @@
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
     </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1">
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="37"/>
       <c r="B20" s="38"/>
       <c r="C20" s="40" t="s">
@@ -3837,7 +3916,7 @@
         <v>86700</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1">
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37"/>
       <c r="B21" s="38"/>
       <c r="C21" s="40" t="s">
@@ -3849,7 +3928,7 @@
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
     </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1">
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="35">
         <v>0.75</v>
       </c>
@@ -3875,7 +3954,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1">
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="37"/>
       <c r="B23" s="38"/>
       <c r="C23" s="40" t="s">
@@ -3898,7 +3977,7 @@
         <v>984300</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1">
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="37"/>
       <c r="B24" s="38"/>
       <c r="C24" s="40" t="s">
@@ -3921,7 +4000,7 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1">
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="37"/>
       <c r="B25" s="38"/>
       <c r="C25" s="40" t="s">
@@ -3943,7 +4022,7 @@
         <v>255000</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1">
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="37"/>
       <c r="B26" s="38"/>
       <c r="C26" s="44"/>
@@ -3953,7 +4032,7 @@
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
     </row>
-    <row r="27" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1">
+    <row r="27" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="31" t="s">
         <v>47</v>
       </c>
@@ -3967,7 +4046,7 @@
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
     </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1">
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="35">
         <v>0.25</v>
       </c>
@@ -3994,7 +4073,7 @@
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
     </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1">
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="35"/>
       <c r="B29" s="45"/>
       <c r="C29" s="40" t="s">
@@ -4008,7 +4087,7 @@
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
     </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1">
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="35"/>
       <c r="B30" s="45"/>
       <c r="C30" s="40" t="s">
@@ -4022,7 +4101,7 @@
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
     </row>
-    <row r="31" spans="1:10" ht="15" customHeight="1">
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="35">
         <v>0.27083333333333331</v>
       </c>
@@ -4042,7 +4121,7 @@
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
     </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1">
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="35"/>
       <c r="B32" s="38"/>
       <c r="C32" s="37" t="s">
@@ -4068,7 +4147,7 @@
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
     </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1">
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="35">
         <v>0.33333333333333331</v>
       </c>
@@ -4096,7 +4175,7 @@
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1">
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="35"/>
       <c r="B34" s="38"/>
       <c r="C34" s="40" t="s">
@@ -4119,7 +4198,7 @@
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
     </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1">
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="35">
         <v>0.41666666666666669</v>
       </c>
@@ -4146,7 +4225,7 @@
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
     </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1">
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="35">
         <v>0.4375</v>
       </c>
@@ -4175,7 +4254,7 @@
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
     </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1">
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="35"/>
       <c r="B37" s="36"/>
       <c r="C37" s="37" t="s">
@@ -4189,7 +4268,7 @@
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
     </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1">
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="35"/>
       <c r="B38" s="38"/>
       <c r="C38" s="37" t="s">
@@ -4203,7 +4282,7 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
     </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1">
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="35"/>
       <c r="B39" s="38"/>
       <c r="C39" s="37" t="s">
@@ -4217,7 +4296,7 @@
       <c r="I39" s="13"/>
       <c r="J39" s="13"/>
     </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1">
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="35"/>
       <c r="B40" s="38"/>
       <c r="C40" s="37" t="s">
@@ -4231,7 +4310,7 @@
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
     </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1">
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="35"/>
       <c r="B41" s="38"/>
       <c r="C41" s="37" t="s">
@@ -4245,7 +4324,7 @@
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
     </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1">
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="35"/>
       <c r="B42" s="38"/>
       <c r="C42" s="37" t="s">
@@ -4259,7 +4338,7 @@
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
     </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1">
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="35"/>
       <c r="B43" s="38"/>
       <c r="C43" s="40" t="s">
@@ -4283,7 +4362,7 @@
       <c r="I43" s="13"/>
       <c r="J43" s="13"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1">
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="35">
         <v>0.58333333333333337</v>
       </c>
@@ -4301,7 +4380,7 @@
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1">
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="35"/>
       <c r="B45" s="36"/>
       <c r="C45" s="40" t="s">
@@ -4326,7 +4405,7 @@
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
     </row>
-    <row r="46" spans="1:10" ht="15" customHeight="1">
+    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="35"/>
       <c r="B46" s="36"/>
       <c r="C46" s="40" t="s">
@@ -4340,7 +4419,7 @@
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
     </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1">
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="35"/>
       <c r="B47" s="36"/>
       <c r="C47" s="37" t="s">
@@ -4365,7 +4444,7 @@
       <c r="I47" s="13"/>
       <c r="J47" s="13"/>
     </row>
-    <row r="48" spans="1:10" ht="15" customHeight="1">
+    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="35">
         <v>0.75</v>
       </c>
@@ -4392,7 +4471,7 @@
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
     </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1">
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="37"/>
       <c r="B49" s="36"/>
       <c r="C49" s="44" t="s">
@@ -4414,7 +4493,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1">
+    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="37"/>
       <c r="B50" s="38"/>
       <c r="C50" s="37" t="s">
@@ -4426,7 +4505,7 @@
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
     </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1">
+    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="37"/>
       <c r="B51" s="38"/>
       <c r="C51" s="37" t="s">
@@ -4438,7 +4517,7 @@
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
     </row>
-    <row r="52" spans="1:10" ht="15" customHeight="1">
+    <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="35">
         <v>0.875</v>
       </c>
@@ -4463,7 +4542,7 @@
         <v>112200</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15" customHeight="1">
+    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="35">
         <v>0.91666666666666663</v>
       </c>
@@ -4486,7 +4565,7 @@
         <v>91800</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1">
+    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="35"/>
       <c r="B54" s="36"/>
       <c r="C54" s="40"/>
@@ -4496,7 +4575,7 @@
       <c r="G54" s="38"/>
       <c r="H54" s="39"/>
     </row>
-    <row r="55" spans="1:10" ht="15" customHeight="1">
+    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="37"/>
       <c r="B55" s="38"/>
       <c r="C55" s="37" t="s">
@@ -4510,7 +4589,7 @@
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1">
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="37"/>
       <c r="B56" s="38"/>
       <c r="C56" s="37" t="s">
@@ -4524,7 +4603,7 @@
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
     </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1">
+    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="37"/>
       <c r="B57" s="38"/>
       <c r="C57" s="37" t="s">
@@ -4536,7 +4615,7 @@
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
     </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1">
+    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="37"/>
       <c r="B58" s="38"/>
       <c r="C58" s="37"/>
@@ -4546,7 +4625,7 @@
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
     </row>
-    <row r="59" spans="1:10" s="15" customFormat="1" ht="15" customHeight="1">
+    <row r="59" spans="1:10" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="47" t="s">
         <v>82</v>
       </c>
@@ -4562,7 +4641,7 @@
       <c r="I59" s="14"/>
       <c r="J59" s="14"/>
     </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1">
+    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="37"/>
       <c r="B60" s="38"/>
       <c r="C60" s="37" t="s">
@@ -4584,7 +4663,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1">
+    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="37"/>
       <c r="B61" s="38"/>
       <c r="C61" s="37" t="s">
@@ -4605,7 +4684,7 @@
         <v>91800</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1">
+    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="35">
         <v>0.33333333333333331</v>
       </c>
@@ -4630,7 +4709,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1">
+    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="35">
         <v>0.4375</v>
       </c>
@@ -4644,7 +4723,7 @@
       <c r="G63" s="38"/>
       <c r="H63" s="38"/>
     </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1">
+    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="35">
         <v>0.48958333333333331</v>
       </c>
@@ -4658,7 +4737,7 @@
       <c r="G64" s="38"/>
       <c r="H64" s="38"/>
     </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1">
+    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="35">
         <v>0.52083333333333337</v>
       </c>
@@ -4672,7 +4751,7 @@
       <c r="G65" s="38"/>
       <c r="H65" s="38"/>
     </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1">
+    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="35">
         <v>0.60416666666666663</v>
       </c>
@@ -4686,7 +4765,7 @@
       <c r="G66" s="38"/>
       <c r="H66" s="38"/>
     </row>
-    <row r="67" spans="1:10" ht="15" customHeight="1">
+    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="35">
         <v>0.63194444444444442</v>
       </c>
@@ -4700,7 +4779,7 @@
       <c r="G67" s="38"/>
       <c r="H67" s="38"/>
     </row>
-    <row r="68" spans="1:10" ht="15" customHeight="1">
+    <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="35">
         <v>0.63888888888888884</v>
       </c>
@@ -4714,7 +4793,7 @@
       <c r="G68" s="38"/>
       <c r="H68" s="38"/>
     </row>
-    <row r="69" spans="1:10" ht="15" customHeight="1">
+    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="35">
         <v>0.78472222222222221</v>
       </c>
@@ -4728,7 +4807,7 @@
       <c r="G69" s="38"/>
       <c r="H69" s="38"/>
     </row>
-    <row r="70" spans="1:10" ht="15" customHeight="1">
+    <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="37"/>
       <c r="B70" s="38"/>
       <c r="C70" s="37"/>
@@ -4738,7 +4817,7 @@
       <c r="G70" s="38"/>
       <c r="H70" s="38"/>
     </row>
-    <row r="71" spans="1:10" ht="15" customHeight="1">
+    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="37"/>
       <c r="B71" s="38"/>
       <c r="C71" s="37" t="s">
@@ -4759,7 +4838,7 @@
         <v>91800</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15" customHeight="1">
+    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="37"/>
       <c r="B72" s="38"/>
       <c r="C72" s="37" t="s">
@@ -4781,7 +4860,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15" customHeight="1">
+    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="37"/>
       <c r="B73" s="38"/>
       <c r="C73" s="37" t="s">
@@ -4793,7 +4872,7 @@
       <c r="G73" s="38"/>
       <c r="H73" s="39"/>
     </row>
-    <row r="74" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1">
+    <row r="74" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="31" t="s">
         <v>97</v>
       </c>
@@ -4807,7 +4886,7 @@
       <c r="I74" s="11"/>
       <c r="J74" s="11"/>
     </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1">
+    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="35"/>
       <c r="B75" s="38"/>
       <c r="C75" s="37" t="s">
@@ -4831,7 +4910,7 @@
       <c r="I75" s="13"/>
       <c r="J75" s="13"/>
     </row>
-    <row r="76" spans="1:10" ht="15" customHeight="1">
+    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="35">
         <v>0.33333333333333331</v>
       </c>
@@ -4854,7 +4933,7 @@
         <v>91800</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1">
+    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="37"/>
       <c r="B77" s="38"/>
       <c r="C77" s="37" t="s">
@@ -4877,7 +4956,7 @@
         <v>238000</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1">
+    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="37"/>
       <c r="B78" s="38"/>
       <c r="C78" s="37" t="s">
@@ -4889,7 +4968,7 @@
       <c r="G78" s="38"/>
       <c r="H78" s="39"/>
     </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1">
+    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="35">
         <v>0.41666666666666669</v>
       </c>
@@ -4916,7 +4995,7 @@
         <v>1275000</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15" customHeight="1">
+    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="35">
         <v>0.45833333333333331</v>
       </c>
@@ -4942,7 +5021,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1">
+    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="35">
         <v>0.54166666666666663</v>
       </c>
@@ -4967,7 +5046,7 @@
         <v>107100</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1">
+    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="35"/>
       <c r="B82" s="36"/>
       <c r="C82" s="37" t="s">
@@ -4990,7 +5069,7 @@
         <v>1683000</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1">
+    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="35">
         <v>0.625</v>
       </c>
@@ -5015,7 +5094,7 @@
         <v>107100</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1">
+    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="35"/>
       <c r="B84" s="36"/>
       <c r="C84" s="37" t="s">
@@ -5037,7 +5116,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1">
+    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="35">
         <v>0.70833333333333337</v>
       </c>
@@ -5062,7 +5141,7 @@
         <v>7226700</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1">
+    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="35">
         <v>0.8125</v>
       </c>
@@ -5087,7 +5166,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1">
+    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="37"/>
       <c r="B87" s="38"/>
       <c r="C87" s="37" t="s">
@@ -5101,7 +5180,7 @@
       <c r="G87" s="38"/>
       <c r="H87" s="39"/>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1">
+    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="37"/>
       <c r="B88" s="38"/>
       <c r="C88" s="54" t="s">
@@ -5124,7 +5203,7 @@
         <v>255000</v>
       </c>
     </row>
-    <row r="89" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1">
+    <row r="89" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="31" t="s">
         <v>117</v>
       </c>
@@ -5136,7 +5215,7 @@
       <c r="G89" s="32"/>
       <c r="H89" s="32"/>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1">
+    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="35">
         <v>0.29166666666666669</v>
       </c>
@@ -5164,7 +5243,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1">
+    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="44"/>
       <c r="B91" s="45"/>
       <c r="C91" s="37" t="s">
@@ -5187,7 +5266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1">
+    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="44"/>
       <c r="B92" s="45"/>
       <c r="C92" s="37" t="s">
@@ -5210,7 +5289,7 @@
         <v>2550000</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1">
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="35">
         <v>0.33333333333333331</v>
       </c>
@@ -5226,7 +5305,7 @@
       <c r="G93" s="38"/>
       <c r="H93" s="38"/>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1">
+    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="37"/>
       <c r="B94" s="38"/>
       <c r="C94" s="40" t="s">
@@ -5240,7 +5319,7 @@
       <c r="G94" s="38"/>
       <c r="H94" s="38"/>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1">
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="37"/>
       <c r="B95" s="38"/>
       <c r="C95" s="40" t="s">
@@ -5252,7 +5331,7 @@
       <c r="G95" s="38"/>
       <c r="H95" s="38"/>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1">
+    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="35">
         <v>0.375</v>
       </c>
@@ -5268,7 +5347,7 @@
       <c r="G96" s="38"/>
       <c r="H96" s="38"/>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1">
+    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="37"/>
       <c r="B97" s="38"/>
       <c r="C97" s="40" t="s">
@@ -5291,7 +5370,7 @@
         <v>76500</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1">
+    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="37"/>
       <c r="B98" s="38"/>
       <c r="C98" s="40" t="s">
@@ -5303,7 +5382,7 @@
       <c r="G98" s="38"/>
       <c r="H98" s="39"/>
     </row>
-    <row r="99" spans="1:8" ht="29.25" customHeight="1">
+    <row r="99" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="35">
         <v>0.45833333333333331</v>
       </c>
@@ -5330,7 +5409,7 @@
         <v>117300</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1">
+    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="37"/>
       <c r="B100" s="38"/>
       <c r="C100" s="40" t="s">
@@ -5342,7 +5421,7 @@
       <c r="G100" s="38"/>
       <c r="H100" s="38"/>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1">
+    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="37"/>
       <c r="B101" s="38"/>
       <c r="C101" s="37"/>
@@ -5352,7 +5431,7 @@
       <c r="G101" s="38"/>
       <c r="H101" s="38"/>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1">
+    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="35">
         <v>0.47916666666666669</v>
       </c>
@@ -5380,7 +5459,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1">
+    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="37"/>
       <c r="B103" s="38"/>
       <c r="C103" s="37" t="s">
@@ -5392,7 +5471,7 @@
       <c r="G103" s="38"/>
       <c r="H103" s="38"/>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1">
+    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="35">
         <v>0.54166666666666663</v>
       </c>
@@ -5419,7 +5498,7 @@
         <v>117300</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1">
+    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="37"/>
       <c r="B105" s="38"/>
       <c r="C105" s="40" t="s">
@@ -5431,7 +5510,7 @@
       <c r="G105" s="38"/>
       <c r="H105" s="38"/>
     </row>
-    <row r="106" spans="1:8" ht="15" customHeight="1">
+    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="35">
         <v>0.58333333333333337</v>
       </c>
@@ -5447,7 +5526,7 @@
       <c r="G106" s="38"/>
       <c r="H106" s="38"/>
     </row>
-    <row r="107" spans="1:8" ht="15" customHeight="1">
+    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="35"/>
       <c r="B107" s="36"/>
       <c r="C107" s="37" t="s">
@@ -5459,7 +5538,7 @@
       <c r="G107" s="38"/>
       <c r="H107" s="38"/>
     </row>
-    <row r="108" spans="1:8" ht="15" customHeight="1">
+    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="35"/>
       <c r="B108" s="36">
         <v>0.75</v>
@@ -5473,7 +5552,7 @@
       <c r="G108" s="38"/>
       <c r="H108" s="38"/>
     </row>
-    <row r="109" spans="1:8" ht="15" customHeight="1">
+    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="35"/>
       <c r="B109" s="36"/>
       <c r="C109" s="40" t="s">
@@ -5496,7 +5575,7 @@
         <v>234600</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15" customHeight="1">
+    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="35"/>
       <c r="B110" s="36"/>
       <c r="C110" s="40" t="s">
@@ -5510,7 +5589,7 @@
       <c r="G110" s="38"/>
       <c r="H110" s="38"/>
     </row>
-    <row r="111" spans="1:8" ht="15" customHeight="1">
+    <row r="111" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="35"/>
       <c r="B111" s="36">
         <v>0.79166666666666663</v>
@@ -5534,7 +5613,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15" customHeight="1">
+    <row r="112" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="35"/>
       <c r="B112" s="36"/>
       <c r="C112" s="37" t="s">
@@ -5546,7 +5625,7 @@
       <c r="G112" s="38"/>
       <c r="H112" s="38"/>
     </row>
-    <row r="113" spans="1:10" ht="15" customHeight="1">
+    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="35"/>
       <c r="B113" s="36"/>
       <c r="C113" s="37" t="s">
@@ -5560,7 +5639,7 @@
       <c r="G113" s="38"/>
       <c r="H113" s="38"/>
     </row>
-    <row r="114" spans="1:10" ht="15" customHeight="1">
+    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="35"/>
       <c r="B114" s="36"/>
       <c r="C114" s="37"/>
@@ -5570,7 +5649,7 @@
       <c r="G114" s="38"/>
       <c r="H114" s="38"/>
     </row>
-    <row r="115" spans="1:10" ht="15" customHeight="1">
+    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="31" t="s">
         <v>151</v>
       </c>
@@ -5584,7 +5663,7 @@
       <c r="I115" s="12"/>
       <c r="J115" s="12"/>
     </row>
-    <row r="116" spans="1:10" ht="15" customHeight="1">
+    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="35"/>
       <c r="B116" s="36">
         <v>0.33333333333333331</v>
@@ -5610,7 +5689,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="15" customHeight="1">
+    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="35"/>
       <c r="B117" s="36"/>
       <c r="C117" s="37"/>
@@ -5620,7 +5699,7 @@
       <c r="G117" s="38"/>
       <c r="H117" s="38"/>
     </row>
-    <row r="118" spans="1:10" ht="15" customHeight="1">
+    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="35"/>
       <c r="B118" s="36">
         <v>0.39583333333333331</v>
@@ -5645,7 +5724,7 @@
         <v>1377000</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="15" customHeight="1">
+    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="35"/>
       <c r="B119" s="36">
         <v>0.45833333333333331</v>
@@ -5670,7 +5749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="15" customHeight="1">
+    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="35"/>
       <c r="B120" s="36">
         <v>0.5</v>
@@ -5696,7 +5775,7 @@
         <v>209100</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="15" customHeight="1">
+    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="35"/>
       <c r="B121" s="36"/>
       <c r="C121" s="54" t="s">
@@ -5710,7 +5789,7 @@
       <c r="G121" s="38"/>
       <c r="H121" s="39"/>
     </row>
-    <row r="122" spans="1:10" ht="15" customHeight="1">
+    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="35"/>
       <c r="B122" s="57"/>
       <c r="C122" s="54" t="s">
@@ -5731,7 +5810,7 @@
         <v>59500</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="15" customHeight="1">
+    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="37"/>
       <c r="B123" s="57">
         <v>0.52083333333333337</v>
@@ -5756,7 +5835,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="15" customHeight="1">
+    <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="37"/>
       <c r="B124" s="57">
         <v>0.58333333333333337</v>
@@ -5781,7 +5860,7 @@
         <v>1110000</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="15" customHeight="1">
+    <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="37"/>
       <c r="B125" s="57">
         <v>0.64583333333333337</v>
@@ -5795,7 +5874,7 @@
       <c r="G125" s="38"/>
       <c r="H125" s="39"/>
     </row>
-    <row r="126" spans="1:10" ht="15" customHeight="1">
+    <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="37"/>
       <c r="B126" s="57"/>
       <c r="C126" s="54" t="s">
@@ -5816,7 +5895,7 @@
         <v>122400</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="15" customHeight="1">
+    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="37"/>
       <c r="B127" s="57">
         <v>0.70833333333333337</v>
@@ -5830,7 +5909,7 @@
       <c r="G127" s="38"/>
       <c r="H127" s="39"/>
     </row>
-    <row r="128" spans="1:10" ht="15" customHeight="1">
+    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="37"/>
       <c r="B128" s="57"/>
       <c r="C128" s="54" t="s">
@@ -5853,7 +5932,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15" customHeight="1">
+    <row r="129" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="37"/>
       <c r="B129" s="57"/>
       <c r="C129" s="69" t="s">
@@ -5865,7 +5944,7 @@
       <c r="G129" s="38"/>
       <c r="H129" s="39"/>
     </row>
-    <row r="130" spans="1:8" ht="156.75" customHeight="1">
+    <row r="130" spans="1:8" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="37"/>
       <c r="B130" s="36">
         <v>0.79166666666666663</v>
@@ -5881,7 +5960,7 @@
       <c r="G130" s="38"/>
       <c r="H130" s="38"/>
     </row>
-    <row r="131" spans="1:8" ht="15" customHeight="1">
+    <row r="131" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="37"/>
       <c r="B131" s="38"/>
       <c r="C131" s="37" t="s">
@@ -5893,7 +5972,7 @@
       <c r="G131" s="38"/>
       <c r="H131" s="38"/>
     </row>
-    <row r="132" spans="1:8" ht="15" customHeight="1">
+    <row r="132" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="37"/>
       <c r="B132" s="38"/>
       <c r="C132" s="37" t="s">
@@ -5914,7 +5993,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15" customHeight="1">
+    <row r="133" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="37"/>
       <c r="B133" s="38"/>
       <c r="C133" s="44" t="s">
@@ -5938,7 +6017,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15" customHeight="1">
+    <row r="134" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="37"/>
       <c r="B134" s="38"/>
       <c r="C134" s="37" t="s">
@@ -5950,7 +6029,7 @@
       <c r="G134" s="38"/>
       <c r="H134" s="38"/>
     </row>
-    <row r="135" spans="1:8" ht="15" customHeight="1">
+    <row r="135" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="37"/>
       <c r="B135" s="38"/>
       <c r="C135" s="54" t="s">
@@ -5962,7 +6041,7 @@
       <c r="G135" s="38"/>
       <c r="H135" s="38"/>
     </row>
-    <row r="136" spans="1:8" ht="15" customHeight="1">
+    <row r="136" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="37"/>
       <c r="B136" s="38"/>
       <c r="C136" s="54" t="s">
@@ -5983,10 +6062,10 @@
         <v>122400</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15" customHeight="1">
+    <row r="137" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="37"/>
       <c r="B137" s="38"/>
-      <c r="C137" s="251" t="s">
+      <c r="C137" s="254" t="s">
         <v>179</v>
       </c>
       <c r="D137" s="38"/>
@@ -5998,10 +6077,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15" customHeight="1">
+    <row r="138" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="37"/>
       <c r="B138" s="38"/>
-      <c r="C138" s="251"/>
+      <c r="C138" s="254"/>
       <c r="D138" s="38"/>
       <c r="E138" s="39"/>
       <c r="F138" s="38"/>
@@ -6011,7 +6090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15" customHeight="1">
+    <row r="139" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="37"/>
       <c r="B139" s="38"/>
       <c r="C139" s="54" t="s">
@@ -6032,7 +6111,7 @@
         <v>122400</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15" customHeight="1">
+    <row r="140" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="37"/>
       <c r="B140" s="38"/>
       <c r="C140" s="37" t="s">
@@ -6044,7 +6123,7 @@
       <c r="G140" s="38"/>
       <c r="H140" s="38"/>
     </row>
-    <row r="141" spans="1:8" ht="15" customHeight="1">
+    <row r="141" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="37"/>
       <c r="B141" s="38"/>
       <c r="C141" s="37" t="s">
@@ -6056,7 +6135,7 @@
       <c r="G141" s="38"/>
       <c r="H141" s="38"/>
     </row>
-    <row r="142" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1">
+    <row r="142" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="58" t="s">
         <v>182</v>
       </c>
@@ -6068,7 +6147,7 @@
       <c r="G142" s="59"/>
       <c r="H142" s="59"/>
     </row>
-    <row r="143" spans="1:8" ht="15" customHeight="1">
+    <row r="143" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="44"/>
       <c r="B143" s="57">
         <v>0.29166666666666669</v>
@@ -6094,7 +6173,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="15" customHeight="1">
+    <row r="144" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="44"/>
       <c r="B144" s="57">
         <v>0.375</v>
@@ -6119,7 +6198,7 @@
         <v>423300</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15" customHeight="1">
+    <row r="145" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="44"/>
       <c r="B145" s="55"/>
       <c r="C145" s="54"/>
@@ -6140,7 +6219,7 @@
         <v>408000</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15" customHeight="1">
+    <row r="146" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="44"/>
       <c r="B146" s="57">
         <v>0.41666666666666669</v>
@@ -6165,7 +6244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15" customHeight="1">
+    <row r="147" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="44"/>
       <c r="B147" s="57">
         <v>0.45833333333333331</v>
@@ -6190,7 +6269,7 @@
         <v>91800</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15" customHeight="1">
+    <row r="148" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="44"/>
       <c r="B148" s="57">
         <v>0.47916666666666669</v>
@@ -6215,7 +6294,7 @@
         <v>612000</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15" customHeight="1">
+    <row r="149" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="37"/>
       <c r="B149" s="36">
         <v>0.60416666666666663</v>
@@ -6240,7 +6319,7 @@
         <v>1785000</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15" customHeight="1">
+    <row r="150" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="37"/>
       <c r="B150" s="36"/>
       <c r="C150" s="37" t="s">
@@ -6261,7 +6340,7 @@
         <v>183600</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15" customHeight="1">
+    <row r="151" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="37"/>
       <c r="B151" s="36"/>
       <c r="C151" s="37" t="s">
@@ -6284,7 +6363,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15" customHeight="1">
+    <row r="152" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="37"/>
       <c r="B152" s="36">
         <v>0.83333333333333337</v>
@@ -6298,7 +6377,7 @@
       <c r="G152" s="38"/>
       <c r="H152" s="38"/>
     </row>
-    <row r="153" spans="1:8" ht="15" customHeight="1">
+    <row r="153" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="37"/>
       <c r="B153" s="36"/>
       <c r="C153" s="37" t="s">
@@ -6319,7 +6398,7 @@
         <v>249900</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15" customHeight="1">
+    <row r="154" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="37"/>
       <c r="B154" s="36"/>
       <c r="C154" s="37" t="s">
@@ -6333,7 +6412,7 @@
       <c r="G154" s="38"/>
       <c r="H154" s="38"/>
     </row>
-    <row r="155" spans="1:8" ht="15" customHeight="1">
+    <row r="155" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="37"/>
       <c r="B155" s="36"/>
       <c r="C155" s="37" t="s">
@@ -6345,7 +6424,7 @@
       <c r="G155" s="38"/>
       <c r="H155" s="38"/>
     </row>
-    <row r="156" spans="1:8" ht="15" customHeight="1">
+    <row r="156" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="37"/>
       <c r="B156" s="36"/>
       <c r="C156" s="37" t="s">
@@ -6357,7 +6436,7 @@
       <c r="G156" s="38"/>
       <c r="H156" s="38"/>
     </row>
-    <row r="157" spans="1:8" ht="15" customHeight="1">
+    <row r="157" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="37"/>
       <c r="B157" s="36"/>
       <c r="C157" s="37" t="s">
@@ -6378,7 +6457,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15" customHeight="1">
+    <row r="158" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="37"/>
       <c r="B158" s="36"/>
       <c r="C158" s="37" t="s">
@@ -6390,7 +6469,7 @@
       <c r="G158" s="38"/>
       <c r="H158" s="38"/>
     </row>
-    <row r="159" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1">
+    <row r="159" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="61" t="s">
         <v>200</v>
       </c>
@@ -6402,7 +6481,7 @@
       <c r="G159" s="61"/>
       <c r="H159" s="61"/>
     </row>
-    <row r="160" spans="1:8" ht="15" customHeight="1">
+    <row r="160" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="37"/>
       <c r="B160" s="38"/>
       <c r="C160" s="37" t="s">
@@ -6416,7 +6495,7 @@
       <c r="G160" s="38"/>
       <c r="H160" s="38"/>
     </row>
-    <row r="161" spans="1:8" ht="15" customHeight="1">
+    <row r="161" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="37"/>
       <c r="B161" s="38"/>
       <c r="C161" s="37" t="s">
@@ -6437,7 +6516,7 @@
         <v>238000</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15" customHeight="1">
+    <row r="162" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="37"/>
       <c r="B162" s="36">
         <v>0.29166666666666669</v>
@@ -6461,7 +6540,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15" customHeight="1">
+    <row r="163" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="37"/>
       <c r="B163" s="36">
         <v>0.3125</v>
@@ -6475,7 +6554,7 @@
       <c r="G163" s="38"/>
       <c r="H163" s="39"/>
     </row>
-    <row r="164" spans="1:8" ht="15" customHeight="1">
+    <row r="164" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="37"/>
       <c r="B164" s="36"/>
       <c r="C164" s="37" t="s">
@@ -6496,7 +6575,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15" customHeight="1">
+    <row r="165" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="37"/>
       <c r="B165" s="36">
         <v>0.375</v>
@@ -6521,7 +6600,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15" customHeight="1">
+    <row r="166" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="37"/>
       <c r="B166" s="57">
         <v>0.45833333333333331</v>
@@ -6546,7 +6625,7 @@
         <v>1020000</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15" customHeight="1">
+    <row r="167" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="37"/>
       <c r="B167" s="57">
         <v>0.5</v>
@@ -6571,7 +6650,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="24.75" customHeight="1">
+    <row r="168" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="37"/>
       <c r="B168" s="57">
         <v>0.5625</v>
@@ -6596,7 +6675,7 @@
         <v>494700</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="36" customHeight="1">
+    <row r="169" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="37"/>
       <c r="B169" s="38" t="s">
         <v>213</v>
@@ -6619,7 +6698,7 @@
         <v>12000000</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15" customHeight="1">
+    <row r="170" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="17"/>
       <c r="B170" s="17"/>
       <c r="C170" s="23"/>
@@ -6629,7 +6708,7 @@
       <c r="G170" s="17"/>
       <c r="H170" s="17"/>
     </row>
-    <row r="171" spans="1:8" ht="15" customHeight="1">
+    <row r="171" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B171" s="17"/>
       <c r="C171" s="23"/>
       <c r="D171" s="23"/>
@@ -6641,7 +6720,7 @@
         <v>74613700</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15" customHeight="1">
+    <row r="172" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B172" s="17"/>
       <c r="C172" s="23"/>
       <c r="D172" s="23"/>
@@ -6680,22 +6759,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L123"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="202" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="91" customWidth="1"/>
-    <col min="3" max="3" width="48.28515625" style="208" customWidth="1"/>
-    <col min="4" max="4" width="33.85546875" style="208" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="169" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" style="203" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="91" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="91" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" style="208" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" style="208" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="169" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.1640625" style="203" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="91" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="169" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" style="91" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" style="91" customWidth="1"/>
-    <col min="11" max="16384" width="10.85546875" style="91"/>
+    <col min="9" max="9" width="12.1640625" style="91" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" style="91" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="91"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="83" customFormat="1">
+    <row r="1" spans="1:10" s="83" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="210" t="s">
         <v>216</v>
       </c>
@@ -6727,12 +6806,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="252" customFormat="1">
-      <c r="A2" s="252" t="s">
+    <row r="2" spans="1:10" s="255" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="255" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="84"/>
       <c r="B3" s="85"/>
       <c r="C3" s="86" t="s">
@@ -6750,7 +6829,7 @@
       <c r="I3" s="90"/>
       <c r="J3" s="90"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="92"/>
       <c r="B4" s="85"/>
       <c r="C4" s="93" t="s">
@@ -6764,7 +6843,7 @@
       <c r="I4" s="85"/>
       <c r="J4" s="85"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="84"/>
       <c r="B5" s="85"/>
       <c r="C5" s="84" t="s">
@@ -6791,7 +6870,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="84"/>
       <c r="B6" s="85"/>
       <c r="C6" s="84" t="s">
@@ -6818,7 +6897,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="93"/>
       <c r="B7" s="85"/>
       <c r="C7" s="93" t="s">
@@ -6832,13 +6911,13 @@
       <c r="I7" s="96"/>
       <c r="J7" s="96"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="84"/>
       <c r="B8" s="85"/>
-      <c r="C8" s="253" t="s">
+      <c r="C8" s="256" t="s">
         <v>230</v>
       </c>
-      <c r="D8" s="253"/>
+      <c r="D8" s="256"/>
       <c r="E8" s="96">
         <v>1500</v>
       </c>
@@ -6848,7 +6927,7 @@
       <c r="I8" s="96"/>
       <c r="J8" s="96"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="84"/>
       <c r="B9" s="85"/>
       <c r="C9" s="84" t="s">
@@ -6864,7 +6943,7 @@
       <c r="I9" s="85"/>
       <c r="J9" s="85"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="84"/>
       <c r="B10" s="85"/>
       <c r="C10" s="84" t="s">
@@ -6880,11 +6959,11 @@
       <c r="I10" s="85"/>
       <c r="J10" s="85"/>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="253" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="256" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="253"/>
+      <c r="B11" s="256"/>
       <c r="C11" s="99">
         <v>27</v>
       </c>
@@ -6896,7 +6975,7 @@
       <c r="I11" s="85"/>
       <c r="J11" s="85"/>
     </row>
-    <row r="12" spans="1:10" s="14" customFormat="1">
+    <row r="12" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="72" t="str">
         <f>"Ngày 1: "&amp;C11&amp;"/11/2025 - Thứ 6 - XUẤT PHÁT TỪ HÀ NỘI + ODAIBA"</f>
         <v>Ngày 1: 27/11/2025 - Thứ 6 - XUẤT PHÁT TỪ HÀ NỘI + ODAIBA</v>
@@ -6911,7 +6990,7 @@
       <c r="I12" s="73"/>
       <c r="J12" s="73"/>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1">
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="114">
         <v>3.8194444444444441E-2</v>
       </c>
@@ -6943,7 +7022,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1">
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -6961,7 +7040,7 @@
       <c r="I14" s="96"/>
       <c r="J14" s="96"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="114">
         <v>0.40277777777777773</v>
       </c>
@@ -6990,7 +7069,7 @@
       <c r="I15" s="96"/>
       <c r="J15" s="96"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="114">
         <v>0.45833333333333331</v>
       </c>
@@ -7020,7 +7099,7 @@
       <c r="I16" s="96"/>
       <c r="J16" s="96"/>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1">
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="114">
         <v>0.45833333333333331</v>
       </c>
@@ -7049,7 +7128,7 @@
       </c>
       <c r="J17" s="96"/>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1">
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="114">
         <v>0.55208333333333337</v>
       </c>
@@ -7078,7 +7157,7 @@
       <c r="I18" s="96"/>
       <c r="J18" s="96"/>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1">
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="114">
         <v>0.58333333333333337</v>
       </c>
@@ -7107,7 +7186,7 @@
       <c r="I19" s="96"/>
       <c r="J19" s="96"/>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1">
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="114">
         <v>0.6875</v>
       </c>
@@ -7128,7 +7207,7 @@
       <c r="I20" s="96"/>
       <c r="J20" s="96"/>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1">
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="114">
         <v>0.75</v>
       </c>
@@ -7157,7 +7236,7 @@
       </c>
       <c r="J21" s="96"/>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1">
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="114">
         <v>0.875</v>
       </c>
@@ -7184,7 +7263,7 @@
       <c r="I22" s="96"/>
       <c r="J22" s="96"/>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1">
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="114">
         <v>0.91666666666666663</v>
       </c>
@@ -7212,7 +7291,7 @@
       <c r="I23" s="96"/>
       <c r="J23" s="96"/>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1">
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="114"/>
       <c r="B24" s="109"/>
       <c r="C24" s="107"/>
@@ -7224,7 +7303,7 @@
       <c r="I24" s="96"/>
       <c r="J24" s="96"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="114"/>
       <c r="B25" s="109"/>
       <c r="C25" s="235" t="s">
@@ -7238,7 +7317,7 @@
       <c r="I25" s="96"/>
       <c r="J25" s="96"/>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="114"/>
       <c r="B26" s="109"/>
       <c r="C26" s="107" t="s">
@@ -7252,7 +7331,7 @@
       <c r="I26" s="96"/>
       <c r="J26" s="96"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="114"/>
       <c r="B27" s="109"/>
       <c r="C27" s="107" t="s">
@@ -7266,7 +7345,7 @@
       <c r="I27" s="96"/>
       <c r="J27" s="96"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="114"/>
       <c r="B28" s="109"/>
       <c r="C28" s="107" t="s">
@@ -7280,7 +7359,7 @@
       <c r="I28" s="96"/>
       <c r="J28" s="96"/>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="114"/>
       <c r="B29" s="109"/>
       <c r="C29" s="107" t="s">
@@ -7294,7 +7373,7 @@
       <c r="I29" s="96"/>
       <c r="J29" s="96"/>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="114"/>
       <c r="B30" s="109"/>
       <c r="C30" s="107" t="s">
@@ -7308,7 +7387,7 @@
       <c r="I30" s="96"/>
       <c r="J30" s="96"/>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="114"/>
       <c r="B31" s="109"/>
       <c r="C31" s="107"/>
@@ -7320,7 +7399,7 @@
       <c r="I31" s="96"/>
       <c r="J31" s="96"/>
     </row>
-    <row r="32" spans="1:12" s="15" customFormat="1">
+    <row r="32" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="72" t="str">
         <f>"Ngày 2: "&amp;C11+1&amp;"/11/2025 - Thứ 7 - PHÚ SĨ 2 NGÀY 1 ĐÊM"</f>
         <v>Ngày 2: 28/11/2025 - Thứ 7 - PHÚ SĨ 2 NGÀY 1 ĐÊM</v>
@@ -7337,7 +7416,7 @@
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="1:12" s="223" customFormat="1">
+    <row r="33" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="217">
         <v>0.25</v>
       </c>
@@ -7366,7 +7445,7 @@
       </c>
       <c r="J33" s="222"/>
     </row>
-    <row r="34" spans="1:12" s="223" customFormat="1">
+    <row r="34" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="224"/>
       <c r="B34" s="222"/>
       <c r="C34" s="225" t="s">
@@ -7380,7 +7459,7 @@
       <c r="I34" s="222"/>
       <c r="J34" s="222"/>
     </row>
-    <row r="35" spans="1:12" s="223" customFormat="1">
+    <row r="35" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="224"/>
       <c r="B35" s="222"/>
       <c r="C35" s="225" t="s">
@@ -7394,7 +7473,7 @@
       <c r="I35" s="222"/>
       <c r="J35" s="222"/>
     </row>
-    <row r="36" spans="1:12" s="223" customFormat="1">
+    <row r="36" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="224"/>
       <c r="B36" s="222"/>
       <c r="C36" s="225" t="s">
@@ -7408,7 +7487,7 @@
       <c r="I36" s="222"/>
       <c r="J36" s="222"/>
     </row>
-    <row r="37" spans="1:12" s="223" customFormat="1">
+    <row r="37" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="224"/>
       <c r="B37" s="222"/>
       <c r="C37" s="225" t="s">
@@ -7422,7 +7501,7 @@
       <c r="I37" s="222"/>
       <c r="J37" s="222"/>
     </row>
-    <row r="38" spans="1:12" s="223" customFormat="1">
+    <row r="38" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="224"/>
       <c r="B38" s="222"/>
       <c r="C38" s="225" t="s">
@@ -7436,7 +7515,7 @@
       <c r="I38" s="222"/>
       <c r="J38" s="222"/>
     </row>
-    <row r="39" spans="1:12" s="223" customFormat="1">
+    <row r="39" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="217">
         <v>0.5</v>
       </c>
@@ -7462,7 +7541,7 @@
       <c r="I39" s="222"/>
       <c r="J39" s="222"/>
     </row>
-    <row r="40" spans="1:12" s="223" customFormat="1">
+    <row r="40" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="224"/>
       <c r="B40" s="222"/>
       <c r="C40" s="219" t="s">
@@ -7487,7 +7566,7 @@
       </c>
       <c r="J40" s="222"/>
     </row>
-    <row r="41" spans="1:12" s="223" customFormat="1">
+    <row r="41" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="224"/>
       <c r="B41" s="222"/>
       <c r="C41" s="219" t="s">
@@ -7501,7 +7580,7 @@
       <c r="I41" s="222"/>
       <c r="J41" s="222"/>
     </row>
-    <row r="42" spans="1:12" s="223" customFormat="1">
+    <row r="42" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="217">
         <v>0.75</v>
       </c>
@@ -7530,7 +7609,7 @@
       </c>
       <c r="J42" s="222"/>
     </row>
-    <row r="43" spans="1:12" s="223" customFormat="1">
+    <row r="43" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="217">
         <v>0.91666666666666663</v>
       </c>
@@ -7558,7 +7637,7 @@
       <c r="I43" s="222"/>
       <c r="J43" s="222"/>
     </row>
-    <row r="44" spans="1:12" s="223" customFormat="1">
+    <row r="44" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="217"/>
       <c r="B44" s="218"/>
       <c r="C44" s="219"/>
@@ -7570,7 +7649,7 @@
       <c r="I44" s="222"/>
       <c r="J44" s="222"/>
     </row>
-    <row r="45" spans="1:12" s="15" customFormat="1">
+    <row r="45" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="72" t="str">
         <f>"Ngày 3: "&amp;C11+2&amp;"/11/2025 - PHÚ SĨ HIDDEN PLACES"</f>
         <v>Ngày 3: 29/11/2025 - PHÚ SĨ HIDDEN PLACES</v>
@@ -7587,7 +7666,7 @@
       <c r="K45" s="14"/>
       <c r="L45" s="14"/>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -7614,7 +7693,7 @@
       <c r="K46" s="130"/>
       <c r="L46" s="130"/>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="114"/>
       <c r="B47" s="85"/>
       <c r="C47" s="107" t="s">
@@ -7639,7 +7718,7 @@
       <c r="I47" s="96"/>
       <c r="J47" s="96"/>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="114"/>
       <c r="B48" s="85"/>
       <c r="C48" s="107" t="s">
@@ -7657,7 +7736,7 @@
       <c r="I48" s="96"/>
       <c r="J48" s="96"/>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="114"/>
       <c r="B49" s="85"/>
       <c r="C49" s="107" t="s">
@@ -7675,7 +7754,7 @@
       <c r="I49" s="96"/>
       <c r="J49" s="96"/>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="114"/>
       <c r="B50" s="85"/>
       <c r="C50" s="107" t="s">
@@ -7693,7 +7772,7 @@
       <c r="I50" s="96"/>
       <c r="J50" s="96"/>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="114"/>
       <c r="B51" s="85"/>
       <c r="C51" s="84"/>
@@ -7705,7 +7784,7 @@
       <c r="I51" s="96"/>
       <c r="J51" s="96"/>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="114"/>
       <c r="B52" s="85"/>
       <c r="C52" s="107" t="s">
@@ -7719,7 +7798,7 @@
       <c r="I52" s="96"/>
       <c r="J52" s="96"/>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="114"/>
       <c r="B53" s="85"/>
       <c r="C53" s="107" t="s">
@@ -7735,7 +7814,7 @@
       <c r="I53" s="96"/>
       <c r="J53" s="96"/>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="114"/>
       <c r="B54" s="85"/>
       <c r="C54" s="107" t="s">
@@ -7751,7 +7830,7 @@
       <c r="I54" s="96"/>
       <c r="J54" s="96"/>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="114"/>
       <c r="B55" s="85"/>
       <c r="C55" s="107" t="s">
@@ -7769,7 +7848,7 @@
       <c r="I55" s="96"/>
       <c r="J55" s="96"/>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" s="114"/>
       <c r="B56" s="85"/>
       <c r="C56" s="84"/>
@@ -7781,7 +7860,7 @@
       <c r="I56" s="96"/>
       <c r="J56" s="96"/>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="114">
         <v>0.5</v>
       </c>
@@ -7807,7 +7886,7 @@
       <c r="I57" s="96"/>
       <c r="J57" s="96"/>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="114">
         <v>0.625</v>
       </c>
@@ -7834,7 +7913,7 @@
       <c r="I58" s="96"/>
       <c r="J58" s="96"/>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="114">
         <v>0.79166666666666663</v>
       </c>
@@ -7861,7 +7940,7 @@
       <c r="I59" s="96"/>
       <c r="J59" s="96"/>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="114"/>
       <c r="B60" s="85"/>
       <c r="C60" s="230" t="s">
@@ -7887,7 +7966,7 @@
       </c>
       <c r="J60" s="96"/>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="114"/>
       <c r="B61" s="85"/>
       <c r="C61" s="84" t="s">
@@ -7913,7 +7992,7 @@
       <c r="I61" s="96"/>
       <c r="J61" s="96"/>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" s="114"/>
       <c r="B62" s="85"/>
       <c r="C62" s="84"/>
@@ -7925,7 +8004,7 @@
       <c r="I62" s="96"/>
       <c r="J62" s="96"/>
     </row>
-    <row r="63" spans="1:10" s="15" customFormat="1">
+    <row r="63" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="72" t="str">
         <f>"Ngày 4: "&amp;C11+3&amp;"/11/2025 - NGHỈ SÁNG, ĐI NAGANO, HAKUBA"</f>
         <v>Ngày 4: 30/11/2025 - NGHỈ SÁNG, ĐI NAGANO, HAKUBA</v>
@@ -7940,7 +8019,7 @@
       <c r="I63" s="73"/>
       <c r="J63" s="73"/>
     </row>
-    <row r="64" spans="1:10" s="223" customFormat="1">
+    <row r="64" spans="1:10" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="217">
         <v>0.33333333333333331</v>
       </c>
@@ -7971,7 +8050,7 @@
       </c>
       <c r="J64" s="222"/>
     </row>
-    <row r="65" spans="1:12" s="223" customFormat="1">
+    <row r="65" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="224"/>
       <c r="B65" s="222"/>
       <c r="C65" s="219" t="s">
@@ -7995,7 +8074,7 @@
       <c r="I65" s="222"/>
       <c r="J65" s="222"/>
     </row>
-    <row r="66" spans="1:12" s="223" customFormat="1">
+    <row r="66" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="224"/>
       <c r="B66" s="222"/>
       <c r="C66" s="219" t="s">
@@ -8020,7 +8099,7 @@
       </c>
       <c r="J66" s="222"/>
     </row>
-    <row r="67" spans="1:12" s="223" customFormat="1">
+    <row r="67" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="217">
         <v>0.58333333333333337</v>
       </c>
@@ -8047,7 +8126,7 @@
       <c r="I67" s="222"/>
       <c r="J67" s="222"/>
     </row>
-    <row r="68" spans="1:12" s="223" customFormat="1">
+    <row r="68" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="224"/>
       <c r="B68" s="222"/>
       <c r="C68" s="219" t="s">
@@ -8070,7 +8149,7 @@
       <c r="I68" s="222"/>
       <c r="J68" s="222"/>
     </row>
-    <row r="69" spans="1:12" s="223" customFormat="1">
+    <row r="69" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="224"/>
       <c r="B69" s="222"/>
       <c r="C69" s="219"/>
@@ -8091,7 +8170,7 @@
       <c r="I69" s="222"/>
       <c r="J69" s="222"/>
     </row>
-    <row r="70" spans="1:12" s="223" customFormat="1">
+    <row r="70" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="226"/>
       <c r="B70" s="218"/>
       <c r="C70" s="219" t="s">
@@ -8114,7 +8193,7 @@
       <c r="I70" s="222"/>
       <c r="J70" s="222"/>
     </row>
-    <row r="71" spans="1:12" s="223" customFormat="1">
+    <row r="71" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="226">
         <v>0.83333333333333337</v>
       </c>
@@ -8140,7 +8219,7 @@
       <c r="I71" s="222"/>
       <c r="J71" s="222"/>
     </row>
-    <row r="72" spans="1:12" s="223" customFormat="1">
+    <row r="72" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="226"/>
       <c r="B72" s="218"/>
       <c r="C72" s="219" t="s">
@@ -8166,7 +8245,7 @@
       <c r="I72" s="222"/>
       <c r="J72" s="222"/>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="114"/>
       <c r="B73" s="109"/>
       <c r="C73" s="84"/>
@@ -8178,7 +8257,7 @@
       <c r="I73" s="85"/>
       <c r="J73" s="85"/>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="72" t="str">
         <f>"Ngày 5: "&amp;"1/12/2025 -  HAKUBA SKI RESORT"</f>
         <v>Ngày 5: 1/12/2025 -  HAKUBA SKI RESORT</v>
@@ -8195,7 +8274,7 @@
       <c r="K74" s="15"/>
       <c r="L74" s="15"/>
     </row>
-    <row r="75" spans="1:12" s="223" customFormat="1">
+    <row r="75" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="217">
         <v>0.33333333333333331</v>
       </c>
@@ -8222,7 +8301,7 @@
       <c r="I75" s="222"/>
       <c r="J75" s="222"/>
     </row>
-    <row r="76" spans="1:12" s="223" customFormat="1">
+    <row r="76" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="224"/>
       <c r="B76" s="222"/>
       <c r="C76" s="219" t="s">
@@ -8247,7 +8326,7 @@
       <c r="I76" s="222"/>
       <c r="J76" s="222"/>
     </row>
-    <row r="77" spans="1:12" s="223" customFormat="1">
+    <row r="77" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="224"/>
       <c r="B77" s="222"/>
       <c r="C77" s="225" t="s">
@@ -8270,7 +8349,7 @@
       <c r="I77" s="222"/>
       <c r="J77" s="222"/>
     </row>
-    <row r="78" spans="1:12" s="223" customFormat="1">
+    <row r="78" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="224"/>
       <c r="B78" s="222"/>
       <c r="C78" s="225" t="s">
@@ -8293,7 +8372,7 @@
       <c r="I78" s="222"/>
       <c r="J78" s="222"/>
     </row>
-    <row r="79" spans="1:12" s="223" customFormat="1">
+    <row r="79" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="224"/>
       <c r="B79" s="222"/>
       <c r="C79" s="225" t="s">
@@ -8316,7 +8395,7 @@
       <c r="I79" s="222"/>
       <c r="J79" s="222"/>
     </row>
-    <row r="80" spans="1:12" s="223" customFormat="1">
+    <row r="80" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="224"/>
       <c r="B80" s="222"/>
       <c r="C80" s="219" t="s">
@@ -8340,7 +8419,7 @@
       <c r="I80" s="222"/>
       <c r="J80" s="222"/>
     </row>
-    <row r="81" spans="1:12" s="223" customFormat="1">
+    <row r="81" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="224"/>
       <c r="B81" s="222"/>
       <c r="C81" s="219" t="s">
@@ -8363,7 +8442,7 @@
       <c r="I81" s="222"/>
       <c r="J81" s="222"/>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="84"/>
       <c r="B82" s="85"/>
       <c r="C82" s="84" t="s">
@@ -8388,7 +8467,7 @@
       </c>
       <c r="J82" s="85"/>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="84"/>
       <c r="B83" s="85"/>
       <c r="C83" s="84" t="s">
@@ -8414,7 +8493,7 @@
       <c r="I83" s="85"/>
       <c r="J83" s="85"/>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="84"/>
       <c r="B84" s="85"/>
       <c r="C84" s="84"/>
@@ -8426,7 +8505,7 @@
       <c r="I84" s="85"/>
       <c r="J84" s="85"/>
     </row>
-    <row r="85" spans="1:12" s="15" customFormat="1">
+    <row r="85" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="186" t="str">
         <f>"Ngày 6: "&amp;"2/12/2025 - HAKUBA _ KYOTO"</f>
         <v>Ngày 6: 2/12/2025 - HAKUBA _ KYOTO</v>
@@ -8441,7 +8520,7 @@
       <c r="I85" s="187"/>
       <c r="J85" s="187"/>
     </row>
-    <row r="86" spans="1:12" ht="31.5">
+    <row r="86" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="157"/>
       <c r="B86" s="174"/>
       <c r="C86" s="164" t="s">
@@ -8466,7 +8545,7 @@
       <c r="I86" s="96"/>
       <c r="J86" s="96"/>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="84"/>
       <c r="B87" s="109"/>
       <c r="C87" s="84" t="s">
@@ -8489,7 +8568,7 @@
       <c r="I87" s="96"/>
       <c r="J87" s="96"/>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="84"/>
       <c r="B88" s="109"/>
       <c r="C88" s="84" t="s">
@@ -8513,7 +8592,7 @@
       <c r="I88" s="96"/>
       <c r="J88" s="96"/>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="84"/>
       <c r="B89" s="109"/>
       <c r="C89" s="84" t="s">
@@ -8538,7 +8617,7 @@
       </c>
       <c r="J89" s="96"/>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="84"/>
       <c r="B90" s="109"/>
       <c r="C90" s="84" t="s">
@@ -8562,7 +8641,7 @@
       <c r="I90" s="96"/>
       <c r="J90" s="96"/>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="84"/>
       <c r="B91" s="109"/>
       <c r="C91" s="84" t="s">
@@ -8588,7 +8667,7 @@
       </c>
       <c r="J91" s="96"/>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="84"/>
       <c r="B92" s="109"/>
       <c r="C92" s="84" t="s">
@@ -8614,7 +8693,7 @@
       <c r="I92" s="96"/>
       <c r="J92" s="96"/>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="84"/>
       <c r="B93" s="109"/>
       <c r="C93" s="84"/>
@@ -8626,7 +8705,7 @@
       <c r="I93" s="96"/>
       <c r="J93" s="96"/>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94" s="194" t="str">
         <f>"Ngày 7: "&amp;"3/12/2025 - ĐI NGẮM LÁ ĐỎ Ở ARMANASHI"</f>
         <v>Ngày 7: 3/12/2025 - ĐI NGẮM LÁ ĐỎ Ở ARMANASHI</v>
@@ -8643,7 +8722,7 @@
       <c r="K94" s="15"/>
       <c r="L94" s="15"/>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="84"/>
       <c r="B95" s="228"/>
       <c r="C95" s="229" t="s">
@@ -8666,7 +8745,7 @@
       <c r="I95" s="85"/>
       <c r="J95" s="85"/>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="84"/>
       <c r="B96" s="228"/>
       <c r="C96" s="232" t="s">
@@ -8689,7 +8768,7 @@
       <c r="I96" s="85"/>
       <c r="J96" s="85"/>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="84"/>
       <c r="B97" s="228"/>
       <c r="C97" s="232" t="s">
@@ -8703,7 +8782,7 @@
       <c r="I97" s="85"/>
       <c r="J97" s="85"/>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="84"/>
       <c r="B98" s="228"/>
       <c r="C98" s="232" t="s">
@@ -8726,7 +8805,7 @@
       <c r="I98" s="85"/>
       <c r="J98" s="85"/>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="84"/>
       <c r="B99" s="228"/>
       <c r="C99" s="229" t="s">
@@ -8749,7 +8828,7 @@
       <c r="I99" s="85"/>
       <c r="J99" s="85"/>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="84"/>
       <c r="B100" s="109"/>
       <c r="C100" s="84" t="s">
@@ -8772,7 +8851,7 @@
       <c r="I100" s="96"/>
       <c r="J100" s="96"/>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="84"/>
       <c r="B101" s="109"/>
       <c r="C101" s="84" t="s">
@@ -8797,7 +8876,7 @@
       </c>
       <c r="J101" s="96"/>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" s="84"/>
       <c r="B102" s="228"/>
       <c r="C102" s="229"/>
@@ -8809,7 +8888,7 @@
       <c r="I102" s="85"/>
       <c r="J102" s="85"/>
     </row>
-    <row r="103" spans="1:10" s="15" customFormat="1">
+    <row r="103" spans="1:10" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="197" t="str">
         <f>"Ngày 8: "&amp;"4/12/2025 - ĐI CHÙA KATSUOJI - CẦU NGUYỆN"</f>
         <v>Ngày 8: 4/12/2025 - ĐI CHÙA KATSUOJI - CẦU NGUYỆN</v>
@@ -8826,7 +8905,7 @@
       <c r="I103" s="195"/>
       <c r="J103" s="195"/>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="84"/>
       <c r="B104" s="109"/>
       <c r="C104" s="84" t="s">
@@ -8849,7 +8928,7 @@
       <c r="I104" s="96"/>
       <c r="J104" s="96"/>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="84"/>
       <c r="B105" s="109"/>
       <c r="C105" s="84" t="s">
@@ -8874,7 +8953,7 @@
       </c>
       <c r="J105" s="96"/>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="84"/>
       <c r="B106" s="109"/>
       <c r="C106" s="84" t="s">
@@ -8888,7 +8967,7 @@
       <c r="I106" s="96"/>
       <c r="J106" s="96"/>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="84"/>
       <c r="B107" s="109"/>
       <c r="C107" s="84" t="s">
@@ -8911,7 +8990,7 @@
       <c r="I107" s="96"/>
       <c r="J107" s="96"/>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A108" s="84"/>
       <c r="B108" s="109"/>
       <c r="C108" s="84"/>
@@ -8923,7 +9002,7 @@
       <c r="I108" s="96"/>
       <c r="J108" s="96"/>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A109" s="84"/>
       <c r="B109" s="109"/>
       <c r="C109" s="84"/>
@@ -8935,7 +9014,7 @@
       <c r="I109" s="96"/>
       <c r="J109" s="96"/>
     </row>
-    <row r="110" spans="1:10" s="15" customFormat="1">
+    <row r="110" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="197" t="str">
         <f>"Ngày 9: "&amp;"5/12/2025 - ĐI VỀ HÀ NỘI"</f>
         <v>Ngày 9: 5/12/2025 - ĐI VỀ HÀ NỘI</v>
@@ -8950,7 +9029,7 @@
       <c r="I110" s="195"/>
       <c r="J110" s="195"/>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="84"/>
       <c r="B111" s="85"/>
       <c r="C111" s="84" t="s">
@@ -8966,7 +9045,7 @@
       <c r="I111" s="85"/>
       <c r="J111" s="85"/>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="84"/>
       <c r="B112" s="85"/>
       <c r="C112" s="84" t="s">
@@ -8990,7 +9069,7 @@
       <c r="I112" s="85"/>
       <c r="J112" s="85"/>
     </row>
-    <row r="113" spans="1:10" s="106" customFormat="1">
+    <row r="113" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="102"/>
       <c r="B113" s="176">
         <v>0.5625</v>
@@ -9017,7 +9096,7 @@
       <c r="I113" s="103"/>
       <c r="J113" s="103"/>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A114" s="114"/>
       <c r="B114" s="109"/>
       <c r="C114" s="84"/>
@@ -9029,7 +9108,7 @@
       <c r="I114" s="200"/>
       <c r="J114" s="200"/>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A115" s="114"/>
       <c r="B115" s="109"/>
       <c r="C115" s="84"/>
@@ -9041,7 +9120,7 @@
       <c r="I115" s="200"/>
       <c r="J115" s="200"/>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="114"/>
       <c r="B116" s="109"/>
       <c r="C116" s="84"/>
@@ -9053,7 +9132,7 @@
       <c r="I116" s="200"/>
       <c r="J116" s="200"/>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A117" s="199"/>
       <c r="B117" s="199"/>
       <c r="C117" s="84"/>
@@ -9065,7 +9144,7 @@
       <c r="I117" s="199"/>
       <c r="J117" s="199"/>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B118" s="199"/>
       <c r="C118" s="84"/>
       <c r="D118" s="84"/>
@@ -9082,7 +9161,7 @@
       </c>
       <c r="J118" s="204"/>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B119" s="199"/>
       <c r="C119" s="84"/>
       <c r="D119" s="84"/>
@@ -9101,7 +9180,7 @@
       </c>
       <c r="J119" s="207"/>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E120" s="169" t="s">
         <v>319</v>
       </c>
@@ -9114,7 +9193,7 @@
         <v>827777.77777777775</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E121" s="169" t="s">
         <v>320</v>
       </c>
@@ -9123,7 +9202,7 @@
         <v>15755180</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E122" s="233" t="s">
         <v>321</v>
       </c>
@@ -9132,7 +9211,7 @@
         <v>7438180</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E123" s="169" t="s">
         <v>322</v>
       </c>
@@ -9171,22 +9250,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L166"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="202" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="91" customWidth="1"/>
-    <col min="3" max="3" width="48.28515625" style="208" customWidth="1"/>
-    <col min="4" max="4" width="33.85546875" style="208" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="169" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.140625" style="203" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="91" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="91" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" style="208" customWidth="1"/>
+    <col min="4" max="4" width="33.83203125" style="208" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" style="169" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.1640625" style="203" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="91" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="169" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" style="91" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" style="91" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1640625" style="91" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" style="91" hidden="1" customWidth="1"/>
     <col min="11" max="16384" width="0" style="91" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="83" customFormat="1">
+    <row r="1" spans="1:12" s="83" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="77" t="s">
         <v>216</v>
       </c>
@@ -9218,12 +9297,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="252" customFormat="1">
-      <c r="A2" s="252" t="s">
+    <row r="2" spans="1:12" s="255" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="255" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="84"/>
       <c r="B3" s="85"/>
       <c r="C3" s="86" t="s">
@@ -9241,7 +9320,7 @@
       <c r="I3" s="90"/>
       <c r="J3" s="90"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="92"/>
       <c r="B4" s="85"/>
       <c r="C4" s="93" t="s">
@@ -9255,7 +9334,7 @@
       <c r="I4" s="85"/>
       <c r="J4" s="85"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="84"/>
       <c r="B5" s="85"/>
       <c r="C5" s="84" t="s">
@@ -9285,7 +9364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="84"/>
       <c r="B6" s="85"/>
       <c r="C6" s="84" t="s">
@@ -9312,7 +9391,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="84"/>
       <c r="B7" s="85"/>
       <c r="C7" s="84" t="s">
@@ -9340,7 +9419,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="84"/>
       <c r="B8" s="85"/>
       <c r="C8" s="84" t="s">
@@ -9363,7 +9442,7 @@
       <c r="I8" s="96"/>
       <c r="J8" s="96"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="93"/>
       <c r="B9" s="85"/>
       <c r="C9" s="93" t="s">
@@ -9377,13 +9456,13 @@
       <c r="I9" s="96"/>
       <c r="J9" s="96"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="84"/>
       <c r="B10" s="85"/>
-      <c r="C10" s="253" t="s">
+      <c r="C10" s="256" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="253"/>
+      <c r="D10" s="256"/>
       <c r="E10" s="96">
         <v>3000</v>
       </c>
@@ -9393,7 +9472,7 @@
       <c r="I10" s="96"/>
       <c r="J10" s="96"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="84"/>
       <c r="B11" s="85"/>
       <c r="C11" s="84" t="s">
@@ -9409,7 +9488,7 @@
       <c r="I11" s="85"/>
       <c r="J11" s="85"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="84"/>
       <c r="B12" s="85"/>
       <c r="C12" s="84" t="s">
@@ -9425,11 +9504,11 @@
       <c r="I12" s="85"/>
       <c r="J12" s="85"/>
     </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="253" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="256" t="s">
         <v>233</v>
       </c>
-      <c r="B13" s="253"/>
+      <c r="B13" s="256"/>
       <c r="C13" s="99">
         <v>13</v>
       </c>
@@ -9441,7 +9520,7 @@
       <c r="I13" s="85"/>
       <c r="J13" s="85"/>
     </row>
-    <row r="14" spans="1:12" s="14" customFormat="1">
+    <row r="14" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="72" t="str">
         <f>"Ngày 1: "&amp;C13&amp;"/6/2025 - Thứ 6 - XUẤT PHÁT TỪ HÀ NỘI"</f>
         <v>Ngày 1: 13/6/2025 - Thứ 6 - XUẤT PHÁT TỪ HÀ NỘI</v>
@@ -9456,7 +9535,7 @@
       <c r="I14" s="73"/>
       <c r="J14" s="73"/>
     </row>
-    <row r="15" spans="1:12" s="106" customFormat="1">
+    <row r="15" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="100"/>
       <c r="B15" s="101">
         <v>0.24652777777777779</v>
@@ -9472,7 +9551,7 @@
       <c r="I15" s="105"/>
       <c r="J15" s="105"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="84"/>
       <c r="B16" s="85"/>
       <c r="C16" s="107" t="s">
@@ -9495,7 +9574,7 @@
       <c r="I16" s="96"/>
       <c r="J16" s="96"/>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="84"/>
       <c r="B17" s="85"/>
       <c r="C17" s="107" t="s">
@@ -9523,7 +9602,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="84"/>
       <c r="B18" s="85"/>
       <c r="C18" s="107" t="s">
@@ -9537,7 +9616,7 @@
       <c r="I18" s="85"/>
       <c r="J18" s="85"/>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="84"/>
       <c r="B19" s="109">
         <v>0.64583333333333337</v>
@@ -9555,7 +9634,7 @@
       <c r="I19" s="85"/>
       <c r="J19" s="85"/>
     </row>
-    <row r="20" spans="1:12" s="106" customFormat="1">
+    <row r="20" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="100">
         <v>0.64583333333333337</v>
       </c>
@@ -9587,7 +9666,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="84"/>
       <c r="B21" s="85"/>
       <c r="C21" s="107" t="s">
@@ -9601,7 +9680,7 @@
       <c r="I21" s="85"/>
       <c r="J21" s="85"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="84"/>
       <c r="B22" s="85"/>
       <c r="C22" s="84" t="s">
@@ -9615,7 +9694,7 @@
       <c r="I22" s="85"/>
       <c r="J22" s="85"/>
     </row>
-    <row r="23" spans="1:12" ht="23.25" customHeight="1">
+    <row r="23" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="84"/>
       <c r="B23" s="85"/>
       <c r="C23" s="107" t="s">
@@ -9640,7 +9719,7 @@
       <c r="I23" s="96"/>
       <c r="J23" s="96"/>
     </row>
-    <row r="24" spans="1:12" s="106" customFormat="1">
+    <row r="24" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="100">
         <v>0.72916666666666663</v>
       </c>
@@ -9658,7 +9737,7 @@
       <c r="I24" s="103"/>
       <c r="J24" s="103"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="114"/>
       <c r="B25" s="109"/>
       <c r="C25" s="107" t="s">
@@ -9683,7 +9762,7 @@
       <c r="I25" s="96"/>
       <c r="J25" s="96"/>
     </row>
-    <row r="26" spans="1:12" ht="47.25">
+    <row r="26" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A26" s="84"/>
       <c r="B26" s="109"/>
       <c r="C26" s="107" t="s">
@@ -9709,7 +9788,7 @@
       <c r="I26" s="96"/>
       <c r="J26" s="96"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="84"/>
       <c r="B27" s="109"/>
       <c r="C27" s="107" t="s">
@@ -9723,7 +9802,7 @@
       <c r="I27" s="96"/>
       <c r="J27" s="96"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="84"/>
       <c r="B28" s="85"/>
       <c r="C28" s="107" t="s">
@@ -9737,7 +9816,7 @@
       <c r="I28" s="85"/>
       <c r="J28" s="85"/>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="84"/>
       <c r="B29" s="85"/>
       <c r="C29" s="107" t="s">
@@ -9751,7 +9830,7 @@
       <c r="I29" s="85"/>
       <c r="J29" s="85"/>
     </row>
-    <row r="30" spans="1:12" s="106" customFormat="1">
+    <row r="30" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="100">
         <v>0.875</v>
       </c>
@@ -9781,7 +9860,7 @@
       </c>
       <c r="J30" s="103"/>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="118">
         <v>0.91666666666666663</v>
       </c>
@@ -9806,7 +9885,7 @@
       <c r="I31" s="96"/>
       <c r="J31" s="96"/>
     </row>
-    <row r="32" spans="1:12" s="15" customFormat="1">
+    <row r="32" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="72" t="str">
         <f>"Ngày 2: "&amp;C13+1&amp;"/6/2025 - Thứ 7 - SENSOJI SHIBUYA - FUJI MUSEUM - SHIBUYA"</f>
         <v>Ngày 2: 14/6/2025 - Thứ 7 - SENSOJI SHIBUYA - FUJI MUSEUM - SHIBUYA</v>
@@ -9823,7 +9902,7 @@
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="1:12" s="106" customFormat="1">
+    <row r="33" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="92"/>
       <c r="B33" s="101">
         <v>0.27083333333333331</v>
@@ -9850,13 +9929,13 @@
       <c r="K33" s="126"/>
       <c r="L33" s="126"/>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="114"/>
       <c r="B34" s="127"/>
-      <c r="C34" s="255" t="s">
+      <c r="C34" s="258" t="s">
         <v>338</v>
       </c>
-      <c r="D34" s="255"/>
+      <c r="D34" s="258"/>
       <c r="E34" s="128"/>
       <c r="F34" s="129"/>
       <c r="G34" s="127"/>
@@ -9866,13 +9945,13 @@
       <c r="K34" s="130"/>
       <c r="L34" s="130"/>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="114"/>
       <c r="B35" s="127"/>
-      <c r="C35" s="256" t="s">
+      <c r="C35" s="259" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="256"/>
+      <c r="D35" s="259"/>
       <c r="E35" s="128"/>
       <c r="F35" s="129"/>
       <c r="G35" s="127"/>
@@ -9882,17 +9961,17 @@
       <c r="K35" s="130"/>
       <c r="L35" s="130"/>
     </row>
-    <row r="36" spans="1:12" s="106" customFormat="1">
+    <row r="36" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="100">
         <v>0.27083333333333331</v>
       </c>
       <c r="B36" s="101">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C36" s="258" t="s">
+      <c r="C36" s="261" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="258"/>
+      <c r="D36" s="261"/>
       <c r="E36" s="132"/>
       <c r="F36" s="133"/>
       <c r="G36" s="134"/>
@@ -9902,7 +9981,7 @@
       <c r="K36" s="126"/>
       <c r="L36" s="126"/>
     </row>
-    <row r="37" spans="1:12" ht="31.5">
+    <row r="37" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="114"/>
       <c r="B37" s="85"/>
       <c r="C37" s="135" t="s">
@@ -9930,7 +10009,7 @@
       <c r="K37" s="130"/>
       <c r="L37" s="130"/>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -9959,7 +10038,7 @@
       <c r="K38" s="130"/>
       <c r="L38" s="130"/>
     </row>
-    <row r="39" spans="1:12" s="144" customFormat="1" ht="63">
+    <row r="39" spans="1:12" s="144" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A39" s="137">
         <v>0.375</v>
       </c>
@@ -9991,7 +10070,7 @@
       <c r="K39" s="143"/>
       <c r="L39" s="143"/>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="114"/>
       <c r="B40" s="109"/>
       <c r="C40" s="131" t="s">
@@ -10009,7 +10088,7 @@
       <c r="K40" s="130"/>
       <c r="L40" s="130"/>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="114"/>
       <c r="B41" s="85"/>
       <c r="C41" s="131" t="s">
@@ -10025,7 +10104,7 @@
       <c r="K41" s="130"/>
       <c r="L41" s="130"/>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="114"/>
       <c r="B42" s="85"/>
       <c r="C42" s="131" t="s">
@@ -10041,7 +10120,7 @@
       <c r="K42" s="130"/>
       <c r="L42" s="130"/>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="114"/>
       <c r="B43" s="85"/>
       <c r="C43" s="131" t="s">
@@ -10057,7 +10136,7 @@
       <c r="K43" s="130"/>
       <c r="L43" s="130"/>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="114"/>
       <c r="B44" s="85"/>
       <c r="C44" s="131" t="s">
@@ -10073,7 +10152,7 @@
       <c r="K44" s="130"/>
       <c r="L44" s="130"/>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="114"/>
       <c r="B45" s="85"/>
       <c r="C45" s="131" t="s">
@@ -10089,7 +10168,7 @@
       <c r="K45" s="130"/>
       <c r="L45" s="130"/>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="114"/>
       <c r="B46" s="85"/>
       <c r="C46" s="131" t="s">
@@ -10114,7 +10193,7 @@
       <c r="K46" s="130"/>
       <c r="L46" s="130"/>
     </row>
-    <row r="47" spans="1:12" s="106" customFormat="1">
+    <row r="47" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="100">
         <v>0.54166666666666663</v>
       </c>
@@ -10136,13 +10215,13 @@
       <c r="K47" s="126"/>
       <c r="L47" s="126"/>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="114"/>
       <c r="B48" s="109"/>
-      <c r="C48" s="257" t="s">
+      <c r="C48" s="260" t="s">
         <v>352</v>
       </c>
-      <c r="D48" s="257"/>
+      <c r="D48" s="260"/>
       <c r="E48" s="96">
         <f>370+220</f>
         <v>590</v>
@@ -10162,7 +10241,7 @@
       <c r="K48" s="130"/>
       <c r="L48" s="130"/>
     </row>
-    <row r="49" spans="1:12" ht="42.95" customHeight="1">
+    <row r="49" spans="1:12" ht="43" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="114"/>
       <c r="B49" s="109"/>
       <c r="C49" s="107" t="s">
@@ -10189,7 +10268,7 @@
       <c r="K49" s="130"/>
       <c r="L49" s="130"/>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="114"/>
       <c r="B50" s="109"/>
       <c r="C50" s="107" t="s">
@@ -10217,7 +10296,7 @@
       <c r="K50" s="130"/>
       <c r="L50" s="130"/>
     </row>
-    <row r="51" spans="1:12" s="106" customFormat="1">
+    <row r="51" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="100">
         <v>0.70833333333333337</v>
       </c>
@@ -10247,7 +10326,7 @@
       <c r="K51" s="126"/>
       <c r="L51" s="126"/>
     </row>
-    <row r="52" spans="1:12" ht="48.95" customHeight="1">
+    <row r="52" spans="1:12" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="84"/>
       <c r="B52" s="85"/>
       <c r="C52" s="107" t="s">
@@ -10273,7 +10352,7 @@
       <c r="I52" s="96"/>
       <c r="J52" s="96"/>
     </row>
-    <row r="53" spans="1:12" ht="12.75" customHeight="1">
+    <row r="53" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="114">
         <v>0.86111111111111116</v>
       </c>
@@ -10300,7 +10379,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="100">
         <v>0.91666666666666663</v>
       </c>
@@ -10325,7 +10404,7 @@
       <c r="I54" s="96"/>
       <c r="J54" s="96"/>
     </row>
-    <row r="55" spans="1:12" s="15" customFormat="1">
+    <row r="55" spans="1:12" s="15" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A55" s="72" t="str">
         <f>"Ngày 3: "&amp;C13+2&amp;"/6/2025 - Chủ Nhật - Tour Phú Sĩ - Mua Tour"</f>
         <v>Ngày 3: 15/6/2025 - Chủ Nhật - Tour Phú Sĩ - Mua Tour</v>
@@ -10344,7 +10423,7 @@
       <c r="K55" s="14"/>
       <c r="L55" s="14"/>
     </row>
-    <row r="56" spans="1:12" s="106" customFormat="1">
+    <row r="56" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="102"/>
       <c r="B56" s="105"/>
       <c r="C56" s="102" t="s">
@@ -10368,7 +10447,7 @@
       <c r="I56" s="103"/>
       <c r="J56" s="103"/>
     </row>
-    <row r="57" spans="1:12" s="156" customFormat="1">
+    <row r="57" spans="1:12" s="156" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="121"/>
       <c r="B57" s="124"/>
       <c r="C57" s="121" t="s">
@@ -10391,7 +10470,7 @@
       <c r="I57" s="122"/>
       <c r="J57" s="122"/>
     </row>
-    <row r="58" spans="1:12" ht="47.25">
+    <row r="58" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A58" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -10423,7 +10502,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="114">
         <v>0.4375</v>
       </c>
@@ -10439,7 +10518,7 @@
       <c r="I59" s="85"/>
       <c r="J59" s="85"/>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="114">
         <v>0.48958333333333331</v>
       </c>
@@ -10455,7 +10534,7 @@
       <c r="I60" s="85"/>
       <c r="J60" s="85"/>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="114">
         <v>0.52083333333333337</v>
       </c>
@@ -10471,7 +10550,7 @@
       <c r="I61" s="85"/>
       <c r="J61" s="85"/>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="114">
         <v>0.60416666666666663</v>
       </c>
@@ -10487,7 +10566,7 @@
       <c r="I62" s="85"/>
       <c r="J62" s="85"/>
     </row>
-    <row r="63" spans="1:12" ht="78.75">
+    <row r="63" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A63" s="114">
         <v>0.63194444444444442</v>
       </c>
@@ -10505,7 +10584,7 @@
       <c r="I63" s="85"/>
       <c r="J63" s="85"/>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="114">
         <v>0.63888888888888884</v>
       </c>
@@ -10521,7 +10600,7 @@
       <c r="I64" s="85"/>
       <c r="J64" s="85"/>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="114">
         <v>0.78472222222222221</v>
       </c>
@@ -10537,7 +10616,7 @@
       <c r="I65" s="85"/>
       <c r="J65" s="85"/>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="84"/>
       <c r="B66" s="85"/>
       <c r="C66" s="84"/>
@@ -10549,7 +10628,7 @@
       <c r="I66" s="85"/>
       <c r="J66" s="85"/>
     </row>
-    <row r="67" spans="1:12" s="106" customFormat="1">
+    <row r="67" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="102"/>
       <c r="B67" s="105"/>
       <c r="C67" s="102" t="s">
@@ -10572,7 +10651,7 @@
       <c r="I67" s="103"/>
       <c r="J67" s="103"/>
     </row>
-    <row r="68" spans="1:12" ht="63">
+    <row r="68" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A68" s="84"/>
       <c r="B68" s="85"/>
       <c r="C68" s="84" t="s">
@@ -10598,7 +10677,7 @@
       <c r="I68" s="96"/>
       <c r="J68" s="96"/>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="84"/>
       <c r="B69" s="85"/>
       <c r="C69" s="84" t="s">
@@ -10621,7 +10700,7 @@
       <c r="I69" s="96"/>
       <c r="J69" s="96"/>
     </row>
-    <row r="70" spans="1:12" s="15" customFormat="1">
+    <row r="70" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="72" t="str">
         <f>"Ngày 4: "&amp;C13+3&amp;"/6/2025 - TOKYO STATION TOKYO TOWER + GINZA MUA SẮM - SAU ĐÓ KYOTO"</f>
         <v>Ngày 4: 16/6/2025 - TOKYO STATION TOKYO TOWER + GINZA MUA SẮM - SAU ĐÓ KYOTO</v>
@@ -10638,7 +10717,7 @@
       <c r="K70" s="14"/>
       <c r="L70" s="14"/>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -10663,7 +10742,7 @@
       <c r="I71" s="96"/>
       <c r="J71" s="96"/>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="114"/>
       <c r="B72" s="85"/>
       <c r="C72" s="84" t="s">
@@ -10686,7 +10765,7 @@
       <c r="I72" s="96"/>
       <c r="J72" s="96"/>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="84"/>
       <c r="B73" s="85"/>
       <c r="C73" s="157" t="s">
@@ -10711,7 +10790,7 @@
       <c r="I73" s="96"/>
       <c r="J73" s="96"/>
     </row>
-    <row r="74" spans="1:12" s="106" customFormat="1">
+    <row r="74" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="137">
         <v>0.35416666666666669</v>
       </c>
@@ -10740,7 +10819,7 @@
       <c r="I74" s="103"/>
       <c r="J74" s="103"/>
     </row>
-    <row r="75" spans="1:12" ht="31.5">
+    <row r="75" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A75" s="114">
         <v>0.47916666666666669</v>
       </c>
@@ -10770,7 +10849,7 @@
       <c r="I75" s="96"/>
       <c r="J75" s="96"/>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="114">
         <v>0.54166666666666663</v>
       </c>
@@ -10797,7 +10876,7 @@
       <c r="I76" s="96"/>
       <c r="J76" s="96"/>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="114"/>
       <c r="B77" s="109"/>
       <c r="C77" s="84" t="s">
@@ -10820,7 +10899,7 @@
       <c r="I77" s="96"/>
       <c r="J77" s="96"/>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="114">
         <v>0.60416666666666663</v>
       </c>
@@ -10838,7 +10917,7 @@
       <c r="I78" s="96"/>
       <c r="J78" s="96"/>
     </row>
-    <row r="79" spans="1:12" ht="31.5">
+    <row r="79" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A79" s="114">
         <v>0.625</v>
       </c>
@@ -10858,7 +10937,7 @@
       <c r="I79" s="96"/>
       <c r="J79" s="96"/>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="114">
         <v>0.6875</v>
       </c>
@@ -10885,7 +10964,7 @@
       <c r="I80" s="96"/>
       <c r="J80" s="96"/>
     </row>
-    <row r="81" spans="1:10" s="106" customFormat="1">
+    <row r="81" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="100">
         <v>0.79166666666666663</v>
       </c>
@@ -10914,7 +10993,7 @@
       </c>
       <c r="J81" s="103"/>
     </row>
-    <row r="82" spans="1:10" ht="31.5">
+    <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="114">
         <v>0.83333333333333337</v>
       </c>
@@ -10942,10 +11021,10 @@
       <c r="I82" s="160"/>
       <c r="J82" s="96"/>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="114"/>
       <c r="B83" s="109"/>
-      <c r="C83" s="254" t="s">
+      <c r="C83" s="257" t="s">
         <v>377</v>
       </c>
       <c r="D83" s="148" t="s">
@@ -10968,10 +11047,10 @@
       <c r="I83" s="160"/>
       <c r="J83" s="96"/>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="114"/>
       <c r="B84" s="109"/>
-      <c r="C84" s="254"/>
+      <c r="C84" s="257"/>
       <c r="D84" s="148" t="s">
         <v>379</v>
       </c>
@@ -10991,7 +11070,7 @@
       <c r="I84" s="160"/>
       <c r="J84" s="96"/>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="84"/>
       <c r="B85" s="85"/>
       <c r="C85" s="84" t="s">
@@ -11007,7 +11086,7 @@
       <c r="I85" s="96"/>
       <c r="J85" s="96"/>
     </row>
-    <row r="86" spans="1:10" ht="47.25">
+    <row r="86" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" s="84"/>
       <c r="B86" s="85"/>
       <c r="C86" s="164" t="s">
@@ -11032,7 +11111,7 @@
       <c r="I86" s="96"/>
       <c r="J86" s="96"/>
     </row>
-    <row r="87" spans="1:10" s="15" customFormat="1">
+    <row r="87" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="72" t="str">
         <f>"Ngày 5: "&amp;C13+4&amp;"/6/2025 - KYOTO"</f>
         <v>Ngày 5: 17/6/2025 - KYOTO</v>
@@ -11047,7 +11126,7 @@
       <c r="I87" s="73"/>
       <c r="J87" s="73"/>
     </row>
-    <row r="88" spans="1:10" s="106" customFormat="1">
+    <row r="88" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="100">
         <v>0.29166666666666669</v>
       </c>
@@ -11077,7 +11156,7 @@
       <c r="I88" s="103"/>
       <c r="J88" s="103"/>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A89" s="157"/>
       <c r="B89" s="127"/>
       <c r="C89" s="84" t="s">
@@ -11102,7 +11181,7 @@
       <c r="I89" s="96"/>
       <c r="J89" s="96"/>
     </row>
-    <row r="90" spans="1:10" s="106" customFormat="1" ht="63">
+    <row r="90" spans="1:10" s="106" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A90" s="125"/>
       <c r="B90" s="134"/>
       <c r="C90" s="102" t="s">
@@ -11131,7 +11210,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -11149,7 +11228,7 @@
       <c r="I91" s="85"/>
       <c r="J91" s="85"/>
     </row>
-    <row r="92" spans="1:10" ht="31.5">
+    <row r="92" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="84"/>
       <c r="B92" s="85"/>
       <c r="C92" s="107" t="s">
@@ -11165,7 +11244,7 @@
       <c r="I92" s="85"/>
       <c r="J92" s="85"/>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="84"/>
       <c r="B93" s="85"/>
       <c r="C93" s="107" t="s">
@@ -11179,7 +11258,7 @@
       <c r="I93" s="85"/>
       <c r="J93" s="85"/>
     </row>
-    <row r="94" spans="1:10" s="106" customFormat="1" ht="31.5">
+    <row r="94" spans="1:10" s="106" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A94" s="100">
         <v>0.45833333333333331</v>
       </c>
@@ -11209,7 +11288,7 @@
       <c r="I94" s="103"/>
       <c r="J94" s="103"/>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" s="84"/>
       <c r="B95" s="85"/>
       <c r="C95" s="107"/>
@@ -11221,7 +11300,7 @@
       <c r="I95" s="85"/>
       <c r="J95" s="85"/>
     </row>
-    <row r="96" spans="1:10" ht="31.5">
+    <row r="96" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="114">
         <v>0.5625</v>
       </c>
@@ -11250,7 +11329,7 @@
       <c r="I96" s="96"/>
       <c r="J96" s="85"/>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="114"/>
       <c r="B97" s="109"/>
       <c r="C97" s="107" t="s">
@@ -11263,7 +11342,7 @@
       <c r="F97" s="91"/>
       <c r="J97" s="96"/>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="114"/>
       <c r="B98" s="109">
         <v>0.66666666666666663</v>
@@ -11279,7 +11358,7 @@
       <c r="I98" s="85"/>
       <c r="J98" s="85"/>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="114"/>
       <c r="C99" s="91"/>
       <c r="D99" s="91"/>
@@ -11287,7 +11366,7 @@
       <c r="F99" s="91"/>
       <c r="J99" s="96"/>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="114"/>
       <c r="B100" s="109">
         <v>0.75</v>
@@ -11303,7 +11382,7 @@
       <c r="I100" s="85"/>
       <c r="J100" s="85"/>
     </row>
-    <row r="101" spans="1:12" s="106" customFormat="1">
+    <row r="101" spans="1:12" s="106" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A101" s="100"/>
       <c r="B101" s="101">
         <v>0.79166666666666663</v>
@@ -11331,7 +11410,7 @@
       <c r="I101" s="103"/>
       <c r="J101" s="103"/>
     </row>
-    <row r="102" spans="1:12">
+    <row r="102" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="114"/>
       <c r="B102" s="109"/>
       <c r="C102" s="84" t="s">
@@ -11347,7 +11426,7 @@
       <c r="I102" s="85"/>
       <c r="J102" s="85"/>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="114"/>
       <c r="B103" s="109"/>
       <c r="C103" s="84"/>
@@ -11359,7 +11438,7 @@
       <c r="I103" s="85"/>
       <c r="J103" s="85"/>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="72" t="str">
         <f>"Ngày 6: "&amp;C13+5&amp;"/6/2025 - CHƠI NỐT KYOTO - SAU ĐÓ OSAKA"</f>
         <v>Ngày 6: 18/6/2025 - CHƠI NỐT KYOTO - SAU ĐÓ OSAKA</v>
@@ -11376,7 +11455,7 @@
       <c r="K104" s="15"/>
       <c r="L104" s="15"/>
     </row>
-    <row r="105" spans="1:12" s="106" customFormat="1">
+    <row r="105" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="100"/>
       <c r="B105" s="101">
         <v>0.33333333333333331</v>
@@ -11404,7 +11483,7 @@
       <c r="I105" s="103"/>
       <c r="J105" s="103"/>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="114"/>
       <c r="B106" s="109"/>
       <c r="C106" s="84"/>
@@ -11416,7 +11495,7 @@
       <c r="I106" s="85"/>
       <c r="J106" s="85"/>
     </row>
-    <row r="107" spans="1:12" s="106" customFormat="1" ht="31.5">
+    <row r="107" spans="1:12" s="106" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A107" s="100">
         <v>0.33333333333333331</v>
       </c>
@@ -11445,7 +11524,7 @@
       <c r="I107" s="103"/>
       <c r="J107" s="103"/>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="114"/>
       <c r="B108" s="109">
         <v>0.41666666666666669</v>
@@ -11471,7 +11550,7 @@
       <c r="I108" s="96"/>
       <c r="J108" s="96"/>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="114"/>
       <c r="B109" s="109">
         <v>0.45833333333333331</v>
@@ -11498,7 +11577,7 @@
       <c r="I109" s="96"/>
       <c r="J109" s="96"/>
     </row>
-    <row r="110" spans="1:12" s="106" customFormat="1">
+    <row r="110" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="100">
         <v>0.45833333333333331</v>
       </c>
@@ -11528,7 +11607,7 @@
       <c r="I110" s="103"/>
       <c r="J110" s="103"/>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="114"/>
       <c r="B111" s="174"/>
       <c r="C111" s="164" t="s">
@@ -11553,7 +11632,7 @@
       <c r="I111" s="96"/>
       <c r="J111" s="96"/>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="114"/>
       <c r="B112" s="174"/>
       <c r="C112" s="164" t="s">
@@ -11569,7 +11648,7 @@
       <c r="I112" s="96"/>
       <c r="J112" s="96"/>
     </row>
-    <row r="113" spans="1:10" s="106" customFormat="1" ht="31.5">
+    <row r="113" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="102"/>
       <c r="B113" s="176">
         <v>0.52083333333333337</v>
@@ -11596,7 +11675,7 @@
       <c r="I113" s="103"/>
       <c r="J113" s="103"/>
     </row>
-    <row r="114" spans="1:10" ht="31.5">
+    <row r="114" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A114" s="84"/>
       <c r="B114" s="174">
         <v>0.58333333333333337</v>
@@ -11627,7 +11706,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="84"/>
       <c r="B115" s="174"/>
       <c r="C115" s="164" t="s">
@@ -11641,7 +11720,7 @@
       <c r="I115" s="96"/>
       <c r="J115" s="152"/>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A116" s="84"/>
       <c r="B116" s="174"/>
       <c r="C116" s="164"/>
@@ -11653,7 +11732,7 @@
       <c r="I116" s="96"/>
       <c r="J116" s="152"/>
     </row>
-    <row r="117" spans="1:10" s="106" customFormat="1" ht="31.5">
+    <row r="117" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A117" s="102"/>
       <c r="B117" s="176">
         <v>0.625</v>
@@ -11674,7 +11753,7 @@
       <c r="I117" s="103"/>
       <c r="J117" s="103"/>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A118" s="84"/>
       <c r="B118" s="174"/>
       <c r="C118" s="164" t="s">
@@ -11688,7 +11767,7 @@
       <c r="I118" s="96"/>
       <c r="J118" s="96"/>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A119" s="84"/>
       <c r="B119" s="174"/>
       <c r="C119" s="177" t="s">
@@ -11711,7 +11790,7 @@
       <c r="I119" s="96"/>
       <c r="J119" s="96"/>
     </row>
-    <row r="120" spans="1:10" s="180" customFormat="1">
+    <row r="120" spans="1:10" s="180" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A120" s="178"/>
       <c r="B120" s="179">
         <v>0.66666666666666663</v>
@@ -11730,7 +11809,7 @@
       <c r="I120" s="112"/>
       <c r="J120" s="112"/>
     </row>
-    <row r="121" spans="1:10" s="182" customFormat="1">
+    <row r="121" spans="1:10" s="182" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A121" s="148"/>
       <c r="B121" s="162"/>
       <c r="C121" s="181" t="s">
@@ -11744,7 +11823,7 @@
       <c r="I121" s="160"/>
       <c r="J121" s="160"/>
     </row>
-    <row r="122" spans="1:10" s="182" customFormat="1">
+    <row r="122" spans="1:10" s="182" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A122" s="148"/>
       <c r="B122" s="162"/>
       <c r="C122" s="181" t="s">
@@ -11767,7 +11846,7 @@
       <c r="I122" s="96"/>
       <c r="J122" s="96"/>
     </row>
-    <row r="123" spans="1:10" s="182" customFormat="1">
+    <row r="123" spans="1:10" s="182" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A123" s="148"/>
       <c r="B123" s="162"/>
       <c r="C123" s="181" t="s">
@@ -11781,7 +11860,7 @@
       <c r="I123" s="160"/>
       <c r="J123" s="160"/>
     </row>
-    <row r="124" spans="1:10" s="106" customFormat="1" ht="267.75">
+    <row r="124" spans="1:10" s="106" customFormat="1" ht="272" x14ac:dyDescent="0.2">
       <c r="A124" s="102"/>
       <c r="B124" s="101">
         <v>0.70833333333333337</v>
@@ -11799,7 +11878,7 @@
       <c r="I124" s="105"/>
       <c r="J124" s="105"/>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A125" s="84"/>
       <c r="B125" s="109"/>
       <c r="C125" s="84"/>
@@ -11811,7 +11890,7 @@
       <c r="I125" s="85"/>
       <c r="J125" s="85"/>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A126" s="84"/>
       <c r="B126" s="85"/>
       <c r="C126" s="84"/>
@@ -11832,7 +11911,7 @@
       <c r="I126" s="96"/>
       <c r="J126" s="96"/>
     </row>
-    <row r="127" spans="1:10" ht="31.5">
+    <row r="127" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A127" s="84"/>
       <c r="B127" s="85"/>
       <c r="C127" s="157" t="s">
@@ -11857,7 +11936,7 @@
       <c r="I127" s="96"/>
       <c r="J127" s="96"/>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A128" s="84"/>
       <c r="B128" s="85"/>
       <c r="C128" s="84" t="s">
@@ -11871,7 +11950,7 @@
       <c r="I128" s="85"/>
       <c r="J128" s="85"/>
     </row>
-    <row r="129" spans="1:10" ht="31.5">
+    <row r="129" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A129" s="84"/>
       <c r="B129" s="85"/>
       <c r="C129" s="84" t="s">
@@ -11896,7 +11975,7 @@
       <c r="I129" s="96"/>
       <c r="J129" s="96"/>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="84"/>
       <c r="B130" s="85"/>
       <c r="C130" s="84" t="s">
@@ -11924,7 +12003,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A131" s="84"/>
       <c r="B131" s="85"/>
       <c r="C131" s="84"/>
@@ -11936,7 +12015,7 @@
       <c r="I131" s="85"/>
       <c r="J131" s="85"/>
     </row>
-    <row r="132" spans="1:10" s="15" customFormat="1">
+    <row r="132" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="186" t="str">
         <f>"Ngày 7: "&amp;C13+6&amp;"/6/2025 - ĐI NARA &amp; CÔNG VIÊN IKOMA SANJO- VÀ MUA SẮM QUÀ Ở OSAKA"</f>
         <v>Ngày 7: 19/6/2025 - ĐI NARA &amp; CÔNG VIÊN IKOMA SANJO- VÀ MUA SẮM QUÀ Ở OSAKA</v>
@@ -11951,7 +12030,7 @@
       <c r="I132" s="187"/>
       <c r="J132" s="187"/>
     </row>
-    <row r="133" spans="1:10" ht="31.5">
+    <row r="133" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A133" s="157"/>
       <c r="B133" s="174">
         <v>0.29166666666666669</v>
@@ -11979,7 +12058,7 @@
       <c r="I133" s="96"/>
       <c r="J133" s="96"/>
     </row>
-    <row r="134" spans="1:10" s="106" customFormat="1" ht="31.5">
+    <row r="134" spans="1:10" s="106" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A134" s="125"/>
       <c r="B134" s="176">
         <v>0.375</v>
@@ -12006,7 +12085,7 @@
       <c r="I134" s="103"/>
       <c r="J134" s="103"/>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="157"/>
       <c r="B135" s="192"/>
       <c r="C135" s="164"/>
@@ -12029,7 +12108,7 @@
       <c r="I135" s="96"/>
       <c r="J135" s="96"/>
     </row>
-    <row r="136" spans="1:10" ht="31.5">
+    <row r="136" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A136" s="157"/>
       <c r="B136" s="174">
         <v>0.41666666666666669</v>
@@ -12056,7 +12135,7 @@
       <c r="I136" s="96"/>
       <c r="J136" s="96"/>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A137" s="157"/>
       <c r="B137" s="174">
         <v>0.45833333333333331</v>
@@ -12083,7 +12162,7 @@
       <c r="I137" s="96"/>
       <c r="J137" s="96"/>
     </row>
-    <row r="138" spans="1:10" ht="31.5">
+    <row r="138" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A138" s="157"/>
       <c r="B138" s="174">
         <v>0.47916666666666669</v>
@@ -12111,7 +12190,7 @@
       <c r="I138" s="96"/>
       <c r="J138" s="96"/>
     </row>
-    <row r="139" spans="1:10" ht="47.25">
+    <row r="139" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A139" s="157"/>
       <c r="B139" s="174"/>
       <c r="C139" s="164" t="s">
@@ -12137,7 +12216,7 @@
       <c r="I139" s="96"/>
       <c r="J139" s="96"/>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A140" s="157"/>
       <c r="B140" s="174"/>
       <c r="C140" s="164"/>
@@ -12149,7 +12228,7 @@
       <c r="I140" s="96"/>
       <c r="J140" s="96"/>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A141" s="84"/>
       <c r="B141" s="109">
         <v>0.79166666666666663</v>
@@ -12165,7 +12244,7 @@
       <c r="I141" s="85"/>
       <c r="J141" s="85"/>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A142" s="84"/>
       <c r="B142" s="109"/>
       <c r="C142" s="84" t="s">
@@ -12188,7 +12267,7 @@
       <c r="I142" s="96"/>
       <c r="J142" s="96"/>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A143" s="84"/>
       <c r="B143" s="109"/>
       <c r="C143" s="84" t="s">
@@ -12214,7 +12293,7 @@
       <c r="I143" s="96"/>
       <c r="J143" s="85"/>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A144" s="84"/>
       <c r="B144" s="109"/>
       <c r="C144" s="84" t="s">
@@ -12228,7 +12307,7 @@
       <c r="I144" s="85"/>
       <c r="J144" s="85"/>
     </row>
-    <row r="145" spans="1:12">
+    <row r="145" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A145" s="84"/>
       <c r="B145" s="109">
         <v>0.875</v>
@@ -12244,7 +12323,7 @@
       <c r="I145" s="85"/>
       <c r="J145" s="85"/>
     </row>
-    <row r="146" spans="1:12">
+    <row r="146" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A146" s="84"/>
       <c r="B146" s="109"/>
       <c r="C146" s="84" t="s">
@@ -12267,7 +12346,7 @@
       <c r="I146" s="96"/>
       <c r="J146" s="96"/>
     </row>
-    <row r="147" spans="1:12">
+    <row r="147" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A147" s="84"/>
       <c r="B147" s="109"/>
       <c r="C147" s="84" t="s">
@@ -12281,7 +12360,7 @@
       <c r="I147" s="85"/>
       <c r="J147" s="85"/>
     </row>
-    <row r="148" spans="1:12">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="194" t="str">
         <f>"Ngày 8: "&amp;C13+7&amp;"/6/2025 - ĐI CHÙA KATSUOJI - CẦU NGUYỆN"</f>
         <v>Ngày 8: 20/6/2025 - ĐI CHÙA KATSUOJI - CẦU NGUYỆN</v>
@@ -12298,7 +12377,7 @@
       <c r="K148" s="15"/>
       <c r="L148" s="15"/>
     </row>
-    <row r="149" spans="1:12">
+    <row r="149" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A149" s="84"/>
       <c r="B149" s="174">
         <v>0.29166666666666669</v>
@@ -12326,7 +12405,7 @@
       <c r="I149" s="85"/>
       <c r="J149" s="85"/>
     </row>
-    <row r="150" spans="1:12">
+    <row r="150" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A150" s="114">
         <v>0.375</v>
       </c>
@@ -12355,7 +12434,7 @@
       <c r="I150" s="85"/>
       <c r="J150" s="85"/>
     </row>
-    <row r="151" spans="1:12" ht="31.5">
+    <row r="151" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A151" s="114"/>
       <c r="B151" s="174"/>
       <c r="C151" s="164" t="s">
@@ -12380,7 +12459,7 @@
       <c r="I151" s="85"/>
       <c r="J151" s="85"/>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A152" s="114">
         <v>0.54166666666666663</v>
       </c>
@@ -12407,7 +12486,7 @@
       <c r="I152" s="85"/>
       <c r="J152" s="85"/>
     </row>
-    <row r="153" spans="1:12">
+    <row r="153" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A153" s="84"/>
       <c r="B153" s="109"/>
       <c r="C153" s="84" t="s">
@@ -12430,7 +12509,7 @@
       <c r="I153" s="85"/>
       <c r="J153" s="85"/>
     </row>
-    <row r="154" spans="1:12">
+    <row r="154" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A154" s="84"/>
       <c r="B154" s="109"/>
       <c r="C154" s="84" t="s">
@@ -12444,7 +12523,7 @@
       <c r="I154" s="85"/>
       <c r="J154" s="85"/>
     </row>
-    <row r="155" spans="1:12" s="15" customFormat="1">
+    <row r="155" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A155" s="197" t="str">
         <f>"Ngày 9: "&amp;C13+8&amp;"/6/2025 - ĐI VỀ HÀ NỘI"</f>
         <v>Ngày 9: 21/6/2025 - ĐI VỀ HÀ NỘI</v>
@@ -12459,7 +12538,7 @@
       <c r="I155" s="195"/>
       <c r="J155" s="195"/>
     </row>
-    <row r="156" spans="1:12">
+    <row r="156" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A156" s="84"/>
       <c r="B156" s="85"/>
       <c r="C156" s="84" t="s">
@@ -12475,7 +12554,7 @@
       <c r="I156" s="85"/>
       <c r="J156" s="85"/>
     </row>
-    <row r="157" spans="1:12">
+    <row r="157" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A157" s="84"/>
       <c r="B157" s="85"/>
       <c r="C157" s="84" t="s">
@@ -12498,7 +12577,7 @@
       <c r="I157" s="96"/>
       <c r="J157" s="96"/>
     </row>
-    <row r="158" spans="1:12">
+    <row r="158" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A158" s="84"/>
       <c r="B158" s="109">
         <v>0.29166666666666669</v>
@@ -12524,7 +12603,7 @@
       <c r="I158" s="96"/>
       <c r="J158" s="96"/>
     </row>
-    <row r="159" spans="1:12" s="106" customFormat="1">
+    <row r="159" spans="1:12" s="106" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A159" s="102"/>
       <c r="B159" s="176">
         <v>0.45833333333333331</v>
@@ -12551,7 +12630,7 @@
       <c r="I159" s="103"/>
       <c r="J159" s="103"/>
     </row>
-    <row r="160" spans="1:12">
+    <row r="160" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A160" s="84"/>
       <c r="B160" s="174">
         <v>0.5</v>
@@ -12578,7 +12657,7 @@
       <c r="I160" s="96"/>
       <c r="J160" s="96"/>
     </row>
-    <row r="161" spans="1:10" s="106" customFormat="1">
+    <row r="161" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A161" s="102"/>
       <c r="B161" s="176">
         <v>0.5625</v>
@@ -12605,7 +12684,7 @@
       <c r="I161" s="103"/>
       <c r="J161" s="103"/>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A162" s="114">
         <v>0.64583333333333337</v>
       </c>
@@ -12635,7 +12714,7 @@
       </c>
       <c r="J162" s="200"/>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A163" s="114"/>
       <c r="B163" s="109"/>
       <c r="C163" s="84"/>
@@ -12656,7 +12735,7 @@
       <c r="I163" s="200"/>
       <c r="J163" s="200"/>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A164" s="199"/>
       <c r="B164" s="199"/>
       <c r="C164" s="84"/>
@@ -12668,7 +12747,7 @@
       <c r="I164" s="199"/>
       <c r="J164" s="199"/>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B165" s="199"/>
       <c r="C165" s="84"/>
       <c r="D165" s="84"/>
@@ -12685,7 +12764,7 @@
       </c>
       <c r="J165" s="204"/>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B166" s="199"/>
       <c r="C166" s="84"/>
       <c r="D166" s="84"/>
@@ -12757,17 +12836,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F55"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18" style="216" customWidth="1"/>
     <col min="2" max="2" width="28" style="216" customWidth="1"/>
     <col min="3" max="3" width="81" style="216" customWidth="1"/>
     <col min="4" max="4" width="38" style="216" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5703125" style="216" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.85546875" style="216"/>
+    <col min="5" max="5" width="6.5" style="216" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.83203125" style="216"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="236" t="s">
         <v>432</v>
       </c>
@@ -12787,17 +12866,17 @@
         <v>437</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="250" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="264" t="s">
         <v>438</v>
       </c>
-      <c r="B2" s="259"/>
-      <c r="C2" s="259"/>
+      <c r="B2" s="265"/>
+      <c r="C2" s="265"/>
       <c r="D2" s="238"/>
       <c r="E2" s="238"/>
       <c r="F2" s="239"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="240" t="s">
         <v>439</v>
       </c>
@@ -12808,10 +12887,10 @@
         <v>441</v>
       </c>
       <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
+      <c r="E3" s="250"/>
       <c r="F3" s="239"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="243" t="s">
         <v>442</v>
       </c>
@@ -12824,12 +12903,12 @@
       <c r="D4" s="245" t="s">
         <v>444</v>
       </c>
-      <c r="E4" s="245"/>
+      <c r="E4" s="251"/>
       <c r="F4" s="246" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="240" t="s">
         <v>446</v>
       </c>
@@ -12842,14 +12921,14 @@
       <c r="D5" s="242" t="s">
         <v>449</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="252" t="s">
         <v>450</v>
       </c>
       <c r="F5" s="247" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="243" t="s">
         <v>452</v>
       </c>
@@ -12862,14 +12941,14 @@
       <c r="D6" s="245" t="s">
         <v>455</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="252" t="s">
         <v>456</v>
       </c>
       <c r="F6" s="246" t="s">
         <v>457</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.75">
+    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="240" t="s">
         <v>458</v>
       </c>
@@ -12880,10 +12959,10 @@
         <v>460</v>
       </c>
       <c r="D7" s="245"/>
-      <c r="E7" s="245"/>
+      <c r="E7" s="251"/>
       <c r="F7" s="239"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="243" t="s">
         <v>461</v>
       </c>
@@ -12896,14 +12975,14 @@
       <c r="D8" s="245" t="s">
         <v>464</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="252" t="s">
         <v>465</v>
       </c>
       <c r="F8" s="246" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="240" t="s">
         <v>467</v>
       </c>
@@ -12916,14 +12995,14 @@
       <c r="D9" s="242" t="s">
         <v>470</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="252" t="s">
         <v>471</v>
       </c>
       <c r="F9" s="246" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="243" t="s">
         <v>473</v>
       </c>
@@ -12934,14 +13013,14 @@
         <v>475</v>
       </c>
       <c r="D10" s="245"/>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="252" t="s">
         <v>476</v>
       </c>
       <c r="F10" s="239"/>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="248">
-        <v>0.875</v>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="249" t="s">
+        <v>595</v>
       </c>
       <c r="B11" s="241" t="s">
         <v>477</v>
@@ -12950,20 +13029,20 @@
         <v>478</v>
       </c>
       <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
+      <c r="E11" s="250"/>
       <c r="F11" s="239"/>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="249" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="262" t="s">
         <v>479</v>
       </c>
-      <c r="B12" s="260"/>
-      <c r="C12" s="260"/>
+      <c r="B12" s="263"/>
+      <c r="C12" s="263"/>
       <c r="D12" s="239"/>
       <c r="E12" s="239"/>
       <c r="F12" s="239"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="240" t="s">
         <v>480</v>
       </c>
@@ -12971,49 +13050,53 @@
         <v>481</v>
       </c>
       <c r="C13" s="242" t="s">
+        <v>576</v>
+      </c>
+      <c r="D13" s="242" t="s">
         <v>482</v>
       </c>
-      <c r="D13" s="242" t="s">
+      <c r="E13" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="F13" s="246" t="s">
         <v>483</v>
       </c>
-      <c r="E13" s="242"/>
-      <c r="F13" s="246" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="243" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="29.25">
-      <c r="A14" s="243" t="s">
+      <c r="B14" s="244" t="s">
+        <v>482</v>
+      </c>
+      <c r="C14" s="245" t="s">
         <v>485</v>
       </c>
-      <c r="B14" s="244" t="s">
-        <v>483</v>
-      </c>
-      <c r="C14" s="245" t="s">
+      <c r="D14" s="245"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="239"/>
+    </row>
+    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="240" t="s">
         <v>486</v>
-      </c>
-      <c r="D14" s="245"/>
-      <c r="E14" s="245"/>
-      <c r="F14" s="239"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="240" t="s">
-        <v>487</v>
       </c>
       <c r="B15" s="241" t="s">
         <v>474</v>
       </c>
       <c r="C15" s="242" t="s">
+        <v>487</v>
+      </c>
+      <c r="D15" s="242" t="s">
         <v>488</v>
       </c>
-      <c r="D15" s="242" t="s">
+      <c r="E15" s="253" t="s">
+        <v>596</v>
+      </c>
+      <c r="F15" s="246" t="s">
         <v>489</v>
       </c>
-      <c r="E15" s="242"/>
-      <c r="F15" s="246" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+    </row>
+    <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="248">
         <v>0.875</v>
       </c>
@@ -13024,98 +13107,98 @@
         <v>478</v>
       </c>
       <c r="D16" s="245"/>
-      <c r="E16" s="245"/>
+      <c r="E16" s="251"/>
       <c r="F16" s="239"/>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="249" t="s">
-        <v>491</v>
-      </c>
-      <c r="B17" s="260"/>
-      <c r="C17" s="260"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="262" t="s">
+        <v>490</v>
+      </c>
+      <c r="B17" s="263"/>
+      <c r="C17" s="263"/>
       <c r="D17" s="239"/>
       <c r="E17" s="239"/>
       <c r="F17" s="239"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="240" t="s">
+        <v>491</v>
+      </c>
+      <c r="B18" s="241" t="s">
         <v>492</v>
       </c>
-      <c r="B18" s="241" t="s">
+      <c r="C18" s="242" t="s">
         <v>493</v>
       </c>
-      <c r="C18" s="242" t="s">
+      <c r="D18" s="242"/>
+      <c r="E18" s="250"/>
+      <c r="F18" s="239"/>
+    </row>
+    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="243" t="s">
         <v>494</v>
       </c>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="239"/>
-    </row>
-    <row r="19" spans="1:6" ht="29.25">
-      <c r="A19" s="243" t="s">
+      <c r="B19" s="244" t="s">
         <v>495</v>
       </c>
-      <c r="B19" s="244" t="s">
+      <c r="C19" s="245" t="s">
         <v>496</v>
       </c>
-      <c r="C19" s="245" t="s">
+      <c r="D19" s="245"/>
+      <c r="E19" s="251"/>
+      <c r="F19" s="239"/>
+    </row>
+    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="240" t="s">
         <v>497</v>
-      </c>
-      <c r="D19" s="245"/>
-      <c r="E19" s="245"/>
-      <c r="F19" s="239"/>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="240" t="s">
-        <v>498</v>
       </c>
       <c r="B20" s="241" t="s">
         <v>453</v>
       </c>
       <c r="C20" s="242" t="s">
+        <v>498</v>
+      </c>
+      <c r="D20" s="242" t="s">
+        <v>577</v>
+      </c>
+      <c r="E20" s="250"/>
+      <c r="F20" s="246" t="s">
         <v>499</v>
       </c>
-      <c r="D20" s="242" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="243" t="s">
         <v>500</v>
       </c>
-      <c r="E20" s="242"/>
-      <c r="F20" s="246" t="s">
+      <c r="B21" s="244" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="243" t="s">
+      <c r="C21" s="245" t="s">
         <v>502</v>
       </c>
-      <c r="B21" s="244" t="s">
+      <c r="D21" s="245"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="239"/>
+    </row>
+    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="240" t="s">
         <v>503</v>
       </c>
-      <c r="C21" s="245" t="s">
+      <c r="B22" s="241" t="s">
         <v>504</v>
       </c>
-      <c r="D21" s="245"/>
-      <c r="E21" s="245"/>
-      <c r="F21" s="239"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="240" t="s">
+      <c r="C22" s="242" t="s">
         <v>505</v>
       </c>
-      <c r="B22" s="241" t="s">
+      <c r="D22" s="242" t="s">
         <v>506</v>
       </c>
-      <c r="C22" s="242" t="s">
+      <c r="E22" s="250"/>
+      <c r="F22" s="246" t="s">
         <v>507</v>
       </c>
-      <c r="D22" s="242" t="s">
-        <v>508</v>
-      </c>
-      <c r="E22" s="242"/>
-      <c r="F22" s="246" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+    </row>
+    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="243" t="s">
         <v>473</v>
       </c>
@@ -13123,436 +13206,474 @@
         <v>474</v>
       </c>
       <c r="C23" s="245" t="s">
+        <v>508</v>
+      </c>
+      <c r="D23" s="245" t="s">
+        <v>578</v>
+      </c>
+      <c r="E23" s="251"/>
+      <c r="F23" s="8" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="262" t="s">
         <v>510</v>
       </c>
-      <c r="D23" s="245"/>
-      <c r="E23" s="245"/>
-      <c r="F23" s="8" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="249" t="s">
-        <v>512</v>
-      </c>
-      <c r="B24" s="260"/>
-      <c r="C24" s="260"/>
+      <c r="B24" s="263"/>
+      <c r="C24" s="263"/>
       <c r="D24" s="239"/>
       <c r="E24" s="239"/>
       <c r="F24" s="239"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="240" t="s">
+        <v>511</v>
+      </c>
+      <c r="B25" s="241" t="s">
+        <v>512</v>
+      </c>
+      <c r="C25" s="242" t="s">
+        <v>584</v>
+      </c>
+      <c r="D25" s="242" t="s">
+        <v>579</v>
+      </c>
+      <c r="E25" s="250"/>
+      <c r="F25" s="239" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="243" t="s">
         <v>513</v>
-      </c>
-      <c r="B25" s="241" t="s">
-        <v>514</v>
-      </c>
-      <c r="C25" s="242" t="s">
-        <v>515</v>
-      </c>
-      <c r="D25" s="242"/>
-      <c r="E25" s="242"/>
-      <c r="F25" s="239"/>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="243" t="s">
-        <v>516</v>
       </c>
       <c r="B26" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C26" s="245" t="s">
+        <v>585</v>
+      </c>
+      <c r="D26" s="245" t="s">
+        <v>575</v>
+      </c>
+      <c r="E26" s="251"/>
+      <c r="F26" s="239" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="240" t="s">
+        <v>514</v>
+      </c>
+      <c r="B27" s="241" t="s">
+        <v>515</v>
+      </c>
+      <c r="C27" s="242" t="s">
+        <v>516</v>
+      </c>
+      <c r="D27" s="242" t="s">
+        <v>574</v>
+      </c>
+      <c r="E27" s="250"/>
+      <c r="F27" s="239" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="243" t="s">
+        <v>503</v>
+      </c>
+      <c r="B28" s="244" t="s">
+        <v>504</v>
+      </c>
+      <c r="C28" s="245" t="s">
+        <v>586</v>
+      </c>
+      <c r="D28" s="245" t="s">
+        <v>580</v>
+      </c>
+      <c r="E28" s="251"/>
+      <c r="F28" s="239" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="240" t="s">
         <v>517</v>
       </c>
-      <c r="D26" s="245"/>
-      <c r="E26" s="245"/>
-      <c r="F26" s="239"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="240" t="s">
+      <c r="B29" s="241" t="s">
         <v>518</v>
       </c>
-      <c r="B27" s="241" t="s">
+      <c r="C29" s="242" t="s">
         <v>519</v>
       </c>
-      <c r="C27" s="242" t="s">
+      <c r="D29" s="242" t="s">
+        <v>581</v>
+      </c>
+      <c r="E29" s="250"/>
+      <c r="F29" s="239" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="262" t="s">
         <v>520</v>
       </c>
-      <c r="D27" s="242"/>
-      <c r="E27" s="242"/>
-      <c r="F27" s="239"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="243" t="s">
-        <v>505</v>
-      </c>
-      <c r="B28" s="244" t="s">
-        <v>506</v>
-      </c>
-      <c r="C28" s="245" t="s">
-        <v>521</v>
-      </c>
-      <c r="D28" s="245"/>
-      <c r="E28" s="245"/>
-      <c r="F28" s="239"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="240" t="s">
-        <v>522</v>
-      </c>
-      <c r="B29" s="241" t="s">
-        <v>523</v>
-      </c>
-      <c r="C29" s="242" t="s">
-        <v>524</v>
-      </c>
-      <c r="D29" s="242"/>
-      <c r="E29" s="242"/>
-      <c r="F29" s="239"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="249" t="s">
-        <v>525</v>
-      </c>
-      <c r="B30" s="260"/>
-      <c r="C30" s="260"/>
+      <c r="B30" s="263"/>
+      <c r="C30" s="263"/>
       <c r="D30" s="239"/>
       <c r="E30" s="239"/>
       <c r="F30" s="239"/>
     </row>
-    <row r="31" spans="1:6" ht="29.25">
+    <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="240" t="s">
+        <v>521</v>
+      </c>
+      <c r="B31" s="241" t="s">
+        <v>522</v>
+      </c>
+      <c r="C31" s="242" t="s">
+        <v>587</v>
+      </c>
+      <c r="D31" s="242" t="s">
+        <v>574</v>
+      </c>
+      <c r="E31" s="250"/>
+      <c r="F31" s="239" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A32" s="243" t="s">
+        <v>523</v>
+      </c>
+      <c r="B32" s="244" t="s">
+        <v>524</v>
+      </c>
+      <c r="C32" s="245" t="s">
+        <v>525</v>
+      </c>
+      <c r="D32" s="245"/>
+      <c r="E32" s="251"/>
+      <c r="F32" s="239"/>
+    </row>
+    <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="240" t="s">
         <v>526</v>
       </c>
-      <c r="B31" s="241" t="s">
+      <c r="B33" s="241" t="s">
         <v>527</v>
       </c>
-      <c r="C31" s="242" t="s">
+      <c r="C33" s="242" t="s">
         <v>528</v>
       </c>
-      <c r="D31" s="242"/>
-      <c r="E31" s="242"/>
-      <c r="F31" s="239"/>
-    </row>
-    <row r="32" spans="1:6" ht="29.25">
-      <c r="A32" s="243" t="s">
-        <v>529</v>
-      </c>
-      <c r="B32" s="244" t="s">
-        <v>530</v>
-      </c>
-      <c r="C32" s="245" t="s">
-        <v>531</v>
-      </c>
-      <c r="D32" s="245"/>
-      <c r="E32" s="245"/>
-      <c r="F32" s="239"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="240" t="s">
-        <v>532</v>
-      </c>
-      <c r="B33" s="241" t="s">
-        <v>533</v>
-      </c>
-      <c r="C33" s="242" t="s">
-        <v>534</v>
-      </c>
       <c r="D33" s="242"/>
-      <c r="E33" s="242"/>
+      <c r="E33" s="250"/>
       <c r="F33" s="239"/>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="243" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="B34" s="244" t="s">
         <v>474</v>
       </c>
       <c r="C34" s="245" t="s">
-        <v>535</v>
-      </c>
-      <c r="D34" s="245"/>
-      <c r="E34" s="245"/>
-      <c r="F34" s="239"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="249" t="s">
-        <v>536</v>
-      </c>
-      <c r="B35" s="260"/>
-      <c r="C35" s="260"/>
+        <v>529</v>
+      </c>
+      <c r="D34" s="245" t="s">
+        <v>589</v>
+      </c>
+      <c r="E34" s="251"/>
+      <c r="F34" s="239" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="262" t="s">
+        <v>530</v>
+      </c>
+      <c r="B35" s="263"/>
+      <c r="C35" s="263"/>
       <c r="D35" s="239"/>
       <c r="E35" s="239"/>
       <c r="F35" s="239"/>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="240" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B36" s="241" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C36" s="242" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D36" s="242"/>
-      <c r="E36" s="242"/>
+      <c r="E36" s="250"/>
       <c r="F36" s="239"/>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="243" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B37" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C37" s="245" t="s">
-        <v>540</v>
-      </c>
-      <c r="D37" s="245"/>
-      <c r="E37" s="245"/>
-      <c r="F37" s="239"/>
-    </row>
-    <row r="38" spans="1:6">
+        <v>534</v>
+      </c>
+      <c r="D37" s="245" t="s">
+        <v>591</v>
+      </c>
+      <c r="E37" s="251"/>
+      <c r="F37" s="239" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="240" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B38" s="241" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="C38" s="242" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="D38" s="242"/>
-      <c r="E38" s="242"/>
+      <c r="E38" s="250"/>
       <c r="F38" s="239"/>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="243" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="B39" s="244" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C39" s="245" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D39" s="245"/>
-      <c r="E39" s="245"/>
+      <c r="E39" s="251"/>
       <c r="F39" s="239"/>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="240" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B40" s="241" t="s">
         <v>474</v>
       </c>
       <c r="C40" s="242" t="s">
-        <v>546</v>
-      </c>
-      <c r="D40" s="242"/>
-      <c r="E40" s="242"/>
-      <c r="F40" s="239"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="249" t="s">
-        <v>547</v>
-      </c>
-      <c r="B41" s="260"/>
-      <c r="C41" s="260"/>
+        <v>540</v>
+      </c>
+      <c r="D40" s="242" t="s">
+        <v>594</v>
+      </c>
+      <c r="E40" s="250"/>
+      <c r="F40" s="239" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="262" t="s">
+        <v>541</v>
+      </c>
+      <c r="B41" s="263"/>
+      <c r="C41" s="263"/>
       <c r="D41" s="239"/>
       <c r="E41" s="239"/>
       <c r="F41" s="239"/>
     </row>
-    <row r="42" spans="1:6" ht="29.25">
+    <row r="42" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="240" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B42" s="241" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C42" s="242" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="D42" s="242"/>
-      <c r="E42" s="242"/>
+      <c r="E42" s="250"/>
       <c r="F42" s="239"/>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="243" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B43" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C43" s="245" t="s">
+        <v>544</v>
+      </c>
+      <c r="D43" s="245"/>
+      <c r="E43" s="251"/>
+      <c r="F43" s="239"/>
+    </row>
+    <row r="44" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="240" t="s">
+        <v>514</v>
+      </c>
+      <c r="B44" s="241" t="s">
+        <v>545</v>
+      </c>
+      <c r="C44" s="242" t="s">
+        <v>546</v>
+      </c>
+      <c r="D44" s="242"/>
+      <c r="E44" s="250"/>
+      <c r="F44" s="239"/>
+    </row>
+    <row r="45" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="243" t="s">
+        <v>547</v>
+      </c>
+      <c r="B45" s="244" t="s">
+        <v>548</v>
+      </c>
+      <c r="C45" s="245" t="s">
+        <v>549</v>
+      </c>
+      <c r="D45" s="245"/>
+      <c r="E45" s="251"/>
+      <c r="F45" s="239"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="262" t="s">
         <v>550</v>
       </c>
-      <c r="D43" s="245"/>
-      <c r="E43" s="245"/>
-      <c r="F43" s="239"/>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="240" t="s">
-        <v>518</v>
-      </c>
-      <c r="B44" s="241" t="s">
-        <v>551</v>
-      </c>
-      <c r="C44" s="242" t="s">
-        <v>552</v>
-      </c>
-      <c r="D44" s="242"/>
-      <c r="E44" s="242"/>
-      <c r="F44" s="239"/>
-    </row>
-    <row r="45" spans="1:6" ht="15.75">
-      <c r="A45" s="243" t="s">
-        <v>553</v>
-      </c>
-      <c r="B45" s="244" t="s">
-        <v>554</v>
-      </c>
-      <c r="C45" s="245" t="s">
-        <v>555</v>
-      </c>
-      <c r="D45" s="245"/>
-      <c r="E45" s="245"/>
-      <c r="F45" s="239"/>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="249" t="s">
-        <v>556</v>
-      </c>
-      <c r="B46" s="260"/>
-      <c r="C46" s="260"/>
+      <c r="B46" s="263"/>
+      <c r="C46" s="263"/>
       <c r="D46" s="239"/>
       <c r="E46" s="239"/>
       <c r="F46" s="239"/>
     </row>
-    <row r="47" spans="1:6" ht="29.25">
+    <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="240" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B47" s="241" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="C47" s="242" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D47" s="242"/>
-      <c r="E47" s="242"/>
+      <c r="E47" s="250"/>
       <c r="F47" s="239"/>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="243" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B48" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C48" s="245" t="s">
+        <v>553</v>
+      </c>
+      <c r="D48" s="245"/>
+      <c r="E48" s="251"/>
+      <c r="F48" s="239"/>
+    </row>
+    <row r="49" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="240" t="s">
+        <v>554</v>
+      </c>
+      <c r="B49" s="241" t="s">
+        <v>555</v>
+      </c>
+      <c r="C49" s="242" t="s">
+        <v>556</v>
+      </c>
+      <c r="D49" s="242"/>
+      <c r="E49" s="250"/>
+      <c r="F49" s="239"/>
+    </row>
+    <row r="50" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="243" t="s">
+        <v>517</v>
+      </c>
+      <c r="B50" s="244" t="s">
+        <v>557</v>
+      </c>
+      <c r="C50" s="245" t="s">
+        <v>558</v>
+      </c>
+      <c r="D50" s="245"/>
+      <c r="E50" s="251"/>
+      <c r="F50" s="239"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="262" t="s">
         <v>559</v>
       </c>
-      <c r="D48" s="245"/>
-      <c r="E48" s="245"/>
-      <c r="F48" s="239"/>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="240" t="s">
-        <v>560</v>
-      </c>
-      <c r="B49" s="241" t="s">
-        <v>561</v>
-      </c>
-      <c r="C49" s="242" t="s">
-        <v>562</v>
-      </c>
-      <c r="D49" s="242"/>
-      <c r="E49" s="242"/>
-      <c r="F49" s="239"/>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="243" t="s">
-        <v>522</v>
-      </c>
-      <c r="B50" s="244" t="s">
-        <v>563</v>
-      </c>
-      <c r="C50" s="245" t="s">
-        <v>564</v>
-      </c>
-      <c r="D50" s="245"/>
-      <c r="E50" s="245"/>
-      <c r="F50" s="239"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="249" t="s">
-        <v>565</v>
-      </c>
-      <c r="B51" s="260"/>
-      <c r="C51" s="260"/>
+      <c r="B51" s="263"/>
+      <c r="C51" s="263"/>
       <c r="D51" s="239"/>
       <c r="E51" s="239"/>
       <c r="F51" s="239"/>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="240" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B52" s="241" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="C52" s="242" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="D52" s="242"/>
-      <c r="E52" s="242"/>
+      <c r="E52" s="250"/>
       <c r="F52" s="239"/>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="243" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="B53" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C53" s="245" t="s">
+        <v>564</v>
+      </c>
+      <c r="D53" s="245"/>
+      <c r="E53" s="251"/>
+      <c r="F53" s="239"/>
+    </row>
+    <row r="54" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="240" t="s">
+        <v>565</v>
+      </c>
+      <c r="B54" s="241" t="s">
+        <v>566</v>
+      </c>
+      <c r="C54" s="242" t="s">
+        <v>567</v>
+      </c>
+      <c r="D54" s="242"/>
+      <c r="E54" s="250"/>
+      <c r="F54" s="239"/>
+    </row>
+    <row r="55" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="243" t="s">
+        <v>568</v>
+      </c>
+      <c r="B55" s="244" t="s">
+        <v>569</v>
+      </c>
+      <c r="C55" s="245" t="s">
         <v>570</v>
       </c>
-      <c r="D53" s="245"/>
-      <c r="E53" s="245"/>
-      <c r="F53" s="239"/>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54" s="240" t="s">
-        <v>571</v>
-      </c>
-      <c r="B54" s="241" t="s">
-        <v>572</v>
-      </c>
-      <c r="C54" s="242" t="s">
-        <v>573</v>
-      </c>
-      <c r="D54" s="242"/>
-      <c r="E54" s="242"/>
-      <c r="F54" s="239"/>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55" s="243" t="s">
-        <v>574</v>
-      </c>
-      <c r="B55" s="244" t="s">
-        <v>575</v>
-      </c>
-      <c r="C55" s="245" t="s">
-        <v>576</v>
-      </c>
       <c r="D55" s="245"/>
-      <c r="E55" s="245"/>
+      <c r="E55" s="251"/>
       <c r="F55" s="239"/>
     </row>
   </sheetData>
@@ -13581,14 +13702,33 @@
     <hyperlink ref="E8" r:id="rId11" xr:uid="{C57DE3BC-5611-4857-AF68-85AE0077E820}"/>
     <hyperlink ref="E5" r:id="rId12" xr:uid="{51324F1C-9EC8-4171-933D-4D6E14F3B038}"/>
     <hyperlink ref="E9" r:id="rId13" xr:uid="{2B5871D6-0326-4F93-B09F-9BD757F4381C}"/>
-    <hyperlink ref="E10" r:id="rId14" xr:uid="{A32D7BDB-2BBC-4255-9428-0E5F6DEE5AE6}"/>
+    <hyperlink ref="E10" r:id="rId14" xr:uid="{8E723CD2-8DD2-4F75-A351-8FF96F018CD7}"/>
+    <hyperlink ref="E15" r:id="rId15" xr:uid="{C118B728-A488-1C49-AB12-0008E7D7FA65}"/>
+    <hyperlink ref="E13" r:id="rId16" display="../../../../../:i:/r/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/2_day2_disney.png?d=wc296c5a87d344b5b919adbf3ef69f77b&amp;csf=1&amp;web=1&amp;e=W92T7o" xr:uid="{A127C563-4395-834B-8788-273A8353BC20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId15"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId17"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005A4695005C4BEE4A8751FEE2C473E10D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df7fcaa21f93254d26451ff7a6d04ad2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xmlns:ns4="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fefbcb393e90fe08e3723c038b505a33" ns3:_="" ns4:_="">
     <xsd:import namespace="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
@@ -13827,31 +13967,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6EF48D-28DC-4A85-AE0A-77598A9ABE97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7"/>
+    <ds:schemaRef ds:uri="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6EF48D-28DC-4A85-AE0A-77598A9ABE97}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
+    <ds:schemaRef ds:uri="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="215" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2628DAD-FC95-4949-A4FD-DFB277BCC235}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4EAD76F-4DF5-4D69-89D2-96B3009EE5BA}"/>
   <bookViews>
-    <workbookView xWindow="1120" yWindow="500" windowWidth="27680" windowHeight="17500" tabRatio="458" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
   <sheets>
     <sheet name="CHI PHÍ" sheetId="5" state="hidden" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="612">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1859,10 +1859,52 @@
     <t>21:00</t>
   </si>
   <si>
-    <t>https://bscvn-my.sharepoint.com/:i:/g/personal/minhpq_bsc_com_vn/IQC7CiWwxjiVRIplj078Znx4Acaavv8CDm1gdMSwltIEihE?e=c4WJI5</t>
-  </si>
-  <si>
-    <t>2_day2_disney</t>
+    <t>2_day2_disney.png</t>
+  </si>
+  <si>
+    <t>2_day2_sushiro.png</t>
+  </si>
+  <si>
+    <t>4_day4_food.png</t>
+  </si>
+  <si>
+    <t>4_day4_hotel.png</t>
+  </si>
+  <si>
+    <t>5_day5_kamikochi.png</t>
+  </si>
+  <si>
+    <t>5_day5_nakanoyu.png</t>
+  </si>
+  <si>
+    <t>3_day3_hotel.png</t>
+  </si>
+  <si>
+    <t>3_day3_food.png</t>
+  </si>
+  <si>
+    <t>3_day3_oshino.png</t>
+  </si>
+  <si>
+    <t>4_day4_lake bake.png</t>
+  </si>
+  <si>
+    <t>4_day4_koshuya.png</t>
+  </si>
+  <si>
+    <t>6_day6_soba.png</t>
+  </si>
+  <si>
+    <t>6_day6_hotel.png</t>
+  </si>
+  <si>
+    <t>6_day6_travel.png</t>
+  </si>
+  <si>
+    <t>6_day6_museum.png</t>
+  </si>
+  <si>
+    <t>7_day7_bamboo.png</t>
   </si>
 </sst>
 </file>
@@ -2273,7 +2315,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="266">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2951,33 +2993,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2986,6 +3001,30 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3003,10 +3042,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3327,19 +3362,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{875223EB-0A06-774B-8ABB-FD2B6BEACF61}">
   <dimension ref="B1:J14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5" style="2"/>
-    <col min="2" max="2" width="31.83203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.5" style="2"/>
-    <col min="6" max="6" width="19.6640625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.5" style="2"/>
-    <col min="8" max="8" width="12.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="11.5" style="2"/>
+    <col min="1" max="1" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="31.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.42578125" style="2"/>
+    <col min="6" max="6" width="19.7109375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.42578125" style="2"/>
+    <col min="8" max="8" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -3357,7 +3392,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
@@ -3376,7 +3411,7 @@
         <v>6500000</v>
       </c>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
@@ -3395,13 +3430,13 @@
         <v>1800000</v>
       </c>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="H4" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>7</v>
       </c>
@@ -3423,7 +3458,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
@@ -3445,7 +3480,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
@@ -3464,7 +3499,7 @@
         <v>1666666.6666666667</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
@@ -3486,7 +3521,7 @@
         <v>2374900</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
@@ -3501,7 +3536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
@@ -3523,7 +3558,7 @@
         <v>8500000</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
@@ -3545,12 +3580,12 @@
         <v>2040000</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
@@ -3571,19 +3606,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0814982B-01D3-4F78-9AD3-6ACFB0D4A3C4}">
   <dimension ref="A1:J172"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="18" customWidth="1"/>
-    <col min="2" max="2" width="9.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="65.5" style="66" customWidth="1"/>
-    <col min="4" max="4" width="50.5" style="67" customWidth="1"/>
-    <col min="5" max="5" width="16.5" style="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="9.1640625" style="10" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" style="10" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" style="18" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="65.42578125" style="66" customWidth="1"/>
+    <col min="4" max="4" width="50.42578125" style="67" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="10" customWidth="1"/>
     <col min="9" max="16384" width="0" style="10" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23"/>
       <c r="B1" s="24"/>
       <c r="C1" s="25" t="s">
@@ -3601,7 +3636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>19</v>
       </c>
@@ -3613,7 +3648,7 @@
       <c r="G2" s="24"/>
       <c r="H2" s="24"/>
     </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="23"/>
       <c r="B3" s="24"/>
       <c r="C3" s="23" t="s">
@@ -3639,7 +3674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="23" t="s">
@@ -3660,7 +3695,7 @@
         <v>3900000</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="23"/>
       <c r="B5" s="24"/>
       <c r="C5" s="23" t="s">
@@ -3682,7 +3717,7 @@
         <v>525000</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>24</v>
       </c>
@@ -3694,7 +3729,7 @@
       <c r="G6" s="24"/>
       <c r="H6" s="30"/>
     </row>
-    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23"/>
       <c r="B7" s="24"/>
       <c r="C7" s="23" t="s">
@@ -3708,7 +3743,7 @@
       <c r="G7" s="24"/>
       <c r="H7" s="30"/>
     </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23"/>
       <c r="B8" s="24"/>
       <c r="C8" s="23" t="s">
@@ -3722,7 +3757,7 @@
       <c r="G8" s="24"/>
       <c r="H8" s="24"/>
     </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="23"/>
       <c r="B9" s="24"/>
       <c r="C9" s="23" t="s">
@@ -3736,7 +3771,7 @@
       <c r="G9" s="24"/>
       <c r="H9" s="24"/>
     </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="23"/>
       <c r="B10" s="24"/>
       <c r="C10" s="23"/>
@@ -3746,7 +3781,7 @@
       <c r="G10" s="24"/>
       <c r="H10" s="24"/>
     </row>
-    <row r="11" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" s="11" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="s">
         <v>28</v>
       </c>
@@ -3758,7 +3793,7 @@
       <c r="G11" s="32"/>
       <c r="H11" s="32"/>
     </row>
-    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="35">
         <v>0.20833333333333334</v>
       </c>
@@ -3774,7 +3809,7 @@
       <c r="G12" s="38"/>
       <c r="H12" s="38"/>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
       <c r="B13" s="38"/>
       <c r="C13" s="40" t="s">
@@ -3795,7 +3830,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="37"/>
       <c r="B14" s="38"/>
       <c r="C14" s="40" t="s">
@@ -3816,7 +3851,7 @@
         <v>9300000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
       <c r="B15" s="38"/>
       <c r="C15" s="40" t="s">
@@ -3828,7 +3863,7 @@
       <c r="G15" s="38"/>
       <c r="H15" s="38"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
       <c r="B16" s="36">
         <v>0.64583333333333337</v>
@@ -3842,7 +3877,7 @@
       <c r="G16" s="38"/>
       <c r="H16" s="38"/>
     </row>
-    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="35">
         <v>0.66666666666666663</v>
       </c>
@@ -3869,7 +3904,7 @@
         <v>6400000</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37"/>
       <c r="B18" s="38"/>
       <c r="C18" s="40" t="s">
@@ -3881,7 +3916,7 @@
       <c r="G18" s="38"/>
       <c r="H18" s="38"/>
     </row>
-    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="37"/>
       <c r="B19" s="38"/>
       <c r="C19" s="37" t="s">
@@ -3893,7 +3928,7 @@
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
     </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="37"/>
       <c r="B20" s="38"/>
       <c r="C20" s="40" t="s">
@@ -3916,7 +3951,7 @@
         <v>86700</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="37"/>
       <c r="B21" s="38"/>
       <c r="C21" s="40" t="s">
@@ -3928,7 +3963,7 @@
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
     </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="35">
         <v>0.75</v>
       </c>
@@ -3954,7 +3989,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="37"/>
       <c r="B23" s="38"/>
       <c r="C23" s="40" t="s">
@@ -3977,7 +4012,7 @@
         <v>984300</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="37"/>
       <c r="B24" s="38"/>
       <c r="C24" s="40" t="s">
@@ -4000,7 +4035,7 @@
         <v>1500000</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="37"/>
       <c r="B25" s="38"/>
       <c r="C25" s="40" t="s">
@@ -4022,7 +4057,7 @@
         <v>255000</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="37"/>
       <c r="B26" s="38"/>
       <c r="C26" s="44"/>
@@ -4032,7 +4067,7 @@
       <c r="G26" s="38"/>
       <c r="H26" s="38"/>
     </row>
-    <row r="27" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="s">
         <v>47</v>
       </c>
@@ -4046,7 +4081,7 @@
       <c r="I27" s="11"/>
       <c r="J27" s="11"/>
     </row>
-    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="35">
         <v>0.25</v>
       </c>
@@ -4073,7 +4108,7 @@
       <c r="I28" s="13"/>
       <c r="J28" s="13"/>
     </row>
-    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="35"/>
       <c r="B29" s="45"/>
       <c r="C29" s="40" t="s">
@@ -4087,7 +4122,7 @@
       <c r="I29" s="13"/>
       <c r="J29" s="13"/>
     </row>
-    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="35"/>
       <c r="B30" s="45"/>
       <c r="C30" s="40" t="s">
@@ -4101,7 +4136,7 @@
       <c r="I30" s="13"/>
       <c r="J30" s="13"/>
     </row>
-    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="35">
         <v>0.27083333333333331</v>
       </c>
@@ -4121,7 +4156,7 @@
       <c r="I31" s="13"/>
       <c r="J31" s="13"/>
     </row>
-    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="35"/>
       <c r="B32" s="38"/>
       <c r="C32" s="37" t="s">
@@ -4147,7 +4182,7 @@
       <c r="I32" s="13"/>
       <c r="J32" s="13"/>
     </row>
-    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="35">
         <v>0.33333333333333331</v>
       </c>
@@ -4175,7 +4210,7 @@
       <c r="I33" s="13"/>
       <c r="J33" s="13"/>
     </row>
-    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="35"/>
       <c r="B34" s="38"/>
       <c r="C34" s="40" t="s">
@@ -4198,7 +4233,7 @@
       <c r="I34" s="13"/>
       <c r="J34" s="13"/>
     </row>
-    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="35">
         <v>0.41666666666666669</v>
       </c>
@@ -4225,7 +4260,7 @@
       <c r="I35" s="13"/>
       <c r="J35" s="13"/>
     </row>
-    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="35">
         <v>0.4375</v>
       </c>
@@ -4254,7 +4289,7 @@
       <c r="I36" s="13"/>
       <c r="J36" s="13"/>
     </row>
-    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="35"/>
       <c r="B37" s="36"/>
       <c r="C37" s="37" t="s">
@@ -4268,7 +4303,7 @@
       <c r="I37" s="13"/>
       <c r="J37" s="13"/>
     </row>
-    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="35"/>
       <c r="B38" s="38"/>
       <c r="C38" s="37" t="s">
@@ -4282,7 +4317,7 @@
       <c r="I38" s="13"/>
       <c r="J38" s="13"/>
     </row>
-    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="35"/>
       <c r="B39" s="38"/>
       <c r="C39" s="37" t="s">
@@ -4296,7 +4331,7 @@
       <c r="I39" s="13"/>
       <c r="J39" s="13"/>
     </row>
-    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="35"/>
       <c r="B40" s="38"/>
       <c r="C40" s="37" t="s">
@@ -4310,7 +4345,7 @@
       <c r="I40" s="13"/>
       <c r="J40" s="13"/>
     </row>
-    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="35"/>
       <c r="B41" s="38"/>
       <c r="C41" s="37" t="s">
@@ -4324,7 +4359,7 @@
       <c r="I41" s="13"/>
       <c r="J41" s="13"/>
     </row>
-    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="35"/>
       <c r="B42" s="38"/>
       <c r="C42" s="37" t="s">
@@ -4338,7 +4373,7 @@
       <c r="I42" s="13"/>
       <c r="J42" s="13"/>
     </row>
-    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="35"/>
       <c r="B43" s="38"/>
       <c r="C43" s="40" t="s">
@@ -4362,7 +4397,7 @@
       <c r="I43" s="13"/>
       <c r="J43" s="13"/>
     </row>
-    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="35">
         <v>0.58333333333333337</v>
       </c>
@@ -4380,7 +4415,7 @@
       <c r="I44" s="13"/>
       <c r="J44" s="13"/>
     </row>
-    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="35"/>
       <c r="B45" s="36"/>
       <c r="C45" s="40" t="s">
@@ -4405,7 +4440,7 @@
       <c r="I45" s="13"/>
       <c r="J45" s="13"/>
     </row>
-    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="35"/>
       <c r="B46" s="36"/>
       <c r="C46" s="40" t="s">
@@ -4419,7 +4454,7 @@
       <c r="I46" s="13"/>
       <c r="J46" s="13"/>
     </row>
-    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="35"/>
       <c r="B47" s="36"/>
       <c r="C47" s="37" t="s">
@@ -4444,7 +4479,7 @@
       <c r="I47" s="13"/>
       <c r="J47" s="13"/>
     </row>
-    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="35">
         <v>0.75</v>
       </c>
@@ -4471,7 +4506,7 @@
       <c r="I48" s="13"/>
       <c r="J48" s="13"/>
     </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="37"/>
       <c r="B49" s="36"/>
       <c r="C49" s="44" t="s">
@@ -4493,7 +4528,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="37"/>
       <c r="B50" s="38"/>
       <c r="C50" s="37" t="s">
@@ -4505,7 +4540,7 @@
       <c r="G50" s="38"/>
       <c r="H50" s="38"/>
     </row>
-    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="37"/>
       <c r="B51" s="38"/>
       <c r="C51" s="37" t="s">
@@ -4517,7 +4552,7 @@
       <c r="G51" s="38"/>
       <c r="H51" s="38"/>
     </row>
-    <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="35">
         <v>0.875</v>
       </c>
@@ -4542,7 +4577,7 @@
         <v>112200</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="35">
         <v>0.91666666666666663</v>
       </c>
@@ -4565,7 +4600,7 @@
         <v>91800</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="35"/>
       <c r="B54" s="36"/>
       <c r="C54" s="40"/>
@@ -4575,7 +4610,7 @@
       <c r="G54" s="38"/>
       <c r="H54" s="39"/>
     </row>
-    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="37"/>
       <c r="B55" s="38"/>
       <c r="C55" s="37" t="s">
@@ -4589,7 +4624,7 @@
       <c r="G55" s="38"/>
       <c r="H55" s="38"/>
     </row>
-    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="37"/>
       <c r="B56" s="38"/>
       <c r="C56" s="37" t="s">
@@ -4603,7 +4638,7 @@
       <c r="G56" s="38"/>
       <c r="H56" s="38"/>
     </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="37"/>
       <c r="B57" s="38"/>
       <c r="C57" s="37" t="s">
@@ -4615,7 +4650,7 @@
       <c r="G57" s="38"/>
       <c r="H57" s="38"/>
     </row>
-    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="37"/>
       <c r="B58" s="38"/>
       <c r="C58" s="37"/>
@@ -4625,7 +4660,7 @@
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
     </row>
-    <row r="59" spans="1:10" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="47" t="s">
         <v>82</v>
       </c>
@@ -4641,7 +4676,7 @@
       <c r="I59" s="14"/>
       <c r="J59" s="14"/>
     </row>
-    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="37"/>
       <c r="B60" s="38"/>
       <c r="C60" s="37" t="s">
@@ -4663,7 +4698,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="37"/>
       <c r="B61" s="38"/>
       <c r="C61" s="37" t="s">
@@ -4684,7 +4719,7 @@
         <v>91800</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="35">
         <v>0.33333333333333331</v>
       </c>
@@ -4709,7 +4744,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="35">
         <v>0.4375</v>
       </c>
@@ -4723,7 +4758,7 @@
       <c r="G63" s="38"/>
       <c r="H63" s="38"/>
     </row>
-    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="35">
         <v>0.48958333333333331</v>
       </c>
@@ -4737,7 +4772,7 @@
       <c r="G64" s="38"/>
       <c r="H64" s="38"/>
     </row>
-    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="35">
         <v>0.52083333333333337</v>
       </c>
@@ -4751,7 +4786,7 @@
       <c r="G65" s="38"/>
       <c r="H65" s="38"/>
     </row>
-    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="35">
         <v>0.60416666666666663</v>
       </c>
@@ -4765,7 +4800,7 @@
       <c r="G66" s="38"/>
       <c r="H66" s="38"/>
     </row>
-    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="35">
         <v>0.63194444444444442</v>
       </c>
@@ -4779,7 +4814,7 @@
       <c r="G67" s="38"/>
       <c r="H67" s="38"/>
     </row>
-    <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="35">
         <v>0.63888888888888884</v>
       </c>
@@ -4793,7 +4828,7 @@
       <c r="G68" s="38"/>
       <c r="H68" s="38"/>
     </row>
-    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="35">
         <v>0.78472222222222221</v>
       </c>
@@ -4807,7 +4842,7 @@
       <c r="G69" s="38"/>
       <c r="H69" s="38"/>
     </row>
-    <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="37"/>
       <c r="B70" s="38"/>
       <c r="C70" s="37"/>
@@ -4817,7 +4852,7 @@
       <c r="G70" s="38"/>
       <c r="H70" s="38"/>
     </row>
-    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="37"/>
       <c r="B71" s="38"/>
       <c r="C71" s="37" t="s">
@@ -4838,7 +4873,7 @@
         <v>91800</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="37"/>
       <c r="B72" s="38"/>
       <c r="C72" s="37" t="s">
@@ -4860,7 +4895,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="37"/>
       <c r="B73" s="38"/>
       <c r="C73" s="37" t="s">
@@ -4872,7 +4907,7 @@
       <c r="G73" s="38"/>
       <c r="H73" s="39"/>
     </row>
-    <row r="74" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="31" t="s">
         <v>97</v>
       </c>
@@ -4886,7 +4921,7 @@
       <c r="I74" s="11"/>
       <c r="J74" s="11"/>
     </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="35"/>
       <c r="B75" s="38"/>
       <c r="C75" s="37" t="s">
@@ -4910,7 +4945,7 @@
       <c r="I75" s="13"/>
       <c r="J75" s="13"/>
     </row>
-    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="35">
         <v>0.33333333333333331</v>
       </c>
@@ -4933,7 +4968,7 @@
         <v>91800</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="37"/>
       <c r="B77" s="38"/>
       <c r="C77" s="37" t="s">
@@ -4956,7 +4991,7 @@
         <v>238000</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="37"/>
       <c r="B78" s="38"/>
       <c r="C78" s="37" t="s">
@@ -4968,7 +5003,7 @@
       <c r="G78" s="38"/>
       <c r="H78" s="39"/>
     </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="35">
         <v>0.41666666666666669</v>
       </c>
@@ -4995,7 +5030,7 @@
         <v>1275000</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="35">
         <v>0.45833333333333331</v>
       </c>
@@ -5021,7 +5056,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="35">
         <v>0.54166666666666663</v>
       </c>
@@ -5046,7 +5081,7 @@
         <v>107100</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="35"/>
       <c r="B82" s="36"/>
       <c r="C82" s="37" t="s">
@@ -5069,7 +5104,7 @@
         <v>1683000</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="35">
         <v>0.625</v>
       </c>
@@ -5094,7 +5129,7 @@
         <v>107100</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="36"/>
       <c r="C84" s="37" t="s">
@@ -5116,7 +5151,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="35">
         <v>0.70833333333333337</v>
       </c>
@@ -5141,7 +5176,7 @@
         <v>7226700</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="35">
         <v>0.8125</v>
       </c>
@@ -5166,7 +5201,7 @@
         <v>2500000</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="37"/>
       <c r="B87" s="38"/>
       <c r="C87" s="37" t="s">
@@ -5180,7 +5215,7 @@
       <c r="G87" s="38"/>
       <c r="H87" s="39"/>
     </row>
-    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="37"/>
       <c r="B88" s="38"/>
       <c r="C88" s="54" t="s">
@@ -5203,7 +5238,7 @@
         <v>255000</v>
       </c>
     </row>
-    <row r="89" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="31" t="s">
         <v>117</v>
       </c>
@@ -5215,7 +5250,7 @@
       <c r="G89" s="32"/>
       <c r="H89" s="32"/>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="35">
         <v>0.29166666666666669</v>
       </c>
@@ -5243,7 +5278,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="44"/>
       <c r="B91" s="45"/>
       <c r="C91" s="37" t="s">
@@ -5266,7 +5301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="44"/>
       <c r="B92" s="45"/>
       <c r="C92" s="37" t="s">
@@ -5289,7 +5324,7 @@
         <v>2550000</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="35">
         <v>0.33333333333333331</v>
       </c>
@@ -5305,7 +5340,7 @@
       <c r="G93" s="38"/>
       <c r="H93" s="38"/>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="37"/>
       <c r="B94" s="38"/>
       <c r="C94" s="40" t="s">
@@ -5319,7 +5354,7 @@
       <c r="G94" s="38"/>
       <c r="H94" s="38"/>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="37"/>
       <c r="B95" s="38"/>
       <c r="C95" s="40" t="s">
@@ -5331,7 +5366,7 @@
       <c r="G95" s="38"/>
       <c r="H95" s="38"/>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="35">
         <v>0.375</v>
       </c>
@@ -5347,7 +5382,7 @@
       <c r="G96" s="38"/>
       <c r="H96" s="38"/>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="37"/>
       <c r="B97" s="38"/>
       <c r="C97" s="40" t="s">
@@ -5370,7 +5405,7 @@
         <v>76500</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="37"/>
       <c r="B98" s="38"/>
       <c r="C98" s="40" t="s">
@@ -5382,7 +5417,7 @@
       <c r="G98" s="38"/>
       <c r="H98" s="39"/>
     </row>
-    <row r="99" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="35">
         <v>0.45833333333333331</v>
       </c>
@@ -5409,7 +5444,7 @@
         <v>117300</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="37"/>
       <c r="B100" s="38"/>
       <c r="C100" s="40" t="s">
@@ -5421,7 +5456,7 @@
       <c r="G100" s="38"/>
       <c r="H100" s="38"/>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="37"/>
       <c r="B101" s="38"/>
       <c r="C101" s="37"/>
@@ -5431,7 +5466,7 @@
       <c r="G101" s="38"/>
       <c r="H101" s="38"/>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="35">
         <v>0.47916666666666669</v>
       </c>
@@ -5459,7 +5494,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="37"/>
       <c r="B103" s="38"/>
       <c r="C103" s="37" t="s">
@@ -5471,7 +5506,7 @@
       <c r="G103" s="38"/>
       <c r="H103" s="38"/>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="35">
         <v>0.54166666666666663</v>
       </c>
@@ -5498,7 +5533,7 @@
         <v>117300</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="37"/>
       <c r="B105" s="38"/>
       <c r="C105" s="40" t="s">
@@ -5510,7 +5545,7 @@
       <c r="G105" s="38"/>
       <c r="H105" s="38"/>
     </row>
-    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="35">
         <v>0.58333333333333337</v>
       </c>
@@ -5526,7 +5561,7 @@
       <c r="G106" s="38"/>
       <c r="H106" s="38"/>
     </row>
-    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="35"/>
       <c r="B107" s="36"/>
       <c r="C107" s="37" t="s">
@@ -5538,7 +5573,7 @@
       <c r="G107" s="38"/>
       <c r="H107" s="38"/>
     </row>
-    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="35"/>
       <c r="B108" s="36">
         <v>0.75</v>
@@ -5552,7 +5587,7 @@
       <c r="G108" s="38"/>
       <c r="H108" s="38"/>
     </row>
-    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="35"/>
       <c r="B109" s="36"/>
       <c r="C109" s="40" t="s">
@@ -5575,7 +5610,7 @@
         <v>234600</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="35"/>
       <c r="B110" s="36"/>
       <c r="C110" s="40" t="s">
@@ -5589,7 +5624,7 @@
       <c r="G110" s="38"/>
       <c r="H110" s="38"/>
     </row>
-    <row r="111" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="35"/>
       <c r="B111" s="36">
         <v>0.79166666666666663</v>
@@ -5613,7 +5648,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="35"/>
       <c r="B112" s="36"/>
       <c r="C112" s="37" t="s">
@@ -5625,7 +5660,7 @@
       <c r="G112" s="38"/>
       <c r="H112" s="38"/>
     </row>
-    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="35"/>
       <c r="B113" s="36"/>
       <c r="C113" s="37" t="s">
@@ -5639,7 +5674,7 @@
       <c r="G113" s="38"/>
       <c r="H113" s="38"/>
     </row>
-    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="35"/>
       <c r="B114" s="36"/>
       <c r="C114" s="37"/>
@@ -5649,7 +5684,7 @@
       <c r="G114" s="38"/>
       <c r="H114" s="38"/>
     </row>
-    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="31" t="s">
         <v>151</v>
       </c>
@@ -5663,7 +5698,7 @@
       <c r="I115" s="12"/>
       <c r="J115" s="12"/>
     </row>
-    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="35"/>
       <c r="B116" s="36">
         <v>0.33333333333333331</v>
@@ -5689,7 +5724,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="35"/>
       <c r="B117" s="36"/>
       <c r="C117" s="37"/>
@@ -5699,7 +5734,7 @@
       <c r="G117" s="38"/>
       <c r="H117" s="38"/>
     </row>
-    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="35"/>
       <c r="B118" s="36">
         <v>0.39583333333333331</v>
@@ -5724,7 +5759,7 @@
         <v>1377000</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="35"/>
       <c r="B119" s="36">
         <v>0.45833333333333331</v>
@@ -5749,7 +5784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="35"/>
       <c r="B120" s="36">
         <v>0.5</v>
@@ -5775,7 +5810,7 @@
         <v>209100</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="35"/>
       <c r="B121" s="36"/>
       <c r="C121" s="54" t="s">
@@ -5789,7 +5824,7 @@
       <c r="G121" s="38"/>
       <c r="H121" s="39"/>
     </row>
-    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="35"/>
       <c r="B122" s="57"/>
       <c r="C122" s="54" t="s">
@@ -5810,7 +5845,7 @@
         <v>59500</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="37"/>
       <c r="B123" s="57">
         <v>0.52083333333333337</v>
@@ -5835,7 +5870,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="37"/>
       <c r="B124" s="57">
         <v>0.58333333333333337</v>
@@ -5860,7 +5895,7 @@
         <v>1110000</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="37"/>
       <c r="B125" s="57">
         <v>0.64583333333333337</v>
@@ -5874,7 +5909,7 @@
       <c r="G125" s="38"/>
       <c r="H125" s="39"/>
     </row>
-    <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="37"/>
       <c r="B126" s="57"/>
       <c r="C126" s="54" t="s">
@@ -5895,7 +5930,7 @@
         <v>122400</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="37"/>
       <c r="B127" s="57">
         <v>0.70833333333333337</v>
@@ -5909,7 +5944,7 @@
       <c r="G127" s="38"/>
       <c r="H127" s="39"/>
     </row>
-    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="37"/>
       <c r="B128" s="57"/>
       <c r="C128" s="54" t="s">
@@ -5932,7 +5967,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="129" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="37"/>
       <c r="B129" s="57"/>
       <c r="C129" s="69" t="s">
@@ -5944,7 +5979,7 @@
       <c r="G129" s="38"/>
       <c r="H129" s="39"/>
     </row>
-    <row r="130" spans="1:8" ht="156.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:8" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="37"/>
       <c r="B130" s="36">
         <v>0.79166666666666663</v>
@@ -5960,7 +5995,7 @@
       <c r="G130" s="38"/>
       <c r="H130" s="38"/>
     </row>
-    <row r="131" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="37"/>
       <c r="B131" s="38"/>
       <c r="C131" s="37" t="s">
@@ -5972,7 +6007,7 @@
       <c r="G131" s="38"/>
       <c r="H131" s="38"/>
     </row>
-    <row r="132" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="37"/>
       <c r="B132" s="38"/>
       <c r="C132" s="37" t="s">
@@ -5993,7 +6028,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="37"/>
       <c r="B133" s="38"/>
       <c r="C133" s="44" t="s">
@@ -6017,7 +6052,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="37"/>
       <c r="B134" s="38"/>
       <c r="C134" s="37" t="s">
@@ -6029,7 +6064,7 @@
       <c r="G134" s="38"/>
       <c r="H134" s="38"/>
     </row>
-    <row r="135" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="37"/>
       <c r="B135" s="38"/>
       <c r="C135" s="54" t="s">
@@ -6041,7 +6076,7 @@
       <c r="G135" s="38"/>
       <c r="H135" s="38"/>
     </row>
-    <row r="136" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="37"/>
       <c r="B136" s="38"/>
       <c r="C136" s="54" t="s">
@@ -6062,10 +6097,10 @@
         <v>122400</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="37"/>
       <c r="B137" s="38"/>
-      <c r="C137" s="254" t="s">
+      <c r="C137" s="257" t="s">
         <v>179</v>
       </c>
       <c r="D137" s="38"/>
@@ -6077,10 +6112,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="37"/>
       <c r="B138" s="38"/>
-      <c r="C138" s="254"/>
+      <c r="C138" s="257"/>
       <c r="D138" s="38"/>
       <c r="E138" s="39"/>
       <c r="F138" s="38"/>
@@ -6090,7 +6125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="37"/>
       <c r="B139" s="38"/>
       <c r="C139" s="54" t="s">
@@ -6111,7 +6146,7 @@
         <v>122400</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="37"/>
       <c r="B140" s="38"/>
       <c r="C140" s="37" t="s">
@@ -6123,7 +6158,7 @@
       <c r="G140" s="38"/>
       <c r="H140" s="38"/>
     </row>
-    <row r="141" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="37"/>
       <c r="B141" s="38"/>
       <c r="C141" s="37" t="s">
@@ -6135,7 +6170,7 @@
       <c r="G141" s="38"/>
       <c r="H141" s="38"/>
     </row>
-    <row r="142" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="58" t="s">
         <v>182</v>
       </c>
@@ -6147,7 +6182,7 @@
       <c r="G142" s="59"/>
       <c r="H142" s="59"/>
     </row>
-    <row r="143" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="44"/>
       <c r="B143" s="57">
         <v>0.29166666666666669</v>
@@ -6173,7 +6208,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="44"/>
       <c r="B144" s="57">
         <v>0.375</v>
@@ -6198,7 +6233,7 @@
         <v>423300</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="44"/>
       <c r="B145" s="55"/>
       <c r="C145" s="54"/>
@@ -6219,7 +6254,7 @@
         <v>408000</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="44"/>
       <c r="B146" s="57">
         <v>0.41666666666666669</v>
@@ -6244,7 +6279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="44"/>
       <c r="B147" s="57">
         <v>0.45833333333333331</v>
@@ -6269,7 +6304,7 @@
         <v>91800</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="44"/>
       <c r="B148" s="57">
         <v>0.47916666666666669</v>
@@ -6294,7 +6329,7 @@
         <v>612000</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="37"/>
       <c r="B149" s="36">
         <v>0.60416666666666663</v>
@@ -6319,7 +6354,7 @@
         <v>1785000</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="37"/>
       <c r="B150" s="36"/>
       <c r="C150" s="37" t="s">
@@ -6340,7 +6375,7 @@
         <v>183600</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="37"/>
       <c r="B151" s="36"/>
       <c r="C151" s="37" t="s">
@@ -6363,7 +6398,7 @@
         <v>510000</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="37"/>
       <c r="B152" s="36">
         <v>0.83333333333333337</v>
@@ -6377,7 +6412,7 @@
       <c r="G152" s="38"/>
       <c r="H152" s="38"/>
     </row>
-    <row r="153" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="37"/>
       <c r="B153" s="36"/>
       <c r="C153" s="37" t="s">
@@ -6398,7 +6433,7 @@
         <v>249900</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="37"/>
       <c r="B154" s="36"/>
       <c r="C154" s="37" t="s">
@@ -6412,7 +6447,7 @@
       <c r="G154" s="38"/>
       <c r="H154" s="38"/>
     </row>
-    <row r="155" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="37"/>
       <c r="B155" s="36"/>
       <c r="C155" s="37" t="s">
@@ -6424,7 +6459,7 @@
       <c r="G155" s="38"/>
       <c r="H155" s="38"/>
     </row>
-    <row r="156" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="37"/>
       <c r="B156" s="36"/>
       <c r="C156" s="37" t="s">
@@ -6436,7 +6471,7 @@
       <c r="G156" s="38"/>
       <c r="H156" s="38"/>
     </row>
-    <row r="157" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="37"/>
       <c r="B157" s="36"/>
       <c r="C157" s="37" t="s">
@@ -6457,7 +6492,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="37"/>
       <c r="B158" s="36"/>
       <c r="C158" s="37" t="s">
@@ -6469,7 +6504,7 @@
       <c r="G158" s="38"/>
       <c r="H158" s="38"/>
     </row>
-    <row r="159" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:8" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="61" t="s">
         <v>200</v>
       </c>
@@ -6481,7 +6516,7 @@
       <c r="G159" s="61"/>
       <c r="H159" s="61"/>
     </row>
-    <row r="160" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="37"/>
       <c r="B160" s="38"/>
       <c r="C160" s="37" t="s">
@@ -6495,7 +6530,7 @@
       <c r="G160" s="38"/>
       <c r="H160" s="38"/>
     </row>
-    <row r="161" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="37"/>
       <c r="B161" s="38"/>
       <c r="C161" s="37" t="s">
@@ -6516,7 +6551,7 @@
         <v>238000</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="37"/>
       <c r="B162" s="36">
         <v>0.29166666666666669</v>
@@ -6540,7 +6575,7 @@
         <v>153000</v>
       </c>
     </row>
-    <row r="163" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="37"/>
       <c r="B163" s="36">
         <v>0.3125</v>
@@ -6554,7 +6589,7 @@
       <c r="G163" s="38"/>
       <c r="H163" s="39"/>
     </row>
-    <row r="164" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="37"/>
       <c r="B164" s="36"/>
       <c r="C164" s="37" t="s">
@@ -6575,7 +6610,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="37"/>
       <c r="B165" s="36">
         <v>0.375</v>
@@ -6600,7 +6635,7 @@
         <v>170000</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="37"/>
       <c r="B166" s="57">
         <v>0.45833333333333331</v>
@@ -6625,7 +6660,7 @@
         <v>1020000</v>
       </c>
     </row>
-    <row r="167" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="37"/>
       <c r="B167" s="57">
         <v>0.5</v>
@@ -6650,7 +6685,7 @@
         <v>96900</v>
       </c>
     </row>
-    <row r="168" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="37"/>
       <c r="B168" s="57">
         <v>0.5625</v>
@@ -6675,7 +6710,7 @@
         <v>494700</v>
       </c>
     </row>
-    <row r="169" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="37"/>
       <c r="B169" s="38" t="s">
         <v>213</v>
@@ -6698,7 +6733,7 @@
         <v>12000000</v>
       </c>
     </row>
-    <row r="170" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="17"/>
       <c r="B170" s="17"/>
       <c r="C170" s="23"/>
@@ -6708,7 +6743,7 @@
       <c r="G170" s="17"/>
       <c r="H170" s="17"/>
     </row>
-    <row r="171" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B171" s="17"/>
       <c r="C171" s="23"/>
       <c r="D171" s="23"/>
@@ -6720,7 +6755,7 @@
         <v>74613700</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B172" s="17"/>
       <c r="C172" s="23"/>
       <c r="D172" s="23"/>
@@ -6759,22 +6794,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L123"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="202" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="91" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" style="208" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" style="208" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="169" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.1640625" style="203" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="91" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="91" customWidth="1"/>
+    <col min="3" max="3" width="48.28515625" style="208" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" style="208" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="169" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="203" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="91" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="169" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" style="91" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" style="91" customWidth="1"/>
-    <col min="11" max="16384" width="10.83203125" style="91"/>
+    <col min="9" max="9" width="12.140625" style="91" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" style="91" customWidth="1"/>
+    <col min="11" max="16384" width="10.85546875" style="91"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="83" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="83" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="210" t="s">
         <v>216</v>
       </c>
@@ -6806,12 +6841,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="255" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="255" t="s">
+    <row r="2" spans="1:10" s="258" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="258" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="84"/>
       <c r="B3" s="85"/>
       <c r="C3" s="86" t="s">
@@ -6829,7 +6864,7 @@
       <c r="I3" s="90"/>
       <c r="J3" s="90"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="92"/>
       <c r="B4" s="85"/>
       <c r="C4" s="93" t="s">
@@ -6843,7 +6878,7 @@
       <c r="I4" s="85"/>
       <c r="J4" s="85"/>
     </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="84"/>
       <c r="B5" s="85"/>
       <c r="C5" s="84" t="s">
@@ -6870,7 +6905,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="84"/>
       <c r="B6" s="85"/>
       <c r="C6" s="84" t="s">
@@ -6897,7 +6932,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="93"/>
       <c r="B7" s="85"/>
       <c r="C7" s="93" t="s">
@@ -6911,13 +6946,13 @@
       <c r="I7" s="96"/>
       <c r="J7" s="96"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="84"/>
       <c r="B8" s="85"/>
-      <c r="C8" s="256" t="s">
+      <c r="C8" s="259" t="s">
         <v>230</v>
       </c>
-      <c r="D8" s="256"/>
+      <c r="D8" s="259"/>
       <c r="E8" s="96">
         <v>1500</v>
       </c>
@@ -6927,7 +6962,7 @@
       <c r="I8" s="96"/>
       <c r="J8" s="96"/>
     </row>
-    <row r="9" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="84"/>
       <c r="B9" s="85"/>
       <c r="C9" s="84" t="s">
@@ -6943,7 +6978,7 @@
       <c r="I9" s="85"/>
       <c r="J9" s="85"/>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="84"/>
       <c r="B10" s="85"/>
       <c r="C10" s="84" t="s">
@@ -6959,11 +6994,11 @@
       <c r="I10" s="85"/>
       <c r="J10" s="85"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="256" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="259" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="256"/>
+      <c r="B11" s="259"/>
       <c r="C11" s="99">
         <v>27</v>
       </c>
@@ -6975,7 +7010,7 @@
       <c r="I11" s="85"/>
       <c r="J11" s="85"/>
     </row>
-    <row r="12" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="72" t="str">
         <f>"Ngày 1: "&amp;C11&amp;"/11/2025 - Thứ 6 - XUẤT PHÁT TỪ HÀ NỘI + ODAIBA"</f>
         <v>Ngày 1: 27/11/2025 - Thứ 6 - XUẤT PHÁT TỪ HÀ NỘI + ODAIBA</v>
@@ -6990,7 +7025,7 @@
       <c r="I12" s="73"/>
       <c r="J12" s="73"/>
     </row>
-    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="114">
         <v>3.8194444444444441E-2</v>
       </c>
@@ -7022,7 +7057,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -7040,7 +7075,7 @@
       <c r="I14" s="96"/>
       <c r="J14" s="96"/>
     </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="114">
         <v>0.40277777777777773</v>
       </c>
@@ -7069,7 +7104,7 @@
       <c r="I15" s="96"/>
       <c r="J15" s="96"/>
     </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="114">
         <v>0.45833333333333331</v>
       </c>
@@ -7099,7 +7134,7 @@
       <c r="I16" s="96"/>
       <c r="J16" s="96"/>
     </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="114">
         <v>0.45833333333333331</v>
       </c>
@@ -7128,7 +7163,7 @@
       </c>
       <c r="J17" s="96"/>
     </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="114">
         <v>0.55208333333333337</v>
       </c>
@@ -7157,7 +7192,7 @@
       <c r="I18" s="96"/>
       <c r="J18" s="96"/>
     </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="114">
         <v>0.58333333333333337</v>
       </c>
@@ -7186,7 +7221,7 @@
       <c r="I19" s="96"/>
       <c r="J19" s="96"/>
     </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="114">
         <v>0.6875</v>
       </c>
@@ -7207,7 +7242,7 @@
       <c r="I20" s="96"/>
       <c r="J20" s="96"/>
     </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="114">
         <v>0.75</v>
       </c>
@@ -7236,7 +7271,7 @@
       </c>
       <c r="J21" s="96"/>
     </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="114">
         <v>0.875</v>
       </c>
@@ -7263,7 +7298,7 @@
       <c r="I22" s="96"/>
       <c r="J22" s="96"/>
     </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="114">
         <v>0.91666666666666663</v>
       </c>
@@ -7291,7 +7326,7 @@
       <c r="I23" s="96"/>
       <c r="J23" s="96"/>
     </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="114"/>
       <c r="B24" s="109"/>
       <c r="C24" s="107"/>
@@ -7303,7 +7338,7 @@
       <c r="I24" s="96"/>
       <c r="J24" s="96"/>
     </row>
-    <row r="25" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="114"/>
       <c r="B25" s="109"/>
       <c r="C25" s="235" t="s">
@@ -7317,7 +7352,7 @@
       <c r="I25" s="96"/>
       <c r="J25" s="96"/>
     </row>
-    <row r="26" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="114"/>
       <c r="B26" s="109"/>
       <c r="C26" s="107" t="s">
@@ -7331,7 +7366,7 @@
       <c r="I26" s="96"/>
       <c r="J26" s="96"/>
     </row>
-    <row r="27" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="114"/>
       <c r="B27" s="109"/>
       <c r="C27" s="107" t="s">
@@ -7345,7 +7380,7 @@
       <c r="I27" s="96"/>
       <c r="J27" s="96"/>
     </row>
-    <row r="28" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="114"/>
       <c r="B28" s="109"/>
       <c r="C28" s="107" t="s">
@@ -7359,7 +7394,7 @@
       <c r="I28" s="96"/>
       <c r="J28" s="96"/>
     </row>
-    <row r="29" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="114"/>
       <c r="B29" s="109"/>
       <c r="C29" s="107" t="s">
@@ -7373,7 +7408,7 @@
       <c r="I29" s="96"/>
       <c r="J29" s="96"/>
     </row>
-    <row r="30" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="114"/>
       <c r="B30" s="109"/>
       <c r="C30" s="107" t="s">
@@ -7387,7 +7422,7 @@
       <c r="I30" s="96"/>
       <c r="J30" s="96"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="114"/>
       <c r="B31" s="109"/>
       <c r="C31" s="107"/>
@@ -7399,7 +7434,7 @@
       <c r="I31" s="96"/>
       <c r="J31" s="96"/>
     </row>
-    <row r="32" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="72" t="str">
         <f>"Ngày 2: "&amp;C11+1&amp;"/11/2025 - Thứ 7 - PHÚ SĨ 2 NGÀY 1 ĐÊM"</f>
         <v>Ngày 2: 28/11/2025 - Thứ 7 - PHÚ SĨ 2 NGÀY 1 ĐÊM</v>
@@ -7416,7 +7451,7 @@
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="217">
         <v>0.25</v>
       </c>
@@ -7445,7 +7480,7 @@
       </c>
       <c r="J33" s="222"/>
     </row>
-    <row r="34" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="224"/>
       <c r="B34" s="222"/>
       <c r="C34" s="225" t="s">
@@ -7459,7 +7494,7 @@
       <c r="I34" s="222"/>
       <c r="J34" s="222"/>
     </row>
-    <row r="35" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="224"/>
       <c r="B35" s="222"/>
       <c r="C35" s="225" t="s">
@@ -7473,7 +7508,7 @@
       <c r="I35" s="222"/>
       <c r="J35" s="222"/>
     </row>
-    <row r="36" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="224"/>
       <c r="B36" s="222"/>
       <c r="C36" s="225" t="s">
@@ -7487,7 +7522,7 @@
       <c r="I36" s="222"/>
       <c r="J36" s="222"/>
     </row>
-    <row r="37" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="224"/>
       <c r="B37" s="222"/>
       <c r="C37" s="225" t="s">
@@ -7501,7 +7536,7 @@
       <c r="I37" s="222"/>
       <c r="J37" s="222"/>
     </row>
-    <row r="38" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="224"/>
       <c r="B38" s="222"/>
       <c r="C38" s="225" t="s">
@@ -7515,7 +7550,7 @@
       <c r="I38" s="222"/>
       <c r="J38" s="222"/>
     </row>
-    <row r="39" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="217">
         <v>0.5</v>
       </c>
@@ -7541,7 +7576,7 @@
       <c r="I39" s="222"/>
       <c r="J39" s="222"/>
     </row>
-    <row r="40" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="224"/>
       <c r="B40" s="222"/>
       <c r="C40" s="219" t="s">
@@ -7566,7 +7601,7 @@
       </c>
       <c r="J40" s="222"/>
     </row>
-    <row r="41" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="224"/>
       <c r="B41" s="222"/>
       <c r="C41" s="219" t="s">
@@ -7580,7 +7615,7 @@
       <c r="I41" s="222"/>
       <c r="J41" s="222"/>
     </row>
-    <row r="42" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="217">
         <v>0.75</v>
       </c>
@@ -7609,7 +7644,7 @@
       </c>
       <c r="J42" s="222"/>
     </row>
-    <row r="43" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="217">
         <v>0.91666666666666663</v>
       </c>
@@ -7637,7 +7672,7 @@
       <c r="I43" s="222"/>
       <c r="J43" s="222"/>
     </row>
-    <row r="44" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="217"/>
       <c r="B44" s="218"/>
       <c r="C44" s="219"/>
@@ -7649,7 +7684,7 @@
       <c r="I44" s="222"/>
       <c r="J44" s="222"/>
     </row>
-    <row r="45" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="72" t="str">
         <f>"Ngày 3: "&amp;C11+2&amp;"/11/2025 - PHÚ SĨ HIDDEN PLACES"</f>
         <v>Ngày 3: 29/11/2025 - PHÚ SĨ HIDDEN PLACES</v>
@@ -7666,7 +7701,7 @@
       <c r="K45" s="14"/>
       <c r="L45" s="14"/>
     </row>
-    <row r="46" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -7693,7 +7728,7 @@
       <c r="K46" s="130"/>
       <c r="L46" s="130"/>
     </row>
-    <row r="47" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="114"/>
       <c r="B47" s="85"/>
       <c r="C47" s="107" t="s">
@@ -7718,7 +7753,7 @@
       <c r="I47" s="96"/>
       <c r="J47" s="96"/>
     </row>
-    <row r="48" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="114"/>
       <c r="B48" s="85"/>
       <c r="C48" s="107" t="s">
@@ -7736,7 +7771,7 @@
       <c r="I48" s="96"/>
       <c r="J48" s="96"/>
     </row>
-    <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="114"/>
       <c r="B49" s="85"/>
       <c r="C49" s="107" t="s">
@@ -7754,7 +7789,7 @@
       <c r="I49" s="96"/>
       <c r="J49" s="96"/>
     </row>
-    <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="114"/>
       <c r="B50" s="85"/>
       <c r="C50" s="107" t="s">
@@ -7772,7 +7807,7 @@
       <c r="I50" s="96"/>
       <c r="J50" s="96"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="114"/>
       <c r="B51" s="85"/>
       <c r="C51" s="84"/>
@@ -7784,7 +7819,7 @@
       <c r="I51" s="96"/>
       <c r="J51" s="96"/>
     </row>
-    <row r="52" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="114"/>
       <c r="B52" s="85"/>
       <c r="C52" s="107" t="s">
@@ -7798,7 +7833,7 @@
       <c r="I52" s="96"/>
       <c r="J52" s="96"/>
     </row>
-    <row r="53" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="114"/>
       <c r="B53" s="85"/>
       <c r="C53" s="107" t="s">
@@ -7814,7 +7849,7 @@
       <c r="I53" s="96"/>
       <c r="J53" s="96"/>
     </row>
-    <row r="54" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="114"/>
       <c r="B54" s="85"/>
       <c r="C54" s="107" t="s">
@@ -7830,7 +7865,7 @@
       <c r="I54" s="96"/>
       <c r="J54" s="96"/>
     </row>
-    <row r="55" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="114"/>
       <c r="B55" s="85"/>
       <c r="C55" s="107" t="s">
@@ -7848,7 +7883,7 @@
       <c r="I55" s="96"/>
       <c r="J55" s="96"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="114"/>
       <c r="B56" s="85"/>
       <c r="C56" s="84"/>
@@ -7860,7 +7895,7 @@
       <c r="I56" s="96"/>
       <c r="J56" s="96"/>
     </row>
-    <row r="57" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="114">
         <v>0.5</v>
       </c>
@@ -7886,7 +7921,7 @@
       <c r="I57" s="96"/>
       <c r="J57" s="96"/>
     </row>
-    <row r="58" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="114">
         <v>0.625</v>
       </c>
@@ -7913,7 +7948,7 @@
       <c r="I58" s="96"/>
       <c r="J58" s="96"/>
     </row>
-    <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="114">
         <v>0.79166666666666663</v>
       </c>
@@ -7940,7 +7975,7 @@
       <c r="I59" s="96"/>
       <c r="J59" s="96"/>
     </row>
-    <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="114"/>
       <c r="B60" s="85"/>
       <c r="C60" s="230" t="s">
@@ -7966,7 +8001,7 @@
       </c>
       <c r="J60" s="96"/>
     </row>
-    <row r="61" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="114"/>
       <c r="B61" s="85"/>
       <c r="C61" s="84" t="s">
@@ -7992,7 +8027,7 @@
       <c r="I61" s="96"/>
       <c r="J61" s="96"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="114"/>
       <c r="B62" s="85"/>
       <c r="C62" s="84"/>
@@ -8004,7 +8039,7 @@
       <c r="I62" s="96"/>
       <c r="J62" s="96"/>
     </row>
-    <row r="63" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="72" t="str">
         <f>"Ngày 4: "&amp;C11+3&amp;"/11/2025 - NGHỈ SÁNG, ĐI NAGANO, HAKUBA"</f>
         <v>Ngày 4: 30/11/2025 - NGHỈ SÁNG, ĐI NAGANO, HAKUBA</v>
@@ -8019,7 +8054,7 @@
       <c r="I63" s="73"/>
       <c r="J63" s="73"/>
     </row>
-    <row r="64" spans="1:10" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="217">
         <v>0.33333333333333331</v>
       </c>
@@ -8050,7 +8085,7 @@
       </c>
       <c r="J64" s="222"/>
     </row>
-    <row r="65" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="224"/>
       <c r="B65" s="222"/>
       <c r="C65" s="219" t="s">
@@ -8074,7 +8109,7 @@
       <c r="I65" s="222"/>
       <c r="J65" s="222"/>
     </row>
-    <row r="66" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="224"/>
       <c r="B66" s="222"/>
       <c r="C66" s="219" t="s">
@@ -8099,7 +8134,7 @@
       </c>
       <c r="J66" s="222"/>
     </row>
-    <row r="67" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="217">
         <v>0.58333333333333337</v>
       </c>
@@ -8126,7 +8161,7 @@
       <c r="I67" s="222"/>
       <c r="J67" s="222"/>
     </row>
-    <row r="68" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="224"/>
       <c r="B68" s="222"/>
       <c r="C68" s="219" t="s">
@@ -8149,7 +8184,7 @@
       <c r="I68" s="222"/>
       <c r="J68" s="222"/>
     </row>
-    <row r="69" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="224"/>
       <c r="B69" s="222"/>
       <c r="C69" s="219"/>
@@ -8170,7 +8205,7 @@
       <c r="I69" s="222"/>
       <c r="J69" s="222"/>
     </row>
-    <row r="70" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="226"/>
       <c r="B70" s="218"/>
       <c r="C70" s="219" t="s">
@@ -8193,7 +8228,7 @@
       <c r="I70" s="222"/>
       <c r="J70" s="222"/>
     </row>
-    <row r="71" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="226">
         <v>0.83333333333333337</v>
       </c>
@@ -8219,7 +8254,7 @@
       <c r="I71" s="222"/>
       <c r="J71" s="222"/>
     </row>
-    <row r="72" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="226"/>
       <c r="B72" s="218"/>
       <c r="C72" s="219" t="s">
@@ -8245,7 +8280,7 @@
       <c r="I72" s="222"/>
       <c r="J72" s="222"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="114"/>
       <c r="B73" s="109"/>
       <c r="C73" s="84"/>
@@ -8257,7 +8292,7 @@
       <c r="I73" s="85"/>
       <c r="J73" s="85"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="72" t="str">
         <f>"Ngày 5: "&amp;"1/12/2025 -  HAKUBA SKI RESORT"</f>
         <v>Ngày 5: 1/12/2025 -  HAKUBA SKI RESORT</v>
@@ -8274,7 +8309,7 @@
       <c r="K74" s="15"/>
       <c r="L74" s="15"/>
     </row>
-    <row r="75" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="217">
         <v>0.33333333333333331</v>
       </c>
@@ -8301,7 +8336,7 @@
       <c r="I75" s="222"/>
       <c r="J75" s="222"/>
     </row>
-    <row r="76" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="224"/>
       <c r="B76" s="222"/>
       <c r="C76" s="219" t="s">
@@ -8326,7 +8361,7 @@
       <c r="I76" s="222"/>
       <c r="J76" s="222"/>
     </row>
-    <row r="77" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="224"/>
       <c r="B77" s="222"/>
       <c r="C77" s="225" t="s">
@@ -8349,7 +8384,7 @@
       <c r="I77" s="222"/>
       <c r="J77" s="222"/>
     </row>
-    <row r="78" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="224"/>
       <c r="B78" s="222"/>
       <c r="C78" s="225" t="s">
@@ -8372,7 +8407,7 @@
       <c r="I78" s="222"/>
       <c r="J78" s="222"/>
     </row>
-    <row r="79" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="224"/>
       <c r="B79" s="222"/>
       <c r="C79" s="225" t="s">
@@ -8395,7 +8430,7 @@
       <c r="I79" s="222"/>
       <c r="J79" s="222"/>
     </row>
-    <row r="80" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="224"/>
       <c r="B80" s="222"/>
       <c r="C80" s="219" t="s">
@@ -8419,7 +8454,7 @@
       <c r="I80" s="222"/>
       <c r="J80" s="222"/>
     </row>
-    <row r="81" spans="1:12" s="223" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" s="223" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="224"/>
       <c r="B81" s="222"/>
       <c r="C81" s="219" t="s">
@@ -8442,7 +8477,7 @@
       <c r="I81" s="222"/>
       <c r="J81" s="222"/>
     </row>
-    <row r="82" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="84"/>
       <c r="B82" s="85"/>
       <c r="C82" s="84" t="s">
@@ -8467,7 +8502,7 @@
       </c>
       <c r="J82" s="85"/>
     </row>
-    <row r="83" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="84"/>
       <c r="B83" s="85"/>
       <c r="C83" s="84" t="s">
@@ -8493,7 +8528,7 @@
       <c r="I83" s="85"/>
       <c r="J83" s="85"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="84"/>
       <c r="B84" s="85"/>
       <c r="C84" s="84"/>
@@ -8505,7 +8540,7 @@
       <c r="I84" s="85"/>
       <c r="J84" s="85"/>
     </row>
-    <row r="85" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="186" t="str">
         <f>"Ngày 6: "&amp;"2/12/2025 - HAKUBA _ KYOTO"</f>
         <v>Ngày 6: 2/12/2025 - HAKUBA _ KYOTO</v>
@@ -8520,7 +8555,7 @@
       <c r="I85" s="187"/>
       <c r="J85" s="187"/>
     </row>
-    <row r="86" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A86" s="157"/>
       <c r="B86" s="174"/>
       <c r="C86" s="164" t="s">
@@ -8545,7 +8580,7 @@
       <c r="I86" s="96"/>
       <c r="J86" s="96"/>
     </row>
-    <row r="87" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="84"/>
       <c r="B87" s="109"/>
       <c r="C87" s="84" t="s">
@@ -8568,7 +8603,7 @@
       <c r="I87" s="96"/>
       <c r="J87" s="96"/>
     </row>
-    <row r="88" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="84"/>
       <c r="B88" s="109"/>
       <c r="C88" s="84" t="s">
@@ -8592,7 +8627,7 @@
       <c r="I88" s="96"/>
       <c r="J88" s="96"/>
     </row>
-    <row r="89" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="84"/>
       <c r="B89" s="109"/>
       <c r="C89" s="84" t="s">
@@ -8617,7 +8652,7 @@
       </c>
       <c r="J89" s="96"/>
     </row>
-    <row r="90" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="84"/>
       <c r="B90" s="109"/>
       <c r="C90" s="84" t="s">
@@ -8641,7 +8676,7 @@
       <c r="I90" s="96"/>
       <c r="J90" s="96"/>
     </row>
-    <row r="91" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="84"/>
       <c r="B91" s="109"/>
       <c r="C91" s="84" t="s">
@@ -8667,7 +8702,7 @@
       </c>
       <c r="J91" s="96"/>
     </row>
-    <row r="92" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="84"/>
       <c r="B92" s="109"/>
       <c r="C92" s="84" t="s">
@@ -8693,7 +8728,7 @@
       <c r="I92" s="96"/>
       <c r="J92" s="96"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="84"/>
       <c r="B93" s="109"/>
       <c r="C93" s="84"/>
@@ -8705,7 +8740,7 @@
       <c r="I93" s="96"/>
       <c r="J93" s="96"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="194" t="str">
         <f>"Ngày 7: "&amp;"3/12/2025 - ĐI NGẮM LÁ ĐỎ Ở ARMANASHI"</f>
         <v>Ngày 7: 3/12/2025 - ĐI NGẮM LÁ ĐỎ Ở ARMANASHI</v>
@@ -8722,7 +8757,7 @@
       <c r="K94" s="15"/>
       <c r="L94" s="15"/>
     </row>
-    <row r="95" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="84"/>
       <c r="B95" s="228"/>
       <c r="C95" s="229" t="s">
@@ -8745,7 +8780,7 @@
       <c r="I95" s="85"/>
       <c r="J95" s="85"/>
     </row>
-    <row r="96" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="84"/>
       <c r="B96" s="228"/>
       <c r="C96" s="232" t="s">
@@ -8768,7 +8803,7 @@
       <c r="I96" s="85"/>
       <c r="J96" s="85"/>
     </row>
-    <row r="97" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="84"/>
       <c r="B97" s="228"/>
       <c r="C97" s="232" t="s">
@@ -8782,7 +8817,7 @@
       <c r="I97" s="85"/>
       <c r="J97" s="85"/>
     </row>
-    <row r="98" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="84"/>
       <c r="B98" s="228"/>
       <c r="C98" s="232" t="s">
@@ -8805,7 +8840,7 @@
       <c r="I98" s="85"/>
       <c r="J98" s="85"/>
     </row>
-    <row r="99" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="84"/>
       <c r="B99" s="228"/>
       <c r="C99" s="229" t="s">
@@ -8828,7 +8863,7 @@
       <c r="I99" s="85"/>
       <c r="J99" s="85"/>
     </row>
-    <row r="100" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="84"/>
       <c r="B100" s="109"/>
       <c r="C100" s="84" t="s">
@@ -8851,7 +8886,7 @@
       <c r="I100" s="96"/>
       <c r="J100" s="96"/>
     </row>
-    <row r="101" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="84"/>
       <c r="B101" s="109"/>
       <c r="C101" s="84" t="s">
@@ -8876,7 +8911,7 @@
       </c>
       <c r="J101" s="96"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="84"/>
       <c r="B102" s="228"/>
       <c r="C102" s="229"/>
@@ -8888,7 +8923,7 @@
       <c r="I102" s="85"/>
       <c r="J102" s="85"/>
     </row>
-    <row r="103" spans="1:10" s="15" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="197" t="str">
         <f>"Ngày 8: "&amp;"4/12/2025 - ĐI CHÙA KATSUOJI - CẦU NGUYỆN"</f>
         <v>Ngày 8: 4/12/2025 - ĐI CHÙA KATSUOJI - CẦU NGUYỆN</v>
@@ -8905,7 +8940,7 @@
       <c r="I103" s="195"/>
       <c r="J103" s="195"/>
     </row>
-    <row r="104" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="84"/>
       <c r="B104" s="109"/>
       <c r="C104" s="84" t="s">
@@ -8928,7 +8963,7 @@
       <c r="I104" s="96"/>
       <c r="J104" s="96"/>
     </row>
-    <row r="105" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="84"/>
       <c r="B105" s="109"/>
       <c r="C105" s="84" t="s">
@@ -8953,7 +8988,7 @@
       </c>
       <c r="J105" s="96"/>
     </row>
-    <row r="106" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="84"/>
       <c r="B106" s="109"/>
       <c r="C106" s="84" t="s">
@@ -8967,7 +9002,7 @@
       <c r="I106" s="96"/>
       <c r="J106" s="96"/>
     </row>
-    <row r="107" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="84"/>
       <c r="B107" s="109"/>
       <c r="C107" s="84" t="s">
@@ -8990,7 +9025,7 @@
       <c r="I107" s="96"/>
       <c r="J107" s="96"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="84"/>
       <c r="B108" s="109"/>
       <c r="C108" s="84"/>
@@ -9002,7 +9037,7 @@
       <c r="I108" s="96"/>
       <c r="J108" s="96"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="84"/>
       <c r="B109" s="109"/>
       <c r="C109" s="84"/>
@@ -9014,7 +9049,7 @@
       <c r="I109" s="96"/>
       <c r="J109" s="96"/>
     </row>
-    <row r="110" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="197" t="str">
         <f>"Ngày 9: "&amp;"5/12/2025 - ĐI VỀ HÀ NỘI"</f>
         <v>Ngày 9: 5/12/2025 - ĐI VỀ HÀ NỘI</v>
@@ -9029,7 +9064,7 @@
       <c r="I110" s="195"/>
       <c r="J110" s="195"/>
     </row>
-    <row r="111" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="84"/>
       <c r="B111" s="85"/>
       <c r="C111" s="84" t="s">
@@ -9045,7 +9080,7 @@
       <c r="I111" s="85"/>
       <c r="J111" s="85"/>
     </row>
-    <row r="112" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="84"/>
       <c r="B112" s="85"/>
       <c r="C112" s="84" t="s">
@@ -9069,7 +9104,7 @@
       <c r="I112" s="85"/>
       <c r="J112" s="85"/>
     </row>
-    <row r="113" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="102"/>
       <c r="B113" s="176">
         <v>0.5625</v>
@@ -9096,7 +9131,7 @@
       <c r="I113" s="103"/>
       <c r="J113" s="103"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="114"/>
       <c r="B114" s="109"/>
       <c r="C114" s="84"/>
@@ -9108,7 +9143,7 @@
       <c r="I114" s="200"/>
       <c r="J114" s="200"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="114"/>
       <c r="B115" s="109"/>
       <c r="C115" s="84"/>
@@ -9120,7 +9155,7 @@
       <c r="I115" s="200"/>
       <c r="J115" s="200"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="114"/>
       <c r="B116" s="109"/>
       <c r="C116" s="84"/>
@@ -9132,7 +9167,7 @@
       <c r="I116" s="200"/>
       <c r="J116" s="200"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="199"/>
       <c r="B117" s="199"/>
       <c r="C117" s="84"/>
@@ -9144,7 +9179,7 @@
       <c r="I117" s="199"/>
       <c r="J117" s="199"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B118" s="199"/>
       <c r="C118" s="84"/>
       <c r="D118" s="84"/>
@@ -9161,7 +9196,7 @@
       </c>
       <c r="J118" s="204"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B119" s="199"/>
       <c r="C119" s="84"/>
       <c r="D119" s="84"/>
@@ -9180,7 +9215,7 @@
       </c>
       <c r="J119" s="207"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E120" s="169" t="s">
         <v>319</v>
       </c>
@@ -9193,7 +9228,7 @@
         <v>827777.77777777775</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E121" s="169" t="s">
         <v>320</v>
       </c>
@@ -9202,7 +9237,7 @@
         <v>15755180</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E122" s="233" t="s">
         <v>321</v>
       </c>
@@ -9211,7 +9246,7 @@
         <v>7438180</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="E123" s="169" t="s">
         <v>322</v>
       </c>
@@ -9250,22 +9285,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L166"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="202" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="91" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" style="208" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" style="208" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" style="169" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.1640625" style="203" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="91" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="91" customWidth="1"/>
+    <col min="3" max="3" width="48.28515625" style="208" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" style="208" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="169" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" style="203" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="91" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16" style="169" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" style="91" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" style="91" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" style="91" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="19.28515625" style="91" hidden="1" customWidth="1"/>
     <col min="11" max="16384" width="0" style="91" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="83" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" s="83" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="77" t="s">
         <v>216</v>
       </c>
@@ -9297,12 +9332,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="255" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="255" t="s">
+    <row r="2" spans="1:12" s="258" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="258" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="84"/>
       <c r="B3" s="85"/>
       <c r="C3" s="86" t="s">
@@ -9320,7 +9355,7 @@
       <c r="I3" s="90"/>
       <c r="J3" s="90"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="92"/>
       <c r="B4" s="85"/>
       <c r="C4" s="93" t="s">
@@ -9334,7 +9369,7 @@
       <c r="I4" s="85"/>
       <c r="J4" s="85"/>
     </row>
-    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="84"/>
       <c r="B5" s="85"/>
       <c r="C5" s="84" t="s">
@@ -9364,7 +9399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="84"/>
       <c r="B6" s="85"/>
       <c r="C6" s="84" t="s">
@@ -9391,7 +9426,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="84"/>
       <c r="B7" s="85"/>
       <c r="C7" s="84" t="s">
@@ -9419,7 +9454,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="84"/>
       <c r="B8" s="85"/>
       <c r="C8" s="84" t="s">
@@ -9442,7 +9477,7 @@
       <c r="I8" s="96"/>
       <c r="J8" s="96"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="93"/>
       <c r="B9" s="85"/>
       <c r="C9" s="93" t="s">
@@ -9456,13 +9491,13 @@
       <c r="I9" s="96"/>
       <c r="J9" s="96"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="84"/>
       <c r="B10" s="85"/>
-      <c r="C10" s="256" t="s">
+      <c r="C10" s="259" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="256"/>
+      <c r="D10" s="259"/>
       <c r="E10" s="96">
         <v>3000</v>
       </c>
@@ -9472,7 +9507,7 @@
       <c r="I10" s="96"/>
       <c r="J10" s="96"/>
     </row>
-    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="84"/>
       <c r="B11" s="85"/>
       <c r="C11" s="84" t="s">
@@ -9488,7 +9523,7 @@
       <c r="I11" s="85"/>
       <c r="J11" s="85"/>
     </row>
-    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="84"/>
       <c r="B12" s="85"/>
       <c r="C12" s="84" t="s">
@@ -9504,11 +9539,11 @@
       <c r="I12" s="85"/>
       <c r="J12" s="85"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="256" t="s">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="259" t="s">
         <v>233</v>
       </c>
-      <c r="B13" s="256"/>
+      <c r="B13" s="259"/>
       <c r="C13" s="99">
         <v>13</v>
       </c>
@@ -9520,7 +9555,7 @@
       <c r="I13" s="85"/>
       <c r="J13" s="85"/>
     </row>
-    <row r="14" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="72" t="str">
         <f>"Ngày 1: "&amp;C13&amp;"/6/2025 - Thứ 6 - XUẤT PHÁT TỪ HÀ NỘI"</f>
         <v>Ngày 1: 13/6/2025 - Thứ 6 - XUẤT PHÁT TỪ HÀ NỘI</v>
@@ -9535,7 +9570,7 @@
       <c r="I14" s="73"/>
       <c r="J14" s="73"/>
     </row>
-    <row r="15" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="100"/>
       <c r="B15" s="101">
         <v>0.24652777777777779</v>
@@ -9551,7 +9586,7 @@
       <c r="I15" s="105"/>
       <c r="J15" s="105"/>
     </row>
-    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="84"/>
       <c r="B16" s="85"/>
       <c r="C16" s="107" t="s">
@@ -9574,7 +9609,7 @@
       <c r="I16" s="96"/>
       <c r="J16" s="96"/>
     </row>
-    <row r="17" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="84"/>
       <c r="B17" s="85"/>
       <c r="C17" s="107" t="s">
@@ -9602,7 +9637,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="84"/>
       <c r="B18" s="85"/>
       <c r="C18" s="107" t="s">
@@ -9616,7 +9651,7 @@
       <c r="I18" s="85"/>
       <c r="J18" s="85"/>
     </row>
-    <row r="19" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="84"/>
       <c r="B19" s="109">
         <v>0.64583333333333337</v>
@@ -9634,7 +9669,7 @@
       <c r="I19" s="85"/>
       <c r="J19" s="85"/>
     </row>
-    <row r="20" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="100">
         <v>0.64583333333333337</v>
       </c>
@@ -9666,7 +9701,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="84"/>
       <c r="B21" s="85"/>
       <c r="C21" s="107" t="s">
@@ -9680,7 +9715,7 @@
       <c r="I21" s="85"/>
       <c r="J21" s="85"/>
     </row>
-    <row r="22" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="84"/>
       <c r="B22" s="85"/>
       <c r="C22" s="84" t="s">
@@ -9694,7 +9729,7 @@
       <c r="I22" s="85"/>
       <c r="J22" s="85"/>
     </row>
-    <row r="23" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="84"/>
       <c r="B23" s="85"/>
       <c r="C23" s="107" t="s">
@@ -9719,7 +9754,7 @@
       <c r="I23" s="96"/>
       <c r="J23" s="96"/>
     </row>
-    <row r="24" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="100">
         <v>0.72916666666666663</v>
       </c>
@@ -9737,7 +9772,7 @@
       <c r="I24" s="103"/>
       <c r="J24" s="103"/>
     </row>
-    <row r="25" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="114"/>
       <c r="B25" s="109"/>
       <c r="C25" s="107" t="s">
@@ -9762,7 +9797,7 @@
       <c r="I25" s="96"/>
       <c r="J25" s="96"/>
     </row>
-    <row r="26" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A26" s="84"/>
       <c r="B26" s="109"/>
       <c r="C26" s="107" t="s">
@@ -9788,7 +9823,7 @@
       <c r="I26" s="96"/>
       <c r="J26" s="96"/>
     </row>
-    <row r="27" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="84"/>
       <c r="B27" s="109"/>
       <c r="C27" s="107" t="s">
@@ -9802,7 +9837,7 @@
       <c r="I27" s="96"/>
       <c r="J27" s="96"/>
     </row>
-    <row r="28" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="84"/>
       <c r="B28" s="85"/>
       <c r="C28" s="107" t="s">
@@ -9816,7 +9851,7 @@
       <c r="I28" s="85"/>
       <c r="J28" s="85"/>
     </row>
-    <row r="29" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="84"/>
       <c r="B29" s="85"/>
       <c r="C29" s="107" t="s">
@@ -9830,7 +9865,7 @@
       <c r="I29" s="85"/>
       <c r="J29" s="85"/>
     </row>
-    <row r="30" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="100">
         <v>0.875</v>
       </c>
@@ -9860,7 +9895,7 @@
       </c>
       <c r="J30" s="103"/>
     </row>
-    <row r="31" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="118">
         <v>0.91666666666666663</v>
       </c>
@@ -9885,7 +9920,7 @@
       <c r="I31" s="96"/>
       <c r="J31" s="96"/>
     </row>
-    <row r="32" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="72" t="str">
         <f>"Ngày 2: "&amp;C13+1&amp;"/6/2025 - Thứ 7 - SENSOJI SHIBUYA - FUJI MUSEUM - SHIBUYA"</f>
         <v>Ngày 2: 14/6/2025 - Thứ 7 - SENSOJI SHIBUYA - FUJI MUSEUM - SHIBUYA</v>
@@ -9902,7 +9937,7 @@
       <c r="K32" s="14"/>
       <c r="L32" s="14"/>
     </row>
-    <row r="33" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="92"/>
       <c r="B33" s="101">
         <v>0.27083333333333331</v>
@@ -9929,13 +9964,13 @@
       <c r="K33" s="126"/>
       <c r="L33" s="126"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="114"/>
       <c r="B34" s="127"/>
-      <c r="C34" s="258" t="s">
+      <c r="C34" s="261" t="s">
         <v>338</v>
       </c>
-      <c r="D34" s="258"/>
+      <c r="D34" s="261"/>
       <c r="E34" s="128"/>
       <c r="F34" s="129"/>
       <c r="G34" s="127"/>
@@ -9945,13 +9980,13 @@
       <c r="K34" s="130"/>
       <c r="L34" s="130"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="114"/>
       <c r="B35" s="127"/>
-      <c r="C35" s="259" t="s">
+      <c r="C35" s="262" t="s">
         <v>50</v>
       </c>
-      <c r="D35" s="259"/>
+      <c r="D35" s="262"/>
       <c r="E35" s="128"/>
       <c r="F35" s="129"/>
       <c r="G35" s="127"/>
@@ -9961,17 +9996,17 @@
       <c r="K35" s="130"/>
       <c r="L35" s="130"/>
     </row>
-    <row r="36" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="100">
         <v>0.27083333333333331</v>
       </c>
       <c r="B36" s="101">
         <v>0.33333333333333331</v>
       </c>
-      <c r="C36" s="261" t="s">
+      <c r="C36" s="264" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="261"/>
+      <c r="D36" s="264"/>
       <c r="E36" s="132"/>
       <c r="F36" s="133"/>
       <c r="G36" s="134"/>
@@ -9981,7 +10016,7 @@
       <c r="K36" s="126"/>
       <c r="L36" s="126"/>
     </row>
-    <row r="37" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A37" s="114"/>
       <c r="B37" s="85"/>
       <c r="C37" s="135" t="s">
@@ -10009,7 +10044,7 @@
       <c r="K37" s="130"/>
       <c r="L37" s="130"/>
     </row>
-    <row r="38" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -10038,7 +10073,7 @@
       <c r="K38" s="130"/>
       <c r="L38" s="130"/>
     </row>
-    <row r="39" spans="1:12" s="144" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" s="144" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A39" s="137">
         <v>0.375</v>
       </c>
@@ -10070,7 +10105,7 @@
       <c r="K39" s="143"/>
       <c r="L39" s="143"/>
     </row>
-    <row r="40" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="114"/>
       <c r="B40" s="109"/>
       <c r="C40" s="131" t="s">
@@ -10088,7 +10123,7 @@
       <c r="K40" s="130"/>
       <c r="L40" s="130"/>
     </row>
-    <row r="41" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="114"/>
       <c r="B41" s="85"/>
       <c r="C41" s="131" t="s">
@@ -10104,7 +10139,7 @@
       <c r="K41" s="130"/>
       <c r="L41" s="130"/>
     </row>
-    <row r="42" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="114"/>
       <c r="B42" s="85"/>
       <c r="C42" s="131" t="s">
@@ -10120,7 +10155,7 @@
       <c r="K42" s="130"/>
       <c r="L42" s="130"/>
     </row>
-    <row r="43" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="114"/>
       <c r="B43" s="85"/>
       <c r="C43" s="131" t="s">
@@ -10136,7 +10171,7 @@
       <c r="K43" s="130"/>
       <c r="L43" s="130"/>
     </row>
-    <row r="44" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="114"/>
       <c r="B44" s="85"/>
       <c r="C44" s="131" t="s">
@@ -10152,7 +10187,7 @@
       <c r="K44" s="130"/>
       <c r="L44" s="130"/>
     </row>
-    <row r="45" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="114"/>
       <c r="B45" s="85"/>
       <c r="C45" s="131" t="s">
@@ -10168,7 +10203,7 @@
       <c r="K45" s="130"/>
       <c r="L45" s="130"/>
     </row>
-    <row r="46" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="114"/>
       <c r="B46" s="85"/>
       <c r="C46" s="131" t="s">
@@ -10193,7 +10228,7 @@
       <c r="K46" s="130"/>
       <c r="L46" s="130"/>
     </row>
-    <row r="47" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="100">
         <v>0.54166666666666663</v>
       </c>
@@ -10215,13 +10250,13 @@
       <c r="K47" s="126"/>
       <c r="L47" s="126"/>
     </row>
-    <row r="48" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="114"/>
       <c r="B48" s="109"/>
-      <c r="C48" s="260" t="s">
+      <c r="C48" s="263" t="s">
         <v>352</v>
       </c>
-      <c r="D48" s="260"/>
+      <c r="D48" s="263"/>
       <c r="E48" s="96">
         <f>370+220</f>
         <v>590</v>
@@ -10241,7 +10276,7 @@
       <c r="K48" s="130"/>
       <c r="L48" s="130"/>
     </row>
-    <row r="49" spans="1:12" ht="43" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="42.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="114"/>
       <c r="B49" s="109"/>
       <c r="C49" s="107" t="s">
@@ -10268,7 +10303,7 @@
       <c r="K49" s="130"/>
       <c r="L49" s="130"/>
     </row>
-    <row r="50" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="114"/>
       <c r="B50" s="109"/>
       <c r="C50" s="107" t="s">
@@ -10296,7 +10331,7 @@
       <c r="K50" s="130"/>
       <c r="L50" s="130"/>
     </row>
-    <row r="51" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="100">
         <v>0.70833333333333337</v>
       </c>
@@ -10326,7 +10361,7 @@
       <c r="K51" s="126"/>
       <c r="L51" s="126"/>
     </row>
-    <row r="52" spans="1:12" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="48.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="84"/>
       <c r="B52" s="85"/>
       <c r="C52" s="107" t="s">
@@ -10352,7 +10387,7 @@
       <c r="I52" s="96"/>
       <c r="J52" s="96"/>
     </row>
-    <row r="53" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="114">
         <v>0.86111111111111116</v>
       </c>
@@ -10379,7 +10414,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="100">
         <v>0.91666666666666663</v>
       </c>
@@ -10404,7 +10439,7 @@
       <c r="I54" s="96"/>
       <c r="J54" s="96"/>
     </row>
-    <row r="55" spans="1:12" s="15" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="72" t="str">
         <f>"Ngày 3: "&amp;C13+2&amp;"/6/2025 - Chủ Nhật - Tour Phú Sĩ - Mua Tour"</f>
         <v>Ngày 3: 15/6/2025 - Chủ Nhật - Tour Phú Sĩ - Mua Tour</v>
@@ -10423,7 +10458,7 @@
       <c r="K55" s="14"/>
       <c r="L55" s="14"/>
     </row>
-    <row r="56" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="102"/>
       <c r="B56" s="105"/>
       <c r="C56" s="102" t="s">
@@ -10447,7 +10482,7 @@
       <c r="I56" s="103"/>
       <c r="J56" s="103"/>
     </row>
-    <row r="57" spans="1:12" s="156" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" s="156" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="121"/>
       <c r="B57" s="124"/>
       <c r="C57" s="121" t="s">
@@ -10470,7 +10505,7 @@
       <c r="I57" s="122"/>
       <c r="J57" s="122"/>
     </row>
-    <row r="58" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A58" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -10502,7 +10537,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="114">
         <v>0.4375</v>
       </c>
@@ -10518,7 +10553,7 @@
       <c r="I59" s="85"/>
       <c r="J59" s="85"/>
     </row>
-    <row r="60" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="114">
         <v>0.48958333333333331</v>
       </c>
@@ -10534,7 +10569,7 @@
       <c r="I60" s="85"/>
       <c r="J60" s="85"/>
     </row>
-    <row r="61" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="114">
         <v>0.52083333333333337</v>
       </c>
@@ -10550,7 +10585,7 @@
       <c r="I61" s="85"/>
       <c r="J61" s="85"/>
     </row>
-    <row r="62" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="114">
         <v>0.60416666666666663</v>
       </c>
@@ -10566,7 +10601,7 @@
       <c r="I62" s="85"/>
       <c r="J62" s="85"/>
     </row>
-    <row r="63" spans="1:12" ht="64" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="78.75" x14ac:dyDescent="0.25">
       <c r="A63" s="114">
         <v>0.63194444444444442</v>
       </c>
@@ -10584,7 +10619,7 @@
       <c r="I63" s="85"/>
       <c r="J63" s="85"/>
     </row>
-    <row r="64" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="114">
         <v>0.63888888888888884</v>
       </c>
@@ -10600,7 +10635,7 @@
       <c r="I64" s="85"/>
       <c r="J64" s="85"/>
     </row>
-    <row r="65" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="114">
         <v>0.78472222222222221</v>
       </c>
@@ -10616,7 +10651,7 @@
       <c r="I65" s="85"/>
       <c r="J65" s="85"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="84"/>
       <c r="B66" s="85"/>
       <c r="C66" s="84"/>
@@ -10628,7 +10663,7 @@
       <c r="I66" s="85"/>
       <c r="J66" s="85"/>
     </row>
-    <row r="67" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="102"/>
       <c r="B67" s="105"/>
       <c r="C67" s="102" t="s">
@@ -10651,7 +10686,7 @@
       <c r="I67" s="103"/>
       <c r="J67" s="103"/>
     </row>
-    <row r="68" spans="1:12" ht="48" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="63" x14ac:dyDescent="0.25">
       <c r="A68" s="84"/>
       <c r="B68" s="85"/>
       <c r="C68" s="84" t="s">
@@ -10677,7 +10712,7 @@
       <c r="I68" s="96"/>
       <c r="J68" s="96"/>
     </row>
-    <row r="69" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="84"/>
       <c r="B69" s="85"/>
       <c r="C69" s="84" t="s">
@@ -10700,7 +10735,7 @@
       <c r="I69" s="96"/>
       <c r="J69" s="96"/>
     </row>
-    <row r="70" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="72" t="str">
         <f>"Ngày 4: "&amp;C13+3&amp;"/6/2025 - TOKYO STATION TOKYO TOWER + GINZA MUA SẮM - SAU ĐÓ KYOTO"</f>
         <v>Ngày 4: 16/6/2025 - TOKYO STATION TOKYO TOWER + GINZA MUA SẮM - SAU ĐÓ KYOTO</v>
@@ -10717,7 +10752,7 @@
       <c r="K70" s="14"/>
       <c r="L70" s="14"/>
     </row>
-    <row r="71" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -10742,7 +10777,7 @@
       <c r="I71" s="96"/>
       <c r="J71" s="96"/>
     </row>
-    <row r="72" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="114"/>
       <c r="B72" s="85"/>
       <c r="C72" s="84" t="s">
@@ -10765,7 +10800,7 @@
       <c r="I72" s="96"/>
       <c r="J72" s="96"/>
     </row>
-    <row r="73" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="84"/>
       <c r="B73" s="85"/>
       <c r="C73" s="157" t="s">
@@ -10790,7 +10825,7 @@
       <c r="I73" s="96"/>
       <c r="J73" s="96"/>
     </row>
-    <row r="74" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="137">
         <v>0.35416666666666669</v>
       </c>
@@ -10819,7 +10854,7 @@
       <c r="I74" s="103"/>
       <c r="J74" s="103"/>
     </row>
-    <row r="75" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A75" s="114">
         <v>0.47916666666666669</v>
       </c>
@@ -10849,7 +10884,7 @@
       <c r="I75" s="96"/>
       <c r="J75" s="96"/>
     </row>
-    <row r="76" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="114">
         <v>0.54166666666666663</v>
       </c>
@@ -10876,7 +10911,7 @@
       <c r="I76" s="96"/>
       <c r="J76" s="96"/>
     </row>
-    <row r="77" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="114"/>
       <c r="B77" s="109"/>
       <c r="C77" s="84" t="s">
@@ -10899,7 +10934,7 @@
       <c r="I77" s="96"/>
       <c r="J77" s="96"/>
     </row>
-    <row r="78" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="114">
         <v>0.60416666666666663</v>
       </c>
@@ -10917,7 +10952,7 @@
       <c r="I78" s="96"/>
       <c r="J78" s="96"/>
     </row>
-    <row r="79" spans="1:12" ht="32" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A79" s="114">
         <v>0.625</v>
       </c>
@@ -10937,7 +10972,7 @@
       <c r="I79" s="96"/>
       <c r="J79" s="96"/>
     </row>
-    <row r="80" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="114">
         <v>0.6875</v>
       </c>
@@ -10964,7 +10999,7 @@
       <c r="I80" s="96"/>
       <c r="J80" s="96"/>
     </row>
-    <row r="81" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="100">
         <v>0.79166666666666663</v>
       </c>
@@ -10993,7 +11028,7 @@
       </c>
       <c r="J81" s="103"/>
     </row>
-    <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A82" s="114">
         <v>0.83333333333333337</v>
       </c>
@@ -11021,10 +11056,10 @@
       <c r="I82" s="160"/>
       <c r="J82" s="96"/>
     </row>
-    <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="114"/>
       <c r="B83" s="109"/>
-      <c r="C83" s="257" t="s">
+      <c r="C83" s="260" t="s">
         <v>377</v>
       </c>
       <c r="D83" s="148" t="s">
@@ -11047,10 +11082,10 @@
       <c r="I83" s="160"/>
       <c r="J83" s="96"/>
     </row>
-    <row r="84" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="114"/>
       <c r="B84" s="109"/>
-      <c r="C84" s="257"/>
+      <c r="C84" s="260"/>
       <c r="D84" s="148" t="s">
         <v>379</v>
       </c>
@@ -11070,7 +11105,7 @@
       <c r="I84" s="160"/>
       <c r="J84" s="96"/>
     </row>
-    <row r="85" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="84"/>
       <c r="B85" s="85"/>
       <c r="C85" s="84" t="s">
@@ -11086,7 +11121,7 @@
       <c r="I85" s="96"/>
       <c r="J85" s="96"/>
     </row>
-    <row r="86" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A86" s="84"/>
       <c r="B86" s="85"/>
       <c r="C86" s="164" t="s">
@@ -11111,7 +11146,7 @@
       <c r="I86" s="96"/>
       <c r="J86" s="96"/>
     </row>
-    <row r="87" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="72" t="str">
         <f>"Ngày 5: "&amp;C13+4&amp;"/6/2025 - KYOTO"</f>
         <v>Ngày 5: 17/6/2025 - KYOTO</v>
@@ -11126,7 +11161,7 @@
       <c r="I87" s="73"/>
       <c r="J87" s="73"/>
     </row>
-    <row r="88" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="100">
         <v>0.29166666666666669</v>
       </c>
@@ -11156,7 +11191,7 @@
       <c r="I88" s="103"/>
       <c r="J88" s="103"/>
     </row>
-    <row r="89" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="157"/>
       <c r="B89" s="127"/>
       <c r="C89" s="84" t="s">
@@ -11181,7 +11216,7 @@
       <c r="I89" s="96"/>
       <c r="J89" s="96"/>
     </row>
-    <row r="90" spans="1:10" s="106" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" s="106" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A90" s="125"/>
       <c r="B90" s="134"/>
       <c r="C90" s="102" t="s">
@@ -11210,7 +11245,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="114">
         <v>0.33333333333333331</v>
       </c>
@@ -11228,7 +11263,7 @@
       <c r="I91" s="85"/>
       <c r="J91" s="85"/>
     </row>
-    <row r="92" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A92" s="84"/>
       <c r="B92" s="85"/>
       <c r="C92" s="107" t="s">
@@ -11244,7 +11279,7 @@
       <c r="I92" s="85"/>
       <c r="J92" s="85"/>
     </row>
-    <row r="93" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="84"/>
       <c r="B93" s="85"/>
       <c r="C93" s="107" t="s">
@@ -11258,7 +11293,7 @@
       <c r="I93" s="85"/>
       <c r="J93" s="85"/>
     </row>
-    <row r="94" spans="1:10" s="106" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" s="106" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A94" s="100">
         <v>0.45833333333333331</v>
       </c>
@@ -11288,7 +11323,7 @@
       <c r="I94" s="103"/>
       <c r="J94" s="103"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="84"/>
       <c r="B95" s="85"/>
       <c r="C95" s="107"/>
@@ -11300,7 +11335,7 @@
       <c r="I95" s="85"/>
       <c r="J95" s="85"/>
     </row>
-    <row r="96" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A96" s="114">
         <v>0.5625</v>
       </c>
@@ -11329,7 +11364,7 @@
       <c r="I96" s="96"/>
       <c r="J96" s="85"/>
     </row>
-    <row r="97" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="114"/>
       <c r="B97" s="109"/>
       <c r="C97" s="107" t="s">
@@ -11342,7 +11377,7 @@
       <c r="F97" s="91"/>
       <c r="J97" s="96"/>
     </row>
-    <row r="98" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="114"/>
       <c r="B98" s="109">
         <v>0.66666666666666663</v>
@@ -11358,7 +11393,7 @@
       <c r="I98" s="85"/>
       <c r="J98" s="85"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="114"/>
       <c r="C99" s="91"/>
       <c r="D99" s="91"/>
@@ -11366,7 +11401,7 @@
       <c r="F99" s="91"/>
       <c r="J99" s="96"/>
     </row>
-    <row r="100" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="114"/>
       <c r="B100" s="109">
         <v>0.75</v>
@@ -11382,7 +11417,7 @@
       <c r="I100" s="85"/>
       <c r="J100" s="85"/>
     </row>
-    <row r="101" spans="1:12" s="106" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="100"/>
       <c r="B101" s="101">
         <v>0.79166666666666663</v>
@@ -11410,7 +11445,7 @@
       <c r="I101" s="103"/>
       <c r="J101" s="103"/>
     </row>
-    <row r="102" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="114"/>
       <c r="B102" s="109"/>
       <c r="C102" s="84" t="s">
@@ -11426,7 +11461,7 @@
       <c r="I102" s="85"/>
       <c r="J102" s="85"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="114"/>
       <c r="B103" s="109"/>
       <c r="C103" s="84"/>
@@ -11438,7 +11473,7 @@
       <c r="I103" s="85"/>
       <c r="J103" s="85"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="72" t="str">
         <f>"Ngày 6: "&amp;C13+5&amp;"/6/2025 - CHƠI NỐT KYOTO - SAU ĐÓ OSAKA"</f>
         <v>Ngày 6: 18/6/2025 - CHƠI NỐT KYOTO - SAU ĐÓ OSAKA</v>
@@ -11455,7 +11490,7 @@
       <c r="K104" s="15"/>
       <c r="L104" s="15"/>
     </row>
-    <row r="105" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="100"/>
       <c r="B105" s="101">
         <v>0.33333333333333331</v>
@@ -11483,7 +11518,7 @@
       <c r="I105" s="103"/>
       <c r="J105" s="103"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="114"/>
       <c r="B106" s="109"/>
       <c r="C106" s="84"/>
@@ -11495,7 +11530,7 @@
       <c r="I106" s="85"/>
       <c r="J106" s="85"/>
     </row>
-    <row r="107" spans="1:12" s="106" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" s="106" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A107" s="100">
         <v>0.33333333333333331</v>
       </c>
@@ -11524,7 +11559,7 @@
       <c r="I107" s="103"/>
       <c r="J107" s="103"/>
     </row>
-    <row r="108" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="114"/>
       <c r="B108" s="109">
         <v>0.41666666666666669</v>
@@ -11550,7 +11585,7 @@
       <c r="I108" s="96"/>
       <c r="J108" s="96"/>
     </row>
-    <row r="109" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="114"/>
       <c r="B109" s="109">
         <v>0.45833333333333331</v>
@@ -11577,7 +11612,7 @@
       <c r="I109" s="96"/>
       <c r="J109" s="96"/>
     </row>
-    <row r="110" spans="1:12" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="100">
         <v>0.45833333333333331</v>
       </c>
@@ -11607,7 +11642,7 @@
       <c r="I110" s="103"/>
       <c r="J110" s="103"/>
     </row>
-    <row r="111" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="114"/>
       <c r="B111" s="174"/>
       <c r="C111" s="164" t="s">
@@ -11632,7 +11667,7 @@
       <c r="I111" s="96"/>
       <c r="J111" s="96"/>
     </row>
-    <row r="112" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="114"/>
       <c r="B112" s="174"/>
       <c r="C112" s="164" t="s">
@@ -11648,7 +11683,7 @@
       <c r="I112" s="96"/>
       <c r="J112" s="96"/>
     </row>
-    <row r="113" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" s="106" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A113" s="102"/>
       <c r="B113" s="176">
         <v>0.52083333333333337</v>
@@ -11675,7 +11710,7 @@
       <c r="I113" s="103"/>
       <c r="J113" s="103"/>
     </row>
-    <row r="114" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A114" s="84"/>
       <c r="B114" s="174">
         <v>0.58333333333333337</v>
@@ -11706,7 +11741,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="84"/>
       <c r="B115" s="174"/>
       <c r="C115" s="164" t="s">
@@ -11720,7 +11755,7 @@
       <c r="I115" s="96"/>
       <c r="J115" s="152"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="84"/>
       <c r="B116" s="174"/>
       <c r="C116" s="164"/>
@@ -11732,7 +11767,7 @@
       <c r="I116" s="96"/>
       <c r="J116" s="152"/>
     </row>
-    <row r="117" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" s="106" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A117" s="102"/>
       <c r="B117" s="176">
         <v>0.625</v>
@@ -11753,7 +11788,7 @@
       <c r="I117" s="103"/>
       <c r="J117" s="103"/>
     </row>
-    <row r="118" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="84"/>
       <c r="B118" s="174"/>
       <c r="C118" s="164" t="s">
@@ -11767,7 +11802,7 @@
       <c r="I118" s="96"/>
       <c r="J118" s="96"/>
     </row>
-    <row r="119" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="84"/>
       <c r="B119" s="174"/>
       <c r="C119" s="177" t="s">
@@ -11790,7 +11825,7 @@
       <c r="I119" s="96"/>
       <c r="J119" s="96"/>
     </row>
-    <row r="120" spans="1:10" s="180" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" s="180" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="178"/>
       <c r="B120" s="179">
         <v>0.66666666666666663</v>
@@ -11809,7 +11844,7 @@
       <c r="I120" s="112"/>
       <c r="J120" s="112"/>
     </row>
-    <row r="121" spans="1:10" s="182" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" s="182" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="148"/>
       <c r="B121" s="162"/>
       <c r="C121" s="181" t="s">
@@ -11823,7 +11858,7 @@
       <c r="I121" s="160"/>
       <c r="J121" s="160"/>
     </row>
-    <row r="122" spans="1:10" s="182" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" s="182" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="148"/>
       <c r="B122" s="162"/>
       <c r="C122" s="181" t="s">
@@ -11846,7 +11881,7 @@
       <c r="I122" s="96"/>
       <c r="J122" s="96"/>
     </row>
-    <row r="123" spans="1:10" s="182" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" s="182" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="148"/>
       <c r="B123" s="162"/>
       <c r="C123" s="181" t="s">
@@ -11860,7 +11895,7 @@
       <c r="I123" s="160"/>
       <c r="J123" s="160"/>
     </row>
-    <row r="124" spans="1:10" s="106" customFormat="1" ht="272" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" s="106" customFormat="1" ht="267.75" x14ac:dyDescent="0.25">
       <c r="A124" s="102"/>
       <c r="B124" s="101">
         <v>0.70833333333333337</v>
@@ -11878,7 +11913,7 @@
       <c r="I124" s="105"/>
       <c r="J124" s="105"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="84"/>
       <c r="B125" s="109"/>
       <c r="C125" s="84"/>
@@ -11890,7 +11925,7 @@
       <c r="I125" s="85"/>
       <c r="J125" s="85"/>
     </row>
-    <row r="126" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="84"/>
       <c r="B126" s="85"/>
       <c r="C126" s="84"/>
@@ -11911,7 +11946,7 @@
       <c r="I126" s="96"/>
       <c r="J126" s="96"/>
     </row>
-    <row r="127" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A127" s="84"/>
       <c r="B127" s="85"/>
       <c r="C127" s="157" t="s">
@@ -11936,7 +11971,7 @@
       <c r="I127" s="96"/>
       <c r="J127" s="96"/>
     </row>
-    <row r="128" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="84"/>
       <c r="B128" s="85"/>
       <c r="C128" s="84" t="s">
@@ -11950,7 +11985,7 @@
       <c r="I128" s="85"/>
       <c r="J128" s="85"/>
     </row>
-    <row r="129" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A129" s="84"/>
       <c r="B129" s="85"/>
       <c r="C129" s="84" t="s">
@@ -11975,7 +12010,7 @@
       <c r="I129" s="96"/>
       <c r="J129" s="96"/>
     </row>
-    <row r="130" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="84"/>
       <c r="B130" s="85"/>
       <c r="C130" s="84" t="s">
@@ -12003,7 +12038,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="84"/>
       <c r="B131" s="85"/>
       <c r="C131" s="84"/>
@@ -12015,7 +12050,7 @@
       <c r="I131" s="85"/>
       <c r="J131" s="85"/>
     </row>
-    <row r="132" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="186" t="str">
         <f>"Ngày 7: "&amp;C13+6&amp;"/6/2025 - ĐI NARA &amp; CÔNG VIÊN IKOMA SANJO- VÀ MUA SẮM QUÀ Ở OSAKA"</f>
         <v>Ngày 7: 19/6/2025 - ĐI NARA &amp; CÔNG VIÊN IKOMA SANJO- VÀ MUA SẮM QUÀ Ở OSAKA</v>
@@ -12030,7 +12065,7 @@
       <c r="I132" s="187"/>
       <c r="J132" s="187"/>
     </row>
-    <row r="133" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A133" s="157"/>
       <c r="B133" s="174">
         <v>0.29166666666666669</v>
@@ -12058,7 +12093,7 @@
       <c r="I133" s="96"/>
       <c r="J133" s="96"/>
     </row>
-    <row r="134" spans="1:10" s="106" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" s="106" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A134" s="125"/>
       <c r="B134" s="176">
         <v>0.375</v>
@@ -12085,7 +12120,7 @@
       <c r="I134" s="103"/>
       <c r="J134" s="103"/>
     </row>
-    <row r="135" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="157"/>
       <c r="B135" s="192"/>
       <c r="C135" s="164"/>
@@ -12108,7 +12143,7 @@
       <c r="I135" s="96"/>
       <c r="J135" s="96"/>
     </row>
-    <row r="136" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A136" s="157"/>
       <c r="B136" s="174">
         <v>0.41666666666666669</v>
@@ -12135,7 +12170,7 @@
       <c r="I136" s="96"/>
       <c r="J136" s="96"/>
     </row>
-    <row r="137" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="157"/>
       <c r="B137" s="174">
         <v>0.45833333333333331</v>
@@ -12162,7 +12197,7 @@
       <c r="I137" s="96"/>
       <c r="J137" s="96"/>
     </row>
-    <row r="138" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A138" s="157"/>
       <c r="B138" s="174">
         <v>0.47916666666666669</v>
@@ -12190,7 +12225,7 @@
       <c r="I138" s="96"/>
       <c r="J138" s="96"/>
     </row>
-    <row r="139" spans="1:10" ht="34" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A139" s="157"/>
       <c r="B139" s="174"/>
       <c r="C139" s="164" t="s">
@@ -12216,7 +12251,7 @@
       <c r="I139" s="96"/>
       <c r="J139" s="96"/>
     </row>
-    <row r="140" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="157"/>
       <c r="B140" s="174"/>
       <c r="C140" s="164"/>
@@ -12228,7 +12263,7 @@
       <c r="I140" s="96"/>
       <c r="J140" s="96"/>
     </row>
-    <row r="141" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="84"/>
       <c r="B141" s="109">
         <v>0.79166666666666663</v>
@@ -12244,7 +12279,7 @@
       <c r="I141" s="85"/>
       <c r="J141" s="85"/>
     </row>
-    <row r="142" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="84"/>
       <c r="B142" s="109"/>
       <c r="C142" s="84" t="s">
@@ -12267,7 +12302,7 @@
       <c r="I142" s="96"/>
       <c r="J142" s="96"/>
     </row>
-    <row r="143" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="84"/>
       <c r="B143" s="109"/>
       <c r="C143" s="84" t="s">
@@ -12293,7 +12328,7 @@
       <c r="I143" s="96"/>
       <c r="J143" s="85"/>
     </row>
-    <row r="144" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="84"/>
       <c r="B144" s="109"/>
       <c r="C144" s="84" t="s">
@@ -12307,7 +12342,7 @@
       <c r="I144" s="85"/>
       <c r="J144" s="85"/>
     </row>
-    <row r="145" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A145" s="84"/>
       <c r="B145" s="109">
         <v>0.875</v>
@@ -12323,7 +12358,7 @@
       <c r="I145" s="85"/>
       <c r="J145" s="85"/>
     </row>
-    <row r="146" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A146" s="84"/>
       <c r="B146" s="109"/>
       <c r="C146" s="84" t="s">
@@ -12346,7 +12381,7 @@
       <c r="I146" s="96"/>
       <c r="J146" s="96"/>
     </row>
-    <row r="147" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A147" s="84"/>
       <c r="B147" s="109"/>
       <c r="C147" s="84" t="s">
@@ -12360,7 +12395,7 @@
       <c r="I147" s="85"/>
       <c r="J147" s="85"/>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A148" s="194" t="str">
         <f>"Ngày 8: "&amp;C13+7&amp;"/6/2025 - ĐI CHÙA KATSUOJI - CẦU NGUYỆN"</f>
         <v>Ngày 8: 20/6/2025 - ĐI CHÙA KATSUOJI - CẦU NGUYỆN</v>
@@ -12377,7 +12412,7 @@
       <c r="K148" s="15"/>
       <c r="L148" s="15"/>
     </row>
-    <row r="149" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A149" s="84"/>
       <c r="B149" s="174">
         <v>0.29166666666666669</v>
@@ -12405,7 +12440,7 @@
       <c r="I149" s="85"/>
       <c r="J149" s="85"/>
     </row>
-    <row r="150" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A150" s="114">
         <v>0.375</v>
       </c>
@@ -12434,7 +12469,7 @@
       <c r="I150" s="85"/>
       <c r="J150" s="85"/>
     </row>
-    <row r="151" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A151" s="114"/>
       <c r="B151" s="174"/>
       <c r="C151" s="164" t="s">
@@ -12459,7 +12494,7 @@
       <c r="I151" s="85"/>
       <c r="J151" s="85"/>
     </row>
-    <row r="152" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A152" s="114">
         <v>0.54166666666666663</v>
       </c>
@@ -12486,7 +12521,7 @@
       <c r="I152" s="85"/>
       <c r="J152" s="85"/>
     </row>
-    <row r="153" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A153" s="84"/>
       <c r="B153" s="109"/>
       <c r="C153" s="84" t="s">
@@ -12509,7 +12544,7 @@
       <c r="I153" s="85"/>
       <c r="J153" s="85"/>
     </row>
-    <row r="154" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A154" s="84"/>
       <c r="B154" s="109"/>
       <c r="C154" s="84" t="s">
@@ -12523,7 +12558,7 @@
       <c r="I154" s="85"/>
       <c r="J154" s="85"/>
     </row>
-    <row r="155" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="197" t="str">
         <f>"Ngày 9: "&amp;C13+8&amp;"/6/2025 - ĐI VỀ HÀ NỘI"</f>
         <v>Ngày 9: 21/6/2025 - ĐI VỀ HÀ NỘI</v>
@@ -12538,7 +12573,7 @@
       <c r="I155" s="195"/>
       <c r="J155" s="195"/>
     </row>
-    <row r="156" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A156" s="84"/>
       <c r="B156" s="85"/>
       <c r="C156" s="84" t="s">
@@ -12554,7 +12589,7 @@
       <c r="I156" s="85"/>
       <c r="J156" s="85"/>
     </row>
-    <row r="157" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A157" s="84"/>
       <c r="B157" s="85"/>
       <c r="C157" s="84" t="s">
@@ -12577,7 +12612,7 @@
       <c r="I157" s="96"/>
       <c r="J157" s="96"/>
     </row>
-    <row r="158" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A158" s="84"/>
       <c r="B158" s="109">
         <v>0.29166666666666669</v>
@@ -12603,7 +12638,7 @@
       <c r="I158" s="96"/>
       <c r="J158" s="96"/>
     </row>
-    <row r="159" spans="1:12" s="106" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="102"/>
       <c r="B159" s="176">
         <v>0.45833333333333331</v>
@@ -12630,7 +12665,7 @@
       <c r="I159" s="103"/>
       <c r="J159" s="103"/>
     </row>
-    <row r="160" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A160" s="84"/>
       <c r="B160" s="174">
         <v>0.5</v>
@@ -12657,7 +12692,7 @@
       <c r="I160" s="96"/>
       <c r="J160" s="96"/>
     </row>
-    <row r="161" spans="1:10" s="106" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" s="106" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="102"/>
       <c r="B161" s="176">
         <v>0.5625</v>
@@ -12684,7 +12719,7 @@
       <c r="I161" s="103"/>
       <c r="J161" s="103"/>
     </row>
-    <row r="162" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="114">
         <v>0.64583333333333337</v>
       </c>
@@ -12714,7 +12749,7 @@
       </c>
       <c r="J162" s="200"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="114"/>
       <c r="B163" s="109"/>
       <c r="C163" s="84"/>
@@ -12735,7 +12770,7 @@
       <c r="I163" s="200"/>
       <c r="J163" s="200"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="199"/>
       <c r="B164" s="199"/>
       <c r="C164" s="84"/>
@@ -12747,7 +12782,7 @@
       <c r="I164" s="199"/>
       <c r="J164" s="199"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B165" s="199"/>
       <c r="C165" s="84"/>
       <c r="D165" s="84"/>
@@ -12764,7 +12799,7 @@
       </c>
       <c r="J165" s="204"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B166" s="199"/>
       <c r="C166" s="84"/>
       <c r="D166" s="84"/>
@@ -12836,17 +12871,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="216" customWidth="1"/>
     <col min="2" max="2" width="28" style="216" customWidth="1"/>
     <col min="3" max="3" width="81" style="216" customWidth="1"/>
     <col min="4" max="4" width="38" style="216" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5" style="216" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="216"/>
+    <col min="5" max="5" width="26.140625" style="216" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="216"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="236" t="s">
         <v>432</v>
       </c>
@@ -12866,17 +12901,17 @@
         <v>437</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="264" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="255" t="s">
         <v>438</v>
       </c>
-      <c r="B2" s="265"/>
-      <c r="C2" s="265"/>
+      <c r="B2" s="256"/>
+      <c r="C2" s="256"/>
       <c r="D2" s="238"/>
       <c r="E2" s="238"/>
       <c r="F2" s="239"/>
     </row>
-    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="240" t="s">
         <v>439</v>
       </c>
@@ -12890,7 +12925,7 @@
       <c r="E3" s="250"/>
       <c r="F3" s="239"/>
     </row>
-    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="243" t="s">
         <v>442</v>
       </c>
@@ -12908,7 +12943,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="240" t="s">
         <v>446</v>
       </c>
@@ -12928,7 +12963,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="243" t="s">
         <v>452</v>
       </c>
@@ -12948,7 +12983,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="240" t="s">
         <v>458</v>
       </c>
@@ -12962,7 +12997,7 @@
       <c r="E7" s="251"/>
       <c r="F7" s="239"/>
     </row>
-    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="243" t="s">
         <v>461</v>
       </c>
@@ -12982,7 +13017,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="240" t="s">
         <v>467</v>
       </c>
@@ -13002,7 +13037,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="243" t="s">
         <v>473</v>
       </c>
@@ -13018,7 +13053,7 @@
       </c>
       <c r="F10" s="239"/>
     </row>
-    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="249" t="s">
         <v>595</v>
       </c>
@@ -13032,17 +13067,17 @@
       <c r="E11" s="250"/>
       <c r="F11" s="239"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="262" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="253" t="s">
         <v>479</v>
       </c>
-      <c r="B12" s="263"/>
-      <c r="C12" s="263"/>
+      <c r="B12" s="254"/>
+      <c r="C12" s="254"/>
       <c r="D12" s="239"/>
       <c r="E12" s="239"/>
       <c r="F12" s="239"/>
     </row>
-    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="240" t="s">
         <v>480</v>
       </c>
@@ -13056,13 +13091,13 @@
         <v>482</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F13" s="246" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="243" t="s">
         <v>484</v>
       </c>
@@ -13076,7 +13111,7 @@
       <c r="E14" s="251"/>
       <c r="F14" s="239"/>
     </row>
-    <row r="15" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="240" t="s">
         <v>486</v>
       </c>
@@ -13089,14 +13124,14 @@
       <c r="D15" s="242" t="s">
         <v>488</v>
       </c>
-      <c r="E15" s="253" t="s">
-        <v>596</v>
+      <c r="E15" s="8" t="s">
+        <v>597</v>
       </c>
       <c r="F15" s="246" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="248">
         <v>0.875</v>
       </c>
@@ -13110,17 +13145,17 @@
       <c r="E16" s="251"/>
       <c r="F16" s="239"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="262" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="253" t="s">
         <v>490</v>
       </c>
-      <c r="B17" s="263"/>
-      <c r="C17" s="263"/>
+      <c r="B17" s="254"/>
+      <c r="C17" s="254"/>
       <c r="D17" s="239"/>
       <c r="E17" s="239"/>
       <c r="F17" s="239"/>
     </row>
-    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="240" t="s">
         <v>491</v>
       </c>
@@ -13134,7 +13169,7 @@
       <c r="E18" s="250"/>
       <c r="F18" s="239"/>
     </row>
-    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="243" t="s">
         <v>494</v>
       </c>
@@ -13145,10 +13180,12 @@
         <v>496</v>
       </c>
       <c r="D19" s="245"/>
-      <c r="E19" s="251"/>
+      <c r="E19" s="8" t="s">
+        <v>604</v>
+      </c>
       <c r="F19" s="239"/>
     </row>
-    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="240" t="s">
         <v>497</v>
       </c>
@@ -13161,12 +13198,14 @@
       <c r="D20" s="242" t="s">
         <v>577</v>
       </c>
-      <c r="E20" s="250"/>
+      <c r="E20" s="8" t="s">
+        <v>603</v>
+      </c>
       <c r="F20" s="246" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="243" t="s">
         <v>500</v>
       </c>
@@ -13180,7 +13219,7 @@
       <c r="E21" s="251"/>
       <c r="F21" s="239"/>
     </row>
-    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="240" t="s">
         <v>503</v>
       </c>
@@ -13193,12 +13232,14 @@
       <c r="D22" s="242" t="s">
         <v>506</v>
       </c>
-      <c r="E22" s="250"/>
+      <c r="E22" s="8" t="s">
+        <v>602</v>
+      </c>
       <c r="F22" s="246" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="243" t="s">
         <v>473</v>
       </c>
@@ -13216,17 +13257,17 @@
         <v>509</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="262" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="253" t="s">
         <v>510</v>
       </c>
-      <c r="B24" s="263"/>
-      <c r="C24" s="263"/>
+      <c r="B24" s="254"/>
+      <c r="C24" s="254"/>
       <c r="D24" s="239"/>
       <c r="E24" s="239"/>
       <c r="F24" s="239"/>
     </row>
-    <row r="25" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="240" t="s">
         <v>511</v>
       </c>
@@ -13239,12 +13280,14 @@
       <c r="D25" s="242" t="s">
         <v>579</v>
       </c>
-      <c r="E25" s="250"/>
+      <c r="E25" s="8" t="s">
+        <v>605</v>
+      </c>
       <c r="F25" s="239" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="243" t="s">
         <v>513</v>
       </c>
@@ -13257,12 +13300,14 @@
       <c r="D26" s="245" t="s">
         <v>575</v>
       </c>
-      <c r="E26" s="251"/>
+      <c r="E26" s="8" t="s">
+        <v>606</v>
+      </c>
       <c r="F26" s="239" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="240" t="s">
         <v>514</v>
       </c>
@@ -13280,7 +13325,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="243" t="s">
         <v>503</v>
       </c>
@@ -13293,12 +13338,14 @@
       <c r="D28" s="245" t="s">
         <v>580</v>
       </c>
-      <c r="E28" s="251"/>
+      <c r="E28" s="8" t="s">
+        <v>599</v>
+      </c>
       <c r="F28" s="239" t="s">
         <v>582</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="240" t="s">
         <v>517</v>
       </c>
@@ -13311,22 +13358,24 @@
       <c r="D29" s="242" t="s">
         <v>581</v>
       </c>
-      <c r="E29" s="250"/>
+      <c r="E29" s="8" t="s">
+        <v>598</v>
+      </c>
       <c r="F29" s="239" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="262" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="253" t="s">
         <v>520</v>
       </c>
-      <c r="B30" s="263"/>
-      <c r="C30" s="263"/>
+      <c r="B30" s="254"/>
+      <c r="C30" s="254"/>
       <c r="D30" s="239"/>
       <c r="E30" s="239"/>
       <c r="F30" s="239"/>
     </row>
-    <row r="31" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="240" t="s">
         <v>521</v>
       </c>
@@ -13339,12 +13388,14 @@
       <c r="D31" s="242" t="s">
         <v>574</v>
       </c>
-      <c r="E31" s="250"/>
+      <c r="E31" s="8" t="s">
+        <v>601</v>
+      </c>
       <c r="F31" s="239" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="243" t="s">
         <v>523</v>
       </c>
@@ -13355,10 +13406,12 @@
         <v>525</v>
       </c>
       <c r="D32" s="245"/>
-      <c r="E32" s="251"/>
+      <c r="E32" s="8" t="s">
+        <v>600</v>
+      </c>
       <c r="F32" s="239"/>
     </row>
-    <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="240" t="s">
         <v>526</v>
       </c>
@@ -13372,7 +13425,7 @@
       <c r="E33" s="250"/>
       <c r="F33" s="239"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="243" t="s">
         <v>517</v>
       </c>
@@ -13390,17 +13443,17 @@
         <v>590</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="262" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="253" t="s">
         <v>530</v>
       </c>
-      <c r="B35" s="263"/>
-      <c r="C35" s="263"/>
+      <c r="B35" s="254"/>
+      <c r="C35" s="254"/>
       <c r="D35" s="239"/>
       <c r="E35" s="239"/>
       <c r="F35" s="239"/>
     </row>
-    <row r="36" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="240" t="s">
         <v>531</v>
       </c>
@@ -13411,10 +13464,12 @@
         <v>533</v>
       </c>
       <c r="D36" s="242"/>
-      <c r="E36" s="250"/>
+      <c r="E36" s="8" t="s">
+        <v>610</v>
+      </c>
       <c r="F36" s="239"/>
     </row>
-    <row r="37" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="243" t="s">
         <v>513</v>
       </c>
@@ -13427,12 +13482,14 @@
       <c r="D37" s="245" t="s">
         <v>591</v>
       </c>
-      <c r="E37" s="251"/>
+      <c r="E37" s="8" t="s">
+        <v>607</v>
+      </c>
       <c r="F37" s="239" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="240" t="s">
         <v>514</v>
       </c>
@@ -13443,10 +13500,12 @@
         <v>536</v>
       </c>
       <c r="D38" s="242"/>
-      <c r="E38" s="250"/>
+      <c r="E38" s="8" t="s">
+        <v>609</v>
+      </c>
       <c r="F38" s="239"/>
     </row>
-    <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="243" t="s">
         <v>537</v>
       </c>
@@ -13456,11 +13515,17 @@
       <c r="C39" s="245" t="s">
         <v>538</v>
       </c>
-      <c r="D39" s="245"/>
-      <c r="E39" s="251"/>
-      <c r="F39" s="239"/>
-    </row>
-    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="D39" s="242" t="s">
+        <v>594</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="F39" s="239" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="240" t="s">
         <v>539</v>
       </c>
@@ -13470,25 +13535,21 @@
       <c r="C40" s="242" t="s">
         <v>540</v>
       </c>
-      <c r="D40" s="242" t="s">
-        <v>594</v>
-      </c>
-      <c r="E40" s="250"/>
-      <c r="F40" s="239" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A41" s="262" t="s">
+      <c r="D40" s="242"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="239"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="253" t="s">
         <v>541</v>
       </c>
-      <c r="B41" s="263"/>
-      <c r="C41" s="263"/>
+      <c r="B41" s="254"/>
+      <c r="C41" s="254"/>
       <c r="D41" s="239"/>
       <c r="E41" s="239"/>
       <c r="F41" s="239"/>
     </row>
-    <row r="42" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="240" t="s">
         <v>494</v>
       </c>
@@ -13499,10 +13560,12 @@
         <v>543</v>
       </c>
       <c r="D42" s="242"/>
-      <c r="E42" s="250"/>
+      <c r="E42" s="8" t="s">
+        <v>611</v>
+      </c>
       <c r="F42" s="239"/>
     </row>
-    <row r="43" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="243" t="s">
         <v>497</v>
       </c>
@@ -13516,7 +13579,7 @@
       <c r="E43" s="251"/>
       <c r="F43" s="239"/>
     </row>
-    <row r="44" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="240" t="s">
         <v>514</v>
       </c>
@@ -13530,7 +13593,7 @@
       <c r="E44" s="250"/>
       <c r="F44" s="239"/>
     </row>
-    <row r="45" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="243" t="s">
         <v>547</v>
       </c>
@@ -13544,17 +13607,17 @@
       <c r="E45" s="251"/>
       <c r="F45" s="239"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="262" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="253" t="s">
         <v>550</v>
       </c>
-      <c r="B46" s="263"/>
-      <c r="C46" s="263"/>
+      <c r="B46" s="254"/>
+      <c r="C46" s="254"/>
       <c r="D46" s="239"/>
       <c r="E46" s="239"/>
       <c r="F46" s="239"/>
     </row>
-    <row r="47" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="240" t="s">
         <v>531</v>
       </c>
@@ -13568,7 +13631,7 @@
       <c r="E47" s="250"/>
       <c r="F47" s="239"/>
     </row>
-    <row r="48" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="243" t="s">
         <v>513</v>
       </c>
@@ -13582,7 +13645,7 @@
       <c r="E48" s="251"/>
       <c r="F48" s="239"/>
     </row>
-    <row r="49" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="240" t="s">
         <v>554</v>
       </c>
@@ -13596,7 +13659,7 @@
       <c r="E49" s="250"/>
       <c r="F49" s="239"/>
     </row>
-    <row r="50" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="243" t="s">
         <v>517</v>
       </c>
@@ -13610,17 +13673,17 @@
       <c r="E50" s="251"/>
       <c r="F50" s="239"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="262" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="253" t="s">
         <v>559</v>
       </c>
-      <c r="B51" s="263"/>
-      <c r="C51" s="263"/>
+      <c r="B51" s="254"/>
+      <c r="C51" s="254"/>
       <c r="D51" s="239"/>
       <c r="E51" s="239"/>
       <c r="F51" s="239"/>
     </row>
-    <row r="52" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="240" t="s">
         <v>560</v>
       </c>
@@ -13634,7 +13697,7 @@
       <c r="E52" s="250"/>
       <c r="F52" s="239"/>
     </row>
-    <row r="53" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="243" t="s">
         <v>563</v>
       </c>
@@ -13648,7 +13711,7 @@
       <c r="E53" s="251"/>
       <c r="F53" s="239"/>
     </row>
-    <row r="54" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="240" t="s">
         <v>565</v>
       </c>
@@ -13662,7 +13725,7 @@
       <c r="E54" s="250"/>
       <c r="F54" s="239"/>
     </row>
-    <row r="55" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="243" t="s">
         <v>568</v>
       </c>
@@ -13703,32 +13766,29 @@
     <hyperlink ref="E5" r:id="rId12" xr:uid="{51324F1C-9EC8-4171-933D-4D6E14F3B038}"/>
     <hyperlink ref="E9" r:id="rId13" xr:uid="{2B5871D6-0326-4F93-B09F-9BD757F4381C}"/>
     <hyperlink ref="E10" r:id="rId14" xr:uid="{8E723CD2-8DD2-4F75-A351-8FF96F018CD7}"/>
-    <hyperlink ref="E15" r:id="rId15" xr:uid="{C118B728-A488-1C49-AB12-0008E7D7FA65}"/>
-    <hyperlink ref="E13" r:id="rId16" display="../../../../../:i:/r/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/2_day2_disney.png?d=wc296c5a87d344b5b919adbf3ef69f77b&amp;csf=1&amp;web=1&amp;e=W92T7o" xr:uid="{A127C563-4395-834B-8788-273A8353BC20}"/>
+    <hyperlink ref="E13" r:id="rId15" display="../../../../../:i:/r/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/2_day2_disney.png?d=wc296c5a87d344b5b919adbf3ef69f77b&amp;csf=1&amp;web=1&amp;e=W92T7o" xr:uid="{A127C563-4395-834B-8788-273A8353BC20}"/>
+    <hyperlink ref="E15" r:id="rId16" display="../../../../../:i:/r/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/2_day2_sushiro.png?d=wb0250abb38c644958a658f4efc667c78&amp;csf=1&amp;web=1&amp;e=sTFbPf" xr:uid="{190682BC-0E7E-0F41-962B-58506C0F8BD0}"/>
+    <hyperlink ref="E29" r:id="rId17" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQASN3PAbS_HQIQR0_FD5n1SAYmOugjFcG6-uReJwtgcCYE?e=rWuANF" xr:uid="{14B42E94-EAB4-49CE-8D82-634EF37DDE61}"/>
+    <hyperlink ref="E28" r:id="rId18" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQB4flsAI45cT5GSnsKF_MDyATLDL6sOsro-94ct9itxw2E?e=EcabOO" xr:uid="{070D46B9-DBEE-4997-88E3-49C9B34F002F}"/>
+    <hyperlink ref="E32" r:id="rId19" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQDVbhGnxaZFTrkivsTz8W1bAasMUv2Dp_DAc_5yASeD4jc?e=Yzxj9t" xr:uid="{C5332A44-7860-4F7C-960D-16FF2F265C88}"/>
+    <hyperlink ref="E31" r:id="rId20" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQDF_KiPSjFrR7ZlWEvC0H4SAb_fZExec5v9qbF93OoLF24?e=z1Dw9D" xr:uid="{73386BD0-603A-482D-92FF-59D863A29F48}"/>
+    <hyperlink ref="E22" r:id="rId21" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBfyu8zoXY_S5rF3ovv-j0hAS_Dfy_5GKsvUkE7i_A5ifY?e=h7e9ry" xr:uid="{BE3752B1-CE3A-4AF5-8F43-D003129F56DD}"/>
+    <hyperlink ref="E20" r:id="rId22" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBeIlMjtNl0So0gL7wAUJ8RAYxZvAF52IWD65LYwj9HdDg?e=Mgw4oP" xr:uid="{11B684D5-51AE-450C-AA0C-F2C510630764}"/>
+    <hyperlink ref="E19" r:id="rId23" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQDgLzikkDBqRLl3xapqOwDcATte0JTl3J8WdYBzek6Tw7Q?e=Uq0g0C" xr:uid="{743F2D6C-ECC8-4036-BC04-F4192BC1ED40}"/>
+    <hyperlink ref="E25" r:id="rId24" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBtCFI7kvt6S4y0muApJt5iAVkKRs1rJwS249vVPd4-ruQ?e=fAZj4X" xr:uid="{B5209840-EABA-43BE-89C4-CFE907B6FDEB}"/>
+    <hyperlink ref="E26" r:id="rId25" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBglvt4QjBBQajia7NdromiAQo2Yakgyt_EjAYVvmRmn4E?e=eE8Exg" xr:uid="{E8D17240-227D-4451-8E14-2C32E5173B22}"/>
+    <hyperlink ref="E37" r:id="rId26" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQCreXQiRgOFS7ggHlFNPGp-AWqnApOir01Hof4dqpVIekQ?e=mUwQxU" xr:uid="{FF254E55-70F6-47B4-A75D-9C56C001803A}"/>
+    <hyperlink ref="E38" r:id="rId27" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQAO8_8SJog3Q4lH799OHOszARpKVXVJW3V-h72xMUw-LtY?e=fHJkTy" xr:uid="{9DE7349E-5DAC-489D-9BA1-920BCD256779}"/>
+    <hyperlink ref="E36" r:id="rId28" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQAi5aJIKv75Q5U5vm6kHBDjARkqNOrYQa7d-mPqOmt_l9M?e=odHoQX" xr:uid="{2B6E1CBF-87A2-4134-BE94-277B3CC7FFB9}"/>
+    <hyperlink ref="E42" r:id="rId29" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBvxNjcSnLqT7jKgOPhtaV8AWmmNNqk6oh9a1lt8vbQuno?e=btuKan" xr:uid="{38E5D752-73C6-4466-B72D-45897A20A545}"/>
+    <hyperlink ref="E39" r:id="rId30" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQAB-UbxLXE3QalHQcXGuVhMAY7ZhR4RXior7Gu8u3jicQ4?e=iFyZcH" xr:uid="{072046B0-F592-4B21-9C7B-E122D9FE42AE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId17"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId31"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005A4695005C4BEE4A8751FEE2C473E10D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df7fcaa21f93254d26451ff7a6d04ad2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xmlns:ns4="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fefbcb393e90fe08e3723c038b505a33" ns3:_="" ns4:_="">
     <xsd:import namespace="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
@@ -13967,32 +14027,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6EF48D-28DC-4A85-AE0A-77598A9ABE97}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7"/>
-    <ds:schemaRef ds:uri="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14009,4 +14061,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC6EF48D-28DC-4A85-AE0A-77598A9ABE97}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7"/>
+    <ds:schemaRef ds:uri="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4EAD76F-4DF5-4D69-89D2-96B3009EE5BA}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7289F77C-0872-4599-A591-E6EFF1EB460D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1045" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="617">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1745,9 +1745,6 @@
     <t>Dinner &amp; Souvenirs</t>
   </si>
   <si>
-    <t>Kyoto farewell dinner &amp; traditional Matcha souvenir shopping.</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Day 9: Kyoto • Kansai Airport • Hanoi</t>
   </si>
   <si>
@@ -1905,6 +1902,24 @@
   </si>
   <si>
     <t>7_day7_bamboo.png</t>
+  </si>
+  <si>
+    <t>7_day7_train.png</t>
+  </si>
+  <si>
+    <t>7_day7_pizza.png</t>
+  </si>
+  <si>
+    <t>8_day8_gion.png</t>
+  </si>
+  <si>
+    <t>8_day8_unagi.png</t>
+  </si>
+  <si>
+    <t>8_day8_nara.png</t>
+  </si>
+  <si>
+    <t>Kyoto farewell dinner &amp; traditional Matcha souvenir shopping. Dinner at Sukiya</t>
   </si>
 </sst>
 </file>
@@ -13055,7 +13070,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="249" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B11" s="241" t="s">
         <v>477</v>
@@ -13085,13 +13100,13 @@
         <v>481</v>
       </c>
       <c r="C13" s="242" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D13" s="242" t="s">
         <v>482</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F13" s="246" t="s">
         <v>483</v>
@@ -13125,7 +13140,7 @@
         <v>488</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F15" s="246" t="s">
         <v>489</v>
@@ -13181,7 +13196,7 @@
       </c>
       <c r="D19" s="245"/>
       <c r="E19" s="8" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F19" s="239"/>
     </row>
@@ -13196,10 +13211,10 @@
         <v>498</v>
       </c>
       <c r="D20" s="242" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F20" s="246" t="s">
         <v>499</v>
@@ -13233,7 +13248,7 @@
         <v>506</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F22" s="246" t="s">
         <v>507</v>
@@ -13250,7 +13265,7 @@
         <v>508</v>
       </c>
       <c r="D23" s="245" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E23" s="251"/>
       <c r="F23" s="8" t="s">
@@ -13275,16 +13290,16 @@
         <v>512</v>
       </c>
       <c r="C25" s="242" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D25" s="242" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F25" s="239" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -13295,16 +13310,16 @@
         <v>453</v>
       </c>
       <c r="C26" s="245" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D26" s="245" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F26" s="239" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -13318,11 +13333,11 @@
         <v>516</v>
       </c>
       <c r="D27" s="242" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E27" s="250"/>
       <c r="F27" s="239" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -13333,16 +13348,16 @@
         <v>504</v>
       </c>
       <c r="C28" s="245" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D28" s="245" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F28" s="239" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -13356,13 +13371,13 @@
         <v>519</v>
       </c>
       <c r="D29" s="242" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F29" s="239" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -13383,16 +13398,16 @@
         <v>522</v>
       </c>
       <c r="C31" s="242" t="s">
+        <v>586</v>
+      </c>
+      <c r="D31" s="242" t="s">
+        <v>573</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="F31" s="239" t="s">
         <v>587</v>
-      </c>
-      <c r="D31" s="242" t="s">
-        <v>574</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>601</v>
-      </c>
-      <c r="F31" s="239" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -13407,7 +13422,7 @@
       </c>
       <c r="D32" s="245"/>
       <c r="E32" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F32" s="239"/>
     </row>
@@ -13436,11 +13451,11 @@
         <v>529</v>
       </c>
       <c r="D34" s="245" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E34" s="251"/>
       <c r="F34" s="239" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -13465,7 +13480,7 @@
       </c>
       <c r="D36" s="242"/>
       <c r="E36" s="8" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F36" s="239"/>
     </row>
@@ -13480,13 +13495,13 @@
         <v>534</v>
       </c>
       <c r="D37" s="245" t="s">
+        <v>590</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="F37" s="239" t="s">
         <v>591</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="F37" s="239" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -13501,7 +13516,7 @@
       </c>
       <c r="D38" s="242"/>
       <c r="E38" s="8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F38" s="239"/>
     </row>
@@ -13516,13 +13531,13 @@
         <v>538</v>
       </c>
       <c r="D39" s="242" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F39" s="239" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -13561,7 +13576,7 @@
       </c>
       <c r="D42" s="242"/>
       <c r="E42" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F42" s="239"/>
     </row>
@@ -13590,7 +13605,9 @@
         <v>546</v>
       </c>
       <c r="D44" s="242"/>
-      <c r="E44" s="250"/>
+      <c r="E44" s="8" t="s">
+        <v>611</v>
+      </c>
       <c r="F44" s="239"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -13604,7 +13621,9 @@
         <v>549</v>
       </c>
       <c r="D45" s="245"/>
-      <c r="E45" s="251"/>
+      <c r="E45" s="8" t="s">
+        <v>612</v>
+      </c>
       <c r="F45" s="239"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -13628,7 +13647,9 @@
         <v>552</v>
       </c>
       <c r="D47" s="242"/>
-      <c r="E47" s="250"/>
+      <c r="E47" s="8" t="s">
+        <v>613</v>
+      </c>
       <c r="F47" s="239"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -13642,7 +13663,9 @@
         <v>553</v>
       </c>
       <c r="D48" s="245"/>
-      <c r="E48" s="251"/>
+      <c r="E48" s="8" t="s">
+        <v>614</v>
+      </c>
       <c r="F48" s="239"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -13656,7 +13679,9 @@
         <v>556</v>
       </c>
       <c r="D49" s="242"/>
-      <c r="E49" s="250"/>
+      <c r="E49" s="8" t="s">
+        <v>615</v>
+      </c>
       <c r="F49" s="239"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -13667,7 +13692,7 @@
         <v>557</v>
       </c>
       <c r="C50" s="245" t="s">
-        <v>558</v>
+        <v>616</v>
       </c>
       <c r="D50" s="245"/>
       <c r="E50" s="251"/>
@@ -13675,7 +13700,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="253" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B51" s="254"/>
       <c r="C51" s="254"/>
@@ -13685,13 +13710,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="240" t="s">
+        <v>559</v>
+      </c>
+      <c r="B52" s="241" t="s">
         <v>560</v>
       </c>
-      <c r="B52" s="241" t="s">
+      <c r="C52" s="242" t="s">
         <v>561</v>
-      </c>
-      <c r="C52" s="242" t="s">
-        <v>562</v>
       </c>
       <c r="D52" s="242"/>
       <c r="E52" s="250"/>
@@ -13699,13 +13724,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="243" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B53" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C53" s="245" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D53" s="245"/>
       <c r="E53" s="251"/>
@@ -13713,13 +13738,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="240" t="s">
+        <v>564</v>
+      </c>
+      <c r="B54" s="241" t="s">
         <v>565</v>
       </c>
-      <c r="B54" s="241" t="s">
+      <c r="C54" s="242" t="s">
         <v>566</v>
-      </c>
-      <c r="C54" s="242" t="s">
-        <v>567</v>
       </c>
       <c r="D54" s="242"/>
       <c r="E54" s="250"/>
@@ -13727,13 +13752,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="243" t="s">
+        <v>567</v>
+      </c>
+      <c r="B55" s="244" t="s">
         <v>568</v>
       </c>
-      <c r="B55" s="244" t="s">
+      <c r="C55" s="245" t="s">
         <v>569</v>
-      </c>
-      <c r="C55" s="245" t="s">
-        <v>570</v>
       </c>
       <c r="D55" s="245"/>
       <c r="E55" s="251"/>
@@ -13782,9 +13807,14 @@
     <hyperlink ref="E36" r:id="rId28" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQAi5aJIKv75Q5U5vm6kHBDjARkqNOrYQa7d-mPqOmt_l9M?e=odHoQX" xr:uid="{2B6E1CBF-87A2-4134-BE94-277B3CC7FFB9}"/>
     <hyperlink ref="E42" r:id="rId29" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBvxNjcSnLqT7jKgOPhtaV8AWmmNNqk6oh9a1lt8vbQuno?e=btuKan" xr:uid="{38E5D752-73C6-4466-B72D-45897A20A545}"/>
     <hyperlink ref="E39" r:id="rId30" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQAB-UbxLXE3QalHQcXGuVhMAY7ZhR4RXior7Gu8u3jicQ4?e=iFyZcH" xr:uid="{072046B0-F592-4B21-9C7B-E122D9FE42AE}"/>
+    <hyperlink ref="E44" r:id="rId31" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQCMDsm-cXytSrMd_2AsKK9rAexWEsufMEj4eRK-hf43jbY?e=ki8ssH" xr:uid="{414A8FBD-C238-4CD6-8144-C94627BB946F}"/>
+    <hyperlink ref="E45" r:id="rId32" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBuagFda6KEQLdJQxAPyzQIAXHRwhrheicUfs557gRiOdY?e=LeZ2a1" xr:uid="{C4EF7A10-6175-4B2C-AC44-311F983866BF}"/>
+    <hyperlink ref="E47" r:id="rId33" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBFE0qgiEGLT4MoTK3gdmuTASMCfsn-oI0Q48ttZEdKGy8?e=bIP6eJ" xr:uid="{776B393A-91D9-4A8D-B892-566419B6B1BF}"/>
+    <hyperlink ref="E48" r:id="rId34" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBbK0oEKOLiS6e6S3WODu0YAcall48pO6VlsUn_tzRXYBo?e=kR4APw" xr:uid="{F0B9731E-50CC-41FC-BF46-0A9929D1F4FC}"/>
+    <hyperlink ref="E49" r:id="rId35" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQDN3mn-pXumRq_7HUsZQPoOAT__vEn4Yk9Nx376hc7c1J0?e=uP0ehC" xr:uid="{DC3492E8-1EB1-4B3F-A764-2F78CEA84404}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId31"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId36"/>
 </worksheet>
 </file>
 

--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7289F77C-0872-4599-A591-E6EFF1EB460D}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{684A8C4B-AF99-47DE-9279-F7149DF921CA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1050" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="629">
   <si>
     <t>Đơn giá</t>
   </si>
@@ -1700,18 +1700,12 @@
     <t>Arashiyama Sights</t>
   </si>
   <si>
-    <t>Morning stroll in Bamboo Grove, Hozu River scenic boat tour &amp; visit moss temple Otagi Nenbutsu-ji.</t>
-  </si>
-  <si>
     <t>Kyoto style Udon noodles &amp; sweets at Ogura Cha-Ya.</t>
   </si>
   <si>
     <t>Sagano Romantic Train</t>
   </si>
   <si>
-    <t>Vintage scenic train ride along Sagano romantic river gorge.</t>
-  </si>
-  <si>
     <t>17:00 - 19:30</t>
   </si>
   <si>
@@ -1920,6 +1914,48 @@
   </si>
   <si>
     <t>Kyoto farewell dinner &amp; traditional Matcha souvenir shopping. Dinner at Sukiya</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/1e471XSYSH6i2k5x8</t>
+  </si>
+  <si>
+    <t>Boat Rental Boarding</t>
+  </si>
+  <si>
+    <t>Morning stroll in Bamboo Grove &amp; visit moss temple Otagi Nenbutsu-ji.</t>
+  </si>
+  <si>
+    <t>Hozu River scenic boat tour</t>
+  </si>
+  <si>
+    <t>Bamboo Grove</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/roLsEvwaGtW57c5x5</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/dFzWPyLP4fn9B2ZR6</t>
+  </si>
+  <si>
+    <t>Pizza Restaurant</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/3M4ACDEmUwSknxXW6</t>
+  </si>
+  <si>
+    <t>Unagi Restaurant</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/jNcHH5W7jbrYFafF6</t>
+  </si>
+  <si>
+    <t>Nara Park</t>
+  </si>
+  <si>
+    <t>Gion Starbucks</t>
+  </si>
+  <si>
+    <t>https://maps.app.goo.gl/Lcn3t16zCf3ddAAF6</t>
   </si>
 </sst>
 </file>
@@ -13070,7 +13106,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="249" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B11" s="241" t="s">
         <v>477</v>
@@ -13100,13 +13136,13 @@
         <v>481</v>
       </c>
       <c r="C13" s="242" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D13" s="242" t="s">
         <v>482</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F13" s="246" t="s">
         <v>483</v>
@@ -13140,7 +13176,7 @@
         <v>488</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F15" s="246" t="s">
         <v>489</v>
@@ -13196,7 +13232,7 @@
       </c>
       <c r="D19" s="245"/>
       <c r="E19" s="8" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F19" s="239"/>
     </row>
@@ -13211,10 +13247,10 @@
         <v>498</v>
       </c>
       <c r="D20" s="242" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F20" s="246" t="s">
         <v>499</v>
@@ -13248,7 +13284,7 @@
         <v>506</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F22" s="246" t="s">
         <v>507</v>
@@ -13265,7 +13301,7 @@
         <v>508</v>
       </c>
       <c r="D23" s="245" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E23" s="251"/>
       <c r="F23" s="8" t="s">
@@ -13290,16 +13326,16 @@
         <v>512</v>
       </c>
       <c r="C25" s="242" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D25" s="242" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F25" s="239" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -13310,16 +13346,16 @@
         <v>453</v>
       </c>
       <c r="C26" s="245" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D26" s="245" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F26" s="239" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -13333,11 +13369,11 @@
         <v>516</v>
       </c>
       <c r="D27" s="242" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E27" s="250"/>
       <c r="F27" s="239" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -13348,16 +13384,16 @@
         <v>504</v>
       </c>
       <c r="C28" s="245" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D28" s="245" t="s">
+        <v>577</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="F28" s="239" t="s">
         <v>579</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="F28" s="239" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -13371,13 +13407,13 @@
         <v>519</v>
       </c>
       <c r="D29" s="242" t="s">
+        <v>578</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="F29" s="239" t="s">
         <v>580</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>597</v>
-      </c>
-      <c r="F29" s="239" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -13398,16 +13434,16 @@
         <v>522</v>
       </c>
       <c r="C31" s="242" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D31" s="242" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F31" s="239" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -13422,7 +13458,7 @@
       </c>
       <c r="D32" s="245"/>
       <c r="E32" s="8" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F32" s="239"/>
     </row>
@@ -13451,11 +13487,11 @@
         <v>529</v>
       </c>
       <c r="D34" s="245" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E34" s="251"/>
       <c r="F34" s="239" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -13480,7 +13516,7 @@
       </c>
       <c r="D36" s="242"/>
       <c r="E36" s="8" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F36" s="239"/>
     </row>
@@ -13495,13 +13531,13 @@
         <v>534</v>
       </c>
       <c r="D37" s="245" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F37" s="239" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -13516,7 +13552,7 @@
       </c>
       <c r="D38" s="242"/>
       <c r="E38" s="8" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F38" s="239"/>
     </row>
@@ -13531,13 +13567,13 @@
         <v>538</v>
       </c>
       <c r="D39" s="242" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F39" s="239" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -13564,7 +13600,7 @@
       <c r="E41" s="239"/>
       <c r="F41" s="239"/>
     </row>
-    <row r="42" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="240" t="s">
         <v>494</v>
       </c>
@@ -13572,13 +13608,17 @@
         <v>542</v>
       </c>
       <c r="C42" s="242" t="s">
-        <v>543</v>
-      </c>
-      <c r="D42" s="242"/>
+        <v>617</v>
+      </c>
+      <c r="D42" s="242" t="s">
+        <v>619</v>
+      </c>
       <c r="E42" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="F42" s="239"/>
+        <v>608</v>
+      </c>
+      <c r="F42" s="239" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="243" t="s">
@@ -13588,7 +13628,7 @@
         <v>453</v>
       </c>
       <c r="C43" s="245" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D43" s="245"/>
       <c r="E43" s="251"/>
@@ -13599,36 +13639,44 @@
         <v>514</v>
       </c>
       <c r="B44" s="241" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C44" s="242" t="s">
-        <v>546</v>
-      </c>
-      <c r="D44" s="242"/>
+        <v>618</v>
+      </c>
+      <c r="D44" s="242" t="s">
+        <v>616</v>
+      </c>
       <c r="E44" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="F44" s="239"/>
+        <v>609</v>
+      </c>
+      <c r="F44" s="239" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="243" t="s">
+        <v>545</v>
+      </c>
+      <c r="B45" s="244" t="s">
+        <v>546</v>
+      </c>
+      <c r="C45" s="245" t="s">
         <v>547</v>
       </c>
-      <c r="B45" s="244" t="s">
-        <v>548</v>
-      </c>
-      <c r="C45" s="245" t="s">
-        <v>549</v>
-      </c>
-      <c r="D45" s="245"/>
+      <c r="D45" s="245" t="s">
+        <v>622</v>
+      </c>
       <c r="E45" s="8" t="s">
-        <v>612</v>
-      </c>
-      <c r="F45" s="239"/>
+        <v>610</v>
+      </c>
+      <c r="F45" s="239" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="253" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B46" s="254"/>
       <c r="C46" s="254"/>
@@ -13641,16 +13689,20 @@
         <v>531</v>
       </c>
       <c r="B47" s="241" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C47" s="242" t="s">
-        <v>552</v>
-      </c>
-      <c r="D47" s="242"/>
+        <v>550</v>
+      </c>
+      <c r="D47" s="242" t="s">
+        <v>627</v>
+      </c>
       <c r="E47" s="8" t="s">
-        <v>613</v>
-      </c>
-      <c r="F47" s="239"/>
+        <v>611</v>
+      </c>
+      <c r="F47" s="239" t="s">
+        <v>628</v>
+      </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="243" t="s">
@@ -13660,39 +13712,47 @@
         <v>453</v>
       </c>
       <c r="C48" s="245" t="s">
-        <v>553</v>
-      </c>
-      <c r="D48" s="245"/>
+        <v>551</v>
+      </c>
+      <c r="D48" s="245" t="s">
+        <v>624</v>
+      </c>
       <c r="E48" s="8" t="s">
-        <v>614</v>
-      </c>
-      <c r="F48" s="239"/>
+        <v>612</v>
+      </c>
+      <c r="F48" s="239" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="240" t="s">
+        <v>552</v>
+      </c>
+      <c r="B49" s="241" t="s">
+        <v>553</v>
+      </c>
+      <c r="C49" s="242" t="s">
         <v>554</v>
       </c>
-      <c r="B49" s="241" t="s">
-        <v>555</v>
-      </c>
-      <c r="C49" s="242" t="s">
-        <v>556</v>
-      </c>
-      <c r="D49" s="242"/>
+      <c r="D49" s="242" t="s">
+        <v>626</v>
+      </c>
       <c r="E49" s="8" t="s">
-        <v>615</v>
-      </c>
-      <c r="F49" s="239"/>
+        <v>613</v>
+      </c>
+      <c r="F49" s="239" t="s">
+        <v>625</v>
+      </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="243" t="s">
         <v>517</v>
       </c>
       <c r="B50" s="244" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C50" s="245" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D50" s="245"/>
       <c r="E50" s="251"/>
@@ -13700,7 +13760,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="253" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B51" s="254"/>
       <c r="C51" s="254"/>
@@ -13710,13 +13770,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="240" t="s">
+        <v>557</v>
+      </c>
+      <c r="B52" s="241" t="s">
+        <v>558</v>
+      </c>
+      <c r="C52" s="242" t="s">
         <v>559</v>
-      </c>
-      <c r="B52" s="241" t="s">
-        <v>560</v>
-      </c>
-      <c r="C52" s="242" t="s">
-        <v>561</v>
       </c>
       <c r="D52" s="242"/>
       <c r="E52" s="250"/>
@@ -13724,13 +13784,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="243" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B53" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C53" s="245" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D53" s="245"/>
       <c r="E53" s="251"/>
@@ -13738,13 +13798,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="240" t="s">
+        <v>562</v>
+      </c>
+      <c r="B54" s="241" t="s">
+        <v>563</v>
+      </c>
+      <c r="C54" s="242" t="s">
         <v>564</v>
-      </c>
-      <c r="B54" s="241" t="s">
-        <v>565</v>
-      </c>
-      <c r="C54" s="242" t="s">
-        <v>566</v>
       </c>
       <c r="D54" s="242"/>
       <c r="E54" s="250"/>
@@ -13752,13 +13812,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="243" t="s">
+        <v>565</v>
+      </c>
+      <c r="B55" s="244" t="s">
+        <v>566</v>
+      </c>
+      <c r="C55" s="245" t="s">
         <v>567</v>
-      </c>
-      <c r="B55" s="244" t="s">
-        <v>568</v>
-      </c>
-      <c r="C55" s="245" t="s">
-        <v>569</v>
       </c>
       <c r="D55" s="245"/>
       <c r="E55" s="251"/>
@@ -13807,11 +13867,11 @@
     <hyperlink ref="E36" r:id="rId28" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQAi5aJIKv75Q5U5vm6kHBDjARkqNOrYQa7d-mPqOmt_l9M?e=odHoQX" xr:uid="{2B6E1CBF-87A2-4134-BE94-277B3CC7FFB9}"/>
     <hyperlink ref="E42" r:id="rId29" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBvxNjcSnLqT7jKgOPhtaV8AWmmNNqk6oh9a1lt8vbQuno?e=btuKan" xr:uid="{38E5D752-73C6-4466-B72D-45897A20A545}"/>
     <hyperlink ref="E39" r:id="rId30" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQAB-UbxLXE3QalHQcXGuVhMAY7ZhR4RXior7Gu8u3jicQ4?e=iFyZcH" xr:uid="{072046B0-F592-4B21-9C7B-E122D9FE42AE}"/>
-    <hyperlink ref="E44" r:id="rId31" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQCMDsm-cXytSrMd_2AsKK9rAexWEsufMEj4eRK-hf43jbY?e=ki8ssH" xr:uid="{414A8FBD-C238-4CD6-8144-C94627BB946F}"/>
-    <hyperlink ref="E45" r:id="rId32" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBuagFda6KEQLdJQxAPyzQIAXHRwhrheicUfs557gRiOdY?e=LeZ2a1" xr:uid="{C4EF7A10-6175-4B2C-AC44-311F983866BF}"/>
-    <hyperlink ref="E47" r:id="rId33" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBFE0qgiEGLT4MoTK3gdmuTASMCfsn-oI0Q48ttZEdKGy8?e=bIP6eJ" xr:uid="{776B393A-91D9-4A8D-B892-566419B6B1BF}"/>
-    <hyperlink ref="E48" r:id="rId34" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBbK0oEKOLiS6e6S3WODu0YAcall48pO6VlsUn_tzRXYBo?e=kR4APw" xr:uid="{F0B9731E-50CC-41FC-BF46-0A9929D1F4FC}"/>
-    <hyperlink ref="E49" r:id="rId35" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQDN3mn-pXumRq_7HUsZQPoOAT__vEn4Yk9Nx376hc7c1J0?e=uP0ehC" xr:uid="{DC3492E8-1EB1-4B3F-A764-2F78CEA84404}"/>
+    <hyperlink ref="E45" r:id="rId31" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBuagFda6KEQLdJQxAPyzQIAXHRwhrheicUfs557gRiOdY?e=LeZ2a1" xr:uid="{C4EF7A10-6175-4B2C-AC44-311F983866BF}"/>
+    <hyperlink ref="E47" r:id="rId32" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBFE0qgiEGLT4MoTK3gdmuTASMCfsn-oI0Q48ttZEdKGy8?e=bIP6eJ" xr:uid="{776B393A-91D9-4A8D-B892-566419B6B1BF}"/>
+    <hyperlink ref="E48" r:id="rId33" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQBbK0oEKOLiS6e6S3WODu0YAcall48pO6VlsUn_tzRXYBo?e=kR4APw" xr:uid="{F0B9731E-50CC-41FC-BF46-0A9929D1F4FC}"/>
+    <hyperlink ref="E49" r:id="rId34" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQDN3mn-pXumRq_7HUsZQPoOAT__vEn4Yk9Nx376hc7c1J0?e=uP0ehC" xr:uid="{DC3492E8-1EB1-4B3F-A764-2F78CEA84404}"/>
+    <hyperlink ref="E44" r:id="rId35" display="../../../../../:i:/g/personal/minhpq_bsc_com_vn/IQCMDsm-cXytSrMd_2AsKK9rAexWEsufMEj4eRK-hf43jbY?e=p9lxX0" xr:uid="{19EF1E07-911D-4B4A-8D8A-88DF318FF2A8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId36"/>

--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{684A8C4B-AF99-47DE-9279-F7149DF921CA}"/>
+  <xr:revisionPtr revIDLastSave="276" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A40AFE6C-7F4F-4E73-9796-AB7F711D87F3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -1703,9 +1703,6 @@
     <t>Kyoto style Udon noodles &amp; sweets at Ogura Cha-Ya.</t>
   </si>
   <si>
-    <t>Sagano Romantic Train</t>
-  </si>
-  <si>
     <t>17:00 - 19:30</t>
   </si>
   <si>
@@ -1956,6 +1953,9 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/Lcn3t16zCf3ddAAF6</t>
+  </si>
+  <si>
+    <t>Scenic Boat</t>
   </si>
 </sst>
 </file>
@@ -13106,7 +13106,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="249" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B11" s="241" t="s">
         <v>477</v>
@@ -13136,13 +13136,13 @@
         <v>481</v>
       </c>
       <c r="C13" s="242" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D13" s="242" t="s">
         <v>482</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F13" s="246" t="s">
         <v>483</v>
@@ -13176,7 +13176,7 @@
         <v>488</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F15" s="246" t="s">
         <v>489</v>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="D19" s="245"/>
       <c r="E19" s="8" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F19" s="239"/>
     </row>
@@ -13247,10 +13247,10 @@
         <v>498</v>
       </c>
       <c r="D20" s="242" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F20" s="246" t="s">
         <v>499</v>
@@ -13284,7 +13284,7 @@
         <v>506</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F22" s="246" t="s">
         <v>507</v>
@@ -13301,7 +13301,7 @@
         <v>508</v>
       </c>
       <c r="D23" s="245" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E23" s="251"/>
       <c r="F23" s="8" t="s">
@@ -13326,16 +13326,16 @@
         <v>512</v>
       </c>
       <c r="C25" s="242" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D25" s="242" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F25" s="239" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -13346,16 +13346,16 @@
         <v>453</v>
       </c>
       <c r="C26" s="245" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D26" s="245" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F26" s="239" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -13369,11 +13369,11 @@
         <v>516</v>
       </c>
       <c r="D27" s="242" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E27" s="250"/>
       <c r="F27" s="239" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -13384,16 +13384,16 @@
         <v>504</v>
       </c>
       <c r="C28" s="245" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D28" s="245" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F28" s="239" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -13407,13 +13407,13 @@
         <v>519</v>
       </c>
       <c r="D29" s="242" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F29" s="239" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -13434,16 +13434,16 @@
         <v>522</v>
       </c>
       <c r="C31" s="242" t="s">
+        <v>583</v>
+      </c>
+      <c r="D31" s="242" t="s">
+        <v>570</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="F31" s="239" t="s">
         <v>584</v>
-      </c>
-      <c r="D31" s="242" t="s">
-        <v>571</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="F31" s="239" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="D32" s="245"/>
       <c r="E32" s="8" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="F32" s="239"/>
     </row>
@@ -13487,11 +13487,11 @@
         <v>529</v>
       </c>
       <c r="D34" s="245" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E34" s="251"/>
       <c r="F34" s="239" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="D36" s="242"/>
       <c r="E36" s="8" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="F36" s="239"/>
     </row>
@@ -13531,13 +13531,13 @@
         <v>534</v>
       </c>
       <c r="D37" s="245" t="s">
+        <v>587</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="F37" s="239" t="s">
         <v>588</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="F37" s="239" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -13552,7 +13552,7 @@
       </c>
       <c r="D38" s="242"/>
       <c r="E38" s="8" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F38" s="239"/>
     </row>
@@ -13567,13 +13567,13 @@
         <v>538</v>
       </c>
       <c r="D39" s="242" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F39" s="239" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -13608,16 +13608,16 @@
         <v>542</v>
       </c>
       <c r="C42" s="242" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D42" s="242" t="s">
+        <v>618</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="F42" s="239" t="s">
         <v>619</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>608</v>
-      </c>
-      <c r="F42" s="239" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -13639,44 +13639,44 @@
         <v>514</v>
       </c>
       <c r="B44" s="241" t="s">
-        <v>544</v>
+        <v>628</v>
       </c>
       <c r="C44" s="242" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D44" s="242" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F44" s="239" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="243" t="s">
+        <v>544</v>
+      </c>
+      <c r="B45" s="244" t="s">
         <v>545</v>
       </c>
-      <c r="B45" s="244" t="s">
+      <c r="C45" s="245" t="s">
         <v>546</v>
       </c>
-      <c r="C45" s="245" t="s">
-        <v>547</v>
-      </c>
       <c r="D45" s="245" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F45" s="239" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="253" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B46" s="254"/>
       <c r="C46" s="254"/>
@@ -13689,19 +13689,19 @@
         <v>531</v>
       </c>
       <c r="B47" s="241" t="s">
+        <v>548</v>
+      </c>
+      <c r="C47" s="242" t="s">
         <v>549</v>
       </c>
-      <c r="C47" s="242" t="s">
-        <v>550</v>
-      </c>
       <c r="D47" s="242" t="s">
+        <v>626</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="F47" s="239" t="s">
         <v>627</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="F47" s="239" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -13712,36 +13712,36 @@
         <v>453</v>
       </c>
       <c r="C48" s="245" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D48" s="245" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F48" s="239" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="240" t="s">
+        <v>551</v>
+      </c>
+      <c r="B49" s="241" t="s">
         <v>552</v>
       </c>
-      <c r="B49" s="241" t="s">
+      <c r="C49" s="242" t="s">
         <v>553</v>
       </c>
-      <c r="C49" s="242" t="s">
-        <v>554</v>
-      </c>
       <c r="D49" s="242" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="F49" s="239" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -13749,10 +13749,10 @@
         <v>517</v>
       </c>
       <c r="B50" s="244" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C50" s="245" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="D50" s="245"/>
       <c r="E50" s="251"/>
@@ -13760,7 +13760,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="253" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B51" s="254"/>
       <c r="C51" s="254"/>
@@ -13770,13 +13770,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="240" t="s">
+        <v>556</v>
+      </c>
+      <c r="B52" s="241" t="s">
         <v>557</v>
       </c>
-      <c r="B52" s="241" t="s">
+      <c r="C52" s="242" t="s">
         <v>558</v>
-      </c>
-      <c r="C52" s="242" t="s">
-        <v>559</v>
       </c>
       <c r="D52" s="242"/>
       <c r="E52" s="250"/>
@@ -13784,13 +13784,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="243" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B53" s="244" t="s">
         <v>453</v>
       </c>
       <c r="C53" s="245" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D53" s="245"/>
       <c r="E53" s="251"/>
@@ -13798,13 +13798,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="240" t="s">
+        <v>561</v>
+      </c>
+      <c r="B54" s="241" t="s">
         <v>562</v>
       </c>
-      <c r="B54" s="241" t="s">
+      <c r="C54" s="242" t="s">
         <v>563</v>
-      </c>
-      <c r="C54" s="242" t="s">
-        <v>564</v>
       </c>
       <c r="D54" s="242"/>
       <c r="E54" s="250"/>
@@ -13812,13 +13812,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="243" t="s">
+        <v>564</v>
+      </c>
+      <c r="B55" s="244" t="s">
         <v>565</v>
       </c>
-      <c r="B55" s="244" t="s">
+      <c r="C55" s="245" t="s">
         <v>566</v>
-      </c>
-      <c r="C55" s="245" t="s">
-        <v>567</v>
       </c>
       <c r="D55" s="245"/>
       <c r="E55" s="251"/>

--- a/japantour.xlsx
+++ b/japantour.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bscvn-my.sharepoint.com/personal/minhpq_bsc_com_vn/Documents/09_CODER/00_travel-app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="276" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A40AFE6C-7F4F-4E73-9796-AB7F711D87F3}"/>
+  <xr:revisionPtr revIDLastSave="277" documentId="13_ncr:1_{4CBA3FCD-3F21-4F99-9320-E2DF1148D8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BF8FB36-C5D6-4C67-8474-79DCC0851529}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="458" activeTab="4" xr2:uid="{1D34A874-FA64-408A-8A73-D0DA492D543E}"/>
   </bookViews>
@@ -1394,9 +1394,6 @@
     <t>On Flight</t>
   </si>
   <si>
-    <t>Depart HAN on flight VJ 932 to NRT</t>
-  </si>
-  <si>
     <t>08:00 - 11:00</t>
   </si>
   <si>
@@ -1956,6 +1953,9 @@
   </si>
   <si>
     <t>Scenic Boat</t>
+  </si>
+  <si>
+    <t>Depart HAN on flight VJ 932 to NRT (From HAN to NRT)</t>
   </si>
 </sst>
 </file>
@@ -12970,7 +12970,7 @@
         <v>440</v>
       </c>
       <c r="C3" s="242" t="s">
-        <v>441</v>
+        <v>628</v>
       </c>
       <c r="D3" s="242"/>
       <c r="E3" s="250"/>
@@ -12978,71 +12978,71 @@
     </row>
     <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="243" t="s">
+        <v>441</v>
+      </c>
+      <c r="B4" s="244" t="s">
         <v>442</v>
       </c>
-      <c r="B4" s="244" t="s">
+      <c r="C4" s="245" t="s">
+        <v>442</v>
+      </c>
+      <c r="D4" s="245" t="s">
         <v>443</v>
-      </c>
-      <c r="C4" s="245" t="s">
-        <v>443</v>
-      </c>
-      <c r="D4" s="245" t="s">
-        <v>444</v>
       </c>
       <c r="E4" s="251"/>
       <c r="F4" s="246" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="240" t="s">
+        <v>445</v>
+      </c>
+      <c r="B5" s="241" t="s">
         <v>446</v>
       </c>
-      <c r="B5" s="241" t="s">
+      <c r="C5" s="242" t="s">
         <v>447</v>
       </c>
-      <c r="C5" s="242" t="s">
+      <c r="D5" s="242" t="s">
         <v>448</v>
       </c>
-      <c r="D5" s="242" t="s">
+      <c r="E5" s="252" t="s">
         <v>449</v>
       </c>
-      <c r="E5" s="252" t="s">
+      <c r="F5" s="247" t="s">
         <v>450</v>
-      </c>
-      <c r="F5" s="247" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="243" t="s">
+        <v>451</v>
+      </c>
+      <c r="B6" s="244" t="s">
         <v>452</v>
       </c>
-      <c r="B6" s="244" t="s">
+      <c r="C6" s="245" t="s">
         <v>453</v>
       </c>
-      <c r="C6" s="245" t="s">
+      <c r="D6" s="245" t="s">
         <v>454</v>
       </c>
-      <c r="D6" s="245" t="s">
+      <c r="E6" s="252" t="s">
         <v>455</v>
       </c>
-      <c r="E6" s="252" t="s">
+      <c r="F6" s="246" t="s">
         <v>456</v>
-      </c>
-      <c r="F6" s="246" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="240" t="s">
+        <v>457</v>
+      </c>
+      <c r="B7" s="244" t="s">
         <v>458</v>
       </c>
-      <c r="B7" s="244" t="s">
+      <c r="C7" s="245" t="s">
         <v>459</v>
-      </c>
-      <c r="C7" s="245" t="s">
-        <v>460</v>
       </c>
       <c r="D7" s="245"/>
       <c r="E7" s="251"/>
@@ -13050,69 +13050,69 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="243" t="s">
+        <v>460</v>
+      </c>
+      <c r="B8" s="244" t="s">
         <v>461</v>
       </c>
-      <c r="B8" s="244" t="s">
+      <c r="C8" s="245" t="s">
         <v>462</v>
       </c>
-      <c r="C8" s="245" t="s">
+      <c r="D8" s="245" t="s">
         <v>463</v>
       </c>
-      <c r="D8" s="245" t="s">
+      <c r="E8" s="252" t="s">
         <v>464</v>
       </c>
-      <c r="E8" s="252" t="s">
+      <c r="F8" s="246" t="s">
         <v>465</v>
-      </c>
-      <c r="F8" s="246" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="240" t="s">
+        <v>466</v>
+      </c>
+      <c r="B9" s="241" t="s">
         <v>467</v>
       </c>
-      <c r="B9" s="241" t="s">
+      <c r="C9" s="242" t="s">
         <v>468</v>
       </c>
-      <c r="C9" s="242" t="s">
+      <c r="D9" s="242" t="s">
         <v>469</v>
       </c>
-      <c r="D9" s="242" t="s">
+      <c r="E9" s="252" t="s">
         <v>470</v>
       </c>
-      <c r="E9" s="252" t="s">
+      <c r="F9" s="246" t="s">
         <v>471</v>
-      </c>
-      <c r="F9" s="246" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="243" t="s">
+        <v>472</v>
+      </c>
+      <c r="B10" s="244" t="s">
         <v>473</v>
       </c>
-      <c r="B10" s="244" t="s">
+      <c r="C10" s="245" t="s">
         <v>474</v>
-      </c>
-      <c r="C10" s="245" t="s">
-        <v>475</v>
       </c>
       <c r="D10" s="245"/>
       <c r="E10" s="252" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F10" s="239"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="249" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B11" s="241" t="s">
+        <v>476</v>
+      </c>
+      <c r="C11" s="242" t="s">
         <v>477</v>
-      </c>
-      <c r="C11" s="242" t="s">
-        <v>478</v>
       </c>
       <c r="D11" s="242"/>
       <c r="E11" s="250"/>
@@ -13120,7 +13120,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="253" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B12" s="254"/>
       <c r="C12" s="254"/>
@@ -13130,33 +13130,33 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="240" t="s">
+        <v>479</v>
+      </c>
+      <c r="B13" s="241" t="s">
         <v>480</v>
       </c>
-      <c r="B13" s="241" t="s">
+      <c r="C13" s="242" t="s">
+        <v>571</v>
+      </c>
+      <c r="D13" s="242" t="s">
         <v>481</v>
       </c>
-      <c r="C13" s="242" t="s">
-        <v>572</v>
-      </c>
-      <c r="D13" s="242" t="s">
+      <c r="E13" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="F13" s="246" t="s">
         <v>482</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>592</v>
-      </c>
-      <c r="F13" s="246" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="243" t="s">
+        <v>483</v>
+      </c>
+      <c r="B14" s="244" t="s">
+        <v>481</v>
+      </c>
+      <c r="C14" s="245" t="s">
         <v>484</v>
-      </c>
-      <c r="B14" s="244" t="s">
-        <v>482</v>
-      </c>
-      <c r="C14" s="245" t="s">
-        <v>485</v>
       </c>
       <c r="D14" s="245"/>
       <c r="E14" s="251"/>
@@ -13164,22 +13164,22 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="240" t="s">
+        <v>485</v>
+      </c>
+      <c r="B15" s="241" t="s">
+        <v>473</v>
+      </c>
+      <c r="C15" s="242" t="s">
         <v>486</v>
       </c>
-      <c r="B15" s="241" t="s">
-        <v>474</v>
-      </c>
-      <c r="C15" s="242" t="s">
+      <c r="D15" s="242" t="s">
         <v>487</v>
       </c>
-      <c r="D15" s="242" t="s">
+      <c r="E15" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="F15" s="246" t="s">
         <v>488</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="F15" s="246" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -13187,10 +13187,10 @@
         <v>0.875</v>
       </c>
       <c r="B16" s="241" t="s">
+        <v>476</v>
+      </c>
+      <c r="C16" s="242" t="s">
         <v>477</v>
-      </c>
-      <c r="C16" s="242" t="s">
-        <v>478</v>
       </c>
       <c r="D16" s="245"/>
       <c r="E16" s="251"/>
@@ -13198,7 +13198,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="253" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B17" s="254"/>
       <c r="C17" s="254"/>
@@ -13208,13 +13208,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="240" t="s">
+        <v>490</v>
+      </c>
+      <c r="B18" s="241" t="s">
         <v>491</v>
       </c>
-      <c r="B18" s="241" t="s">
+      <c r="C18" s="242" t="s">
         <v>492</v>
-      </c>
-      <c r="C18" s="242" t="s">
-        <v>493</v>
       </c>
       <c r="D18" s="242"/>
       <c r="E18" s="250"/>
@@ -13222,49 +13222,49 @@
     </row>
     <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="243" t="s">
+        <v>493</v>
+      </c>
+      <c r="B19" s="244" t="s">
         <v>494</v>
       </c>
-      <c r="B19" s="244" t="s">
+      <c r="C19" s="245" t="s">
         <v>495</v>
-      </c>
-      <c r="C19" s="245" t="s">
-        <v>496</v>
       </c>
       <c r="D19" s="245"/>
       <c r="E19" s="8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F19" s="239"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="240" t="s">
+        <v>496</v>
+      </c>
+      <c r="B20" s="241" t="s">
+        <v>452</v>
+      </c>
+      <c r="C20" s="242" t="s">
         <v>497</v>
       </c>
-      <c r="B20" s="241" t="s">
-        <v>453</v>
-      </c>
-      <c r="C20" s="242" t="s">
+      <c r="D20" s="242" t="s">
+        <v>572</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="F20" s="246" t="s">
         <v>498</v>
-      </c>
-      <c r="D20" s="242" t="s">
-        <v>573</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>599</v>
-      </c>
-      <c r="F20" s="246" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="243" t="s">
+        <v>499</v>
+      </c>
+      <c r="B21" s="244" t="s">
         <v>500</v>
       </c>
-      <c r="B21" s="244" t="s">
+      <c r="C21" s="245" t="s">
         <v>501</v>
-      </c>
-      <c r="C21" s="245" t="s">
-        <v>502</v>
       </c>
       <c r="D21" s="245"/>
       <c r="E21" s="251"/>
@@ -13272,45 +13272,45 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="240" t="s">
+        <v>502</v>
+      </c>
+      <c r="B22" s="241" t="s">
         <v>503</v>
       </c>
-      <c r="B22" s="241" t="s">
+      <c r="C22" s="242" t="s">
         <v>504</v>
       </c>
-      <c r="C22" s="242" t="s">
+      <c r="D22" s="242" t="s">
         <v>505</v>
       </c>
-      <c r="D22" s="242" t="s">
+      <c r="E22" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="F22" s="246" t="s">
         <v>506</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="F22" s="246" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="243" t="s">
+        <v>472</v>
+      </c>
+      <c r="B23" s="244" t="s">
         <v>473</v>
       </c>
-      <c r="B23" s="244" t="s">
-        <v>474</v>
-      </c>
       <c r="C23" s="245" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D23" s="245" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E23" s="251"/>
       <c r="F23" s="8" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="253" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B24" s="254"/>
       <c r="C24" s="254"/>
@@ -13320,105 +13320,105 @@
     </row>
     <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="240" t="s">
+        <v>510</v>
+      </c>
+      <c r="B25" s="241" t="s">
         <v>511</v>
       </c>
-      <c r="B25" s="241" t="s">
-        <v>512</v>
-      </c>
       <c r="C25" s="242" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D25" s="242" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F25" s="239" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="243" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B26" s="244" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C26" s="245" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D26" s="245" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F26" s="239" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="240" t="s">
+        <v>513</v>
+      </c>
+      <c r="B27" s="241" t="s">
         <v>514</v>
       </c>
-      <c r="B27" s="241" t="s">
+      <c r="C27" s="242" t="s">
         <v>515</v>
       </c>
-      <c r="C27" s="242" t="s">
-        <v>516</v>
-      </c>
       <c r="D27" s="242" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E27" s="250"/>
       <c r="F27" s="239" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="243" t="s">
+        <v>502</v>
+      </c>
+      <c r="B28" s="244" t="s">
         <v>503</v>
       </c>
-      <c r="B28" s="244" t="s">
-        <v>504</v>
-      </c>
       <c r="C28" s="245" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D28" s="245" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F28" s="239" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="240" t="s">
+        <v>516</v>
+      </c>
+      <c r="B29" s="241" t="s">
         <v>517</v>
       </c>
-      <c r="B29" s="241" t="s">
+      <c r="C29" s="242" t="s">
         <v>518</v>
       </c>
-      <c r="C29" s="242" t="s">
-        <v>519</v>
-      </c>
       <c r="D29" s="242" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F29" s="239" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="253" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B30" s="254"/>
       <c r="C30" s="254"/>
@@ -13428,49 +13428,49 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="240" t="s">
+        <v>520</v>
+      </c>
+      <c r="B31" s="241" t="s">
         <v>521</v>
       </c>
-      <c r="B31" s="241" t="s">
-        <v>522</v>
-      </c>
       <c r="C31" s="242" t="s">
+        <v>582</v>
+      </c>
+      <c r="D31" s="242" t="s">
+        <v>569</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="F31" s="239" t="s">
         <v>583</v>
-      </c>
-      <c r="D31" s="242" t="s">
-        <v>570</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>597</v>
-      </c>
-      <c r="F31" s="239" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="243" t="s">
+        <v>522</v>
+      </c>
+      <c r="B32" s="244" t="s">
         <v>523</v>
       </c>
-      <c r="B32" s="244" t="s">
+      <c r="C32" s="245" t="s">
         <v>524</v>
-      </c>
-      <c r="C32" s="245" t="s">
-        <v>525</v>
       </c>
       <c r="D32" s="245"/>
       <c r="E32" s="8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="F32" s="239"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="240" t="s">
+        <v>525</v>
+      </c>
+      <c r="B33" s="241" t="s">
         <v>526</v>
       </c>
-      <c r="B33" s="241" t="s">
+      <c r="C33" s="242" t="s">
         <v>527</v>
-      </c>
-      <c r="C33" s="242" t="s">
-        <v>528</v>
       </c>
       <c r="D33" s="242"/>
       <c r="E33" s="250"/>
@@ -13478,25 +13478,25 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="243" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B34" s="244" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C34" s="245" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D34" s="245" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E34" s="251"/>
       <c r="F34" s="239" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="253" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B35" s="254"/>
       <c r="C35" s="254"/>
@@ -13506,85 +13506,85 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="240" t="s">
+        <v>530</v>
+      </c>
+      <c r="B36" s="241" t="s">
         <v>531</v>
       </c>
-      <c r="B36" s="241" t="s">
+      <c r="C36" s="242" t="s">
         <v>532</v>
-      </c>
-      <c r="C36" s="242" t="s">
-        <v>533</v>
       </c>
       <c r="D36" s="242"/>
       <c r="E36" s="8" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="F36" s="239"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="243" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B37" s="244" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C37" s="245" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D37" s="245" t="s">
+        <v>586</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="F37" s="239" t="s">
         <v>587</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>603</v>
-      </c>
-      <c r="F37" s="239" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="240" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B38" s="241" t="s">
+        <v>534</v>
+      </c>
+      <c r="C38" s="242" t="s">
         <v>535</v>
-      </c>
-      <c r="C38" s="242" t="s">
-        <v>536</v>
       </c>
       <c r="D38" s="242"/>
       <c r="E38" s="8" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F38" s="239"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="243" t="s">
+        <v>536</v>
+      </c>
+      <c r="B39" s="244" t="s">
+        <v>503</v>
+      </c>
+      <c r="C39" s="245" t="s">
         <v>537</v>
       </c>
-      <c r="B39" s="244" t="s">
-        <v>504</v>
-      </c>
-      <c r="C39" s="245" t="s">
-        <v>538</v>
-      </c>
       <c r="D39" s="242" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F39" s="239" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="240" t="s">
+        <v>538</v>
+      </c>
+      <c r="B40" s="241" t="s">
+        <v>473</v>
+      </c>
+      <c r="C40" s="242" t="s">
         <v>539</v>
-      </c>
-      <c r="B40" s="241" t="s">
-        <v>474</v>
-      </c>
-      <c r="C40" s="242" t="s">
-        <v>540</v>
       </c>
       <c r="D40" s="242"/>
       <c r="E40" s="8"/>
@@ -13592,7 +13592,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="253" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B41" s="254"/>
       <c r="C41" s="254"/>
@@ -13602,33 +13602,33 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="240" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B42" s="241" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C42" s="242" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D42" s="242" t="s">
+        <v>617</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="F42" s="239" t="s">
         <v>618</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="F42" s="239" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="243" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B43" s="244" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C43" s="245" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D43" s="245"/>
       <c r="E43" s="251"/>
@@ -13636,47 +13636,47 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="240" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B44" s="241" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C44" s="242" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D44" s="242" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F44" s="239" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="243" t="s">
+        <v>543</v>
+      </c>
+      <c r="B45" s="244" t="s">
         <v>544</v>
       </c>
-      <c r="B45" s="244" t="s">
+      <c r="C45" s="245" t="s">
         <v>545</v>
       </c>
-      <c r="C45" s="245" t="s">
-        <v>546</v>
-      </c>
       <c r="D45" s="245" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F45" s="239" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="253" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B46" s="254"/>
       <c r="C46" s="254"/>
@@ -13686,73 +13686,73 @@
     </row>
     <row r="47" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="240" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B47" s="241" t="s">
+        <v>547</v>
+      </c>
+      <c r="C47" s="242" t="s">
         <v>548</v>
       </c>
-      <c r="C47" s="242" t="s">
-        <v>549</v>
-      </c>
       <c r="D47" s="242" t="s">
+        <v>625</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="F47" s="239" t="s">
         <v>626</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>610</v>
-      </c>
-      <c r="F47" s="239" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="243" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B48" s="244" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C48" s="245" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D48" s="245" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F48" s="239" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="240" t="s">
+        <v>550</v>
+      </c>
+      <c r="B49" s="241" t="s">
         <v>551</v>
       </c>
-      <c r="B49" s="241" t="s">
+      <c r="C49" s="242" t="s">
         <v>552</v>
       </c>
-      <c r="C49" s="242" t="s">
-        <v>553</v>
-      </c>
       <c r="D49" s="242" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F49" s="239" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="243" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B50" s="244" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C50" s="245" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D50" s="245"/>
       <c r="E50" s="251"/>
@@ -13760,7 +13760,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="253" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B51" s="254"/>
       <c r="C51" s="254"/>
@@ -13770,13 +13770,13 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="240" t="s">
+        <v>555</v>
+      </c>
+      <c r="B52" s="241" t="s">
         <v>556</v>
       </c>
-      <c r="B52" s="241" t="s">
+      <c r="C52" s="242" t="s">
         <v>557</v>
-      </c>
-      <c r="C52" s="242" t="s">
-        <v>558</v>
       </c>
       <c r="D52" s="242"/>
       <c r="E52" s="250"/>
@@ -13784,13 +13784,13 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="243" t="s">
+        <v>558</v>
+      </c>
+      <c r="B53" s="244" t="s">
+        <v>452</v>
+      </c>
+      <c r="C53" s="245" t="s">
         <v>559</v>
-      </c>
-      <c r="B53" s="244" t="s">
-        <v>453</v>
-      </c>
-      <c r="C53" s="245" t="s">
-        <v>560</v>
       </c>
       <c r="D53" s="245"/>
       <c r="E53" s="251"/>
@@ -13798,13 +13798,13 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="240" t="s">
+        <v>560</v>
+      </c>
+      <c r="B54" s="241" t="s">
         <v>561</v>
       </c>
-      <c r="B54" s="241" t="s">
+      <c r="C54" s="242" t="s">
         <v>562</v>
-      </c>
-      <c r="C54" s="242" t="s">
-        <v>563</v>
       </c>
       <c r="D54" s="242"/>
       <c r="E54" s="250"/>
@@ -13812,13 +13812,13 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="243" t="s">
+        <v>563</v>
+      </c>
+      <c r="B55" s="244" t="s">
         <v>564</v>
       </c>
-      <c r="B55" s="244" t="s">
+      <c r="C55" s="245" t="s">
         <v>565</v>
-      </c>
-      <c r="C55" s="245" t="s">
-        <v>566</v>
       </c>
       <c r="D55" s="245"/>
       <c r="E55" s="251"/>
@@ -13879,6 +13879,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005A4695005C4BEE4A8751FEE2C473E10D" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="df7fcaa21f93254d26451ff7a6d04ad2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xmlns:ns4="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fefbcb393e90fe08e3723c038b505a33" ns3:_="" ns4:_="">
     <xsd:import namespace="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
@@ -14117,38 +14134,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
-    <ds:schemaRef ds:uri="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -14171,9 +14160,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8E275EF-C000-4518-B0F8-FE9A60820B51}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A59486CE-8728-40BE-973B-B64C7CD06C40}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8ee09cf5-53a8-4aeb-94af-927f54a7d6d8"/>
+    <ds:schemaRef ds:uri="ecf1487c-a58a-4bc0-a420-fb42a2a3dfc7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>